--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="117" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="486">
   <si>
     <t>ID</t>
   </si>
@@ -1465,6 +1465,81 @@
   </si>
   <si>
     <t>17/09/2026 16:14:07</t>
+  </si>
+  <si>
+    <t>6ab20c3388ce3e06cc4940be</t>
+  </si>
+  <si>
+    <t>21/09/2026 23:17:07</t>
+  </si>
+  <si>
+    <t>22/09/2026 02:03:47</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>6ab20c3288ce3e06cc494082</t>
+  </si>
+  <si>
+    <t>21/09/2026 20:32:03</t>
+  </si>
+  <si>
+    <t>22/09/2026 02:03:46</t>
+  </si>
+  <si>
+    <t>6ab20c3288ce3e06cc49407c</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:04:37</t>
+  </si>
+  <si>
+    <t>6ab20c3188ce3e06cc494050</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:21:50</t>
+  </si>
+  <si>
+    <t>22/09/2026 02:03:45</t>
+  </si>
+  <si>
+    <t>6ab35bcaa4adeea581715e48</t>
+  </si>
+  <si>
+    <t>22/09/2026 23:22:32</t>
+  </si>
+  <si>
+    <t>23/09/2026 01:55:38</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>13188‐</t>
+  </si>
+  <si>
+    <t>6ab35bc9a4adeea581715e10</t>
+  </si>
+  <si>
+    <t>22/09/2026 21:28:02</t>
+  </si>
+  <si>
+    <t>23/09/2026 01:55:37</t>
+  </si>
+  <si>
+    <t>6ab35bc9a4adeea581715df2</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:09:51</t>
+  </si>
+  <si>
+    <t>6ab35bc8a4adeea581715dc2</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:41:52</t>
+  </si>
+  <si>
+    <t>23/09/2026 01:55:36</t>
   </si>
 </sst>
 </file>
@@ -1527,6 +1602,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2025,14 +2101,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1257300</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2097,14 +2173,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>28574</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>600074</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>345975</xdr:rowOff>
     </xdr:to>
@@ -2175,8 +2251,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1276350</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
@@ -2243,7 +2319,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46286.365372916669" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="154">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46288.580346990741" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="162">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2274,7 +2350,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="38">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="40">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2313,6 +2389,8 @@
         <s v="16/09/2026"/>
         <s v="18/09/2026"/>
         <s v="17/09/2026"/>
+        <s v="21/09/2026"/>
+        <s v="22/09/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2367,7 +2445,7 @@
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="10"/>
     </cacheField>
     <cacheField name="Carne no Osso Perna Esquerda" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="147"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="10"/>
     </cacheField>
     <cacheField name="Refile Perna" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="21" maxValue="155"/>
@@ -2385,13 +2463,13 @@
       <sharedItems containsMixedTypes="1" containsNumber="1" minValue="2" maxValue="145"/>
     </cacheField>
     <cacheField name="% Peito Limpo na esteira" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="-120.00000000000003" maxValue="90"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="25" maxValue="90"/>
     </cacheField>
     <cacheField name="6.1 Erro de Corte" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="30"/>
     </cacheField>
     <cacheField name="% Erro de Corte da Porcionadora" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="55.000000000000007"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="5" maxValue="55.000000000000007"/>
     </cacheField>
     <cacheField name="Qualidade Acomodação" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="10"/>
@@ -2421,7 +2499,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="154">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="162">
   <r>
     <x v="0"/>
     <m/>
@@ -3006,7 +3084,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="48"/>
     <n v="24"/>
     <n v="43"/>
@@ -3046,7 +3124,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="61"/>
     <n v="30.5"/>
     <n v="43"/>
@@ -3086,7 +3164,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="38"/>
@@ -3126,7 +3204,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="32"/>
@@ -3166,7 +3244,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="43"/>
@@ -3206,7 +3284,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="46"/>
     <n v="23"/>
     <n v="42"/>
@@ -3246,7 +3324,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="38"/>
     <n v="19"/>
     <n v="43"/>
@@ -3286,7 +3364,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="37"/>
     <n v="18.5"/>
     <n v="41"/>
@@ -3326,7 +3404,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="38"/>
     <n v="19"/>
     <n v="42"/>
@@ -3366,7 +3444,7 @@
     <n v="10"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="69"/>
     <n v="34.5"/>
     <n v="40"/>
@@ -3406,7 +3484,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="38"/>
     <n v="19"/>
     <n v="39"/>
@@ -3446,7 +3524,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="32"/>
     <n v="16"/>
     <n v="43"/>
@@ -3486,7 +3564,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="47"/>
     <n v="23.5"/>
     <n v="45"/>
@@ -3526,7 +3604,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="47"/>
     <n v="23.5"/>
     <n v="48"/>
@@ -3566,7 +3644,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="49"/>
     <n v="24.5"/>
     <n v="38"/>
@@ -3606,7 +3684,7 @@
     <n v="10"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="83"/>
     <n v="41.5"/>
     <n v="32"/>
@@ -3646,7 +3724,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="48"/>
@@ -3686,7 +3764,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="48"/>
@@ -3726,7 +3804,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="38"/>
     <n v="19"/>
     <n v="49"/>
@@ -3766,7 +3844,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="46"/>
     <n v="23"/>
     <n v="43"/>
@@ -3806,7 +3884,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="49"/>
@@ -3846,7 +3924,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="47"/>
     <n v="23.5"/>
     <n v="46"/>
@@ -3886,7 +3964,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="48"/>
@@ -3926,7 +4004,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="43"/>
     <n v="21.5"/>
     <n v="46"/>
@@ -3966,7 +4044,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="55"/>
@@ -4006,7 +4084,7 @@
     <n v="5"/>
     <s v="Retirou a Cartilagem,_x000a_Riscou o Sassami em X"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="43"/>
     <n v="21.5"/>
     <n v="49"/>
@@ -4046,7 +4124,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="28"/>
     <n v="14.000000000000002"/>
     <n v="62"/>
@@ -4086,7 +4164,7 @@
     <s v=""/>
     <s v=""/>
     <s v=""/>
-    <m/>
+    <s v=""/>
     <s v=""/>
     <s v=""/>
     <n v="54"/>
@@ -4126,7 +4204,7 @@
     <n v="7"/>
     <s v="Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="32"/>
     <n v="16"/>
     <n v="51"/>
@@ -4166,7 +4244,7 @@
     <s v=""/>
     <s v=""/>
     <s v=""/>
-    <m/>
+    <s v=""/>
     <s v=""/>
     <s v=""/>
     <s v=""/>
@@ -4206,7 +4284,7 @@
     <n v="7"/>
     <s v="Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="30"/>
     <n v="15"/>
     <n v="42"/>
@@ -4246,7 +4324,7 @@
     <s v=""/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <s v=""/>
-    <m/>
+    <s v=""/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="43"/>
@@ -4286,7 +4364,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <s v=""/>
-    <m/>
+    <s v=""/>
     <n v="33"/>
     <n v="16.5"/>
     <n v="40"/>
@@ -4326,7 +4404,7 @@
     <s v=""/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="87"/>
     <n v="43.5"/>
     <n v="48"/>
@@ -4366,7 +4444,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="58"/>
     <n v="28.999999999999996"/>
     <n v="33"/>
@@ -4406,7 +4484,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="39"/>
@@ -4446,7 +4524,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="40"/>
     <n v="20"/>
     <n v="37"/>
@@ -4486,7 +4564,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="46"/>
     <n v="23"/>
     <n v="36"/>
@@ -4526,7 +4604,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="43"/>
     <n v="21.5"/>
     <n v="32"/>
@@ -4566,7 +4644,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="49"/>
@@ -4606,7 +4684,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="42"/>
     <n v="21"/>
     <n v="49"/>
@@ -4646,7 +4724,7 @@
     <n v="5"/>
     <s v="Retirou a Cartilagem,_x000a_Riscou o Sassami em X"/>
     <s v=""/>
-    <m/>
+    <s v=""/>
     <n v="37"/>
     <n v="18.5"/>
     <n v="41"/>
@@ -4686,7 +4764,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="33"/>
     <n v="16.5"/>
     <n v="33"/>
@@ -4726,7 +4804,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="40"/>
     <n v="20"/>
     <n v="47"/>
@@ -4766,7 +4844,7 @@
     <s v=""/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="46"/>
     <n v="23"/>
     <n v="32"/>
@@ -4806,7 +4884,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="40"/>
     <n v="20"/>
     <n v="43"/>
@@ -4846,7 +4924,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="35"/>
     <n v="17.5"/>
     <n v="48"/>
@@ -4886,7 +4964,7 @@
     <n v="7"/>
     <s v="Retirou a Cartilagem,_x000a_Riscou o Sassami em X"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="55"/>
     <n v="27.500000000000004"/>
     <n v="42"/>
@@ -4926,7 +5004,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="5"/>
-    <m/>
+    <n v="5"/>
     <n v="61"/>
     <n v="30.5"/>
     <n v="37"/>
@@ -4966,7 +5044,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <s v=""/>
-    <m/>
+    <s v=""/>
     <n v="44"/>
     <n v="22"/>
     <n v="35"/>
@@ -5006,7 +5084,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="42"/>
     <n v="21"/>
     <n v="41"/>
@@ -5046,7 +5124,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="35"/>
@@ -5086,7 +5164,7 @@
     <s v=""/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="30"/>
@@ -5126,7 +5204,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="30"/>
     <n v="15"/>
     <n v="46"/>
@@ -5166,7 +5244,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="21"/>
     <n v="10.5"/>
     <n v="45"/>
@@ -5206,13 +5284,13 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="34"/>
     <n v="17"/>
     <n v="4"/>
     <n v="33"/>
     <n v="2"/>
-    <n v="-65"/>
+    <m/>
     <n v="3"/>
     <n v="15"/>
     <n v="7"/>
@@ -5246,7 +5324,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="44"/>
     <n v="22"/>
     <n v="29"/>
@@ -5286,7 +5364,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="50"/>
     <n v="25"/>
     <n v="49"/>
@@ -5326,13 +5404,13 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="40"/>
     <n v="20"/>
     <n v="4"/>
     <n v="33"/>
     <n v="2"/>
-    <n v="-65"/>
+    <m/>
     <n v="4"/>
     <n v="20"/>
     <n v="7"/>
@@ -5366,7 +5444,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="30"/>
     <n v="15"/>
     <n v="41"/>
@@ -5406,7 +5484,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="45"/>
     <n v="22.5"/>
     <n v="38"/>
@@ -5446,7 +5524,7 @@
     <n v="7"/>
     <s v="Cortou o Vazio,_x000a_Usou o garfo na retirada de Sassami"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="37"/>
     <n v="18.5"/>
     <n v="38"/>
@@ -5486,7 +5564,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="54"/>
     <n v="27"/>
     <n v="39"/>
@@ -5526,7 +5604,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="39"/>
     <n v="19.5"/>
     <n v="37"/>
@@ -5566,7 +5644,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="31"/>
     <n v="15.5"/>
     <n v="290"/>
@@ -5606,7 +5684,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="43"/>
     <n v="21.5"/>
     <n v="52"/>
@@ -5646,7 +5724,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="51"/>
     <n v="25.5"/>
     <n v="46"/>
@@ -5686,7 +5764,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="37"/>
     <n v="18.5"/>
     <n v="46"/>
@@ -5726,7 +5804,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="39"/>
@@ -5766,7 +5844,7 @@
     <s v=""/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="30"/>
     <n v="15"/>
     <n v="37"/>
@@ -5806,7 +5884,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <m/>
+    <n v="7"/>
     <n v="42"/>
     <n v="21"/>
     <n v="36"/>
@@ -5846,7 +5924,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="44"/>
     <n v="22"/>
     <n v="34"/>
@@ -5886,7 +5964,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
+    <n v="10"/>
     <n v="43"/>
     <n v="21.5"/>
     <n v="54"/>
@@ -5926,367 +6004,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <m/>
-    <n v="36"/>
-    <n v="18"/>
-    <n v="41"/>
-    <n v="3"/>
-    <n v="20.5"/>
-    <n v="85"/>
-    <n v="5"/>
-    <n v="25"/>
-    <n v="7"/>
-    <n v="42846"/>
-    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
-    <s v="assinatura"/>
-    <s v="assinatura"/>
-    <n v="3009"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="6a97b15843066e508049f780"/>
-    <s v="01/09/2026 18:48:54"/>
-    <s v="02/09/2026 02:17:12"/>
-    <s v="Ranieli"/>
-    <x v="26"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="24"/>
-    <n v="28"/>
-    <n v="76"/>
-    <n v="72"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
-    <s v=""/>
-    <m/>
-    <n v="41"/>
-    <n v="20.5"/>
-    <n v="36"/>
-    <n v="6"/>
-    <n v="18"/>
-    <n v="70"/>
-    <n v="6"/>
-    <n v="30"/>
     <n v="10"/>
-    <n v="15106"/>
-    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
-    <s v="assinatura"/>
-    <s v="assinatura"/>
-    <n v="4343"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="6a97b15743066e508049f756"/>
-    <s v="01/09/2026 16:32:01"/>
-    <s v="02/09/2026 02:17:11"/>
-    <s v="Ranieli"/>
-    <x v="26"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="19"/>
-    <n v="32"/>
-    <n v="81"/>
-    <n v="68"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
-    <n v="7"/>
-    <m/>
-    <n v="48"/>
-    <n v="24"/>
-    <n v="34"/>
-    <n v="5"/>
-    <n v="17"/>
-    <n v="75"/>
-    <n v="7"/>
-    <n v="35"/>
-    <n v="7"/>
-    <n v="40762"/>
-    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
-    <s v="assinatura"/>
-    <s v="assinatura"/>
-    <n v="3231"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="6a95c84f18e7857fd2a40611"/>
-    <m/>
-    <m/>
-    <s v="Alana"/>
-    <x v="25"/>
-    <n v="1"/>
-    <n v="10"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="17"/>
-    <n v="12"/>
-    <n v="83"/>
-    <n v="88"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="10"/>
-    <s v=""/>
-    <n v="10"/>
-    <m/>
-    <n v="86"/>
-    <n v="43"/>
-    <n v="43"/>
-    <n v="11"/>
-    <n v="21.5"/>
-    <n v="44.999999999999993"/>
-    <n v="2"/>
-    <n v="10"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="6a91d3cb5b2e8247e4dde965"/>
-    <m/>
-    <m/>
-    <s v="Alana"/>
-    <x v="24"/>
-    <n v="1"/>
-    <n v="10"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="21"/>
-    <n v="39"/>
-    <n v="79"/>
-    <n v="61"/>
-    <n v="10"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="5"/>
-    <n v="7"/>
-    <s v=""/>
-    <n v="7"/>
-    <m/>
-    <n v="71"/>
-    <n v="35.5"/>
-    <n v="78"/>
-    <n v="15"/>
-    <n v="39"/>
-    <n v="25"/>
-    <n v="4"/>
-    <n v="20"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="6a8ee1b8ff3419aa350c3bbe"/>
-    <m/>
-    <m/>
-    <s v="Alana"/>
-    <x v="22"/>
-    <n v="1"/>
-    <n v="10"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="9"/>
-    <n v="44"/>
-    <n v="91"/>
-    <n v="56"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="10"/>
-    <n v="5"/>
-    <s v=""/>
-    <n v="10"/>
-    <m/>
-    <n v="50"/>
-    <n v="25"/>
-    <n v="57"/>
-    <n v="6"/>
-    <n v="28.499999999999996"/>
-    <n v="70"/>
-    <n v="2"/>
-    <n v="10"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="6a8ddfc854cc3955acac26a1"/>
-    <m/>
-    <m/>
-    <s v="Alana"/>
-    <x v="21"/>
-    <n v="1"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="14"/>
-    <n v="36"/>
-    <n v="86"/>
-    <n v="64"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <s v=""/>
-    <n v="10"/>
-    <m/>
-    <s v=""/>
-    <s v=""/>
-    <m/>
-    <n v="8"/>
-    <s v=""/>
-    <n v="60"/>
-    <n v="1"/>
-    <n v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="6a8c8e9c3b4a65e677cc0d51"/>
-    <m/>
-    <m/>
-    <s v="Alana"/>
-    <x v="20"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="17"/>
-    <n v="31"/>
-    <n v="83"/>
-    <n v="69"/>
-    <n v="10"/>
-    <n v="7"/>
-    <n v="10"/>
-    <n v="5"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="37"/>
-    <n v="7"/>
-    <m/>
-    <n v="44"/>
-    <n v="22"/>
-    <m/>
-    <n v="13"/>
-    <s v=""/>
-    <n v="35"/>
-    <n v="1"/>
-    <n v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="6a97b15943066e508049f7be"/>
-    <s v="02/09/2026 00:21:23"/>
-    <s v="02/09/2026 02:17:13"/>
-    <s v="Ranieli"/>
-    <x v="26"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="19"/>
-    <n v="42"/>
-    <n v="81"/>
-    <n v="58"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="7"/>
-    <n v="5"/>
-    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
-    <n v="10"/>
-    <s v=""/>
-    <n v="43"/>
-    <n v="21.5"/>
-    <n v="54"/>
-    <n v="5"/>
-    <n v="27"/>
-    <n v="75"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="7"/>
-    <n v="864048"/>
-    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
-    <s v="assinatura"/>
-    <s v="assinatura"/>
-    <n v="3620"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="6a97b15843066e508049f786"/>
-    <s v="01/09/2026 21:39:41"/>
-    <s v="02/09/2026 02:17:12"/>
-    <s v="Ranieli"/>
-    <x v="26"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="25"/>
-    <n v="36"/>
-    <n v="75"/>
-    <n v="64"/>
-    <n v="5"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="5"/>
-    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
-    <n v="10"/>
-    <s v=""/>
     <n v="36"/>
     <n v="18"/>
     <n v="41"/>
@@ -6366,7 +6084,367 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
+    <n v="7"/>
+    <n v="48"/>
+    <n v="24"/>
+    <n v="34"/>
+    <n v="5"/>
+    <n v="17"/>
+    <n v="75"/>
+    <n v="7"/>
+    <n v="35"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3231"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="6a95c84f18e7857fd2a40611"/>
+    <m/>
+    <m/>
+    <s v="Alana"/>
+    <x v="25"/>
+    <n v="1"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="17"/>
+    <n v="12"/>
+    <n v="83"/>
+    <n v="88"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="10"/>
     <s v=""/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="86"/>
+    <n v="43"/>
+    <n v="43"/>
+    <n v="11"/>
+    <n v="21.5"/>
+    <n v="44.999999999999993"/>
+    <n v="2"/>
+    <n v="10"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="6a91d3cb5b2e8247e4dde965"/>
+    <m/>
+    <m/>
+    <s v="Alana"/>
+    <x v="24"/>
+    <n v="1"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="21"/>
+    <n v="39"/>
+    <n v="79"/>
+    <n v="61"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="7"/>
+    <s v=""/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="71"/>
+    <n v="35.5"/>
+    <n v="78"/>
+    <n v="15"/>
+    <n v="39"/>
+    <n v="25"/>
+    <n v="4"/>
+    <n v="20"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="6a8ee1b8ff3419aa350c3bbe"/>
+    <m/>
+    <m/>
+    <s v="Alana"/>
+    <x v="22"/>
+    <n v="1"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="9"/>
+    <n v="44"/>
+    <n v="91"/>
+    <n v="56"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="5"/>
+    <s v=""/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="50"/>
+    <n v="25"/>
+    <n v="57"/>
+    <n v="6"/>
+    <n v="28.499999999999996"/>
+    <n v="70"/>
+    <n v="2"/>
+    <n v="10"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="6a8ddfc854cc3955acac26a1"/>
+    <m/>
+    <m/>
+    <s v="Alana"/>
+    <x v="21"/>
+    <n v="1"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="14"/>
+    <n v="36"/>
+    <n v="86"/>
+    <n v="64"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v=""/>
+    <n v="10"/>
+    <n v="10"/>
+    <s v=""/>
+    <s v=""/>
+    <m/>
+    <n v="8"/>
+    <s v=""/>
+    <n v="60"/>
+    <n v="1"/>
+    <n v="5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="6a8c8e9c3b4a65e677cc0d51"/>
+    <m/>
+    <m/>
+    <s v="Alana"/>
+    <x v="20"/>
+    <n v="1"/>
+    <n v="5"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="17"/>
+    <n v="31"/>
+    <n v="83"/>
+    <n v="69"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="37"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="44"/>
+    <n v="22"/>
+    <m/>
+    <n v="13"/>
+    <s v=""/>
+    <n v="35"/>
+    <n v="1"/>
+    <n v="5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6a97b15943066e508049f7be"/>
+    <s v="02/09/2026 00:21:23"/>
+    <s v="02/09/2026 02:17:13"/>
+    <s v="Ranieli"/>
+    <x v="26"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="19"/>
+    <n v="42"/>
+    <n v="81"/>
+    <n v="58"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="43"/>
+    <n v="21.5"/>
+    <n v="54"/>
+    <n v="5"/>
+    <n v="27"/>
+    <n v="75"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="864048"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3620"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6a97b15843066e508049f786"/>
+    <s v="01/09/2026 21:39:41"/>
+    <s v="02/09/2026 02:17:12"/>
+    <s v="Ranieli"/>
+    <x v="26"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="36"/>
+    <n v="75"/>
+    <n v="64"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="36"/>
+    <n v="18"/>
+    <n v="41"/>
+    <n v="3"/>
+    <n v="20.5"/>
+    <n v="85"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="7"/>
+    <n v="42846"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3009"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6a97b15843066e508049f780"/>
+    <s v="01/09/2026 18:48:54"/>
+    <s v="02/09/2026 02:17:12"/>
+    <s v="Ranieli"/>
+    <x v="26"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="24"/>
+    <n v="28"/>
+    <n v="76"/>
+    <n v="72"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="41"/>
+    <n v="20.5"/>
+    <n v="36"/>
+    <n v="6"/>
+    <n v="18"/>
+    <n v="70"/>
+    <n v="6"/>
+    <n v="30"/>
+    <n v="10"/>
+    <n v="15106"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="4343"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6a97b15743066e508049f756"/>
+    <s v="01/09/2026 16:32:01"/>
+    <s v="02/09/2026 02:17:11"/>
+    <s v="Ranieli"/>
+    <x v="26"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="19"/>
+    <n v="32"/>
+    <n v="81"/>
+    <n v="68"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
     <n v="48"/>
     <n v="24"/>
     <n v="34"/>
@@ -6406,7 +6484,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
     <n v="7"/>
-    <s v=""/>
+    <n v="7"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="39"/>
@@ -6526,7 +6604,7 @@
     <n v="7"/>
     <s v="Retirou a Cartilagem,_x000a_Riscou o Sassami em X"/>
     <n v="10"/>
-    <s v=""/>
+    <n v="10"/>
     <n v="41"/>
     <n v="20.5"/>
     <n v="41"/>
@@ -6566,7 +6644,7 @@
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <s v=""/>
+    <n v="10"/>
     <n v="52"/>
     <n v="26"/>
     <n v="38"/>
@@ -6606,7 +6684,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <s v=""/>
+    <n v="10"/>
     <n v="25"/>
     <n v="12.5"/>
     <n v="37"/>
@@ -6646,7 +6724,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <s v=""/>
+    <n v="10"/>
     <n v="56"/>
     <n v="28.000000000000004"/>
     <n v="48"/>
@@ -6686,13 +6764,13 @@
     <n v="5"/>
     <s v="Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem,_x000a_Riscou o Sassami em X"/>
     <n v="7"/>
-    <s v=""/>
+    <n v="7"/>
     <n v="47"/>
     <n v="23.5"/>
     <n v="44"/>
     <n v="44"/>
     <n v="22"/>
-    <n v="-120.00000000000003"/>
+    <m/>
     <n v="3"/>
     <n v="15"/>
     <n v="7"/>
@@ -6726,7 +6804,7 @@
     <n v="5"/>
     <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
     <n v="10"/>
-    <s v=""/>
+    <n v="10"/>
     <n v="43"/>
     <n v="21.5"/>
     <n v="41"/>
@@ -6774,7 +6852,7 @@
     <n v="25.5"/>
     <n v="30"/>
     <n v="0"/>
-    <n v="0"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -6925,7 +7003,7 @@
     <n v="7"/>
     <n v="7"/>
     <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
-    <s v=""/>
+    <n v="7"/>
     <n v="7"/>
     <n v="71"/>
     <n v="35.5"/>
@@ -6974,7 +7052,7 @@
     <n v="24"/>
     <n v="25"/>
     <n v="0"/>
-    <n v="0"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -7806,13 +7884,13 @@
     <n v="5"/>
     <m/>
     <n v="7"/>
-    <n v="123"/>
+    <m/>
     <n v="61.5"/>
     <n v="66"/>
     <n v="13"/>
     <n v="33"/>
     <n v="35"/>
-    <n v="0"/>
+    <m/>
     <n v="0"/>
     <m/>
     <m/>
@@ -7846,13 +7924,13 @@
     <n v="10"/>
     <m/>
     <n v="10"/>
-    <n v="107"/>
+    <m/>
     <n v="53.5"/>
     <n v="91"/>
     <n v="14"/>
     <n v="45.5"/>
     <n v="30"/>
-    <n v="6"/>
+    <m/>
     <n v="30"/>
     <m/>
     <m/>
@@ -7886,13 +7964,13 @@
     <n v="5"/>
     <m/>
     <n v="7"/>
-    <n v="105"/>
+    <m/>
     <n v="52.5"/>
     <n v="48"/>
     <n v="14"/>
     <n v="24"/>
     <n v="30"/>
-    <n v="6"/>
+    <m/>
     <n v="30"/>
     <m/>
     <m/>
@@ -7926,13 +8004,13 @@
     <n v="5"/>
     <m/>
     <n v="7"/>
-    <n v="147"/>
+    <m/>
     <n v="73.5"/>
     <n v="68"/>
     <n v="10"/>
     <n v="34"/>
     <n v="50"/>
-    <n v="0"/>
+    <m/>
     <n v="0"/>
     <m/>
     <m/>
@@ -8582,12 +8660,332 @@
     <s v="assinatura"/>
     <n v="3341"/>
   </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab20c3388ce3e06cc4940be"/>
+    <s v="21/09/2026 23:17:07"/>
+    <s v="22/09/2026 02:03:47"/>
+    <s v="Ranieli"/>
+    <x v="38"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="28"/>
+    <n v="51"/>
+    <n v="72"/>
+    <n v="49"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="47"/>
+    <n v="23.5"/>
+    <n v="41"/>
+    <n v="4"/>
+    <n v="20.5"/>
+    <n v="80"/>
+    <n v="7"/>
+    <n v="35"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="5707"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab20c3288ce3e06cc494082"/>
+    <s v="21/09/2026 20:32:03"/>
+    <s v="22/09/2026 02:03:46"/>
+    <s v="Ranieli"/>
+    <x v="38"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="35"/>
+    <n v="41"/>
+    <n v="65"/>
+    <n v="59"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="50"/>
+    <n v="25"/>
+    <n v="35"/>
+    <n v="8"/>
+    <n v="17.5"/>
+    <n v="60"/>
+    <n v="8"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3358"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab20c3288ce3e06cc49407c"/>
+    <s v="21/09/2026 18:04:37"/>
+    <s v="22/09/2026 02:03:46"/>
+    <s v="Ranieli"/>
+    <x v="38"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="30"/>
+    <n v="22"/>
+    <n v="70"/>
+    <n v="78"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="58"/>
+    <n v="28.999999999999996"/>
+    <n v="34"/>
+    <n v="9"/>
+    <n v="17"/>
+    <n v="55"/>
+    <n v="6"/>
+    <n v="30"/>
+    <n v="7"/>
+    <n v="42854"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="4382"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab20c3188ce3e06cc494050"/>
+    <s v="21/09/2026 16:21:50"/>
+    <s v="22/09/2026 02:03:45"/>
+    <s v="Ranieli"/>
+    <x v="38"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="38"/>
+    <n v="54"/>
+    <n v="62"/>
+    <n v="46"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="37"/>
+    <n v="18.5"/>
+    <n v="31"/>
+    <n v="8"/>
+    <n v="15.5"/>
+    <n v="60"/>
+    <n v="8"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="220359"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3127"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab35bcaa4adeea581715e48"/>
+    <s v="22/09/2026 23:22:32"/>
+    <s v="23/09/2026 01:55:38"/>
+    <s v="Ranieli"/>
+    <x v="39"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="19"/>
+    <n v="29"/>
+    <n v="81"/>
+    <n v="71"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="65"/>
+    <n v="32.5"/>
+    <n v="48"/>
+    <n v="3"/>
+    <n v="24"/>
+    <n v="85"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <s v="13188‐"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="5908"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab35bc9a4adeea581715e10"/>
+    <s v="22/09/2026 21:28:02"/>
+    <s v="23/09/2026 01:55:37"/>
+    <s v="Ranieli"/>
+    <x v="39"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="21"/>
+    <n v="27"/>
+    <n v="79"/>
+    <n v="73"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="59"/>
+    <n v="29.5"/>
+    <n v="42"/>
+    <n v="7"/>
+    <n v="21"/>
+    <n v="65"/>
+    <n v="10"/>
+    <n v="50"/>
+    <n v="5"/>
+    <n v="42862"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3322"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab35bc9a4adeea581715df2"/>
+    <s v="22/09/2026 18:09:51"/>
+    <s v="23/09/2026 01:55:37"/>
+    <s v="Ranieli"/>
+    <x v="39"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="21"/>
+    <n v="52"/>
+    <n v="79"/>
+    <n v="48"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="46"/>
+    <n v="23"/>
+    <n v="36"/>
+    <n v="5"/>
+    <n v="18"/>
+    <n v="75"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="4032"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab35bc8a4adeea581715dc2"/>
+    <s v="22/09/2026 16:41:52"/>
+    <s v="23/09/2026 01:55:36"/>
+    <s v="Ranieli"/>
+    <x v="39"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="17"/>
+    <n v="50"/>
+    <n v="83"/>
+    <n v="50"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <n v="44"/>
+    <n v="3"/>
+    <n v="22"/>
+    <n v="85"/>
+    <n v="7"/>
+    <n v="35"/>
+    <n v="10"/>
+    <n v="995638"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="2478"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:AF118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="117" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="U117:AH118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="10">
@@ -8608,7 +9006,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="39">
+      <items count="41">
         <item x="26"/>
         <item x="28"/>
         <item x="27"/>
@@ -8634,6 +9032,8 @@
         <item x="17"/>
         <item x="18"/>
         <item x="19"/>
+        <item x="38"/>
+        <item x="39"/>
         <item x="20"/>
         <item x="21"/>
         <item x="22"/>
@@ -8689,7 +9089,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="12">
+  <colItems count="14">
     <i>
       <x/>
     </i>
@@ -8725,6 +9125,12 @@
     </i>
     <i>
       <x v="21"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -8809,8 +9215,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL155" totalsRowShown="0">
-  <autoFilter ref="A1:AL155"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL163" totalsRowShown="0">
+  <autoFilter ref="A1:AL163"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -9182,9 +9588,9 @@
   <dimension ref="A1:AR118"/>
   <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.85546875" style="25" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" style="25" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="1" max="2" width="9.85546875" style="25" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="29.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" customWidth="1"/>
     <col min="7" max="18" width="9.140625" style="25" customWidth="1"/>
@@ -9303,11 +9709,11 @@
       </c>
       <c r="AG3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>21/09/2026</v>
       </c>
       <c r="AH3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>22/09/2026</v>
       </c>
       <c r="AI3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -9573,7 +9979,7 @@
       </c>
       <c r="O5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],O$3),"")</f>
-        <v>6.9454545454545453</v>
+        <v>6.9523809523809526</v>
       </c>
       <c r="P5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],P$3),"")</f>
@@ -9636,13 +10042,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG5" s="12" t="str">
+      <c r="AG5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH5" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AI$3),"")</f>
@@ -9738,7 +10144,7 @@
       </c>
       <c r="O6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.8524590163934427</v>
+        <v>6.8695652173913047</v>
       </c>
       <c r="P6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -9801,13 +10207,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG6" s="9" t="str">
+      <c r="AG6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH6" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -10073,7 +10479,7 @@
       </c>
       <c r="O8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],O$3),"")</f>
-        <v>7.1607142857142856</v>
+        <v>7.140625</v>
       </c>
       <c r="P8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
@@ -10136,13 +10542,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG8" s="12" t="str">
+      <c r="AG8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH8" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AI$3),"")</f>
@@ -10238,7 +10644,7 @@
       </c>
       <c r="O9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.338709677419355</v>
+        <v>7.3</v>
       </c>
       <c r="P9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10301,13 +10707,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG9" s="9" t="str">
+      <c r="AG9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH9" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -10636,13 +11042,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG11" s="12" t="str">
+      <c r="AG11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH11" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AI$3),"")</f>
@@ -10738,7 +11144,7 @@
       </c>
       <c r="O12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.096774193548387</v>
+        <v>7.0857142857142854</v>
       </c>
       <c r="P12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10801,13 +11207,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG12" s="9" t="str">
+      <c r="AG12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH12" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -11073,7 +11479,7 @@
       </c>
       <c r="O14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],O$3),"")</f>
-        <v>5.3928571428571432</v>
+        <v>5.375</v>
       </c>
       <c r="P14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
@@ -11136,13 +11542,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AF$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="AG14" s="12" t="str">
+      <c r="AG14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH14" s="12" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="AH14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AI$3),"")</f>
@@ -11238,7 +11644,7 @@
       </c>
       <c r="O15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>5.4838709677419351</v>
+        <v>5.4571428571428573</v>
       </c>
       <c r="P15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11301,13 +11707,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="AG15" s="9" t="str">
+      <c r="AG15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH15" s="9" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="AH15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -11573,7 +11979,7 @@
       </c>
       <c r="O17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.83017857142857143</v>
+        <v>0.81874999999999998</v>
       </c>
       <c r="P17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
@@ -11636,13 +12042,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AF$3)/100,"")</f>
         <v>0.86250000000000004</v>
       </c>
-      <c r="AG17" s="16" t="str">
+      <c r="AG17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH17" s="16" t="str">
+        <v>0.67249999999999999</v>
+      </c>
+      <c r="AH17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.80500000000000005</v>
       </c>
       <c r="AI17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AI$3)/100,"")</f>
@@ -11738,7 +12144,7 @@
       </c>
       <c r="O18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.82564516129032262</v>
+        <v>0.81571428571428573</v>
       </c>
       <c r="P18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -11801,13 +12207,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
         <v>0.86250000000000004</v>
       </c>
-      <c r="AG18" s="10" t="str">
+      <c r="AG18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH18" s="10" t="str">
+        <v>0.67249999999999999</v>
+      </c>
+      <c r="AH18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.80500000000000005</v>
       </c>
       <c r="AI18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
@@ -12073,7 +12479,7 @@
       </c>
       <c r="O20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63803571428571426</v>
+        <v>0.63234374999999998</v>
       </c>
       <c r="P20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
@@ -12136,13 +12542,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AF$3)/100,"")</f>
         <v>0.69750000000000001</v>
       </c>
-      <c r="AG20" s="16" t="str">
+      <c r="AG20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH20" s="16" t="str">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AH20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.60499999999999998</v>
       </c>
       <c r="AI20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AI$3)/100,"")</f>
@@ -12238,7 +12644,7 @@
       </c>
       <c r="O21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63967741935483868</v>
+        <v>0.63428571428571434</v>
       </c>
       <c r="P21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -12301,13 +12707,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
         <v>0.69750000000000001</v>
       </c>
-      <c r="AG21" s="10" t="str">
+      <c r="AG21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH21" s="10" t="str">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AH21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.60499999999999998</v>
       </c>
       <c r="AI21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
@@ -12573,7 +12979,7 @@
       </c>
       <c r="O23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],O$3),"")</f>
-        <v>6.6785714285714288</v>
+        <v>6.6875</v>
       </c>
       <c r="P23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
@@ -12636,13 +13042,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG23" s="12" t="str">
+      <c r="AG23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH23" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AI23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AI$3),"")</f>
@@ -12738,7 +13144,7 @@
       </c>
       <c r="O24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.790322580645161</v>
+        <v>6.7857142857142856</v>
       </c>
       <c r="P24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -12801,13 +13207,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG24" s="9" t="str">
+      <c r="AG24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH24" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AI24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -13073,7 +13479,7 @@
       </c>
       <c r="O26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],O$3),"")</f>
-        <v>6.872727272727273</v>
+        <v>6.8888888888888893</v>
       </c>
       <c r="P26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
@@ -13136,13 +13542,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG26" s="12" t="str">
+      <c r="AG26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH26" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AI$3),"")</f>
@@ -13238,7 +13644,7 @@
       </c>
       <c r="O27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.081967213114754</v>
+        <v>7.0724637681159424</v>
       </c>
       <c r="P27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13301,13 +13707,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG27" s="9" t="str">
+      <c r="AG27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH27" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -13636,13 +14042,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG29" s="12" t="str">
+      <c r="AG29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH29" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AI$3),"")</f>
@@ -13738,7 +14144,7 @@
       </c>
       <c r="O30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.290322580645161</v>
+        <v>7.2571428571428571</v>
       </c>
       <c r="P30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13801,13 +14207,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG30" s="9" t="str">
+      <c r="AG30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH30" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -14073,7 +14479,7 @@
       </c>
       <c r="O32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],O$3),"")</f>
-        <v>6.8928571428571432</v>
+        <v>6.90625</v>
       </c>
       <c r="P32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
@@ -14136,13 +14542,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG32" s="12" t="str">
+      <c r="AG32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH32" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AI$3),"")</f>
@@ -14238,7 +14644,7 @@
       </c>
       <c r="O33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0483870967741939</v>
+        <v>7.0428571428571427</v>
       </c>
       <c r="P33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14301,13 +14707,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG33" s="9" t="str">
+      <c r="AG33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH33" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -14573,7 +14979,7 @@
       </c>
       <c r="O35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],O$3),"")</f>
-        <v>7.0535714285714288</v>
+        <v>7.046875</v>
       </c>
       <c r="P35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],P$3),"")</f>
@@ -14636,13 +15042,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG35" s="12" t="str">
+      <c r="AG35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH35" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AI$3),"")</f>
@@ -14738,7 +15144,7 @@
       </c>
       <c r="O36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.193548387096774</v>
+        <v>7.1714285714285717</v>
       </c>
       <c r="P36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14801,13 +15207,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AG36" s="9" t="str">
+      <c r="AG36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH36" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -15073,7 +15479,7 @@
       </c>
       <c r="O38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],O$3),"")</f>
-        <v>6.4423076923076925</v>
+        <v>6.3728813559322033</v>
       </c>
       <c r="P38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
@@ -15136,13 +15542,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AF$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="AG38" s="12" t="str">
+      <c r="AG38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH38" s="12" t="str">
+        <v>6</v>
+      </c>
+      <c r="AH38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>5.666666666666667</v>
       </c>
       <c r="AI38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AI$3),"")</f>
@@ -15238,7 +15644,7 @@
       </c>
       <c r="O39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.4655172413793105</v>
+        <v>6.4</v>
       </c>
       <c r="P39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15301,13 +15707,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="AG39" s="9" t="str">
+      <c r="AG39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH39" s="9" t="str">
+        <v>6</v>
+      </c>
+      <c r="AH39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>5.666666666666667</v>
       </c>
       <c r="AI39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -15573,7 +15979,7 @@
       </c>
       <c r="O41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],O$3),"")</f>
-        <v>8.5319148936170208</v>
+        <v>8.5294117647058822</v>
       </c>
       <c r="P41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
@@ -15636,13 +16042,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AF$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AG41" s="12" t="str">
+      <c r="AG41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH41" s="12" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="AH41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AI41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AI$3),"")</f>
@@ -15738,7 +16144,7 @@
       </c>
       <c r="O42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.4716981132075464</v>
+        <v>8.473684210526315</v>
       </c>
       <c r="P42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15801,13 +16207,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AG42" s="9" t="str">
+      <c r="AG42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH42" s="9" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="AH42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AI42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -16073,7 +16479,7 @@
       </c>
       <c r="O44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],O$3),"")</f>
-        <v>8.3829787234042552</v>
+        <v>8.4509803921568629</v>
       </c>
       <c r="P44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
@@ -16136,13 +16542,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AF$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AG44" s="12" t="str">
+      <c r="AG44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH44" s="12" t="str">
+        <v>10</v>
+      </c>
+      <c r="AH44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AI44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AI$3),"")</f>
@@ -16238,7 +16644,7 @@
       </c>
       <c r="O45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.387755102040817</v>
+        <v>8.4528301886792452</v>
       </c>
       <c r="P45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16301,13 +16707,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AG45" s="9" t="str">
+      <c r="AG45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH45" s="9" t="str">
+        <v>10</v>
+      </c>
+      <c r="AH45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AI45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -16573,7 +16979,7 @@
       </c>
       <c r="O47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.24118181818181816</v>
+        <v>0.2431451612903226</v>
       </c>
       <c r="P47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
@@ -16635,13 +17041,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AF$3)/100,"")</f>
         <v>0.24249999999999999</v>
       </c>
-      <c r="AG47" s="16" t="str">
+      <c r="AG47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH47" s="16" t="str">
+        <v>0.24</v>
+      </c>
+      <c r="AH47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.28333333333333333</v>
       </c>
       <c r="AI47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AI$3)/100,"")</f>
@@ -16737,7 +17143,7 @@
       </c>
       <c r="O48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.27918032786885244</v>
+        <v>0.2770588235294118</v>
       </c>
       <c r="P48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -16800,13 +17206,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
         <v>0.24249999999999999</v>
       </c>
-      <c r="AG48" s="10" t="str">
+      <c r="AG48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH48" s="10" t="str">
+        <v>0.24</v>
+      </c>
+      <c r="AH48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.28333333333333333</v>
       </c>
       <c r="AI48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
@@ -17072,7 +17478,7 @@
       </c>
       <c r="O50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.19294642857142857</v>
+        <v>0.19312499999999999</v>
       </c>
       <c r="P50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
@@ -17135,13 +17541,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AF$3)/100,"")</f>
         <v>0.18875</v>
       </c>
-      <c r="AG50" s="16" t="str">
+      <c r="AG50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH50" s="16" t="str">
+        <v>0.17624999999999999</v>
+      </c>
+      <c r="AH50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.21249999999999999</v>
       </c>
       <c r="AI50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AI$3)/100,"")</f>
@@ -17237,7 +17643,7 @@
       </c>
       <c r="O51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.20564516129032259</v>
+        <v>0.20435714285714288</v>
       </c>
       <c r="P51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17300,13 +17706,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
         <v>0.18875</v>
       </c>
-      <c r="AG51" s="10" t="str">
+      <c r="AG51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH51" s="10" t="str">
+        <v>0.17624999999999999</v>
+      </c>
+      <c r="AH51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.21249999999999999</v>
       </c>
       <c r="AI51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
@@ -17572,7 +17978,7 @@
       </c>
       <c r="O53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.76818181818181808</v>
+        <v>0.76031746031746039</v>
       </c>
       <c r="P53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
@@ -17635,13 +18041,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AF$3)/100,"")</f>
         <v>0.77500000000000002</v>
       </c>
-      <c r="AG53" s="16" t="str">
+      <c r="AG53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH53" s="16" t="str">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="AH53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.77500000000000002</v>
       </c>
       <c r="AI53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AI$3)/100,"")</f>
@@ -17737,7 +18143,7 @@
       </c>
       <c r="O54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.75087719298245614</v>
+        <v>0.74538461538461531</v>
       </c>
       <c r="P54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17800,13 +18206,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
         <v>0.77500000000000002</v>
       </c>
-      <c r="AG54" s="10" t="str">
+      <c r="AG54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH54" s="10" t="str">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="AH54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.77500000000000002</v>
       </c>
       <c r="AI54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
@@ -18072,7 +18478,7 @@
       </c>
       <c r="O56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28839285714285717</v>
+        <v>0.29609374999999999</v>
       </c>
       <c r="P56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
@@ -18135,13 +18541,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AF$3)/100,"")</f>
         <v>0.375</v>
       </c>
-      <c r="AG56" s="16" t="str">
+      <c r="AG56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH56" s="16" t="str">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="AH56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.33750000000000002</v>
       </c>
       <c r="AI56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AI$3)/100,"")</f>
@@ -18237,7 +18643,7 @@
       </c>
       <c r="O57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28839285714285717</v>
+        <v>0.29609374999999999</v>
       </c>
       <c r="P57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18300,13 +18706,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
         <v>0.375</v>
       </c>
-      <c r="AG57" s="10" t="str">
+      <c r="AG57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH57" s="10" t="str">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="AH57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
+        <v>0.33750000000000002</v>
       </c>
       <c r="AI57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
@@ -18572,7 +18978,7 @@
       </c>
       <c r="O59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],O$3),"")</f>
-        <v>8.2777777777777786</v>
+        <v>8.32258064516129</v>
       </c>
       <c r="P59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
@@ -18635,13 +19041,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AF$3),"")</f>
         <v>9.25</v>
       </c>
-      <c r="AG59" s="12" t="str">
+      <c r="AG59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH59" s="12" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="AH59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>8.75</v>
       </c>
       <c r="AI59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AI$3),"")</f>
@@ -18737,7 +19143,7 @@
       </c>
       <c r="O60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.2777777777777786</v>
+        <v>8.32258064516129</v>
       </c>
       <c r="P60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -18800,13 +19206,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AF$3),"")</f>
         <v>9.25</v>
       </c>
-      <c r="AG60" s="9" t="str">
+      <c r="AG60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH60" s="9" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="AH60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v/>
+        <v>8.75</v>
       </c>
       <c r="AI60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -18928,8 +19334,12 @@
       <c r="AF118" t="s">
         <v>441</v>
       </c>
-      <c r="AG118"/>
-      <c r="AH118"/>
+      <c r="AG118" t="s">
+        <v>464</v>
+      </c>
+      <c r="AH118" t="s">
+        <v>476</v>
+      </c>
       <c r="AI118"/>
       <c r="AJ118"/>
       <c r="AK118"/>
@@ -19214,7 +19624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL155"/>
+  <dimension ref="A1:AL163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -36023,6 +36433,942 @@
         <v>3341</v>
       </c>
     </row>
+    <row r="156" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B156" s="33" t="s">
+        <v>461</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E156" t="s">
+        <v>18</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G156" s="3">
+        <v>2</v>
+      </c>
+      <c r="H156" s="3">
+        <v>7</v>
+      </c>
+      <c r="I156" s="3">
+        <v>7</v>
+      </c>
+      <c r="J156" s="3">
+        <v>7</v>
+      </c>
+      <c r="K156" s="3">
+        <v>5</v>
+      </c>
+      <c r="L156">
+        <v>28</v>
+      </c>
+      <c r="M156">
+        <v>51</v>
+      </c>
+      <c r="N156">
+        <v>72</v>
+      </c>
+      <c r="O156">
+        <v>49</v>
+      </c>
+      <c r="P156" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q156" s="3">
+        <v>7</v>
+      </c>
+      <c r="R156" s="3">
+        <v>7</v>
+      </c>
+      <c r="S156" s="3">
+        <v>7</v>
+      </c>
+      <c r="T156" s="3">
+        <v>7</v>
+      </c>
+      <c r="U156" s="3">
+        <v>5</v>
+      </c>
+      <c r="V156" t="s">
+        <v>20</v>
+      </c>
+      <c r="W156" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X156" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y156">
+        <v>47</v>
+      </c>
+      <c r="Z156">
+        <v>23.5</v>
+      </c>
+      <c r="AA156">
+        <v>41</v>
+      </c>
+      <c r="AB156">
+        <v>4</v>
+      </c>
+      <c r="AC156">
+        <v>20.5</v>
+      </c>
+      <c r="AD156">
+        <v>80</v>
+      </c>
+      <c r="AE156">
+        <v>7</v>
+      </c>
+      <c r="AF156">
+        <v>35</v>
+      </c>
+      <c r="AG156" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH156" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI156" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ156" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK156" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL156">
+        <v>5707</v>
+      </c>
+    </row>
+    <row r="157" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B157" t="s">
+        <v>465</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E157" t="s">
+        <v>18</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G157" s="3">
+        <v>2</v>
+      </c>
+      <c r="H157" s="3">
+        <v>7</v>
+      </c>
+      <c r="I157" s="3">
+        <v>7</v>
+      </c>
+      <c r="J157" s="3">
+        <v>7</v>
+      </c>
+      <c r="K157" s="3">
+        <v>7</v>
+      </c>
+      <c r="L157">
+        <v>35</v>
+      </c>
+      <c r="M157">
+        <v>41</v>
+      </c>
+      <c r="N157">
+        <v>65</v>
+      </c>
+      <c r="O157">
+        <v>59</v>
+      </c>
+      <c r="P157" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q157" s="3">
+        <v>7</v>
+      </c>
+      <c r="R157" s="3">
+        <v>7</v>
+      </c>
+      <c r="S157" s="3">
+        <v>7</v>
+      </c>
+      <c r="T157" s="3">
+        <v>7</v>
+      </c>
+      <c r="U157" s="3">
+        <v>5</v>
+      </c>
+      <c r="V157" t="s">
+        <v>20</v>
+      </c>
+      <c r="W157" s="3">
+        <v>10</v>
+      </c>
+      <c r="X157" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y157">
+        <v>50</v>
+      </c>
+      <c r="Z157">
+        <v>25</v>
+      </c>
+      <c r="AA157">
+        <v>35</v>
+      </c>
+      <c r="AB157">
+        <v>8</v>
+      </c>
+      <c r="AC157">
+        <v>17.5</v>
+      </c>
+      <c r="AD157">
+        <v>60</v>
+      </c>
+      <c r="AE157">
+        <v>8</v>
+      </c>
+      <c r="AF157">
+        <v>40</v>
+      </c>
+      <c r="AG157" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH157" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI157" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ157" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK157" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL157">
+        <v>3358</v>
+      </c>
+    </row>
+    <row r="158" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B158" t="s">
+        <v>468</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E158" t="s">
+        <v>18</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G158" s="3">
+        <v>2</v>
+      </c>
+      <c r="H158" s="3">
+        <v>7</v>
+      </c>
+      <c r="I158" s="3">
+        <v>7</v>
+      </c>
+      <c r="J158" s="3">
+        <v>7</v>
+      </c>
+      <c r="K158" s="3">
+        <v>5</v>
+      </c>
+      <c r="L158">
+        <v>30</v>
+      </c>
+      <c r="M158">
+        <v>22</v>
+      </c>
+      <c r="N158">
+        <v>70</v>
+      </c>
+      <c r="O158">
+        <v>78</v>
+      </c>
+      <c r="P158" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q158" s="3">
+        <v>7</v>
+      </c>
+      <c r="R158" s="3">
+        <v>7</v>
+      </c>
+      <c r="S158" s="3">
+        <v>7</v>
+      </c>
+      <c r="T158" s="3">
+        <v>7</v>
+      </c>
+      <c r="U158" s="3">
+        <v>7</v>
+      </c>
+      <c r="V158" t="s">
+        <v>20</v>
+      </c>
+      <c r="W158" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X158" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y158">
+        <v>58</v>
+      </c>
+      <c r="Z158">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="AA158">
+        <v>34</v>
+      </c>
+      <c r="AB158">
+        <v>9</v>
+      </c>
+      <c r="AC158">
+        <v>17</v>
+      </c>
+      <c r="AD158">
+        <v>55</v>
+      </c>
+      <c r="AE158">
+        <v>6</v>
+      </c>
+      <c r="AF158">
+        <v>30</v>
+      </c>
+      <c r="AG158" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH158" s="3">
+        <v>42854</v>
+      </c>
+      <c r="AI158" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ158" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK158" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL158">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="159" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B159" t="s">
+        <v>470</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E159" t="s">
+        <v>18</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G159" s="3">
+        <v>2</v>
+      </c>
+      <c r="H159" s="3">
+        <v>7</v>
+      </c>
+      <c r="I159" s="3">
+        <v>7</v>
+      </c>
+      <c r="J159" s="3">
+        <v>7</v>
+      </c>
+      <c r="K159" s="3">
+        <v>5</v>
+      </c>
+      <c r="L159">
+        <v>38</v>
+      </c>
+      <c r="M159">
+        <v>54</v>
+      </c>
+      <c r="N159">
+        <v>62</v>
+      </c>
+      <c r="O159">
+        <v>46</v>
+      </c>
+      <c r="P159" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q159" s="3">
+        <v>7</v>
+      </c>
+      <c r="R159" s="3">
+        <v>7</v>
+      </c>
+      <c r="S159" s="3">
+        <v>7</v>
+      </c>
+      <c r="T159" s="3">
+        <v>7</v>
+      </c>
+      <c r="U159" s="3">
+        <v>7</v>
+      </c>
+      <c r="V159" t="s">
+        <v>171</v>
+      </c>
+      <c r="W159" s="3">
+        <v>7</v>
+      </c>
+      <c r="X159" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y159">
+        <v>37</v>
+      </c>
+      <c r="Z159">
+        <v>18.5</v>
+      </c>
+      <c r="AA159">
+        <v>31</v>
+      </c>
+      <c r="AB159">
+        <v>8</v>
+      </c>
+      <c r="AC159">
+        <v>15.5</v>
+      </c>
+      <c r="AD159">
+        <v>60</v>
+      </c>
+      <c r="AE159">
+        <v>8</v>
+      </c>
+      <c r="AF159">
+        <v>40</v>
+      </c>
+      <c r="AG159" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH159" s="3">
+        <v>220359</v>
+      </c>
+      <c r="AI159" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ159" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK159" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL159">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="160" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B160" s="33" t="s">
+        <v>473</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E160" t="s">
+        <v>18</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G160" s="3">
+        <v>2</v>
+      </c>
+      <c r="H160" s="3">
+        <v>7</v>
+      </c>
+      <c r="I160" s="3">
+        <v>7</v>
+      </c>
+      <c r="J160" s="3">
+        <v>7</v>
+      </c>
+      <c r="K160" s="3">
+        <v>5</v>
+      </c>
+      <c r="L160">
+        <v>19</v>
+      </c>
+      <c r="M160">
+        <v>29</v>
+      </c>
+      <c r="N160">
+        <v>81</v>
+      </c>
+      <c r="O160">
+        <v>71</v>
+      </c>
+      <c r="P160" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q160" s="3">
+        <v>7</v>
+      </c>
+      <c r="R160" s="3">
+        <v>7</v>
+      </c>
+      <c r="S160" s="3">
+        <v>7</v>
+      </c>
+      <c r="T160" s="3">
+        <v>7</v>
+      </c>
+      <c r="U160" s="3">
+        <v>5</v>
+      </c>
+      <c r="V160" t="s">
+        <v>20</v>
+      </c>
+      <c r="W160" s="3">
+        <v>7</v>
+      </c>
+      <c r="X160" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y160">
+        <v>65</v>
+      </c>
+      <c r="Z160">
+        <v>32.5</v>
+      </c>
+      <c r="AA160">
+        <v>48</v>
+      </c>
+      <c r="AB160">
+        <v>3</v>
+      </c>
+      <c r="AC160">
+        <v>24</v>
+      </c>
+      <c r="AD160">
+        <v>85</v>
+      </c>
+      <c r="AE160">
+        <v>5</v>
+      </c>
+      <c r="AF160">
+        <v>25</v>
+      </c>
+      <c r="AG160" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH160" t="s">
+        <v>477</v>
+      </c>
+      <c r="AI160" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ160" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK160" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL160">
+        <v>5908</v>
+      </c>
+    </row>
+    <row r="161" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B161" t="s">
+        <v>478</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E161" t="s">
+        <v>18</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G161" s="3">
+        <v>2</v>
+      </c>
+      <c r="H161" s="3">
+        <v>7</v>
+      </c>
+      <c r="I161" s="3">
+        <v>7</v>
+      </c>
+      <c r="J161" s="3">
+        <v>7</v>
+      </c>
+      <c r="K161" s="3">
+        <v>5</v>
+      </c>
+      <c r="L161">
+        <v>21</v>
+      </c>
+      <c r="M161">
+        <v>27</v>
+      </c>
+      <c r="N161">
+        <v>79</v>
+      </c>
+      <c r="O161">
+        <v>73</v>
+      </c>
+      <c r="P161" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q161" s="3">
+        <v>7</v>
+      </c>
+      <c r="R161" s="3">
+        <v>7</v>
+      </c>
+      <c r="S161" s="3">
+        <v>7</v>
+      </c>
+      <c r="T161" s="3">
+        <v>7</v>
+      </c>
+      <c r="U161" s="3">
+        <v>5</v>
+      </c>
+      <c r="V161" t="s">
+        <v>171</v>
+      </c>
+      <c r="W161" s="3">
+        <v>10</v>
+      </c>
+      <c r="X161" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y161">
+        <v>59</v>
+      </c>
+      <c r="Z161">
+        <v>29.5</v>
+      </c>
+      <c r="AA161">
+        <v>42</v>
+      </c>
+      <c r="AB161">
+        <v>7</v>
+      </c>
+      <c r="AC161">
+        <v>21</v>
+      </c>
+      <c r="AD161">
+        <v>65</v>
+      </c>
+      <c r="AE161">
+        <v>10</v>
+      </c>
+      <c r="AF161">
+        <v>50</v>
+      </c>
+      <c r="AG161" s="3">
+        <v>5</v>
+      </c>
+      <c r="AH161" s="3">
+        <v>42862</v>
+      </c>
+      <c r="AI161" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ161" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK161" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL161">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="162" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B162" t="s">
+        <v>481</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E162" t="s">
+        <v>18</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G162" s="3">
+        <v>2</v>
+      </c>
+      <c r="H162" s="3">
+        <v>7</v>
+      </c>
+      <c r="I162" s="3">
+        <v>7</v>
+      </c>
+      <c r="J162" s="3">
+        <v>7</v>
+      </c>
+      <c r="K162" s="3">
+        <v>5</v>
+      </c>
+      <c r="L162">
+        <v>21</v>
+      </c>
+      <c r="M162">
+        <v>52</v>
+      </c>
+      <c r="N162">
+        <v>79</v>
+      </c>
+      <c r="O162">
+        <v>48</v>
+      </c>
+      <c r="P162" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q162" s="3">
+        <v>7</v>
+      </c>
+      <c r="R162" s="3">
+        <v>7</v>
+      </c>
+      <c r="S162" s="3">
+        <v>7</v>
+      </c>
+      <c r="T162" s="3">
+        <v>7</v>
+      </c>
+      <c r="U162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V162" t="s">
+        <v>171</v>
+      </c>
+      <c r="W162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y162">
+        <v>46</v>
+      </c>
+      <c r="Z162">
+        <v>23</v>
+      </c>
+      <c r="AA162">
+        <v>36</v>
+      </c>
+      <c r="AB162">
+        <v>5</v>
+      </c>
+      <c r="AC162">
+        <v>18</v>
+      </c>
+      <c r="AD162">
+        <v>75</v>
+      </c>
+      <c r="AE162">
+        <v>5</v>
+      </c>
+      <c r="AF162">
+        <v>25</v>
+      </c>
+      <c r="AG162" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH162" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI162" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ162" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK162" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL162">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="163" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B163" t="s">
+        <v>483</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E163" t="s">
+        <v>18</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G163" s="3">
+        <v>2</v>
+      </c>
+      <c r="H163" s="3">
+        <v>7</v>
+      </c>
+      <c r="I163" s="3">
+        <v>7</v>
+      </c>
+      <c r="J163" s="3">
+        <v>7</v>
+      </c>
+      <c r="K163" s="3">
+        <v>5</v>
+      </c>
+      <c r="L163">
+        <v>17</v>
+      </c>
+      <c r="M163">
+        <v>50</v>
+      </c>
+      <c r="N163">
+        <v>83</v>
+      </c>
+      <c r="O163">
+        <v>50</v>
+      </c>
+      <c r="P163" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q163" s="3">
+        <v>7</v>
+      </c>
+      <c r="R163" s="3">
+        <v>7</v>
+      </c>
+      <c r="S163" s="3">
+        <v>7</v>
+      </c>
+      <c r="T163" s="3">
+        <v>7</v>
+      </c>
+      <c r="U163" s="3">
+        <v>7</v>
+      </c>
+      <c r="V163" t="s">
+        <v>171</v>
+      </c>
+      <c r="W163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y163" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z163" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA163">
+        <v>44</v>
+      </c>
+      <c r="AB163">
+        <v>3</v>
+      </c>
+      <c r="AC163">
+        <v>22</v>
+      </c>
+      <c r="AD163">
+        <v>85</v>
+      </c>
+      <c r="AE163">
+        <v>7</v>
+      </c>
+      <c r="AF163">
+        <v>35</v>
+      </c>
+      <c r="AG163" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH163" s="3">
+        <v>995638</v>
+      </c>
+      <c r="AI163" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ163" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK163" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL163">
+        <v>2478</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="117" r:id="rId3"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="498">
   <si>
     <t>ID</t>
   </si>
@@ -490,12 +490,6 @@
     <t>Carne no Front</t>
   </si>
   <si>
-    <t>Eficiência da Pinçagem</t>
-  </si>
-  <si>
-    <t>Eficiência remoção cartilagem</t>
-  </si>
-  <si>
     <t>Medalhão na Asa Meyn</t>
   </si>
   <si>
@@ -1540,6 +1534,48 @@
   </si>
   <si>
     <t>23/09/2026 01:55:36</t>
+  </si>
+  <si>
+    <t>% Eficiência da Pinçagem</t>
+  </si>
+  <si>
+    <t>% Eficiência remoção cartilagem</t>
+  </si>
+  <si>
+    <t>6ab4adae3a9c92219c3dfab7</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:57:14</t>
+  </si>
+  <si>
+    <t>24/09/2026 01:57:18</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>6ab4adad3a9c92219c3dfa6d</t>
+  </si>
+  <si>
+    <t>23/09/2026 21:19:35</t>
+  </si>
+  <si>
+    <t>24/09/2026 01:57:17</t>
+  </si>
+  <si>
+    <t>6ab4adad3a9c92219c3dfa61</t>
+  </si>
+  <si>
+    <t>23/09/2026 17:54:34</t>
+  </si>
+  <si>
+    <t>6ab4adac3a9c92219c3dfa49</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:19:32</t>
+  </si>
+  <si>
+    <t>24/09/2026 01:57:16</t>
   </si>
 </sst>
 </file>
@@ -2319,7 +2355,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46288.580346990741" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="162">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46289.430432986112" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="166">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2350,7 +2386,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="40">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="41">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2391,6 +2427,7 @@
         <s v="17/09/2026"/>
         <s v="21/09/2026"/>
         <s v="22/09/2026"/>
+        <s v="23/09/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2414,10 +2451,10 @@
     <cacheField name="2.3 Cartilagem" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="12" maxValue="380"/>
     </cacheField>
-    <cacheField name="Eficiência da Pinçagem" numFmtId="0">
+    <cacheField name="% Eficiência da Pinçagem" numFmtId="0">
       <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="19" maxValue="94"/>
     </cacheField>
-    <cacheField name="Eficiência remoção cartilagem" numFmtId="0">
+    <cacheField name="% Eficiência remoção cartilagem" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="-280" maxValue="88"/>
     </cacheField>
     <cacheField name="Corte Perna Cone" numFmtId="0">
@@ -2499,7 +2536,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="162">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="166">
   <r>
     <x v="0"/>
     <m/>
@@ -8980,12 +9017,172 @@
     <s v="assinatura"/>
     <n v="2478"/>
   </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab4adae3a9c92219c3dfab7"/>
+    <s v="23/09/2026 22:57:14"/>
+    <s v="24/09/2026 01:57:18"/>
+    <s v="Ranieli"/>
+    <x v="40"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="38"/>
+    <n v="17"/>
+    <n v="62"/>
+    <n v="83"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="54"/>
+    <n v="27"/>
+    <n v="44"/>
+    <n v="3"/>
+    <n v="22"/>
+    <n v="85"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="7"/>
+    <n v="42762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3844"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab4adad3a9c92219c3dfa6d"/>
+    <s v="23/09/2026 21:19:35"/>
+    <s v="24/09/2026 01:57:17"/>
+    <s v="Ranieli"/>
+    <x v="40"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="28"/>
+    <n v="75"/>
+    <n v="72"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="69"/>
+    <n v="34.5"/>
+    <n v="42"/>
+    <n v="7"/>
+    <n v="21"/>
+    <n v="65"/>
+    <n v="6"/>
+    <n v="30"/>
+    <n v="7"/>
+    <n v="42846"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="2053"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab4adad3a9c92219c3dfa61"/>
+    <s v="23/09/2026 17:54:34"/>
+    <s v="24/09/2026 01:57:17"/>
+    <s v="Ranieli"/>
+    <x v="40"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="17"/>
+    <n v="39"/>
+    <n v="83"/>
+    <n v="61"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="53"/>
+    <n v="26.5"/>
+    <n v="33"/>
+    <n v="5"/>
+    <n v="16.5"/>
+    <n v="75"/>
+    <n v="6"/>
+    <n v="30"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="4578"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab4adac3a9c92219c3dfa49"/>
+    <s v="23/09/2026 16:19:32"/>
+    <s v="24/09/2026 01:57:16"/>
+    <s v="Ranieli"/>
+    <x v="40"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="27"/>
+    <n v="16"/>
+    <n v="73"/>
+    <n v="84"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <n v="34"/>
+    <n v="3"/>
+    <n v="17"/>
+    <n v="85"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="10"/>
+    <n v="13188"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="5257"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="117" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:AH118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="U117:AI118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="10">
@@ -9006,7 +9203,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="41">
+      <items count="42">
         <item x="26"/>
         <item x="28"/>
         <item x="27"/>
@@ -9034,6 +9231,7 @@
         <item x="19"/>
         <item x="38"/>
         <item x="39"/>
+        <item x="40"/>
         <item x="20"/>
         <item x="21"/>
         <item x="22"/>
@@ -9057,8 +9255,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -9089,7 +9287,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="14">
+  <colItems count="15">
     <i>
       <x/>
     </i>
@@ -9131,6 +9329,9 @@
     </i>
     <i>
       <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -9215,8 +9416,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL163" totalsRowShown="0">
-  <autoFilter ref="A1:AL163"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL167" totalsRowShown="0">
+  <autoFilter ref="A1:AL167"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -9233,8 +9434,8 @@
     <tableColumn id="12" name="Carne no Front" dataDxfId="8"/>
     <tableColumn id="13" name="2.2 Pinçagem "/>
     <tableColumn id="14" name="2.3 Cartilagem"/>
-    <tableColumn id="15" name="Eficiência da Pinçagem"/>
-    <tableColumn id="16" name="Eficiência remoção cartilagem"/>
+    <tableColumn id="15" name="% Eficiência da Pinçagem"/>
+    <tableColumn id="16" name="% Eficiência remoção cartilagem"/>
     <tableColumn id="17" name="Corte Perna Cone" dataDxfId="7"/>
     <tableColumn id="18" name="Peito na Asa Cone" dataDxfId="6"/>
     <tableColumn id="19" name="Medalhão na Asa Cone" dataDxfId="5"/>
@@ -9606,16 +9807,16 @@
         <v>140</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>141</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>126</v>
@@ -9717,7 +9918,7 @@
       </c>
       <c r="AI3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>23/09/2026</v>
       </c>
       <c r="AJ3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -9979,7 +10180,7 @@
       </c>
       <c r="O5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],O$3),"")</f>
-        <v>6.9523809523809526</v>
+        <v>6.955223880597015</v>
       </c>
       <c r="P5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],P$3),"")</f>
@@ -10050,9 +10251,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI5" s="12" t="str">
+      <c r="AI5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AJ$3),"")</f>
@@ -10144,7 +10345,7 @@
       </c>
       <c r="O6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.8695652173913047</v>
+        <v>6.8767123287671232</v>
       </c>
       <c r="P6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10215,9 +10416,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI6" s="9" t="str">
+      <c r="AI6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -10479,7 +10680,7 @@
       </c>
       <c r="O8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],O$3),"")</f>
-        <v>7.140625</v>
+        <v>7.132352941176471</v>
       </c>
       <c r="P8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
@@ -10550,9 +10751,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI8" s="12" t="str">
+      <c r="AI8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AJ$3),"")</f>
@@ -10644,7 +10845,7 @@
       </c>
       <c r="O9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.3</v>
+        <v>7.2837837837837842</v>
       </c>
       <c r="P9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10715,9 +10916,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI9" s="9" t="str">
+      <c r="AI9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -11050,9 +11251,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI11" s="12" t="str">
+      <c r="AI11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AJ$3),"")</f>
@@ -11144,7 +11345,7 @@
       </c>
       <c r="O12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0857142857142854</v>
+        <v>7.0810810810810807</v>
       </c>
       <c r="P12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11215,9 +11416,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI12" s="9" t="str">
+      <c r="AI12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -11479,7 +11680,7 @@
       </c>
       <c r="O14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],O$3),"")</f>
-        <v>5.375</v>
+        <v>5.382352941176471</v>
       </c>
       <c r="P14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
@@ -11550,9 +11751,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AH$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AI14" s="12" t="str">
+      <c r="AI14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AJ14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AJ$3),"")</f>
@@ -11644,7 +11845,7 @@
       </c>
       <c r="O15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>5.4571428571428573</v>
+        <v>5.4594594594594597</v>
       </c>
       <c r="P15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11715,9 +11916,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AI15" s="9" t="str">
+      <c r="AI15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AJ15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -11765,15 +11966,15 @@
         <v>1</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D16" s="4" t="str">
         <f>IF(E16=0,#REF!,E16)</f>
-        <v>Eficiência da Pinçagem</v>
+        <v>% Eficiência da Pinçagem</v>
       </c>
       <c r="E16" s="39" t="str">
         <f>Coleta!N1</f>
-        <v>Eficiência da Pinçagem</v>
+        <v>% Eficiência da Pinçagem</v>
       </c>
       <c r="F16" s="22">
         <v>1</v>
@@ -11935,11 +12136,11 @@
         <v>2</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D17" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>Eficiência da Pinçagem</v>
+        <v>% Eficiência da Pinçagem</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="23">
@@ -11979,7 +12180,7 @@
       </c>
       <c r="O17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.81874999999999998</v>
+        <v>0.81367647058823533</v>
       </c>
       <c r="P17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
@@ -12050,9 +12251,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AH$3)/100,"")</f>
         <v>0.80500000000000005</v>
       </c>
-      <c r="AI17" s="16" t="str">
+      <c r="AI17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.73250000000000004</v>
       </c>
       <c r="AJ17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AJ$3)/100,"")</f>
@@ -12100,11 +12301,11 @@
         <v>Unidade</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D18" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>Eficiência da Pinçagem</v>
+        <v>% Eficiência da Pinçagem</v>
       </c>
       <c r="E18" s="41"/>
       <c r="F18" s="24" t="s">
@@ -12144,7 +12345,7 @@
       </c>
       <c r="O18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.81571428571428573</v>
+        <v>0.81121621621621631</v>
       </c>
       <c r="P18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -12215,9 +12416,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
         <v>0.80500000000000005</v>
       </c>
-      <c r="AI18" s="10" t="str">
+      <c r="AI18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.73250000000000004</v>
       </c>
       <c r="AJ18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -12265,15 +12466,15 @@
         <v>1</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D19" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>Eficiência remoção cartilagem</v>
+        <v>% Eficiência remoção cartilagem</v>
       </c>
       <c r="E19" s="39" t="str">
         <f>Coleta!O1</f>
-        <v>Eficiência remoção cartilagem</v>
+        <v>% Eficiência remoção cartilagem</v>
       </c>
       <c r="F19" s="22">
         <v>1</v>
@@ -12435,11 +12636,11 @@
         <v>2</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D20" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>Eficiência remoção cartilagem</v>
+        <v>% Eficiência remoção cartilagem</v>
       </c>
       <c r="E20" s="40"/>
       <c r="F20" s="23">
@@ -12479,7 +12680,7 @@
       </c>
       <c r="O20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63234374999999998</v>
+        <v>0.63926470588235296</v>
       </c>
       <c r="P20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
@@ -12550,9 +12751,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AH$3)/100,"")</f>
         <v>0.60499999999999998</v>
       </c>
-      <c r="AI20" s="16" t="str">
+      <c r="AI20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="AJ20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AJ$3)/100,"")</f>
@@ -12600,11 +12801,11 @@
         <v>Unidade</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D21" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>Eficiência remoção cartilagem</v>
+        <v>% Eficiência remoção cartilagem</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="24" t="s">
@@ -12644,7 +12845,7 @@
       </c>
       <c r="O21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63428571428571434</v>
+        <v>0.64054054054054044</v>
       </c>
       <c r="P21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -12715,9 +12916,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
         <v>0.60499999999999998</v>
       </c>
-      <c r="AI21" s="10" t="str">
+      <c r="AI21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="AJ21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -12979,7 +13180,7 @@
       </c>
       <c r="O23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],O$3),"")</f>
-        <v>6.6875</v>
+        <v>6.7058823529411766</v>
       </c>
       <c r="P23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
@@ -13050,9 +13251,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AH$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AI23" s="12" t="str">
+      <c r="AI23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AJ$3),"")</f>
@@ -13144,7 +13345,7 @@
       </c>
       <c r="O24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.7857142857142856</v>
+        <v>6.7972972972972974</v>
       </c>
       <c r="P24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13215,9 +13416,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AI24" s="9" t="str">
+      <c r="AI24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -13479,7 +13680,7 @@
       </c>
       <c r="O26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],O$3),"")</f>
-        <v>6.8888888888888893</v>
+        <v>6.8955223880597014</v>
       </c>
       <c r="P26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
@@ -13550,9 +13751,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI26" s="12" t="str">
+      <c r="AI26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AJ$3),"")</f>
@@ -13644,7 +13845,7 @@
       </c>
       <c r="O27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0724637681159424</v>
+        <v>7.0684931506849313</v>
       </c>
       <c r="P27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13715,9 +13916,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI27" s="9" t="str">
+      <c r="AI27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -14050,9 +14251,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI29" s="12" t="str">
+      <c r="AI29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AJ$3),"")</f>
@@ -14144,7 +14345,7 @@
       </c>
       <c r="O30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2571428571428571</v>
+        <v>7.243243243243243</v>
       </c>
       <c r="P30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14215,9 +14416,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI30" s="9" t="str">
+      <c r="AI30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -14479,7 +14680,7 @@
       </c>
       <c r="O32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],O$3),"")</f>
-        <v>6.90625</v>
+        <v>6.9117647058823533</v>
       </c>
       <c r="P32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
@@ -14550,9 +14751,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI32" s="12" t="str">
+      <c r="AI32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AJ$3),"")</f>
@@ -14644,7 +14845,7 @@
       </c>
       <c r="O33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0428571428571427</v>
+        <v>7.0405405405405403</v>
       </c>
       <c r="P33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14715,9 +14916,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI33" s="9" t="str">
+      <c r="AI33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -14765,7 +14966,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D34" s="4" t="str">
         <f t="shared" si="2"/>
@@ -14935,7 +15136,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D35" s="4" t="str">
         <f t="shared" si="2"/>
@@ -14979,7 +15180,7 @@
       </c>
       <c r="O35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],O$3),"")</f>
-        <v>7.046875</v>
+        <v>7.0441176470588234</v>
       </c>
       <c r="P35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],P$3),"")</f>
@@ -15050,9 +15251,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI35" s="12" t="str">
+      <c r="AI35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AJ$3),"")</f>
@@ -15100,7 +15301,7 @@
         <v>Unidade</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D36" s="4" t="str">
         <f t="shared" si="2"/>
@@ -15144,7 +15345,7 @@
       </c>
       <c r="O36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1714285714285717</v>
+        <v>7.1621621621621623</v>
       </c>
       <c r="P36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15215,9 +15416,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AI36" s="9" t="str">
+      <c r="AI36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -15265,7 +15466,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D37" s="4" t="str">
         <f t="shared" si="2"/>
@@ -15435,7 +15636,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D38" s="4" t="str">
         <f t="shared" si="2"/>
@@ -15479,7 +15680,7 @@
       </c>
       <c r="O38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],O$3),"")</f>
-        <v>6.3728813559322033</v>
+        <v>6.3492063492063489</v>
       </c>
       <c r="P38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
@@ -15550,9 +15751,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AH$3),"")</f>
         <v>5.666666666666667</v>
       </c>
-      <c r="AI38" s="12" t="str">
+      <c r="AI38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AJ38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AJ$3),"")</f>
@@ -15600,7 +15801,7 @@
         <v>Unidade</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D39" s="4" t="str">
         <f t="shared" si="2"/>
@@ -15644,7 +15845,7 @@
       </c>
       <c r="O39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.4</v>
+        <v>6.3768115942028984</v>
       </c>
       <c r="P39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15715,9 +15916,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>5.666666666666667</v>
       </c>
-      <c r="AI39" s="9" t="str">
+      <c r="AI39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AJ39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -15979,7 +16180,7 @@
       </c>
       <c r="O41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],O$3),"")</f>
-        <v>8.5294117647058822</v>
+        <v>8.4716981132075464</v>
       </c>
       <c r="P41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
@@ -16050,9 +16251,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AH$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AI41" s="12" t="str">
+      <c r="AI41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AJ$3),"")</f>
@@ -16144,7 +16345,7 @@
       </c>
       <c r="O42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.473684210526315</v>
+        <v>8.4237288135593218</v>
       </c>
       <c r="P42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16215,9 +16416,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AI42" s="9" t="str">
+      <c r="AI42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -16479,7 +16680,7 @@
       </c>
       <c r="O44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],O$3),"")</f>
-        <v>8.4509803921568629</v>
+        <v>8.4528301886792452</v>
       </c>
       <c r="P44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
@@ -16550,9 +16751,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AH$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AI44" s="12" t="str">
+      <c r="AI44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AJ44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AJ$3),"")</f>
@@ -16644,7 +16845,7 @@
       </c>
       <c r="O45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.4528301886792452</v>
+        <v>8.454545454545455</v>
       </c>
       <c r="P45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16715,9 +16916,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AI45" s="9" t="str">
+      <c r="AI45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AJ45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -16979,7 +17180,7 @@
       </c>
       <c r="O47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.2431451612903226</v>
+        <v>0.24546153846153845</v>
       </c>
       <c r="P47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
@@ -17027,7 +17228,7 @@
         <v>0.26833333333333331</v>
       </c>
       <c r="AC47" s="16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AD47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AD$3)/100,"")</f>
@@ -17049,9 +17250,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AH$3)/100,"")</f>
         <v>0.28333333333333333</v>
       </c>
-      <c r="AI47" s="16" t="str">
+      <c r="AI47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.29333333333333333</v>
       </c>
       <c r="AJ47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AJ$3)/100,"")</f>
@@ -17143,7 +17344,7 @@
       </c>
       <c r="O48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.2770588235294118</v>
+        <v>0.27774647887323944</v>
       </c>
       <c r="P48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17214,9 +17415,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
         <v>0.28333333333333333</v>
       </c>
-      <c r="AI48" s="10" t="str">
+      <c r="AI48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.29333333333333333</v>
       </c>
       <c r="AJ48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -17478,7 +17679,7 @@
       </c>
       <c r="O50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.19312499999999999</v>
+        <v>0.19301470588235292</v>
       </c>
       <c r="P50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
@@ -17549,9 +17750,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AH$3)/100,"")</f>
         <v>0.21249999999999999</v>
       </c>
-      <c r="AI50" s="16" t="str">
+      <c r="AI50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.19125</v>
       </c>
       <c r="AJ50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AJ$3)/100,"")</f>
@@ -17643,7 +17844,7 @@
       </c>
       <c r="O51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.20435714285714288</v>
+        <v>0.20364864864864862</v>
       </c>
       <c r="P51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17714,9 +17915,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
         <v>0.21249999999999999</v>
       </c>
-      <c r="AI51" s="10" t="str">
+      <c r="AI51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.19125</v>
       </c>
       <c r="AJ51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -17978,7 +18179,7 @@
       </c>
       <c r="O53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.76031746031746039</v>
+        <v>0.76119402985074625</v>
       </c>
       <c r="P53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
@@ -18049,9 +18250,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AH$3)/100,"")</f>
         <v>0.77500000000000002</v>
       </c>
-      <c r="AI53" s="16" t="str">
+      <c r="AI53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.77500000000000002</v>
       </c>
       <c r="AJ53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AJ$3)/100,"")</f>
@@ -18143,7 +18344,7 @@
       </c>
       <c r="O54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.74538461538461531</v>
+        <v>0.74710144927536237</v>
       </c>
       <c r="P54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18214,9 +18415,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
         <v>0.77500000000000002</v>
       </c>
-      <c r="AI54" s="10" t="str">
+      <c r="AI54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.77500000000000002</v>
       </c>
       <c r="AJ54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -18478,7 +18679,7 @@
       </c>
       <c r="O56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.29609374999999999</v>
+        <v>0.29191176470588237</v>
       </c>
       <c r="P56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
@@ -18549,9 +18750,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AH$3)/100,"")</f>
         <v>0.33750000000000002</v>
       </c>
-      <c r="AI56" s="16" t="str">
+      <c r="AI56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="AJ56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AJ$3)/100,"")</f>
@@ -18643,7 +18844,7 @@
       </c>
       <c r="O57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.29609374999999999</v>
+        <v>0.29191176470588237</v>
       </c>
       <c r="P57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18714,9 +18915,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
         <v>0.33750000000000002</v>
       </c>
-      <c r="AI57" s="10" t="str">
+      <c r="AI57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="AJ57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -18978,7 +19179,7 @@
       </c>
       <c r="O59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],O$3),"")</f>
-        <v>8.32258064516129</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="P59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
@@ -19049,9 +19250,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AH$3),"")</f>
         <v>8.75</v>
       </c>
-      <c r="AI59" s="12" t="str">
+      <c r="AI59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AJ59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AJ$3),"")</f>
@@ -19143,7 +19344,7 @@
       </c>
       <c r="O60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.32258064516129</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="P60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -19214,9 +19415,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AH$3),"")</f>
         <v>8.75</v>
       </c>
-      <c r="AI60" s="9" t="str">
+      <c r="AI60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AJ60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -19277,7 +19478,7 @@
     </row>
     <row r="117" spans="21:39" x14ac:dyDescent="0.25">
       <c r="U117" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="W117"/>
       <c r="X117"/>
@@ -19299,48 +19500,50 @@
     </row>
     <row r="118" spans="21:39" x14ac:dyDescent="0.25">
       <c r="U118" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="V118" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="W118" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="X118" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Y118" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Z118" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AA118" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AB118" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AC118" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AD118" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AE118" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AF118" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG118" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AH118" t="s">
-        <v>476</v>
-      </c>
-      <c r="AI118"/>
+        <v>474</v>
+      </c>
+      <c r="AI118" t="s">
+        <v>489</v>
+      </c>
       <c r="AJ118"/>
       <c r="AK118"/>
       <c r="AL118"/>
@@ -19624,7 +19827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL163"/>
+  <dimension ref="A1:AL167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -19690,10 +19893,10 @@
         <v>143</v>
       </c>
       <c r="I1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K1" t="s">
         <v>144</v>
@@ -19705,43 +19908,43 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>484</v>
       </c>
       <c r="O1" t="s">
-        <v>146</v>
+        <v>485</v>
       </c>
       <c r="P1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>147</v>
+      </c>
+      <c r="R1" t="s">
+        <v>148</v>
+      </c>
+      <c r="S1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T1" t="s">
         <v>160</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
+        <v>161</v>
+      </c>
+      <c r="V1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>305</v>
+      </c>
+      <c r="X1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Y1" t="s">
         <v>149</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Z1" t="s">
         <v>150</v>
-      </c>
-      <c r="S1" t="s">
-        <v>161</v>
-      </c>
-      <c r="T1" t="s">
-        <v>162</v>
-      </c>
-      <c r="U1" t="s">
-        <v>163</v>
-      </c>
-      <c r="V1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W1" t="s">
-        <v>307</v>
-      </c>
-      <c r="X1" t="s">
-        <v>308</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>152</v>
       </c>
       <c r="AA1" t="s">
         <v>8</v>
@@ -19750,19 +19953,19 @@
         <v>9</v>
       </c>
       <c r="AC1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AD1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AE1" t="s">
         <v>10</v>
       </c>
       <c r="AF1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AH1" t="s">
         <v>11</v>
@@ -23975,19 +24178,19 @@
         <v>AGO</v>
       </c>
       <c r="B47" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E47" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G47" s="3">
         <v>2</v>
@@ -24035,7 +24238,7 @@
         <v>28</v>
       </c>
       <c r="V47" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>28</v>
@@ -24092,19 +24295,19 @@
         <v>AGO</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E48" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G48" s="3">
         <v>2</v>
@@ -24191,7 +24394,7 @@
         <v>42838</v>
       </c>
       <c r="AI48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AJ48" t="s">
         <v>22</v>
@@ -24209,19 +24412,19 @@
         <v>AGO</v>
       </c>
       <c r="B49" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E49" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G49" s="3">
         <v>2</v>
@@ -24326,19 +24529,19 @@
         <v>AGO</v>
       </c>
       <c r="B50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="E50" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G50" s="3">
         <v>2</v>
@@ -24443,19 +24646,19 @@
         <v>AGO</v>
       </c>
       <c r="B51" t="s">
+        <v>179</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="E51" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G51" s="3">
         <v>2</v>
@@ -24560,19 +24763,19 @@
         <v>AGO</v>
       </c>
       <c r="B52" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G52" s="3">
         <v>2</v>
@@ -24677,19 +24880,19 @@
         <v>AGO</v>
       </c>
       <c r="B53" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E53" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G53" s="3">
         <v>2</v>
@@ -24776,7 +24979,7 @@
         <v>42820</v>
       </c>
       <c r="AI53" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AJ53" t="s">
         <v>22</v>
@@ -24794,19 +24997,19 @@
         <v>AGO</v>
       </c>
       <c r="B54" t="s">
+        <v>187</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="E54" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G54" s="3">
         <v>2</v>
@@ -24911,19 +25114,19 @@
         <v>AGO</v>
       </c>
       <c r="B55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="E55" t="s">
         <v>18</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G55" s="3">
         <v>2</v>
@@ -25028,19 +25231,19 @@
         <v>AGO</v>
       </c>
       <c r="B56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="E56" t="s">
         <v>18</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G56" s="3">
         <v>2</v>
@@ -25145,19 +25348,19 @@
         <v>AGO</v>
       </c>
       <c r="B57" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E57" t="s">
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G57" s="3">
         <v>2</v>
@@ -25262,19 +25465,19 @@
         <v>AGO</v>
       </c>
       <c r="B58" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E58" t="s">
         <v>18</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G58" s="3">
         <v>2</v>
@@ -25379,19 +25582,19 @@
         <v>AGO</v>
       </c>
       <c r="B59" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="E59" t="s">
         <v>18</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G59" s="3">
         <v>2</v>
@@ -25478,7 +25681,7 @@
         <v>42838</v>
       </c>
       <c r="AI59" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ59" t="s">
         <v>22</v>
@@ -25496,19 +25699,19 @@
         <v>AGO</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G60" s="3">
         <v>2</v>
@@ -25613,19 +25816,19 @@
         <v>AGO</v>
       </c>
       <c r="B61" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G61" s="3">
         <v>2</v>
@@ -25730,19 +25933,19 @@
         <v>AGO</v>
       </c>
       <c r="B62" t="s">
+        <v>210</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G62" s="3">
         <v>2</v>
@@ -25847,19 +26050,19 @@
         <v>AGO</v>
       </c>
       <c r="B63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>28</v>
@@ -25964,19 +26167,19 @@
         <v>AGO</v>
       </c>
       <c r="B64" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E64" t="s">
         <v>18</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G64" s="3">
         <v>2</v>
@@ -26081,19 +26284,19 @@
         <v>AGO</v>
       </c>
       <c r="B65" t="s">
+        <v>219</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G65" s="3">
         <v>2</v>
@@ -26141,7 +26344,7 @@
         <v>7</v>
       </c>
       <c r="V65" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W65" s="3" t="s">
         <v>28</v>
@@ -26198,19 +26401,19 @@
         <v>AGO</v>
       </c>
       <c r="B66" t="s">
+        <v>222</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="E66" t="s">
         <v>18</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G66" s="3">
         <v>2</v>
@@ -26258,7 +26461,7 @@
         <v>5</v>
       </c>
       <c r="V66" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W66" s="3">
         <v>10</v>
@@ -26315,19 +26518,19 @@
         <v>AGO</v>
       </c>
       <c r="B67" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E67" t="s">
         <v>18</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G67" s="3">
         <v>2</v>
@@ -26432,19 +26635,19 @@
         <v>AGO</v>
       </c>
       <c r="B68" t="s">
+        <v>228</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="E68" t="s">
         <v>18</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G68" s="3">
         <v>2</v>
@@ -26549,19 +26752,19 @@
         <v>AGO</v>
       </c>
       <c r="B69" t="s">
+        <v>231</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="E69" t="s">
         <v>18</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G69" s="3">
         <v>2</v>
@@ -26666,19 +26869,19 @@
         <v>AGO</v>
       </c>
       <c r="B70" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E70" t="s">
         <v>18</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G70" s="3">
         <v>2</v>
@@ -26726,7 +26929,7 @@
         <v>5</v>
       </c>
       <c r="V70" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W70" s="3">
         <v>10</v>
@@ -26783,19 +26986,19 @@
         <v>AGO</v>
       </c>
       <c r="B71" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E71" t="s">
         <v>18</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G71" s="3">
         <v>2</v>
@@ -26843,7 +27046,7 @@
         <v>7</v>
       </c>
       <c r="V71" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W71" s="3">
         <v>7</v>
@@ -26897,19 +27100,19 @@
         <v>AGO</v>
       </c>
       <c r="B72" t="s">
+        <v>239</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="E72" t="s">
         <v>18</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G72" s="3">
         <v>2</v>
@@ -27014,19 +27217,19 @@
         <v>AGO</v>
       </c>
       <c r="B73" t="s">
+        <v>242</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="E73" t="s">
         <v>18</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G73" s="3">
         <v>2</v>
@@ -27131,19 +27334,19 @@
         <v>AGO</v>
       </c>
       <c r="B74" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G74" s="3">
         <v>2</v>
@@ -27245,19 +27448,19 @@
         <v>AGO</v>
       </c>
       <c r="B75" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G75" s="3">
         <v>2</v>
@@ -27362,19 +27565,19 @@
         <v>AGO</v>
       </c>
       <c r="B76" t="s">
+        <v>250</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G76" s="3">
         <v>2</v>
@@ -27422,7 +27625,7 @@
         <v>7</v>
       </c>
       <c r="V76" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W76" s="3">
         <v>10</v>
@@ -27479,19 +27682,19 @@
         <v>AGO</v>
       </c>
       <c r="B77" t="s">
+        <v>253</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="E77" t="s">
         <v>18</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G77" s="3">
         <v>2</v>
@@ -27539,7 +27742,7 @@
         <v>7</v>
       </c>
       <c r="V77" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W77" s="3">
         <v>7</v>
@@ -27596,19 +27799,19 @@
         <v>AGO</v>
       </c>
       <c r="B78" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E78" t="s">
         <v>18</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G78" s="3">
         <v>2</v>
@@ -27713,19 +27916,19 @@
         <v>AGO</v>
       </c>
       <c r="B79" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E79" t="s">
         <v>18</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G79" s="3">
         <v>2</v>
@@ -27773,7 +27976,7 @@
         <v>7</v>
       </c>
       <c r="V79" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W79" s="3">
         <v>7</v>
@@ -27812,7 +28015,7 @@
         <v>992093</v>
       </c>
       <c r="AI79" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AJ79" t="s">
         <v>22</v>
@@ -27830,19 +28033,19 @@
         <v>AGO</v>
       </c>
       <c r="B80" t="s">
+        <v>263</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="E80" t="s">
         <v>18</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G80" s="3">
         <v>2</v>
@@ -27890,7 +28093,7 @@
         <v>7</v>
       </c>
       <c r="V80" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W80" s="3">
         <v>10</v>
@@ -27947,19 +28150,19 @@
         <v>AGO</v>
       </c>
       <c r="B81" t="s">
+        <v>266</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="E81" t="s">
         <v>18</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G81" s="3">
         <v>2</v>
@@ -28064,19 +28267,19 @@
         <v>AGO</v>
       </c>
       <c r="B82" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E82" t="s">
         <v>18</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G82" s="3">
         <v>2</v>
@@ -28181,19 +28384,19 @@
         <v>AGO</v>
       </c>
       <c r="B83" t="s">
+        <v>272</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="E83" t="s">
         <v>18</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G83" s="3">
         <v>2</v>
@@ -28280,7 +28483,7 @@
         <v>15105</v>
       </c>
       <c r="AI83" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AJ83" t="s">
         <v>22</v>
@@ -28298,19 +28501,19 @@
         <v>AGO</v>
       </c>
       <c r="B84" t="s">
+        <v>276</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="E84" t="s">
         <v>18</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G84" s="3">
         <v>2</v>
@@ -28415,19 +28618,19 @@
         <v>AGO</v>
       </c>
       <c r="B85" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E85" t="s">
         <v>18</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G85" s="3">
         <v>2</v>
@@ -28532,19 +28735,19 @@
         <v>AGO</v>
       </c>
       <c r="B86" t="s">
+        <v>282</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="E86" t="s">
         <v>18</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G86" s="3">
         <v>2</v>
@@ -28649,19 +28852,19 @@
         <v>AGO</v>
       </c>
       <c r="B87" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G87" s="3">
         <v>2</v>
@@ -28766,19 +28969,19 @@
         <v>SET</v>
       </c>
       <c r="B88" t="s">
+        <v>287</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="E88" t="s">
         <v>18</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G88" s="3">
         <v>2</v>
@@ -28826,7 +29029,7 @@
         <v>5</v>
       </c>
       <c r="V88" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W88" s="3">
         <v>10</v>
@@ -28883,19 +29086,19 @@
         <v>SET</v>
       </c>
       <c r="B89" t="s">
+        <v>291</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="E89" t="s">
         <v>18</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G89" s="3">
         <v>2</v>
@@ -29000,19 +29203,19 @@
         <v>SET</v>
       </c>
       <c r="B90" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E90" t="s">
         <v>18</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G90" s="3">
         <v>2</v>
@@ -29060,7 +29263,7 @@
         <v>5</v>
       </c>
       <c r="V90" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W90" s="3" t="s">
         <v>28</v>
@@ -29117,19 +29320,19 @@
         <v>SET</v>
       </c>
       <c r="B91" t="s">
+        <v>296</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="E91" t="s">
         <v>18</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G91" s="3">
         <v>2</v>
@@ -29177,7 +29380,7 @@
         <v>5</v>
       </c>
       <c r="V91" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W91" s="3">
         <v>7</v>
@@ -29234,15 +29437,15 @@
         <v>AGO</v>
       </c>
       <c r="B92" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G92" s="3">
         <v>1</v>
@@ -29329,15 +29532,15 @@
         <v>AGO</v>
       </c>
       <c r="B93" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G93" s="3">
         <v>1</v>
@@ -29424,15 +29627,15 @@
         <v>AGO</v>
       </c>
       <c r="B94" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G94" s="3">
         <v>1</v>
@@ -29519,15 +29722,15 @@
         <v>AGO</v>
       </c>
       <c r="B95" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G95" s="3">
         <v>1</v>
@@ -29611,15 +29814,15 @@
         <v>AGO</v>
       </c>
       <c r="B96" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G96" s="3">
         <v>1</v>
@@ -29703,19 +29906,19 @@
         <v>SET</v>
       </c>
       <c r="B97" t="s">
+        <v>287</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="E97" t="s">
         <v>18</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G97" s="3">
         <v>2</v>
@@ -29763,7 +29966,7 @@
         <v>5</v>
       </c>
       <c r="V97" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W97" s="3">
         <v>10</v>
@@ -29820,19 +30023,19 @@
         <v>SET</v>
       </c>
       <c r="B98" t="s">
+        <v>291</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="E98" t="s">
         <v>18</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G98" s="3">
         <v>2</v>
@@ -29937,19 +30140,19 @@
         <v>SET</v>
       </c>
       <c r="B99" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E99" t="s">
         <v>18</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G99" s="3">
         <v>2</v>
@@ -29997,7 +30200,7 @@
         <v>5</v>
       </c>
       <c r="V99" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W99" s="3" t="s">
         <v>28</v>
@@ -30054,19 +30257,19 @@
         <v>SET</v>
       </c>
       <c r="B100" t="s">
+        <v>296</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="E100" t="s">
         <v>18</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G100" s="3">
         <v>2</v>
@@ -30114,7 +30317,7 @@
         <v>5</v>
       </c>
       <c r="V100" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W100" s="3">
         <v>7</v>
@@ -30171,19 +30374,19 @@
         <v>AGO</v>
       </c>
       <c r="B101" t="s">
+        <v>276</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="E101" t="s">
         <v>18</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G101" s="3">
         <v>2</v>
@@ -30288,19 +30491,19 @@
         <v>SET</v>
       </c>
       <c r="B102" t="s">
+        <v>307</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="E102" t="s">
         <v>18</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G102" s="3">
         <v>2</v>
@@ -30387,7 +30590,7 @@
         <v>992093</v>
       </c>
       <c r="AI102" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AJ102" t="s">
         <v>22</v>
@@ -30405,19 +30608,19 @@
         <v>SET</v>
       </c>
       <c r="B103" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E103" t="s">
         <v>18</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G103" s="3">
         <v>2</v>
@@ -30465,7 +30668,7 @@
         <v>7</v>
       </c>
       <c r="V103" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W103" s="3" t="s">
         <v>28</v>
@@ -30522,19 +30725,19 @@
         <v>SET</v>
       </c>
       <c r="B104" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E104" t="s">
         <v>18</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G104" s="3">
         <v>2</v>
@@ -30639,19 +30842,19 @@
         <v>SET</v>
       </c>
       <c r="B105" t="s">
+        <v>315</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="E105" t="s">
         <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G105" s="3">
         <v>2</v>
@@ -30699,7 +30902,7 @@
         <v>7</v>
       </c>
       <c r="V105" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W105" s="3">
         <v>10</v>
@@ -30738,7 +30941,7 @@
         <v>15105</v>
       </c>
       <c r="AI105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AJ105" t="s">
         <v>22</v>
@@ -30756,19 +30959,19 @@
         <v>SET</v>
       </c>
       <c r="B106" t="s">
+        <v>319</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="E106" t="s">
         <v>18</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G106" s="3">
         <v>2</v>
@@ -30816,7 +31019,7 @@
         <v>5</v>
       </c>
       <c r="V106" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W106" s="3">
         <v>10</v>
@@ -30855,7 +31058,7 @@
         <v>42838</v>
       </c>
       <c r="AI106" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AJ106" t="s">
         <v>22</v>
@@ -30873,19 +31076,19 @@
         <v>SET</v>
       </c>
       <c r="B107" t="s">
+        <v>324</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="E107" t="s">
         <v>18</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G107" s="3">
         <v>2</v>
@@ -30933,7 +31136,7 @@
         <v>5</v>
       </c>
       <c r="V107" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W107" s="3">
         <v>10</v>
@@ -30990,19 +31193,19 @@
         <v>SET</v>
       </c>
       <c r="B108" t="s">
+        <v>327</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="E108" t="s">
         <v>18</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G108" s="3">
         <v>2</v>
@@ -31050,7 +31253,7 @@
         <v>5</v>
       </c>
       <c r="V108" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="W108" s="3">
         <v>7</v>
@@ -31104,19 +31307,19 @@
         <v>SET</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E109" t="s">
         <v>18</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G109" s="3">
         <v>2</v>
@@ -31164,7 +31367,7 @@
         <v>5</v>
       </c>
       <c r="V109" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W109" s="3">
         <v>10</v>
@@ -31221,19 +31424,19 @@
         <v>SET</v>
       </c>
       <c r="B110" t="s">
+        <v>333</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E110" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G110" s="3">
         <v>1</v>
@@ -31314,19 +31517,19 @@
         <v>SET</v>
       </c>
       <c r="B111" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="E111" t="s">
         <v>18</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G111" s="3">
         <v>2</v>
@@ -31374,7 +31577,7 @@
         <v>7</v>
       </c>
       <c r="V111" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W111" s="3">
         <v>7</v>
@@ -31431,19 +31634,19 @@
         <v>SET</v>
       </c>
       <c r="B112" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E112" t="s">
         <v>18</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G112" s="3">
         <v>2</v>
@@ -31491,7 +31694,7 @@
         <v>7</v>
       </c>
       <c r="V112" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W112" s="3">
         <v>7</v>
@@ -31548,19 +31751,19 @@
         <v>SET</v>
       </c>
       <c r="B113" t="s">
+        <v>342</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="E113" t="s">
         <v>18</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G113" s="3">
         <v>2</v>
@@ -31608,7 +31811,7 @@
         <v>5</v>
       </c>
       <c r="V113" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W113" s="3">
         <v>7</v>
@@ -31665,19 +31868,19 @@
         <v>SET</v>
       </c>
       <c r="B114" t="s">
+        <v>345</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="E114" t="s">
         <v>18</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G114" s="3">
         <v>2</v>
@@ -31782,19 +31985,19 @@
         <v>SET</v>
       </c>
       <c r="B115" t="s">
+        <v>348</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="E115" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G115" s="3">
         <v>1</v>
@@ -31875,19 +32078,19 @@
         <v>SET</v>
       </c>
       <c r="B116" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="E116" t="s">
         <v>18</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G116" s="3">
         <v>2</v>
@@ -31935,7 +32138,7 @@
         <v>7</v>
       </c>
       <c r="V116" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W116" s="3">
         <v>7</v>
@@ -31974,7 +32177,7 @@
         <v>13188</v>
       </c>
       <c r="AI116" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AJ116" t="s">
         <v>22</v>
@@ -31992,19 +32195,19 @@
         <v>SET</v>
       </c>
       <c r="B117" t="s">
+        <v>356</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="E117" t="s">
         <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G117" s="3">
         <v>2</v>
@@ -32109,19 +32312,19 @@
         <v>SET</v>
       </c>
       <c r="B118" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E118" t="s">
         <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G118" s="3">
         <v>2</v>
@@ -32169,7 +32372,7 @@
         <v>7</v>
       </c>
       <c r="V118" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W118" s="3">
         <v>10</v>
@@ -32208,7 +32411,7 @@
         <v>42862</v>
       </c>
       <c r="AI118" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AJ118" t="s">
         <v>22</v>
@@ -32226,19 +32429,19 @@
         <v>SET</v>
       </c>
       <c r="B119" t="s">
+        <v>361</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="E119" t="s">
         <v>18</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G119" s="3">
         <v>2</v>
@@ -32286,7 +32489,7 @@
         <v>10</v>
       </c>
       <c r="V119" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W119" s="3" t="s">
         <v>28</v>
@@ -32343,19 +32546,19 @@
         <v>SET</v>
       </c>
       <c r="B120" t="s">
+        <v>364</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="E120" t="s">
         <v>18</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G120" s="3">
         <v>2</v>
@@ -32403,7 +32606,7 @@
         <v>7</v>
       </c>
       <c r="V120" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="W120" s="3" t="s">
         <v>28</v>
@@ -32460,19 +32663,19 @@
         <v>SET</v>
       </c>
       <c r="B121" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E121" t="s">
         <v>18</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G121" s="3">
         <v>2</v>
@@ -32520,7 +32723,7 @@
         <v>7</v>
       </c>
       <c r="V121" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W121" s="3">
         <v>10</v>
@@ -32559,7 +32762,7 @@
         <v>929883</v>
       </c>
       <c r="AI121" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ121" t="s">
         <v>22</v>
@@ -32577,19 +32780,19 @@
         <v>SET</v>
       </c>
       <c r="B122" t="s">
+        <v>370</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="E122" t="s">
         <v>18</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G122" s="3">
         <v>2</v>
@@ -32637,7 +32840,7 @@
         <v>7</v>
       </c>
       <c r="V122" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W122" s="3">
         <v>10</v>
@@ -32694,19 +32897,19 @@
         <v>SET</v>
       </c>
       <c r="B123" t="s">
+        <v>373</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="E123" t="s">
         <v>18</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G123" s="3">
         <v>2</v>
@@ -32754,7 +32957,7 @@
         <v>10</v>
       </c>
       <c r="V123" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W123" s="3">
         <v>7</v>
@@ -32811,19 +33014,19 @@
         <v>SET</v>
       </c>
       <c r="B124" t="s">
+        <v>376</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="E124" t="s">
         <v>18</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G124" s="3">
         <v>2</v>
@@ -32928,19 +33131,19 @@
         <v>SET</v>
       </c>
       <c r="B125" t="s">
+        <v>380</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="E125" t="s">
         <v>18</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G125" s="3">
         <v>2</v>
@@ -32988,7 +33191,7 @@
         <v>7</v>
       </c>
       <c r="V125" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W125" s="3">
         <v>10</v>
@@ -33045,19 +33248,19 @@
         <v>SET</v>
       </c>
       <c r="B126" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E126" t="s">
         <v>18</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G126" s="3">
         <v>2</v>
@@ -33162,19 +33365,19 @@
         <v>SET</v>
       </c>
       <c r="B127" t="s">
+        <v>385</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="E127" t="s">
         <v>18</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G127" s="3">
         <v>2</v>
@@ -33222,7 +33425,7 @@
         <v>7</v>
       </c>
       <c r="V127" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W127" s="3">
         <v>7</v>
@@ -33279,19 +33482,19 @@
         <v>SET</v>
       </c>
       <c r="B128" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="E128" t="s">
         <v>18</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G128" s="3">
         <v>2</v>
@@ -33396,19 +33599,19 @@
         <v>SET</v>
       </c>
       <c r="B129" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E129" t="s">
         <v>18</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G129" s="3">
         <v>2</v>
@@ -33513,19 +33716,19 @@
         <v>SET</v>
       </c>
       <c r="B130" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E130" t="s">
         <v>18</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G130" s="3">
         <v>2</v>
@@ -33630,19 +33833,19 @@
         <v>SET</v>
       </c>
       <c r="B131" t="s">
+        <v>396</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="E131" t="s">
         <v>18</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G131" s="3">
         <v>2</v>
@@ -33690,7 +33893,7 @@
         <v>10</v>
       </c>
       <c r="V131" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W131" s="3" t="s">
         <v>28</v>
@@ -33747,19 +33950,19 @@
         <v>SET</v>
       </c>
       <c r="B132" t="s">
+        <v>399</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="E132" t="s">
         <v>18</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G132" s="3">
         <v>2</v>
@@ -33807,7 +34010,7 @@
         <v>7</v>
       </c>
       <c r="V132" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W132" s="3">
         <v>7</v>
@@ -33864,19 +34067,19 @@
         <v>SET</v>
       </c>
       <c r="B133" t="s">
+        <v>403</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="E133" t="s">
         <v>18</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G133" s="3">
         <v>2</v>
@@ -33963,7 +34166,7 @@
         <v>995684</v>
       </c>
       <c r="AI133" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AJ133" t="s">
         <v>22</v>
@@ -33981,19 +34184,19 @@
         <v>SET</v>
       </c>
       <c r="B134" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E134" t="s">
         <v>18</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G134" s="3">
         <v>2</v>
@@ -34041,7 +34244,7 @@
         <v>7</v>
       </c>
       <c r="V134" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W134" s="3">
         <v>7</v>
@@ -34098,19 +34301,19 @@
         <v>SET</v>
       </c>
       <c r="B135" t="s">
+        <v>408</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="E135" t="s">
         <v>18</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G135" s="3">
         <v>2</v>
@@ -34158,7 +34361,7 @@
         <v>5</v>
       </c>
       <c r="V135" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W135" s="3">
         <v>7</v>
@@ -34215,19 +34418,19 @@
         <v>SET</v>
       </c>
       <c r="B136" t="s">
+        <v>411</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="E136" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G136" s="3">
         <v>1</v>
@@ -34303,19 +34506,19 @@
         <v>SET</v>
       </c>
       <c r="B137" t="s">
+        <v>414</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E137" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G137" s="3">
         <v>1</v>
@@ -34391,19 +34594,19 @@
         <v>SET</v>
       </c>
       <c r="B138" t="s">
+        <v>417</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="E138" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G138" s="3">
         <v>1</v>
@@ -34479,19 +34682,19 @@
         <v>SET</v>
       </c>
       <c r="B139" t="s">
+        <v>420</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="E139" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G139" s="3">
         <v>1</v>
@@ -34567,19 +34770,19 @@
         <v>SET</v>
       </c>
       <c r="B140" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="E140" t="s">
         <v>18</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G140" s="3">
         <v>2</v>
@@ -34684,19 +34887,19 @@
         <v>SET</v>
       </c>
       <c r="B141" t="s">
+        <v>428</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="E141" t="s">
         <v>18</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G141" s="3">
         <v>2</v>
@@ -34801,19 +35004,19 @@
         <v>SET</v>
       </c>
       <c r="B142" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E142" t="s">
         <v>18</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G142" s="3">
         <v>2</v>
@@ -34918,19 +35121,19 @@
         <v>SET</v>
       </c>
       <c r="B143" t="s">
+        <v>433</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="E143" t="s">
         <v>18</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G143" s="3">
         <v>2</v>
@@ -34978,7 +35181,7 @@
         <v>28</v>
       </c>
       <c r="V143" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W143" s="3">
         <v>7</v>
@@ -35035,19 +35238,19 @@
         <v>SET</v>
       </c>
       <c r="B144" t="s">
+        <v>399</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="E144" t="s">
         <v>18</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G144" s="3">
         <v>2</v>
@@ -35095,7 +35298,7 @@
         <v>7</v>
       </c>
       <c r="V144" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W144" s="3">
         <v>7</v>
@@ -35152,19 +35355,19 @@
         <v>SET</v>
       </c>
       <c r="B145" t="s">
+        <v>403</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="E145" t="s">
         <v>18</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G145" s="3">
         <v>2</v>
@@ -35251,7 +35454,7 @@
         <v>995684</v>
       </c>
       <c r="AI145" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AJ145" t="s">
         <v>22</v>
@@ -35269,19 +35472,19 @@
         <v>SET</v>
       </c>
       <c r="B146" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E146" t="s">
         <v>18</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G146" s="3">
         <v>2</v>
@@ -35329,7 +35532,7 @@
         <v>7</v>
       </c>
       <c r="V146" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W146" s="3">
         <v>7</v>
@@ -35386,19 +35589,19 @@
         <v>SET</v>
       </c>
       <c r="B147" t="s">
+        <v>408</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="E147" t="s">
         <v>18</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G147" s="3">
         <v>2</v>
@@ -35446,7 +35649,7 @@
         <v>5</v>
       </c>
       <c r="V147" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W147" s="3">
         <v>7</v>
@@ -35503,19 +35706,19 @@
         <v>SET</v>
       </c>
       <c r="B148" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="E148" t="s">
         <v>18</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G148" s="3">
         <v>2</v>
@@ -35563,7 +35766,7 @@
         <v>5</v>
       </c>
       <c r="V148" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W148" s="3" t="s">
         <v>28</v>
@@ -35620,19 +35823,19 @@
         <v>SET</v>
       </c>
       <c r="B149" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E149" t="s">
         <v>18</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G149" s="3">
         <v>2</v>
@@ -35680,7 +35883,7 @@
         <v>7</v>
       </c>
       <c r="V149" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W149" s="3">
         <v>10</v>
@@ -35737,19 +35940,19 @@
         <v>SET</v>
       </c>
       <c r="B150" t="s">
+        <v>442</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="E150" t="s">
         <v>18</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G150" s="3">
         <v>2</v>
@@ -35797,7 +36000,7 @@
         <v>7</v>
       </c>
       <c r="V150" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W150" s="3" t="s">
         <v>28</v>
@@ -35836,7 +36039,7 @@
         <v>13188</v>
       </c>
       <c r="AI150" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AJ150" t="s">
         <v>22</v>
@@ -35854,19 +36057,19 @@
         <v>SET</v>
       </c>
       <c r="B151" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E151" t="s">
         <v>18</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G151" s="3">
         <v>2</v>
@@ -35914,7 +36117,7 @@
         <v>28</v>
       </c>
       <c r="V151" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W151" s="3">
         <v>10</v>
@@ -35953,7 +36156,7 @@
         <v>15105</v>
       </c>
       <c r="AI151" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AJ151" t="s">
         <v>22</v>
@@ -35971,19 +36174,19 @@
         <v>SET</v>
       </c>
       <c r="B152" t="s">
+        <v>448</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="E152" t="s">
         <v>18</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G152" s="3">
         <v>2</v>
@@ -36031,7 +36234,7 @@
         <v>5</v>
       </c>
       <c r="V152" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W152" s="3">
         <v>10</v>
@@ -36088,19 +36291,19 @@
         <v>SET</v>
       </c>
       <c r="B153" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E153" t="s">
         <v>18</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G153" s="3">
         <v>2</v>
@@ -36148,7 +36351,7 @@
         <v>5</v>
       </c>
       <c r="V153" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W153" s="3" t="s">
         <v>28</v>
@@ -36205,19 +36408,19 @@
         <v>SET</v>
       </c>
       <c r="B154" t="s">
+        <v>454</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="E154" t="s">
         <v>18</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G154" s="3">
         <v>2</v>
@@ -36265,7 +36468,7 @@
         <v>5</v>
       </c>
       <c r="V154" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W154" s="3">
         <v>10</v>
@@ -36322,19 +36525,19 @@
         <v>SET</v>
       </c>
       <c r="B155" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E155" t="s">
         <v>18</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G155" s="3">
         <v>2</v>
@@ -36382,7 +36585,7 @@
         <v>7</v>
       </c>
       <c r="V155" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W155" s="3">
         <v>7</v>
@@ -36439,19 +36642,19 @@
         <v>SET</v>
       </c>
       <c r="B156" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="E156" t="s">
         <v>18</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G156" s="3">
         <v>2</v>
@@ -36556,19 +36759,19 @@
         <v>SET</v>
       </c>
       <c r="B157" t="s">
+        <v>463</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="E157" t="s">
         <v>18</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G157" s="3">
         <v>2</v>
@@ -36673,19 +36876,19 @@
         <v>SET</v>
       </c>
       <c r="B158" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E158" t="s">
         <v>18</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G158" s="3">
         <v>2</v>
@@ -36790,19 +36993,19 @@
         <v>SET</v>
       </c>
       <c r="B159" t="s">
+        <v>468</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>472</v>
       </c>
       <c r="E159" t="s">
         <v>18</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G159" s="3">
         <v>2</v>
@@ -36850,7 +37053,7 @@
         <v>7</v>
       </c>
       <c r="V159" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W159" s="3">
         <v>7</v>
@@ -36907,19 +37110,19 @@
         <v>SET</v>
       </c>
       <c r="B160" s="33" t="s">
+        <v>471</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="E160" t="s">
         <v>18</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G160" s="3">
         <v>2</v>
@@ -37003,7 +37206,7 @@
         <v>10</v>
       </c>
       <c r="AH160" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AI160" t="s">
         <v>63</v>
@@ -37024,19 +37227,19 @@
         <v>SET</v>
       </c>
       <c r="B161" t="s">
+        <v>476</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="E161" t="s">
         <v>18</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G161" s="3">
         <v>2</v>
@@ -37084,7 +37287,7 @@
         <v>5</v>
       </c>
       <c r="V161" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W161" s="3">
         <v>10</v>
@@ -37141,19 +37344,19 @@
         <v>SET</v>
       </c>
       <c r="B162" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E162" t="s">
         <v>18</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G162" s="3">
         <v>2</v>
@@ -37201,7 +37404,7 @@
         <v>28</v>
       </c>
       <c r="V162" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W162" s="3" t="s">
         <v>28</v>
@@ -37258,19 +37461,19 @@
         <v>SET</v>
       </c>
       <c r="B163" t="s">
+        <v>481</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="E163" t="s">
         <v>18</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G163" s="3">
         <v>2</v>
@@ -37318,7 +37521,7 @@
         <v>7</v>
       </c>
       <c r="V163" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W163" s="3" t="s">
         <v>28</v>
@@ -37367,6 +37570,474 @@
       </c>
       <c r="AL163">
         <v>2478</v>
+      </c>
+    </row>
+    <row r="164" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B164" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E164" t="s">
+        <v>18</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G164" s="3">
+        <v>2</v>
+      </c>
+      <c r="H164" s="3">
+        <v>7</v>
+      </c>
+      <c r="I164" s="3">
+        <v>7</v>
+      </c>
+      <c r="J164" s="3">
+        <v>7</v>
+      </c>
+      <c r="K164" s="3">
+        <v>7</v>
+      </c>
+      <c r="L164">
+        <v>38</v>
+      </c>
+      <c r="M164">
+        <v>17</v>
+      </c>
+      <c r="N164">
+        <v>62</v>
+      </c>
+      <c r="O164">
+        <v>83</v>
+      </c>
+      <c r="P164" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q164" s="3">
+        <v>7</v>
+      </c>
+      <c r="R164" s="3">
+        <v>7</v>
+      </c>
+      <c r="S164" s="3">
+        <v>7</v>
+      </c>
+      <c r="T164" s="3">
+        <v>7</v>
+      </c>
+      <c r="U164" s="3">
+        <v>5</v>
+      </c>
+      <c r="V164" t="s">
+        <v>169</v>
+      </c>
+      <c r="W164" s="3">
+        <v>7</v>
+      </c>
+      <c r="X164" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y164">
+        <v>54</v>
+      </c>
+      <c r="Z164">
+        <v>27</v>
+      </c>
+      <c r="AA164">
+        <v>44</v>
+      </c>
+      <c r="AB164">
+        <v>3</v>
+      </c>
+      <c r="AC164">
+        <v>22</v>
+      </c>
+      <c r="AD164">
+        <v>85</v>
+      </c>
+      <c r="AE164">
+        <v>3</v>
+      </c>
+      <c r="AF164">
+        <v>15</v>
+      </c>
+      <c r="AG164" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH164" s="3">
+        <v>42762</v>
+      </c>
+      <c r="AI164" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ164" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK164" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL164">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="165" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B165" t="s">
+        <v>490</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E165" t="s">
+        <v>18</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G165" s="3">
+        <v>2</v>
+      </c>
+      <c r="H165" s="3">
+        <v>7</v>
+      </c>
+      <c r="I165" s="3">
+        <v>7</v>
+      </c>
+      <c r="J165" s="3">
+        <v>7</v>
+      </c>
+      <c r="K165" s="3">
+        <v>5</v>
+      </c>
+      <c r="L165">
+        <v>25</v>
+      </c>
+      <c r="M165">
+        <v>28</v>
+      </c>
+      <c r="N165">
+        <v>75</v>
+      </c>
+      <c r="O165">
+        <v>72</v>
+      </c>
+      <c r="P165" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q165" s="3">
+        <v>7</v>
+      </c>
+      <c r="R165" s="3">
+        <v>7</v>
+      </c>
+      <c r="S165" s="3">
+        <v>7</v>
+      </c>
+      <c r="T165" s="3">
+        <v>7</v>
+      </c>
+      <c r="U165" s="3">
+        <v>5</v>
+      </c>
+      <c r="V165" t="s">
+        <v>169</v>
+      </c>
+      <c r="W165" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X165" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y165">
+        <v>69</v>
+      </c>
+      <c r="Z165">
+        <v>34.5</v>
+      </c>
+      <c r="AA165">
+        <v>42</v>
+      </c>
+      <c r="AB165">
+        <v>7</v>
+      </c>
+      <c r="AC165">
+        <v>21</v>
+      </c>
+      <c r="AD165">
+        <v>65</v>
+      </c>
+      <c r="AE165">
+        <v>6</v>
+      </c>
+      <c r="AF165">
+        <v>30</v>
+      </c>
+      <c r="AG165" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH165" s="3">
+        <v>42846</v>
+      </c>
+      <c r="AI165" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ165" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK165" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL165">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="166" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B166" t="s">
+        <v>493</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E166" t="s">
+        <v>18</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G166" s="3">
+        <v>2</v>
+      </c>
+      <c r="H166" s="3">
+        <v>7</v>
+      </c>
+      <c r="I166" s="3">
+        <v>7</v>
+      </c>
+      <c r="J166" s="3">
+        <v>7</v>
+      </c>
+      <c r="K166" s="3">
+        <v>5</v>
+      </c>
+      <c r="L166">
+        <v>17</v>
+      </c>
+      <c r="M166">
+        <v>39</v>
+      </c>
+      <c r="N166">
+        <v>83</v>
+      </c>
+      <c r="O166">
+        <v>61</v>
+      </c>
+      <c r="P166" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q166" s="3">
+        <v>7</v>
+      </c>
+      <c r="R166" s="3">
+        <v>7</v>
+      </c>
+      <c r="S166" s="3">
+        <v>7</v>
+      </c>
+      <c r="T166" s="3">
+        <v>7</v>
+      </c>
+      <c r="U166" s="3">
+        <v>7</v>
+      </c>
+      <c r="V166" t="s">
+        <v>169</v>
+      </c>
+      <c r="W166" s="3">
+        <v>7</v>
+      </c>
+      <c r="X166" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y166">
+        <v>53</v>
+      </c>
+      <c r="Z166">
+        <v>26.5</v>
+      </c>
+      <c r="AA166">
+        <v>33</v>
+      </c>
+      <c r="AB166">
+        <v>5</v>
+      </c>
+      <c r="AC166">
+        <v>16.5</v>
+      </c>
+      <c r="AD166">
+        <v>75</v>
+      </c>
+      <c r="AE166">
+        <v>6</v>
+      </c>
+      <c r="AF166">
+        <v>30</v>
+      </c>
+      <c r="AG166" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH166" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI166" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ166" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK166" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL166">
+        <v>4578</v>
+      </c>
+    </row>
+    <row r="167" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B167" t="s">
+        <v>495</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E167" t="s">
+        <v>18</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G167" s="3">
+        <v>2</v>
+      </c>
+      <c r="H167" s="3">
+        <v>7</v>
+      </c>
+      <c r="I167" s="3">
+        <v>7</v>
+      </c>
+      <c r="J167" s="3">
+        <v>7</v>
+      </c>
+      <c r="K167" s="3">
+        <v>5</v>
+      </c>
+      <c r="L167">
+        <v>27</v>
+      </c>
+      <c r="M167">
+        <v>16</v>
+      </c>
+      <c r="N167">
+        <v>73</v>
+      </c>
+      <c r="O167">
+        <v>84</v>
+      </c>
+      <c r="P167" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q167" s="3">
+        <v>7</v>
+      </c>
+      <c r="R167" s="3">
+        <v>7</v>
+      </c>
+      <c r="S167" s="3">
+        <v>7</v>
+      </c>
+      <c r="T167" s="3">
+        <v>7</v>
+      </c>
+      <c r="U167" s="3">
+        <v>7</v>
+      </c>
+      <c r="V167" t="s">
+        <v>169</v>
+      </c>
+      <c r="W167" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X167" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y167" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z167" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA167">
+        <v>34</v>
+      </c>
+      <c r="AB167">
+        <v>3</v>
+      </c>
+      <c r="AC167">
+        <v>17</v>
+      </c>
+      <c r="AD167">
+        <v>85</v>
+      </c>
+      <c r="AE167">
+        <v>3</v>
+      </c>
+      <c r="AF167">
+        <v>15</v>
+      </c>
+      <c r="AG167" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH167" s="3">
+        <v>13188</v>
+      </c>
+      <c r="AI167" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ167" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK167" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL167">
+        <v>5257</v>
       </c>
     </row>
   </sheetData>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="513">
   <si>
     <t>ID</t>
   </si>
@@ -1576,6 +1576,51 @@
   </si>
   <si>
     <t>24/09/2026 01:57:16</t>
+  </si>
+  <si>
+    <t>6ab4196acffb29c3dcbb8633</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:11:21</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:24:42</t>
+  </si>
+  <si>
+    <t>6ab3c9e16b8938edc4b89fcb</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:10:31</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:45:21</t>
+  </si>
+  <si>
+    <t>6ab1771e596883bd549a0120</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:26:24</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:27:42</t>
+  </si>
+  <si>
+    <t>6aac3f3b03d0d5807441df66</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:23:55</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:27:55</t>
+  </si>
+  <si>
+    <t>6aac246461edf70c814e5585</t>
+  </si>
+  <si>
+    <t>16/09/2026 08:15:01</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:33:24</t>
   </si>
 </sst>
 </file>
@@ -1981,7 +2026,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1990,17 +2044,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2355,7 +2400,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46289.430432986112" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="166">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46289.447432407411" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="171">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2500,13 +2545,13 @@
       <sharedItems containsMixedTypes="1" containsNumber="1" minValue="2" maxValue="145"/>
     </cacheField>
     <cacheField name="% Peito Limpo na esteira" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="25" maxValue="90"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="15" maxValue="90"/>
     </cacheField>
     <cacheField name="6.1 Erro de Corte" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="30"/>
     </cacheField>
     <cacheField name="% Erro de Corte da Porcionadora" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="5" maxValue="55.000000000000007"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="55.000000000000007"/>
     </cacheField>
     <cacheField name="Qualidade Acomodação" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="10"/>
@@ -2536,7 +2581,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="166">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="171">
   <r>
     <x v="0"/>
     <m/>
@@ -9176,6 +9221,206 @@
     <s v="assinatura"/>
     <s v="assinatura"/>
     <n v="5257"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab4196acffb29c3dcbb8633"/>
+    <s v="23/09/2026 14:11:21"/>
+    <s v="23/09/2026 15:24:42"/>
+    <s v="Alana"/>
+    <x v="40"/>
+    <n v="1"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="20"/>
+    <n v="33"/>
+    <n v="80"/>
+    <n v="67"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="10"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="35"/>
+    <n v="17.5"/>
+    <n v="28"/>
+    <n v="14"/>
+    <n v="14.000000000000002"/>
+    <n v="30"/>
+    <n v="3"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab3c9e16b8938edc4b89fcb"/>
+    <s v="22/09/2026 14:10:31"/>
+    <s v="23/09/2026 09:45:21"/>
+    <s v="Alana"/>
+    <x v="39"/>
+    <n v="1"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="26"/>
+    <n v="38"/>
+    <n v="74"/>
+    <n v="62"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="7"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="68"/>
+    <n v="34"/>
+    <n v="17"/>
+    <n v="17"/>
+    <n v="8.5"/>
+    <n v="15"/>
+    <n v="1"/>
+    <n v="5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab1771e596883bd549a0120"/>
+    <s v="21/09/2026 12:26:24"/>
+    <s v="21/09/2026 15:27:42"/>
+    <s v="Alana"/>
+    <x v="38"/>
+    <n v="1"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="19"/>
+    <n v="37"/>
+    <n v="81"/>
+    <n v="63"/>
+    <n v="5"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="52"/>
+    <n v="26"/>
+    <n v="101"/>
+    <n v="13"/>
+    <n v="50.5"/>
+    <n v="35"/>
+    <n v="3"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6aac3f3b03d0d5807441df66"/>
+    <s v="17/09/2026 12:23:55"/>
+    <s v="17/09/2026 16:27:55"/>
+    <s v="Alana"/>
+    <x v="37"/>
+    <n v="1"/>
+    <s v=""/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="12"/>
+    <n v="39"/>
+    <n v="88"/>
+    <n v="61"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="80"/>
+    <n v="40"/>
+    <n v="12"/>
+    <n v="5"/>
+    <n v="6"/>
+    <n v="75"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6aac246461edf70c814e5585"/>
+    <s v="16/09/2026 08:15:01"/>
+    <s v="17/09/2026 14:33:24"/>
+    <s v="Alana"/>
+    <x v="35"/>
+    <n v="1"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="15"/>
+    <n v="25"/>
+    <n v="85"/>
+    <n v="75"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="121"/>
+    <n v="60.5"/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -9416,8 +9661,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL167" totalsRowShown="0">
-  <autoFilter ref="A1:AL167"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL172" totalsRowShown="0">
+  <autoFilter ref="A1:AL172"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -9972,7 +10217,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="39" t="str">
+      <c r="E4" s="35" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -10013,7 +10258,7 @@
       </c>
       <c r="O4" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Mês],O$3),"")</f>
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="P4" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Mês],P$3),"")</f>
@@ -10066,9 +10311,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AC$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AD4" s="26" t="str">
+      <c r="AD4" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AD$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AE4" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AE$3),"")</f>
@@ -10078,17 +10323,17 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG4" s="26" t="str">
+      <c r="AG4" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH4" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AH4" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI4" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AI4" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AJ4" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D4&amp;"]"),Tabela1[Turno],$F4,Tabela1[Data],AJ$3),"")</f>
@@ -10142,7 +10387,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="40"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -10194,7 +10439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="36"/>
+      <c r="S5" s="39"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10307,7 +10552,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="37"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -10345,7 +10590,7 @@
       </c>
       <c r="O6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.8767123287671232</v>
+        <v>6.9350649350649354</v>
       </c>
       <c r="P6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10359,7 +10604,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="37"/>
+      <c r="S6" s="40"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10398,7 +10643,7 @@
       </c>
       <c r="AD6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AE6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AE$3),"")</f>
@@ -10410,7 +10655,7 @@
       </c>
       <c r="AG6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AH6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AH$3),"")</f>
@@ -10418,7 +10663,7 @@
       </c>
       <c r="AI6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AJ6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -10472,7 +10717,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="39" t="str">
+      <c r="E7" s="35" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -10513,7 +10758,7 @@
       </c>
       <c r="O7" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Mês],O$3),"")</f>
-        <v>9</v>
+        <v>8.1818181818181817</v>
       </c>
       <c r="P7" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Mês],P$3),"")</f>
@@ -10566,29 +10811,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AC$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AD7" s="26" t="str">
+      <c r="AD7" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE7" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AE7" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AF7" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG7" s="26" t="str">
+      <c r="AG7" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH7" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH7" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI7" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AI7" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ7" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D7&amp;"]"),Tabela1[Turno],$F7,Tabela1[Data],AJ$3),"")</f>
@@ -10642,7 +10887,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -10694,7 +10939,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="36"/>
+      <c r="S8" s="39"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10807,7 +11052,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="41"/>
+      <c r="E9" s="37"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -10845,7 +11090,7 @@
       </c>
       <c r="O9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2837837837837842</v>
+        <v>7.2784810126582276</v>
       </c>
       <c r="P9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10859,7 +11104,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="37"/>
+      <c r="S9" s="40"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10898,11 +11143,11 @@
       </c>
       <c r="AD9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AE9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AE$3),"")</f>
-        <v>7.75</v>
+        <v>7.2</v>
       </c>
       <c r="AF9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AF$3),"")</f>
@@ -10972,7 +11217,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="39" t="str">
+      <c r="E10" s="35" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -11013,7 +11258,7 @@
       </c>
       <c r="O10" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Mês],O$3),"")</f>
-        <v>8</v>
+        <v>8.3636363636363633</v>
       </c>
       <c r="P10" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Mês],P$3),"")</f>
@@ -11066,29 +11311,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AC$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AD10" s="26" t="str">
+      <c r="AD10" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE10" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AE10" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AF10" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG10" s="26" t="str">
+      <c r="AG10" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH10" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AH10" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI10" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AI10" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AJ10" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D10&amp;"]"),Tabela1[Turno],$F10,Tabela1[Data],AJ$3),"")</f>
@@ -11142,7 +11387,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="40"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -11194,7 +11439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="36"/>
+      <c r="S11" s="39"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11307,7 +11552,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="41"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -11345,7 +11590,7 @@
       </c>
       <c r="O12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0810810810810807</v>
+        <v>7.1898734177215191</v>
       </c>
       <c r="P12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11359,7 +11604,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="37"/>
+      <c r="S12" s="40"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11410,15 +11655,15 @@
       </c>
       <c r="AG12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AH12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AI12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AJ12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -11472,7 +11717,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="39" t="str">
+      <c r="E13" s="35" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -11513,7 +11758,7 @@
       </c>
       <c r="O13" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Mês],O$3),"")</f>
-        <v>6.333333333333333</v>
+        <v>6.5454545454545459</v>
       </c>
       <c r="P13" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Mês],P$3),"")</f>
@@ -11566,29 +11811,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AC$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AD13" s="26" t="str">
+      <c r="AD13" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE13" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AF13" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG13" s="26" t="str">
+      <c r="AG13" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH13" s="26" t="str">
+        <v>5</v>
+      </c>
+      <c r="AH13" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI13" s="26" t="str">
+        <v>5</v>
+      </c>
+      <c r="AI13" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ13" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D13&amp;"]"),Tabela1[Turno],$F13,Tabela1[Data],AJ$3),"")</f>
@@ -11642,7 +11887,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="40"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -11694,7 +11939,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="36"/>
+      <c r="S14" s="39"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -11807,7 +12052,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="41"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -11845,7 +12090,7 @@
       </c>
       <c r="O15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>5.4594594594594597</v>
+        <v>5.5443037974683547</v>
       </c>
       <c r="P15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11859,7 +12104,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="37"/>
+      <c r="S15" s="40"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -11898,11 +12143,11 @@
       </c>
       <c r="AD15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AE$3),"")</f>
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AF$3),"")</f>
@@ -11910,7 +12155,7 @@
       </c>
       <c r="AG15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AH15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AH$3),"")</f>
@@ -11918,7 +12163,7 @@
       </c>
       <c r="AI15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AJ15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -11972,7 +12217,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="39" t="str">
+      <c r="E16" s="35" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -12013,7 +12258,7 @@
       </c>
       <c r="O16" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.78333333333333333</v>
+        <v>0.7981818181818181</v>
       </c>
       <c r="P16" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],P$3)/100,"")</f>
@@ -12027,7 +12272,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="41">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -12066,29 +12311,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AC$3)/100,"")</f>
         <v>0.78</v>
       </c>
-      <c r="AD16" s="28" t="str">
+      <c r="AD16" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AD$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AE16" s="28" t="str">
+        <v>0.85</v>
+      </c>
+      <c r="AE16" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AE$3)/100,"")</f>
-        <v/>
+        <v>0.88</v>
       </c>
       <c r="AF16" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AF$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AG16" s="28" t="str">
+      <c r="AG16" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH16" s="28" t="str">
+        <v>0.81</v>
+      </c>
+      <c r="AH16" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AI16" s="28" t="str">
+        <v>0.74</v>
+      </c>
+      <c r="AI16" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="AJ16" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Data],AJ$3)/100,"")</f>
@@ -12142,7 +12387,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="40"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -12194,7 +12439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="36"/>
+      <c r="S17" s="39"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -12307,7 +12552,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="41"/>
+      <c r="E18" s="37"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -12345,7 +12590,7 @@
       </c>
       <c r="O18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.81121621621621631</v>
+        <v>0.81151898734177208</v>
       </c>
       <c r="P18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -12359,7 +12604,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="37"/>
+      <c r="S18" s="40"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -12398,11 +12643,11 @@
       </c>
       <c r="AD18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AD$3)/100,"")</f>
-        <v>0.83499999999999996</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="AE18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AE$3)/100,"")</f>
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AF18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
@@ -12410,15 +12655,15 @@
       </c>
       <c r="AG18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v>0.67249999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AH18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v>0.80500000000000005</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="AI18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v>0.73250000000000004</v>
+        <v>0.746</v>
       </c>
       <c r="AJ18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -12472,7 +12717,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="39" t="str">
+      <c r="E19" s="35" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -12513,7 +12758,7 @@
       </c>
       <c r="O19" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.65500000000000003</v>
+        <v>0.65545454545454551</v>
       </c>
       <c r="P19" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],P$3)/100,"")</f>
@@ -12527,7 +12772,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="41">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -12566,29 +12811,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AC$3)/100,"")</f>
         <v>0.63</v>
       </c>
-      <c r="AD19" s="28" t="str">
+      <c r="AD19" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AD$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AE19" s="28" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="AE19" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AE$3)/100,"")</f>
-        <v/>
+        <v>0.61</v>
       </c>
       <c r="AF19" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AF$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AG19" s="28" t="str">
+      <c r="AG19" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH19" s="28" t="str">
+        <v>0.63</v>
+      </c>
+      <c r="AH19" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AI19" s="28" t="str">
+        <v>0.62</v>
+      </c>
+      <c r="AI19" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.67</v>
       </c>
       <c r="AJ19" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Data],AJ$3)/100,"")</f>
@@ -12642,7 +12887,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="40"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -12694,7 +12939,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="36"/>
+      <c r="S20" s="39"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -12807,7 +13052,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="41"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -12845,7 +13090,7 @@
       </c>
       <c r="O21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.64054054054054044</v>
+        <v>0.64151898734177204</v>
       </c>
       <c r="P21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -12859,7 +13104,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="37"/>
+      <c r="S21" s="40"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -12898,11 +13143,11 @@
       </c>
       <c r="AD21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AD$3)/100,"")</f>
-        <v>0.69</v>
+        <v>0.70200000000000007</v>
       </c>
       <c r="AE21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AE$3)/100,"")</f>
-        <v>0.7</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="AF21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
@@ -12910,15 +13155,15 @@
       </c>
       <c r="AG21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="AH21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v>0.60499999999999998</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="AI21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v>0.75</v>
+        <v>0.7340000000000001</v>
       </c>
       <c r="AJ21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -12972,7 +13217,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="39" t="str">
+      <c r="E22" s="35" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -13013,7 +13258,7 @@
       </c>
       <c r="O22" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Mês],O$3),"")</f>
-        <v>7.833333333333333</v>
+        <v>7.2727272727272725</v>
       </c>
       <c r="P22" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Mês],P$3),"")</f>
@@ -13066,29 +13311,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AC$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AD22" s="26" t="str">
+      <c r="AD22" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE22" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AE22" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AF22" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG22" s="26" t="str">
+      <c r="AG22" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH22" s="26" t="str">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI22" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AI22" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ22" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D22&amp;"]"),Tabela1[Turno],$F22,Tabela1[Data],AJ$3),"")</f>
@@ -13142,7 +13387,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="40"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -13194,7 +13439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="36"/>
+      <c r="S23" s="39"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -13307,7 +13552,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="41"/>
+      <c r="E24" s="37"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -13345,7 +13590,7 @@
       </c>
       <c r="O24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.7972972972972974</v>
+        <v>6.7848101265822782</v>
       </c>
       <c r="P24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13359,7 +13604,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="37"/>
+      <c r="S24" s="40"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -13398,7 +13643,7 @@
       </c>
       <c r="AD24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AE24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AE$3),"")</f>
@@ -13410,11 +13655,11 @@
       </c>
       <c r="AG24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AH24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -13472,7 +13717,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="39" t="str">
+      <c r="E25" s="35" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -13513,7 +13758,7 @@
       </c>
       <c r="O25" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Mês],O$3),"")</f>
-        <v>9</v>
+        <v>9.454545454545455</v>
       </c>
       <c r="P25" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Mês],P$3),"")</f>
@@ -13566,29 +13811,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AC$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AD25" s="26" t="str">
+      <c r="AD25" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE25" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AE25" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AF25" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG25" s="26" t="str">
+      <c r="AG25" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH25" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AH25" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI25" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AI25" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AJ25" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D25&amp;"]"),Tabela1[Turno],$F25,Tabela1[Data],AJ$3),"")</f>
@@ -13642,7 +13887,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="40"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -13694,7 +13939,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="36"/>
+      <c r="S26" s="39"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -13807,7 +14052,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="41"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -13845,7 +14090,7 @@
       </c>
       <c r="O27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0684931506849313</v>
+        <v>7.2564102564102564</v>
       </c>
       <c r="P27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13859,7 +14104,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="37"/>
+      <c r="S27" s="40"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -13898,11 +14143,11 @@
       </c>
       <c r="AD27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AE27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AE$3),"")</f>
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AF27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AF$3),"")</f>
@@ -13910,15 +14155,15 @@
       </c>
       <c r="AG27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AH27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AI27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AJ27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -13972,7 +14217,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="39" t="str">
+      <c r="E28" s="35" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -14066,29 +14311,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AC$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AD28" s="26" t="str">
+      <c r="AD28" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE28" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AE28" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AF28" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG28" s="26" t="str">
+      <c r="AG28" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH28" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AH28" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI28" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AI28" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AJ28" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D28&amp;"]"),Tabela1[Turno],$F28,Tabela1[Data],AJ$3),"")</f>
@@ -14142,7 +14387,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="40"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -14194,7 +14439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="36"/>
+      <c r="S29" s="39"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14307,7 +14552,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="37"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -14345,7 +14590,7 @@
       </c>
       <c r="O30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.243243243243243</v>
+        <v>7.4177215189873413</v>
       </c>
       <c r="P30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14359,7 +14604,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="37"/>
+      <c r="S30" s="40"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14398,11 +14643,11 @@
       </c>
       <c r="AD30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AE30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AE$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AF30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AF$3),"")</f>
@@ -14410,15 +14655,15 @@
       </c>
       <c r="AG30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AH30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AI30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AJ30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -14472,7 +14717,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="39" t="str">
+      <c r="E31" s="35" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -14513,7 +14758,7 @@
       </c>
       <c r="O31" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Mês],O$3),"")</f>
-        <v>8.5</v>
+        <v>8.0909090909090917</v>
       </c>
       <c r="P31" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Mês],P$3),"")</f>
@@ -14566,29 +14811,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AC$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AD31" s="26" t="str">
+      <c r="AD31" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE31" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AE31" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AF31" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG31" s="26" t="str">
+      <c r="AG31" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH31" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH31" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI31" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AI31" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ31" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D31&amp;"]"),Tabela1[Turno],$F31,Tabela1[Data],AJ$3),"")</f>
@@ -14642,7 +14887,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="40"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -14694,7 +14939,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="36"/>
+      <c r="S32" s="39"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -14807,7 +15052,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="41"/>
+      <c r="E33" s="37"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -14845,7 +15090,7 @@
       </c>
       <c r="O33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0405405405405403</v>
+        <v>7.075949367088608</v>
       </c>
       <c r="P33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14859,7 +15104,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="37"/>
+      <c r="S33" s="40"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -14914,7 +15159,7 @@
       </c>
       <c r="AH33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AI33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AI$3),"")</f>
@@ -14972,7 +15217,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="39" t="str">
+      <c r="E34" s="35" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -15013,7 +15258,7 @@
       </c>
       <c r="O34" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Mês],O$3),"")</f>
-        <v>8.5</v>
+        <v>8.0909090909090917</v>
       </c>
       <c r="P34" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Mês],P$3),"")</f>
@@ -15066,29 +15311,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AC$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AD34" s="26" t="str">
+      <c r="AD34" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE34" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AE34" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AF34" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG34" s="26" t="str">
+      <c r="AG34" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH34" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AH34" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI34" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AI34" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ34" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D34&amp;"]"),Tabela1[Turno],$F34,Tabela1[Data],AJ$3),"")</f>
@@ -15142,7 +15387,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="40"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -15194,7 +15439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="36"/>
+      <c r="S35" s="39"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15307,7 +15552,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="41"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -15345,7 +15590,7 @@
       </c>
       <c r="O36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1621621621621623</v>
+        <v>7.1898734177215191</v>
       </c>
       <c r="P36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15359,7 +15604,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="37"/>
+      <c r="S36" s="40"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15398,7 +15643,7 @@
       </c>
       <c r="AD36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>7.75</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AE36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AE$3),"")</f>
@@ -15472,7 +15717,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="39" t="str">
+      <c r="E37" s="35" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -15513,7 +15758,7 @@
       </c>
       <c r="O37" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Mês],O$3),"")</f>
-        <v>6.666666666666667</v>
+        <v>7</v>
       </c>
       <c r="P37" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Mês],P$3),"")</f>
@@ -15566,29 +15811,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AC$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AD37" s="26" t="str">
+      <c r="AD37" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AD$3),"")</f>
-        <v/>
-      </c>
-      <c r="AE37" s="26" t="str">
+        <v>10</v>
+      </c>
+      <c r="AE37" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AE$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AF37" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AF$3),"")</f>
         <v/>
       </c>
-      <c r="AG37" s="26" t="str">
+      <c r="AG37" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AG$3),"")</f>
-        <v/>
-      </c>
-      <c r="AH37" s="26" t="str">
+        <v>5</v>
+      </c>
+      <c r="AH37" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AH$3),"")</f>
-        <v/>
-      </c>
-      <c r="AI37" s="26" t="str">
+        <v>7</v>
+      </c>
+      <c r="AI37" s="26">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AI$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AJ37" s="26" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D37&amp;"]"),Tabela1[Turno],$F37,Tabela1[Data],AJ$3),"")</f>
@@ -15642,7 +15887,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="40"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -15694,7 +15939,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="36"/>
+      <c r="S38" s="39"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -15807,7 +16052,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="41"/>
+      <c r="E39" s="37"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -15845,7 +16090,7 @@
       </c>
       <c r="O39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.3768115942028984</v>
+        <v>6.4459459459459456</v>
       </c>
       <c r="P39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15859,7 +16104,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="37"/>
+      <c r="S39" s="40"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -15898,11 +16143,11 @@
       </c>
       <c r="AD39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AD$3),"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AE$3),"")</f>
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AF39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AF$3),"")</f>
@@ -15910,15 +16155,15 @@
       </c>
       <c r="AG39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AG$3),"")</f>
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AH39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AH$3),"")</f>
-        <v>5.666666666666667</v>
+        <v>6</v>
       </c>
       <c r="AI39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AI$3),"")</f>
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AJ39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AJ$3),"")</f>
@@ -15972,7 +16217,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="39" t="str">
+      <c r="E40" s="35" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -16142,7 +16387,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="40"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -16194,7 +16439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="36"/>
+      <c r="S41" s="39"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16307,7 +16552,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="37"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -16359,7 +16604,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="37"/>
+      <c r="S42" s="40"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16472,7 +16717,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="39" t="str">
+      <c r="E43" s="35" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -16642,7 +16887,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="40"/>
+      <c r="E44" s="36"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -16694,7 +16939,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="36"/>
+      <c r="S44" s="39"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16807,7 +17052,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="37"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -16859,7 +17104,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="37"/>
+      <c r="S45" s="40"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16972,7 +17217,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="39" t="str">
+      <c r="E46" s="35" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -17013,7 +17258,7 @@
       </c>
       <c r="O46" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.62749999999999995</v>
+        <v>0.50409090909090903</v>
       </c>
       <c r="P46" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],P$3)/100,"")</f>
@@ -17027,7 +17272,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="35">
+      <c r="S46" s="41">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -17066,29 +17311,29 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AC$3)/100,"")</f>
         <v>0.66</v>
       </c>
-      <c r="AD46" s="28" t="str">
+      <c r="AD46" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AD$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AE46" s="28" t="str">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="AE46" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AE$3)/100,"")</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="AF46" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AF$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AG46" s="28" t="str">
+      <c r="AG46" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH46" s="28" t="str">
+        <v>0.26</v>
+      </c>
+      <c r="AH46" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AI46" s="28" t="str">
+        <v>0.34</v>
+      </c>
+      <c r="AI46" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.17499999999999999</v>
       </c>
       <c r="AJ46" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Data],AJ$3)/100,"")</f>
@@ -17142,7 +17387,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="40"/>
+      <c r="E47" s="36"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -17194,7 +17439,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="36"/>
+      <c r="S47" s="39"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -17306,7 +17551,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="41"/>
+      <c r="E48" s="37"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -17344,7 +17589,7 @@
       </c>
       <c r="O48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.27774647887323944</v>
+        <v>0.28289473684210525</v>
       </c>
       <c r="P48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17358,7 +17603,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="37"/>
+      <c r="S48" s="40"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -17397,11 +17642,11 @@
       </c>
       <c r="AD48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AD$3)/100,"")</f>
-        <v>0.2475</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="AE48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AE$3)/100,"")</f>
-        <v>0.27</v>
+        <v>0.29600000000000004</v>
       </c>
       <c r="AF48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
@@ -17409,15 +17654,15 @@
       </c>
       <c r="AG48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v>0.24</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="AH48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v>0.28333333333333333</v>
+        <v>0.29749999999999999</v>
       </c>
       <c r="AI48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v>0.29333333333333333</v>
+        <v>0.26374999999999998</v>
       </c>
       <c r="AJ48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -17471,7 +17716,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="39" t="str">
+      <c r="E49" s="35" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -17512,7 +17757,7 @@
       </c>
       <c r="O49" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.32416666666666666</v>
+        <v>0.27350000000000002</v>
       </c>
       <c r="P49" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],P$3)/100,"")</f>
@@ -17526,7 +17771,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="35">
+      <c r="S49" s="41">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -17569,25 +17814,25 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Data],AD$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AE49" s="28" t="str">
+      <c r="AE49" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Data],AE$3)/100,"")</f>
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="AF49" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Data],AF$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AG49" s="28" t="str">
+      <c r="AG49" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH49" s="28" t="str">
+        <v>0.505</v>
+      </c>
+      <c r="AH49" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AI49" s="28" t="str">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="AI49" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AJ49" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Data],AJ$3)/100,"")</f>
@@ -17641,7 +17886,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="40"/>
+      <c r="E50" s="36"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -17693,7 +17938,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="36"/>
+      <c r="S50" s="39"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -17806,7 +18051,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="41"/>
+      <c r="E51" s="37"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -17844,7 +18089,7 @@
       </c>
       <c r="O51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.20364864864864862</v>
+        <v>0.20333333333333331</v>
       </c>
       <c r="P51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17858,7 +18103,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="37"/>
+      <c r="S51" s="40"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -17901,7 +18146,7 @@
       </c>
       <c r="AE51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AE$3)/100,"")</f>
-        <v>0.1925</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="AF51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
@@ -17909,15 +18154,15 @@
       </c>
       <c r="AG51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v>0.17624999999999999</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="AH51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v>0.21249999999999999</v>
+        <v>0.187</v>
       </c>
       <c r="AI51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v>0.19125</v>
+        <v>0.18100000000000002</v>
       </c>
       <c r="AJ51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -17971,7 +18216,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="39" t="str">
+      <c r="E52" s="35" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -18012,7 +18257,7 @@
       </c>
       <c r="O52" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.27500000000000002</v>
+        <v>0.35</v>
       </c>
       <c r="P52" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],P$3)/100,"")</f>
@@ -18026,7 +18271,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="35">
+      <c r="S52" s="41">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -18069,25 +18314,25 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Data],AD$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AE52" s="28" t="str">
+      <c r="AE52" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Data],AE$3)/100,"")</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="AF52" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Data],AF$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AG52" s="28" t="str">
+      <c r="AG52" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH52" s="28" t="str">
+        <v>0.35</v>
+      </c>
+      <c r="AH52" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AI52" s="28" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="AI52" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="AJ52" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Data],AJ$3)/100,"")</f>
@@ -18141,7 +18386,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="40"/>
+      <c r="E53" s="36"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -18193,7 +18438,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="36"/>
+      <c r="S53" s="39"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -18306,7 +18551,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="41"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -18344,7 +18589,7 @@
       </c>
       <c r="O54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.74710144927536237</v>
+        <v>0.72739726027397256</v>
       </c>
       <c r="P54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18358,7 +18603,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="37"/>
+      <c r="S54" s="40"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -18401,7 +18646,7 @@
       </c>
       <c r="AE54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AE$3)/100,"")</f>
-        <v>0.76249999999999996</v>
+        <v>0.76</v>
       </c>
       <c r="AF54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
@@ -18409,15 +18654,15 @@
       </c>
       <c r="AG54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v>0.63749999999999996</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AH54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v>0.77500000000000002</v>
+        <v>0.65</v>
       </c>
       <c r="AI54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v>0.77500000000000002</v>
+        <v>0.68</v>
       </c>
       <c r="AJ54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -18471,7 +18716,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="39" t="str">
+      <c r="E55" s="35" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -18510,9 +18755,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],N$3)/100,"")</f>
         <v>0.1</v>
       </c>
-      <c r="O55" s="28" t="str">
+      <c r="O55" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],O$3)/100,"")</f>
-        <v/>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="P55" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],P$3)/100,"")</f>
@@ -18526,7 +18771,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="35">
+      <c r="S55" s="41">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -18569,25 +18814,25 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Data],AD$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AE55" s="28" t="str">
+      <c r="AE55" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Data],AE$3)/100,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF55" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Data],AF$3)/100,"")</f>
         <v/>
       </c>
-      <c r="AG55" s="28" t="str">
+      <c r="AG55" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Data],AG$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AH55" s="28" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="AH55" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Data],AH$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AI55" s="28" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="AI55" s="28">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Data],AI$3)/100,"")</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="AJ55" s="28" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Data],AJ$3)/100,"")</f>
@@ -18641,7 +18886,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="40"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -18693,7 +18938,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="36"/>
+      <c r="S56" s="39"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -18806,7 +19051,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="41"/>
+      <c r="E57" s="37"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -18844,7 +19089,7 @@
       </c>
       <c r="O57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.29191176470588237</v>
+        <v>0.28055555555555556</v>
       </c>
       <c r="P57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18858,7 +19103,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="37"/>
+      <c r="S57" s="40"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -18901,7 +19146,7 @@
       </c>
       <c r="AE57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AE$3)/100,"")</f>
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AF$3)/100,"")</f>
@@ -18909,15 +19154,15 @@
       </c>
       <c r="AG57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AG$3)/100,"")</f>
-        <v>0.36249999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="AH57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AH$3)/100,"")</f>
-        <v>0.33750000000000002</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AI57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
-        <v>0.22500000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="AJ57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
@@ -18971,7 +19216,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="39" t="str">
+      <c r="E58" s="35" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -19141,7 +19386,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="40"/>
+      <c r="E59" s="36"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -19193,7 +19438,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="36"/>
+      <c r="S59" s="39"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -19306,7 +19551,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="41"/>
+      <c r="E60" s="37"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -19358,7 +19603,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="37"/>
+      <c r="S60" s="40"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -19551,18 +19796,16 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -19579,16 +19822,18 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -19827,7 +20072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL167"/>
+  <dimension ref="A1:AL172"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -38040,6 +38285,466 @@
         <v>5257</v>
       </c>
     </row>
+    <row r="168" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B168" t="s">
+        <v>498</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E168" t="s">
+        <v>299</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G168" s="3">
+        <v>1</v>
+      </c>
+      <c r="H168" s="3">
+        <v>5</v>
+      </c>
+      <c r="I168" s="3">
+        <v>7</v>
+      </c>
+      <c r="J168" s="3">
+        <v>10</v>
+      </c>
+      <c r="K168" s="3">
+        <v>7</v>
+      </c>
+      <c r="L168">
+        <v>20</v>
+      </c>
+      <c r="M168">
+        <v>33</v>
+      </c>
+      <c r="N168">
+        <v>80</v>
+      </c>
+      <c r="O168">
+        <v>67</v>
+      </c>
+      <c r="P168" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q168" s="3">
+        <v>10</v>
+      </c>
+      <c r="R168" s="3">
+        <v>10</v>
+      </c>
+      <c r="S168" s="3">
+        <v>7</v>
+      </c>
+      <c r="T168" s="3">
+        <v>7</v>
+      </c>
+      <c r="U168" s="3">
+        <v>10</v>
+      </c>
+      <c r="W168" s="3"/>
+      <c r="X168" s="3"/>
+      <c r="Y168">
+        <v>35</v>
+      </c>
+      <c r="Z168">
+        <v>17.5</v>
+      </c>
+      <c r="AA168">
+        <v>28</v>
+      </c>
+      <c r="AB168">
+        <v>14</v>
+      </c>
+      <c r="AC168">
+        <v>14.000000000000002</v>
+      </c>
+      <c r="AD168">
+        <v>30</v>
+      </c>
+      <c r="AE168">
+        <v>3</v>
+      </c>
+      <c r="AF168">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B169" t="s">
+        <v>501</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E169" t="s">
+        <v>299</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G169" s="3">
+        <v>1</v>
+      </c>
+      <c r="H169" s="3">
+        <v>7</v>
+      </c>
+      <c r="I169" s="3">
+        <v>7</v>
+      </c>
+      <c r="J169" s="3">
+        <v>10</v>
+      </c>
+      <c r="K169" s="3">
+        <v>5</v>
+      </c>
+      <c r="L169">
+        <v>26</v>
+      </c>
+      <c r="M169">
+        <v>38</v>
+      </c>
+      <c r="N169">
+        <v>74</v>
+      </c>
+      <c r="O169">
+        <v>62</v>
+      </c>
+      <c r="P169" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q169" s="3">
+        <v>10</v>
+      </c>
+      <c r="R169" s="3">
+        <v>10</v>
+      </c>
+      <c r="S169" s="3">
+        <v>10</v>
+      </c>
+      <c r="T169" s="3">
+        <v>7</v>
+      </c>
+      <c r="U169" s="3">
+        <v>7</v>
+      </c>
+      <c r="W169" s="3"/>
+      <c r="X169" s="3"/>
+      <c r="Y169">
+        <v>68</v>
+      </c>
+      <c r="Z169">
+        <v>34</v>
+      </c>
+      <c r="AA169">
+        <v>17</v>
+      </c>
+      <c r="AB169">
+        <v>17</v>
+      </c>
+      <c r="AC169">
+        <v>8.5</v>
+      </c>
+      <c r="AD169">
+        <v>15</v>
+      </c>
+      <c r="AE169">
+        <v>1</v>
+      </c>
+      <c r="AF169">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B170" t="s">
+        <v>504</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E170" t="s">
+        <v>299</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="G170" s="3">
+        <v>1</v>
+      </c>
+      <c r="H170" s="3">
+        <v>10</v>
+      </c>
+      <c r="I170" s="3">
+        <v>7</v>
+      </c>
+      <c r="J170" s="3">
+        <v>10</v>
+      </c>
+      <c r="K170" s="3">
+        <v>5</v>
+      </c>
+      <c r="L170">
+        <v>19</v>
+      </c>
+      <c r="M170">
+        <v>37</v>
+      </c>
+      <c r="N170">
+        <v>81</v>
+      </c>
+      <c r="O170">
+        <v>63</v>
+      </c>
+      <c r="P170" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q170" s="3">
+        <v>10</v>
+      </c>
+      <c r="R170" s="3">
+        <v>10</v>
+      </c>
+      <c r="S170" s="3">
+        <v>7</v>
+      </c>
+      <c r="T170" s="3">
+        <v>7</v>
+      </c>
+      <c r="U170" s="3">
+        <v>5</v>
+      </c>
+      <c r="W170" s="3"/>
+      <c r="X170" s="3"/>
+      <c r="Y170">
+        <v>52</v>
+      </c>
+      <c r="Z170">
+        <v>26</v>
+      </c>
+      <c r="AA170">
+        <v>101</v>
+      </c>
+      <c r="AB170">
+        <v>13</v>
+      </c>
+      <c r="AC170">
+        <v>50.5</v>
+      </c>
+      <c r="AD170">
+        <v>35</v>
+      </c>
+      <c r="AE170">
+        <v>3</v>
+      </c>
+      <c r="AF170">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B171" t="s">
+        <v>507</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E171" t="s">
+        <v>299</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G171" s="3">
+        <v>1</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I171" s="3">
+        <v>5</v>
+      </c>
+      <c r="J171" s="3">
+        <v>7</v>
+      </c>
+      <c r="K171" s="3">
+        <v>7</v>
+      </c>
+      <c r="L171">
+        <v>12</v>
+      </c>
+      <c r="M171">
+        <v>39</v>
+      </c>
+      <c r="N171">
+        <v>88</v>
+      </c>
+      <c r="O171">
+        <v>61</v>
+      </c>
+      <c r="P171" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q171" s="3">
+        <v>10</v>
+      </c>
+      <c r="R171" s="3">
+        <v>10</v>
+      </c>
+      <c r="S171" s="3">
+        <v>7</v>
+      </c>
+      <c r="T171" s="3">
+        <v>7</v>
+      </c>
+      <c r="U171" s="3">
+        <v>5</v>
+      </c>
+      <c r="W171" s="3"/>
+      <c r="X171" s="3"/>
+      <c r="Y171">
+        <v>80</v>
+      </c>
+      <c r="Z171">
+        <v>40</v>
+      </c>
+      <c r="AA171">
+        <v>12</v>
+      </c>
+      <c r="AB171">
+        <v>5</v>
+      </c>
+      <c r="AC171">
+        <v>6</v>
+      </c>
+      <c r="AD171">
+        <v>75</v>
+      </c>
+      <c r="AE171">
+        <v>0</v>
+      </c>
+      <c r="AF171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B172" t="s">
+        <v>510</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E172" t="s">
+        <v>299</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G172" s="3">
+        <v>1</v>
+      </c>
+      <c r="H172" s="3">
+        <v>10</v>
+      </c>
+      <c r="I172" s="3">
+        <v>10</v>
+      </c>
+      <c r="J172" s="3">
+        <v>7</v>
+      </c>
+      <c r="K172" s="3">
+        <v>10</v>
+      </c>
+      <c r="L172">
+        <v>15</v>
+      </c>
+      <c r="M172">
+        <v>25</v>
+      </c>
+      <c r="N172">
+        <v>85</v>
+      </c>
+      <c r="O172">
+        <v>75</v>
+      </c>
+      <c r="P172" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q172" s="3">
+        <v>10</v>
+      </c>
+      <c r="R172" s="3">
+        <v>10</v>
+      </c>
+      <c r="S172" s="3">
+        <v>7</v>
+      </c>
+      <c r="T172" s="3">
+        <v>10</v>
+      </c>
+      <c r="U172" s="3">
+        <v>10</v>
+      </c>
+      <c r="W172" s="3"/>
+      <c r="X172" s="3"/>
+      <c r="Y172">
+        <v>121</v>
+      </c>
+      <c r="Z172">
+        <v>60.5</v>
+      </c>
+      <c r="AA172" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB172" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC172" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD172" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE172" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF172" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="17" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="526">
   <si>
     <t>ID</t>
   </si>
@@ -1621,6 +1621,49 @@
   </si>
   <si>
     <t>17/09/2026 14:33:24</t>
+  </si>
+  <si>
+    <t>6ab75082adfb4239b44a3df6</t>
+  </si>
+  <si>
+    <t>25/09/2026 23:01:11</t>
+  </si>
+  <si>
+    <t>26/09/2026 01:56:34</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>Data  de validade e produção estão de acordo,
+Selagem está conforme,
+Caixa está sem rasgos e seca</t>
+  </si>
+  <si>
+    <t>6ab75082adfb4239b44a3de4</t>
+  </si>
+  <si>
+    <t>25/09/2026 21:28:25</t>
+  </si>
+  <si>
+    <t>6ab75082adfb4239b44a3dcc</t>
+  </si>
+  <si>
+    <t>25/09/2026 18:26:56</t>
+  </si>
+  <si>
+    <t>Retirou a Cartilagem,
+Usou o garfo na retirada de Sassami,
+Riscou o Sassami em X</t>
+  </si>
+  <si>
+    <t>6ab75081adfb4239b44a3d8e</t>
+  </si>
+  <si>
+    <t>25/09/2026 16:42:15</t>
+  </si>
+  <si>
+    <t>26/09/2026 01:56:33</t>
   </si>
 </sst>
 </file>
@@ -2026,6 +2069,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2034,18 +2089,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2400,7 +2443,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46289.447432407411" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="171">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46293.38420659722" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="175">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2431,7 +2474,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="41">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="42">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2473,6 +2516,7 @@
         <s v="21/09/2026"/>
         <s v="22/09/2026"/>
         <s v="23/09/2026"/>
+        <s v="25/09/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2581,7 +2625,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="171">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="175">
   <r>
     <x v="0"/>
     <m/>
@@ -9422,12 +9466,172 @@
     <m/>
     <m/>
   </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab75082adfb4239b44a3df6"/>
+    <s v="25/09/2026 23:01:11"/>
+    <s v="26/09/2026 01:56:34"/>
+    <s v="Ranieli"/>
+    <x v="41"/>
+    <n v="2"/>
+    <s v=""/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="37"/>
+    <n v="75"/>
+    <n v="63"/>
+    <n v="25"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <n v="55"/>
+    <n v="5"/>
+    <n v="27.500000000000004"/>
+    <n v="75"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="40762"/>
+    <s v="Data  de validade e produção estão de acordo,_x000a_Selagem está conforme,_x000a_Caixa está sem rasgos e seca"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="6547"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab75082adfb4239b44a3de4"/>
+    <s v="25/09/2026 21:28:25"/>
+    <s v="26/09/2026 01:56:34"/>
+    <s v="Ranieli"/>
+    <x v="41"/>
+    <n v="2"/>
+    <s v=""/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="5"/>
+    <n v="27"/>
+    <n v="53"/>
+    <n v="73"/>
+    <n v="47"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <n v="47"/>
+    <n v="4"/>
+    <n v="23.5"/>
+    <n v="80"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="992093"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="2678"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab75082adfb4239b44a3dcc"/>
+    <s v="25/09/2026 18:26:56"/>
+    <s v="26/09/2026 01:56:34"/>
+    <s v="Ranieli"/>
+    <x v="41"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="19"/>
+    <n v="52"/>
+    <n v="81"/>
+    <n v="48"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Retirou a Cartilagem,_x000a_Usou o garfo na retirada de Sassami,_x000a_Riscou o Sassami em X"/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <n v="46"/>
+    <n v="4"/>
+    <n v="23"/>
+    <n v="80"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="5803"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6ab75081adfb4239b44a3d8e"/>
+    <s v="25/09/2026 16:42:15"/>
+    <s v="26/09/2026 01:56:33"/>
+    <s v="Ranieli"/>
+    <x v="41"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="5"/>
+    <n v="9"/>
+    <n v="49"/>
+    <n v="91"/>
+    <n v="51"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="65"/>
+    <n v="32.5"/>
+    <n v="46"/>
+    <n v="6"/>
+    <n v="23"/>
+    <n v="70"/>
+    <n v="5"/>
+    <n v="25"/>
+    <s v=""/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="2814"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:AI118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="U117:AJ118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="10">
@@ -9448,7 +9652,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="42">
+      <items count="43">
         <item x="26"/>
         <item x="28"/>
         <item x="27"/>
@@ -9479,6 +9683,7 @@
         <item x="40"/>
         <item x="20"/>
         <item x="21"/>
+        <item x="41"/>
         <item x="22"/>
         <item x="23"/>
         <item x="24"/>
@@ -9532,7 +9737,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="15">
+  <colItems count="16">
     <i>
       <x/>
     </i>
@@ -9577,6 +9782,9 @@
     </i>
     <i>
       <x v="27"/>
+    </i>
+    <i>
+      <x v="30"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -9661,8 +9869,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL172" totalsRowShown="0">
-  <autoFilter ref="A1:AL172"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL176" totalsRowShown="0">
+  <autoFilter ref="A1:AL176"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -10167,7 +10375,7 @@
       </c>
       <c r="AJ3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>25/09/2026</v>
       </c>
       <c r="AK3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -10217,7 +10425,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="35" t="str">
+      <c r="E4" s="39" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -10387,7 +10595,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="40"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -10425,7 +10633,7 @@
       </c>
       <c r="O5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],O$3),"")</f>
-        <v>6.955223880597015</v>
+        <v>6.9565217391304346</v>
       </c>
       <c r="P5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],P$3),"")</f>
@@ -10439,7 +10647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="39"/>
+      <c r="S5" s="36"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10500,9 +10708,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ5" s="12" t="str">
+      <c r="AJ5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AK$3),"")</f>
@@ -10552,7 +10760,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="37"/>
+      <c r="E6" s="41"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -10590,7 +10798,7 @@
       </c>
       <c r="O6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.9350649350649354</v>
+        <v>6.9367088607594933</v>
       </c>
       <c r="P6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10604,7 +10812,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="40"/>
+      <c r="S6" s="37"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10665,9 +10873,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>6.6</v>
       </c>
-      <c r="AJ6" s="9" t="str">
+      <c r="AJ6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -10717,7 +10925,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="35" t="str">
+      <c r="E7" s="39" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -10887,7 +11095,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="36"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -10925,7 +11133,7 @@
       </c>
       <c r="O8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],O$3),"")</f>
-        <v>7.132352941176471</v>
+        <v>7.125</v>
       </c>
       <c r="P8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
@@ -10939,7 +11147,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="39"/>
+      <c r="S8" s="36"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11000,9 +11208,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ8" s="12" t="str">
+      <c r="AJ8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AK$3),"")</f>
@@ -11052,7 +11260,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="37"/>
+      <c r="E9" s="41"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -11090,7 +11298,7 @@
       </c>
       <c r="O9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2784810126582276</v>
+        <v>7.2650602409638552</v>
       </c>
       <c r="P9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11104,7 +11312,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="40"/>
+      <c r="S9" s="37"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11165,9 +11373,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ9" s="9" t="str">
+      <c r="AJ9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -11217,7 +11425,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="35" t="str">
+      <c r="E10" s="39" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -11387,7 +11595,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="40"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -11425,7 +11633,7 @@
       </c>
       <c r="O11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],O$3),"")</f>
-        <v>7</v>
+        <v>6.9444444444444446</v>
       </c>
       <c r="P11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],P$3),"")</f>
@@ -11439,7 +11647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="39"/>
+      <c r="S11" s="36"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11500,9 +11708,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ11" s="12" t="str">
+      <c r="AJ11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AK11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AK$3),"")</f>
@@ -11552,7 +11760,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="37"/>
+      <c r="E12" s="41"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -11590,7 +11798,7 @@
       </c>
       <c r="O12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1898734177215191</v>
+        <v>7.1325301204819276</v>
       </c>
       <c r="P12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11604,7 +11812,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="40"/>
+      <c r="S12" s="37"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11665,9 +11873,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7.6</v>
       </c>
-      <c r="AJ12" s="9" t="str">
+      <c r="AJ12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AK12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -11717,7 +11925,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="35" t="str">
+      <c r="E13" s="39" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -11887,7 +12095,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -11925,7 +12133,7 @@
       </c>
       <c r="O14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],O$3),"")</f>
-        <v>5.382352941176471</v>
+        <v>5.3611111111111107</v>
       </c>
       <c r="P14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
@@ -11939,7 +12147,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="39"/>
+      <c r="S14" s="36"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12000,9 +12208,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AI$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="AJ14" s="12" t="str">
+      <c r="AJ14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AK$3),"")</f>
@@ -12052,7 +12260,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="41"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -12090,7 +12298,7 @@
       </c>
       <c r="O15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>5.5443037974683547</v>
+        <v>5.5180722891566267</v>
       </c>
       <c r="P15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -12104,7 +12312,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="40"/>
+      <c r="S15" s="37"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12165,9 +12373,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>5.8</v>
       </c>
-      <c r="AJ15" s="9" t="str">
+      <c r="AJ15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -12217,7 +12425,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="35" t="str">
+      <c r="E16" s="39" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -12272,7 +12480,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="41">
+      <c r="S16" s="35">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -12387,7 +12595,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="36"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -12425,7 +12633,7 @@
       </c>
       <c r="O17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.81367647058823533</v>
+        <v>0.81125000000000003</v>
       </c>
       <c r="P17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
@@ -12439,7 +12647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="39"/>
+      <c r="S17" s="36"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -12500,9 +12708,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AI$3)/100,"")</f>
         <v>0.73250000000000004</v>
       </c>
-      <c r="AJ17" s="16" t="str">
+      <c r="AJ17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.77</v>
       </c>
       <c r="AK17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AK$3)/100,"")</f>
@@ -12552,7 +12760,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="37"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -12590,7 +12798,7 @@
       </c>
       <c r="O18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.81151898734177208</v>
+        <v>0.80951807228915673</v>
       </c>
       <c r="P18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -12604,7 +12812,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="40"/>
+      <c r="S18" s="37"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -12665,9 +12873,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
         <v>0.746</v>
       </c>
-      <c r="AJ18" s="10" t="str">
+      <c r="AJ18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.77</v>
       </c>
       <c r="AK18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
@@ -12717,7 +12925,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="35" t="str">
+      <c r="E19" s="39" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -12772,7 +12980,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="41">
+      <c r="S19" s="35">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -12887,7 +13095,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="36"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -12925,7 +13133,7 @@
       </c>
       <c r="O20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63926470588235296</v>
+        <v>0.62749999999999995</v>
       </c>
       <c r="P20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
@@ -12939,7 +13147,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="39"/>
+      <c r="S20" s="36"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13000,9 +13208,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AI$3)/100,"")</f>
         <v>0.75</v>
       </c>
-      <c r="AJ20" s="16" t="str">
+      <c r="AJ20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.42749999999999999</v>
       </c>
       <c r="AK20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AK$3)/100,"")</f>
@@ -13052,7 +13260,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="37"/>
+      <c r="E21" s="41"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -13090,7 +13298,7 @@
       </c>
       <c r="O21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.64151898734177204</v>
+        <v>0.63120481927710836</v>
       </c>
       <c r="P21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -13104,7 +13312,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="40"/>
+      <c r="S21" s="37"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13165,9 +13373,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
         <v>0.7340000000000001</v>
       </c>
-      <c r="AJ21" s="10" t="str">
+      <c r="AJ21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.42749999999999999</v>
       </c>
       <c r="AK21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
@@ -13217,7 +13425,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="35" t="str">
+      <c r="E22" s="39" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -13387,7 +13595,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="36"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -13425,7 +13633,7 @@
       </c>
       <c r="O23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],O$3),"")</f>
-        <v>6.7058823529411766</v>
+        <v>6.6944444444444446</v>
       </c>
       <c r="P23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
@@ -13439,7 +13647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="39"/>
+      <c r="S23" s="36"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -13500,9 +13708,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ23" s="12" t="str">
+      <c r="AJ23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AK23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AK$3),"")</f>
@@ -13552,7 +13760,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="37"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -13590,7 +13798,7 @@
       </c>
       <c r="O24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.7848101265822782</v>
+        <v>6.7710843373493974</v>
       </c>
       <c r="P24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13604,7 +13812,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="40"/>
+      <c r="S24" s="37"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -13665,9 +13873,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ24" s="9" t="str">
+      <c r="AJ24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AK24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -13717,7 +13925,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="35" t="str">
+      <c r="E25" s="39" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -13887,7 +14095,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="36"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -13925,7 +14133,7 @@
       </c>
       <c r="O26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],O$3),"")</f>
-        <v>6.8955223880597014</v>
+        <v>6.901408450704225</v>
       </c>
       <c r="P26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
@@ -13939,7 +14147,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="39"/>
+      <c r="S26" s="36"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14000,9 +14208,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ26" s="12" t="str">
+      <c r="AJ26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AK$3),"")</f>
@@ -14052,7 +14260,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="37"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -14090,7 +14298,7 @@
       </c>
       <c r="O27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2564102564102564</v>
+        <v>7.2439024390243905</v>
       </c>
       <c r="P27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14104,7 +14312,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="40"/>
+      <c r="S27" s="37"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14165,9 +14373,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7.6</v>
       </c>
-      <c r="AJ27" s="9" t="str">
+      <c r="AJ27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -14217,7 +14425,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="35" t="str">
+      <c r="E28" s="39" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -14387,7 +14595,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="36"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -14439,7 +14647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="39"/>
+      <c r="S29" s="36"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14500,9 +14708,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ29" s="12" t="str">
+      <c r="AJ29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AK$3),"")</f>
@@ -14552,7 +14760,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="37"/>
+      <c r="E30" s="41"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -14590,7 +14798,7 @@
       </c>
       <c r="O30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.4177215189873413</v>
+        <v>7.3975903614457827</v>
       </c>
       <c r="P30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14604,7 +14812,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="40"/>
+      <c r="S30" s="37"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14665,9 +14873,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7.6</v>
       </c>
-      <c r="AJ30" s="9" t="str">
+      <c r="AJ30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -14717,7 +14925,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="35" t="str">
+      <c r="E31" s="39" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -14887,7 +15095,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="36"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -14925,7 +15133,7 @@
       </c>
       <c r="O32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],O$3),"")</f>
-        <v>6.9117647058823533</v>
+        <v>6.916666666666667</v>
       </c>
       <c r="P32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
@@ -14939,7 +15147,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="39"/>
+      <c r="S32" s="36"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15000,9 +15208,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ32" s="12" t="str">
+      <c r="AJ32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AK$3),"")</f>
@@ -15052,7 +15260,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="37"/>
+      <c r="E33" s="41"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -15090,7 +15298,7 @@
       </c>
       <c r="O33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.075949367088608</v>
+        <v>7.072289156626506</v>
       </c>
       <c r="P33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15104,7 +15312,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="40"/>
+      <c r="S33" s="37"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15165,9 +15373,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ33" s="9" t="str">
+      <c r="AJ33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -15217,7 +15425,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="35" t="str">
+      <c r="E34" s="39" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -15387,7 +15595,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="36"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -15425,7 +15633,7 @@
       </c>
       <c r="O35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],O$3),"")</f>
-        <v>7.0441176470588234</v>
+        <v>7.041666666666667</v>
       </c>
       <c r="P35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],P$3),"")</f>
@@ -15439,7 +15647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="39"/>
+      <c r="S35" s="36"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15500,9 +15708,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ35" s="12" t="str">
+      <c r="AJ35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AK$3),"")</f>
@@ -15552,7 +15760,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="37"/>
+      <c r="E36" s="41"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -15590,7 +15798,7 @@
       </c>
       <c r="O36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1898734177215191</v>
+        <v>7.1807228915662646</v>
       </c>
       <c r="P36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15604,7 +15812,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="40"/>
+      <c r="S36" s="37"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15665,9 +15873,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ36" s="9" t="str">
+      <c r="AJ36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -15717,7 +15925,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="35" t="str">
+      <c r="E37" s="39" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -15887,7 +16095,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="36"/>
+      <c r="E38" s="40"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -15925,7 +16133,7 @@
       </c>
       <c r="O38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],O$3),"")</f>
-        <v>6.3492063492063489</v>
+        <v>6.2985074626865671</v>
       </c>
       <c r="P38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
@@ -15939,7 +16147,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="39"/>
+      <c r="S38" s="36"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16000,9 +16208,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AI$3),"")</f>
         <v>6</v>
       </c>
-      <c r="AJ38" s="12" t="str">
+      <c r="AJ38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AK38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AK$3),"")</f>
@@ -16052,7 +16260,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="37"/>
+      <c r="E39" s="41"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -16090,7 +16298,7 @@
       </c>
       <c r="O39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.4459459459459456</v>
+        <v>6.3974358974358978</v>
       </c>
       <c r="P39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16104,7 +16312,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="40"/>
+      <c r="S39" s="37"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16165,9 +16373,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>6.8</v>
       </c>
-      <c r="AJ39" s="9" t="str">
+      <c r="AJ39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AK39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -16217,7 +16425,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="35" t="str">
+      <c r="E40" s="39" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -16387,7 +16595,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="36"/>
+      <c r="E41" s="40"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -16425,7 +16633,7 @@
       </c>
       <c r="O41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],O$3),"")</f>
-        <v>8.4716981132075464</v>
+        <v>8.4074074074074066</v>
       </c>
       <c r="P41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
@@ -16439,7 +16647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="39"/>
+      <c r="S41" s="36"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16500,9 +16708,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ41" s="12" t="str">
+      <c r="AJ41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AK$3),"")</f>
@@ -16552,7 +16760,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="37"/>
+      <c r="E42" s="41"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -16590,7 +16798,7 @@
       </c>
       <c r="O42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.4237288135593218</v>
+        <v>8.3666666666666671</v>
       </c>
       <c r="P42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16604,7 +16812,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="40"/>
+      <c r="S42" s="37"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16665,9 +16873,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AJ42" s="9" t="str">
+      <c r="AJ42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -16717,7 +16925,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="35" t="str">
+      <c r="E43" s="39" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -16887,7 +17095,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="36"/>
+      <c r="E44" s="40"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -16925,7 +17133,7 @@
       </c>
       <c r="O44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],O$3),"")</f>
-        <v>8.4528301886792452</v>
+        <v>8.4259259259259256</v>
       </c>
       <c r="P44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
@@ -16939,7 +17147,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="39"/>
+      <c r="S44" s="36"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17000,9 +17208,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AI$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AJ44" s="12" t="str">
+      <c r="AJ44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AK$3),"")</f>
@@ -17052,7 +17260,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="37"/>
+      <c r="E45" s="41"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -17090,7 +17298,7 @@
       </c>
       <c r="O45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.454545454545455</v>
+        <v>8.4285714285714288</v>
       </c>
       <c r="P45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -17104,7 +17312,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="40"/>
+      <c r="S45" s="37"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17165,9 +17373,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AJ45" s="9" t="str">
+      <c r="AJ45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -17217,7 +17425,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="35" t="str">
+      <c r="E46" s="39" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -17272,7 +17480,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="41">
+      <c r="S46" s="35">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -17387,7 +17595,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="36"/>
+      <c r="E47" s="40"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -17425,7 +17633,7 @@
       </c>
       <c r="O47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.24546153846153845</v>
+        <v>0.24666666666666667</v>
       </c>
       <c r="P47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
@@ -17439,7 +17647,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="39"/>
+      <c r="S47" s="36"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -17499,9 +17707,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AI$3)/100,"")</f>
         <v>0.29333333333333333</v>
       </c>
-      <c r="AJ47" s="16" t="str">
+      <c r="AJ47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.32500000000000001</v>
       </c>
       <c r="AK47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AK$3)/100,"")</f>
@@ -17551,7 +17759,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="37"/>
+      <c r="E48" s="41"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -17589,7 +17797,7 @@
       </c>
       <c r="O48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28289473684210525</v>
+        <v>0.28344155844155844</v>
       </c>
       <c r="P48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17603,7 +17811,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="40"/>
+      <c r="S48" s="37"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -17664,9 +17872,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
         <v>0.26374999999999998</v>
       </c>
-      <c r="AJ48" s="10" t="str">
+      <c r="AJ48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.32500000000000001</v>
       </c>
       <c r="AK48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
@@ -17716,7 +17924,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="35" t="str">
+      <c r="E49" s="39" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -17771,7 +17979,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="41">
+      <c r="S49" s="35">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -17886,7 +18094,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="36"/>
+      <c r="E50" s="40"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -17924,7 +18132,7 @@
       </c>
       <c r="O50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.19301470588235292</v>
+        <v>0.1957638888888889</v>
       </c>
       <c r="P50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
@@ -17938,7 +18146,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="39"/>
+      <c r="S50" s="36"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -17999,9 +18207,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AI$3)/100,"")</f>
         <v>0.19125</v>
       </c>
-      <c r="AJ50" s="16" t="str">
+      <c r="AJ50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.24249999999999999</v>
       </c>
       <c r="AK50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AK$3)/100,"")</f>
@@ -18051,7 +18259,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="37"/>
+      <c r="E51" s="41"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -18089,7 +18297,7 @@
       </c>
       <c r="O51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.20333333333333331</v>
+        <v>0.20524390243902438</v>
       </c>
       <c r="P51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18103,7 +18311,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="40"/>
+      <c r="S51" s="37"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -18164,9 +18372,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
         <v>0.18100000000000002</v>
       </c>
-      <c r="AJ51" s="10" t="str">
+      <c r="AJ51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.24249999999999999</v>
       </c>
       <c r="AK51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
@@ -18216,7 +18424,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="35" t="str">
+      <c r="E52" s="39" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -18271,7 +18479,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="41">
+      <c r="S52" s="35">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -18386,7 +18594,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="36"/>
+      <c r="E53" s="40"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -18424,7 +18632,7 @@
       </c>
       <c r="O53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.76119402985074625</v>
+        <v>0.76126760563380291</v>
       </c>
       <c r="P53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
@@ -18438,7 +18646,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="39"/>
+      <c r="S53" s="36"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -18499,9 +18707,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AI$3)/100,"")</f>
         <v>0.77500000000000002</v>
       </c>
-      <c r="AJ53" s="16" t="str">
+      <c r="AJ53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.76249999999999996</v>
       </c>
       <c r="AK53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AK$3)/100,"")</f>
@@ -18551,7 +18759,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="37"/>
+      <c r="E54" s="41"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -18589,7 +18797,7 @@
       </c>
       <c r="O54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.72739726027397256</v>
+        <v>0.72922077922077921</v>
       </c>
       <c r="P54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18603,7 +18811,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="40"/>
+      <c r="S54" s="37"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -18664,9 +18872,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
         <v>0.68</v>
       </c>
-      <c r="AJ54" s="10" t="str">
+      <c r="AJ54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.76249999999999996</v>
       </c>
       <c r="AK54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
@@ -18716,7 +18924,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="35" t="str">
+      <c r="E55" s="39" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -18771,7 +18979,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="41">
+      <c r="S55" s="35">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -18886,7 +19094,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="36"/>
+      <c r="E56" s="40"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -18924,7 +19132,7 @@
       </c>
       <c r="O56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.29191176470588237</v>
+        <v>0.28819444444444442</v>
       </c>
       <c r="P56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
@@ -18938,7 +19146,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="39"/>
+      <c r="S56" s="36"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -18999,9 +19207,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AI$3)/100,"")</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="AJ56" s="16" t="str">
+      <c r="AJ56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="AK56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AK$3)/100,"")</f>
@@ -19051,7 +19259,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="37"/>
+      <c r="E57" s="41"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -19089,7 +19297,7 @@
       </c>
       <c r="O57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28055555555555556</v>
+        <v>0.27763157894736845</v>
       </c>
       <c r="P57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -19103,7 +19311,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="40"/>
+      <c r="S57" s="37"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -19164,9 +19372,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AI$3)/100,"")</f>
         <v>0.21</v>
       </c>
-      <c r="AJ57" s="10" t="str">
+      <c r="AJ57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="AK57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
@@ -19216,7 +19424,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="35" t="str">
+      <c r="E58" s="39" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -19386,7 +19594,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="36"/>
+      <c r="E59" s="40"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -19438,7 +19646,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="39"/>
+      <c r="S59" s="36"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -19499,9 +19707,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AI$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AJ59" s="12" t="str">
+      <c r="AJ59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>8.3333333333333339</v>
       </c>
       <c r="AK59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AK$3),"")</f>
@@ -19551,7 +19759,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="37"/>
+      <c r="E60" s="41"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -19603,7 +19811,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="40"/>
+      <c r="S60" s="37"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -19664,9 +19872,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AI$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AJ60" s="9" t="str">
+      <c r="AJ60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AJ$3),"")</f>
-        <v/>
+        <v>8.3333333333333339</v>
       </c>
       <c r="AK60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AK$3),"")</f>
@@ -19789,23 +19997,27 @@
       <c r="AI118" t="s">
         <v>489</v>
       </c>
-      <c r="AJ118"/>
+      <c r="AJ118" t="s">
+        <v>516</v>
+      </c>
       <c r="AK118"/>
       <c r="AL118"/>
       <c r="AM118"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -19822,18 +20034,16 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -20072,7 +20282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL172"/>
+  <dimension ref="A1:AL176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -38745,6 +38955,474 @@
         <v>28</v>
       </c>
     </row>
+    <row r="173" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B173" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E173" t="s">
+        <v>18</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G173" s="3">
+        <v>2</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I173" s="3">
+        <v>7</v>
+      </c>
+      <c r="J173" s="3">
+        <v>7</v>
+      </c>
+      <c r="K173" s="3">
+        <v>5</v>
+      </c>
+      <c r="L173">
+        <v>37</v>
+      </c>
+      <c r="M173">
+        <v>75</v>
+      </c>
+      <c r="N173">
+        <v>63</v>
+      </c>
+      <c r="O173">
+        <v>25</v>
+      </c>
+      <c r="P173" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q173" s="3">
+        <v>7</v>
+      </c>
+      <c r="R173" s="3">
+        <v>7</v>
+      </c>
+      <c r="S173" s="3">
+        <v>7</v>
+      </c>
+      <c r="T173" s="3">
+        <v>7</v>
+      </c>
+      <c r="U173" s="3">
+        <v>5</v>
+      </c>
+      <c r="V173" t="s">
+        <v>169</v>
+      </c>
+      <c r="W173" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X173" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y173" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z173" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA173">
+        <v>55</v>
+      </c>
+      <c r="AB173">
+        <v>5</v>
+      </c>
+      <c r="AC173">
+        <v>27.500000000000004</v>
+      </c>
+      <c r="AD173">
+        <v>75</v>
+      </c>
+      <c r="AE173">
+        <v>4</v>
+      </c>
+      <c r="AF173">
+        <v>20</v>
+      </c>
+      <c r="AG173" s="3">
+        <v>5</v>
+      </c>
+      <c r="AH173" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI173" t="s">
+        <v>517</v>
+      </c>
+      <c r="AJ173" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK173" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL173">
+        <v>6547</v>
+      </c>
+    </row>
+    <row r="174" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B174" t="s">
+        <v>518</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E174" t="s">
+        <v>18</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G174" s="3">
+        <v>2</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I174" s="3">
+        <v>7</v>
+      </c>
+      <c r="J174" s="3">
+        <v>5</v>
+      </c>
+      <c r="K174" s="3">
+        <v>5</v>
+      </c>
+      <c r="L174">
+        <v>27</v>
+      </c>
+      <c r="M174">
+        <v>53</v>
+      </c>
+      <c r="N174">
+        <v>73</v>
+      </c>
+      <c r="O174">
+        <v>47</v>
+      </c>
+      <c r="P174" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q174" s="3">
+        <v>7</v>
+      </c>
+      <c r="R174" s="3">
+        <v>7</v>
+      </c>
+      <c r="S174" s="3">
+        <v>7</v>
+      </c>
+      <c r="T174" s="3">
+        <v>7</v>
+      </c>
+      <c r="U174" s="3">
+        <v>7</v>
+      </c>
+      <c r="V174" t="s">
+        <v>169</v>
+      </c>
+      <c r="W174" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X174" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y174" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z174" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA174">
+        <v>47</v>
+      </c>
+      <c r="AB174">
+        <v>4</v>
+      </c>
+      <c r="AC174">
+        <v>23.5</v>
+      </c>
+      <c r="AD174">
+        <v>80</v>
+      </c>
+      <c r="AE174">
+        <v>5</v>
+      </c>
+      <c r="AF174">
+        <v>25</v>
+      </c>
+      <c r="AG174" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH174" s="3">
+        <v>992093</v>
+      </c>
+      <c r="AI174" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ174" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK174" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL174">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="175" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B175" t="s">
+        <v>520</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E175" t="s">
+        <v>18</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G175" s="3">
+        <v>2</v>
+      </c>
+      <c r="H175" s="3">
+        <v>7</v>
+      </c>
+      <c r="I175" s="3">
+        <v>7</v>
+      </c>
+      <c r="J175" s="3">
+        <v>7</v>
+      </c>
+      <c r="K175" s="3">
+        <v>5</v>
+      </c>
+      <c r="L175">
+        <v>19</v>
+      </c>
+      <c r="M175">
+        <v>52</v>
+      </c>
+      <c r="N175">
+        <v>81</v>
+      </c>
+      <c r="O175">
+        <v>48</v>
+      </c>
+      <c r="P175" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q175" s="3">
+        <v>7</v>
+      </c>
+      <c r="R175" s="3">
+        <v>7</v>
+      </c>
+      <c r="S175" s="3">
+        <v>7</v>
+      </c>
+      <c r="T175" s="3">
+        <v>7</v>
+      </c>
+      <c r="U175" s="3">
+        <v>5</v>
+      </c>
+      <c r="V175" t="s">
+        <v>522</v>
+      </c>
+      <c r="W175" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X175" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y175" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z175" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA175">
+        <v>46</v>
+      </c>
+      <c r="AB175">
+        <v>4</v>
+      </c>
+      <c r="AC175">
+        <v>23</v>
+      </c>
+      <c r="AD175">
+        <v>80</v>
+      </c>
+      <c r="AE175">
+        <v>4</v>
+      </c>
+      <c r="AF175">
+        <v>20</v>
+      </c>
+      <c r="AG175" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH175" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI175" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ175" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK175" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL175">
+        <v>5803</v>
+      </c>
+    </row>
+    <row r="176" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B176" t="s">
+        <v>523</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E176" t="s">
+        <v>18</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G176" s="3">
+        <v>2</v>
+      </c>
+      <c r="H176" s="3">
+        <v>7</v>
+      </c>
+      <c r="I176" s="3">
+        <v>7</v>
+      </c>
+      <c r="J176" s="3">
+        <v>5</v>
+      </c>
+      <c r="K176" s="3">
+        <v>5</v>
+      </c>
+      <c r="L176">
+        <v>9</v>
+      </c>
+      <c r="M176">
+        <v>49</v>
+      </c>
+      <c r="N176">
+        <v>91</v>
+      </c>
+      <c r="O176">
+        <v>51</v>
+      </c>
+      <c r="P176" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q176" s="3">
+        <v>7</v>
+      </c>
+      <c r="R176" s="3">
+        <v>7</v>
+      </c>
+      <c r="S176" s="3">
+        <v>7</v>
+      </c>
+      <c r="T176" s="3">
+        <v>7</v>
+      </c>
+      <c r="U176" s="3">
+        <v>5</v>
+      </c>
+      <c r="V176" t="s">
+        <v>169</v>
+      </c>
+      <c r="W176" s="3">
+        <v>5</v>
+      </c>
+      <c r="X176" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y176">
+        <v>65</v>
+      </c>
+      <c r="Z176">
+        <v>32.5</v>
+      </c>
+      <c r="AA176">
+        <v>46</v>
+      </c>
+      <c r="AB176">
+        <v>6</v>
+      </c>
+      <c r="AC176">
+        <v>23</v>
+      </c>
+      <c r="AD176">
+        <v>70</v>
+      </c>
+      <c r="AE176">
+        <v>5</v>
+      </c>
+      <c r="AF176">
+        <v>25</v>
+      </c>
+      <c r="AG176" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH176" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI176" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ176" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK176" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL176">
+        <v>2814</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId3"/>
+    <pivotCache cacheId="21" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="537">
   <si>
     <t>ID</t>
   </si>
@@ -1664,6 +1664,39 @@
   </si>
   <si>
     <t>26/09/2026 01:56:33</t>
+  </si>
+  <si>
+    <t>6abb47842d48c2171f434104</t>
+  </si>
+  <si>
+    <t>28/09/2026 23:05:38</t>
+  </si>
+  <si>
+    <t>29/09/2026 02:07:16</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t>6abb47842d48c2171f4340ce</t>
+  </si>
+  <si>
+    <t>28/09/2026 21:34:08</t>
+  </si>
+  <si>
+    <t>6abb47832d48c2171f4340b6</t>
+  </si>
+  <si>
+    <t>28/09/2026 18:12:11</t>
+  </si>
+  <si>
+    <t>29/09/2026 02:07:15</t>
+  </si>
+  <si>
+    <t>6abb47832d48c2171f43408a</t>
+  </si>
+  <si>
+    <t>28/09/2026 16:36:00</t>
   </si>
 </sst>
 </file>
@@ -2069,7 +2102,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2078,17 +2120,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2443,7 +2476,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46293.38420659722" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="175">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46294.380655092595" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="179">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2474,7 +2507,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="42">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="43">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2517,6 +2550,7 @@
         <s v="22/09/2026"/>
         <s v="23/09/2026"/>
         <s v="25/09/2026"/>
+        <s v="28/09/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2625,7 +2659,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="175">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="179">
   <r>
     <x v="0"/>
     <m/>
@@ -9626,12 +9660,172 @@
     <s v="assinatura"/>
     <n v="2814"/>
   </r>
+  <r>
+    <x v="8"/>
+    <s v="6abb47842d48c2171f434104"/>
+    <s v="28/09/2026 23:05:38"/>
+    <s v="29/09/2026 02:07:16"/>
+    <s v="Ranieli"/>
+    <x v="42"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="38"/>
+    <n v="27"/>
+    <n v="62"/>
+    <n v="73"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="73"/>
+    <n v="36.5"/>
+    <n v="57"/>
+    <n v="6"/>
+    <n v="28.499999999999996"/>
+    <n v="70"/>
+    <n v="4"/>
+    <n v="20"/>
+    <s v=""/>
+    <n v="992093"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="6358"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abb47842d48c2171f4340ce"/>
+    <s v="28/09/2026 21:34:08"/>
+    <s v="29/09/2026 02:07:16"/>
+    <s v="Ranieli"/>
+    <x v="42"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="18"/>
+    <n v="24"/>
+    <n v="82"/>
+    <n v="76"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="70"/>
+    <n v="35"/>
+    <n v="38"/>
+    <n v="5"/>
+    <n v="19"/>
+    <n v="75"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3221"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abb47832d48c2171f4340b6"/>
+    <s v="28/09/2026 18:12:11"/>
+    <s v="29/09/2026 02:07:15"/>
+    <s v="Ranieli"/>
+    <x v="42"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="28"/>
+    <n v="14"/>
+    <n v="72"/>
+    <n v="86"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="55"/>
+    <n v="27.500000000000004"/>
+    <n v="44"/>
+    <n v="4"/>
+    <n v="22"/>
+    <n v="80"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="13188"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="3211"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abb47832d48c2171f43408a"/>
+    <s v="28/09/2026 16:36:00"/>
+    <s v="29/09/2026 02:07:15"/>
+    <s v="Ranieli"/>
+    <x v="42"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="18"/>
+    <n v="24"/>
+    <n v="82"/>
+    <n v="76"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <s v=""/>
+    <n v="37"/>
+    <n v="6"/>
+    <n v="18.5"/>
+    <n v="70"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="4926"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:AJ118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="U117:AK118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="10">
@@ -9652,7 +9846,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="43">
+      <items count="44">
         <item x="26"/>
         <item x="28"/>
         <item x="27"/>
@@ -9687,6 +9881,7 @@
         <item x="22"/>
         <item x="23"/>
         <item x="24"/>
+        <item x="42"/>
         <item x="25"/>
         <item x="0"/>
         <item x="1"/>
@@ -9737,7 +9932,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="16">
+  <colItems count="17">
     <i>
       <x/>
     </i>
@@ -9785,6 +9980,9 @@
     </i>
     <i>
       <x v="30"/>
+    </i>
+    <i>
+      <x v="34"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -9869,8 +10067,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL176" totalsRowShown="0">
-  <autoFilter ref="A1:AL176"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL180" totalsRowShown="0">
+  <autoFilter ref="A1:AL180"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -10379,7 +10577,7 @@
       </c>
       <c r="AK3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>28/09/2026</v>
       </c>
       <c r="AL3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -10425,7 +10623,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="39" t="str">
+      <c r="E4" s="35" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -10595,7 +10793,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="40"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -10633,7 +10831,7 @@
       </c>
       <c r="O5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],O$3),"")</f>
-        <v>6.9565217391304346</v>
+        <v>6.9589041095890414</v>
       </c>
       <c r="P5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],P$3),"")</f>
@@ -10647,7 +10845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="36"/>
+      <c r="S5" s="39"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10712,9 +10910,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK5" s="12" t="str">
+      <c r="AK5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AL$3),"")</f>
@@ -10760,7 +10958,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="37"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -10798,7 +10996,7 @@
       </c>
       <c r="O6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.9367088607594933</v>
+        <v>6.9397590361445785</v>
       </c>
       <c r="P6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -10812,7 +11010,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="37"/>
+      <c r="S6" s="40"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10877,9 +11075,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK6" s="9" t="str">
+      <c r="AK6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -10925,7 +11123,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="39" t="str">
+      <c r="E7" s="35" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -11095,7 +11293,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -11133,7 +11331,7 @@
       </c>
       <c r="O8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],O$3),"")</f>
-        <v>7.125</v>
+        <v>7.1184210526315788</v>
       </c>
       <c r="P8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
@@ -11147,7 +11345,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="36"/>
+      <c r="S8" s="39"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11212,9 +11410,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK8" s="12" t="str">
+      <c r="AK8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AL$3),"")</f>
@@ -11260,7 +11458,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="41"/>
+      <c r="E9" s="37"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -11298,7 +11496,7 @@
       </c>
       <c r="O9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2650602409638552</v>
+        <v>7.2528735632183912</v>
       </c>
       <c r="P9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11312,7 +11510,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="37"/>
+      <c r="S9" s="40"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11377,9 +11575,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK9" s="9" t="str">
+      <c r="AK9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -11425,7 +11623,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="39" t="str">
+      <c r="E10" s="35" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -11595,7 +11793,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="40"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -11633,7 +11831,7 @@
       </c>
       <c r="O11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],O$3),"")</f>
-        <v>6.9444444444444446</v>
+        <v>6.9473684210526319</v>
       </c>
       <c r="P11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],P$3),"")</f>
@@ -11647,7 +11845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="36"/>
+      <c r="S11" s="39"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11712,9 +11910,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AJ$3),"")</f>
         <v>6</v>
       </c>
-      <c r="AK11" s="12" t="str">
+      <c r="AK11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AL$3),"")</f>
@@ -11760,7 +11958,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="41"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -11798,7 +11996,7 @@
       </c>
       <c r="O12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1325301204819276</v>
+        <v>7.1264367816091951</v>
       </c>
       <c r="P12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11812,7 +12010,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="37"/>
+      <c r="S12" s="40"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11877,9 +12075,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>6</v>
       </c>
-      <c r="AK12" s="9" t="str">
+      <c r="AK12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -11925,7 +12123,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="39" t="str">
+      <c r="E13" s="35" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -12095,7 +12293,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="40"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -12133,7 +12331,7 @@
       </c>
       <c r="O14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],O$3),"")</f>
-        <v>5.3611111111111107</v>
+        <v>5.3684210526315788</v>
       </c>
       <c r="P14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
@@ -12147,7 +12345,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="36"/>
+      <c r="S14" s="39"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12212,9 +12410,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AJ$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AK14" s="12" t="str">
+      <c r="AK14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AL14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AL$3),"")</f>
@@ -12260,7 +12458,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="41"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -12298,7 +12496,7 @@
       </c>
       <c r="O15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>5.5180722891566267</v>
+        <v>5.5172413793103452</v>
       </c>
       <c r="P15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -12312,7 +12510,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="37"/>
+      <c r="S15" s="40"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12377,9 +12575,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AK15" s="9" t="str">
+      <c r="AK15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AL15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -12425,7 +12623,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="39" t="str">
+      <c r="E16" s="35" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -12480,7 +12678,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="41">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -12595,7 +12793,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="40"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -12633,7 +12831,7 @@
       </c>
       <c r="O17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.81125000000000003</v>
+        <v>0.80776315789473685</v>
       </c>
       <c r="P17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
@@ -12647,7 +12845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="36"/>
+      <c r="S17" s="39"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -12712,9 +12910,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.77</v>
       </c>
-      <c r="AK17" s="16" t="str">
+      <c r="AK17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.745</v>
       </c>
       <c r="AL17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AL$3)/100,"")</f>
@@ -12760,7 +12958,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="41"/>
+      <c r="E18" s="37"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -12798,7 +12996,7 @@
       </c>
       <c r="O18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.80951807228915673</v>
+        <v>0.80655172413793108</v>
       </c>
       <c r="P18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -12812,7 +13010,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="37"/>
+      <c r="S18" s="40"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -12877,9 +13075,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.77</v>
       </c>
-      <c r="AK18" s="10" t="str">
+      <c r="AK18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.745</v>
       </c>
       <c r="AL18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
@@ -12925,7 +13123,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="39" t="str">
+      <c r="E19" s="35" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -12980,7 +13178,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="41">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -13095,7 +13293,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="40"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -13133,7 +13331,7 @@
       </c>
       <c r="O20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.62749999999999995</v>
+        <v>0.63539473684210523</v>
       </c>
       <c r="P20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
@@ -13147,7 +13345,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="36"/>
+      <c r="S20" s="39"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13212,9 +13410,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.42749999999999999</v>
       </c>
-      <c r="AK20" s="16" t="str">
+      <c r="AK20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.77749999999999997</v>
       </c>
       <c r="AL20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AL$3)/100,"")</f>
@@ -13260,7 +13458,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="41"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -13298,7 +13496,7 @@
       </c>
       <c r="O21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63120481927710836</v>
+        <v>0.63793103448275867</v>
       </c>
       <c r="P21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -13312,7 +13510,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="37"/>
+      <c r="S21" s="40"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13377,9 +13575,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.42749999999999999</v>
       </c>
-      <c r="AK21" s="10" t="str">
+      <c r="AK21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.77749999999999997</v>
       </c>
       <c r="AL21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
@@ -13425,7 +13623,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="39" t="str">
+      <c r="E22" s="35" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -13595,7 +13793,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="40"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -13633,7 +13831,7 @@
       </c>
       <c r="O23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],O$3),"")</f>
-        <v>6.6944444444444446</v>
+        <v>6.7105263157894735</v>
       </c>
       <c r="P23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
@@ -13647,7 +13845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="36"/>
+      <c r="S23" s="39"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -13712,9 +13910,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AJ$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AK23" s="12" t="str">
+      <c r="AK23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AL$3),"")</f>
@@ -13760,7 +13958,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="41"/>
+      <c r="E24" s="37"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -13798,7 +13996,7 @@
       </c>
       <c r="O24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.7710843373493974</v>
+        <v>6.7816091954022992</v>
       </c>
       <c r="P24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -13812,7 +14010,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="37"/>
+      <c r="S24" s="40"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -13877,9 +14075,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AK24" s="9" t="str">
+      <c r="AK24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -13925,7 +14123,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="39" t="str">
+      <c r="E25" s="35" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -14095,7 +14293,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="40"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -14133,7 +14331,7 @@
       </c>
       <c r="O26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],O$3),"")</f>
-        <v>6.901408450704225</v>
+        <v>6.9066666666666663</v>
       </c>
       <c r="P26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
@@ -14147,7 +14345,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="36"/>
+      <c r="S26" s="39"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14212,9 +14410,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK26" s="12" t="str">
+      <c r="AK26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AL$3),"")</f>
@@ -14260,7 +14458,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="41"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -14298,7 +14496,7 @@
       </c>
       <c r="O27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2439024390243905</v>
+        <v>7.2325581395348841</v>
       </c>
       <c r="P27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14312,7 +14510,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="37"/>
+      <c r="S27" s="40"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14377,9 +14575,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK27" s="9" t="str">
+      <c r="AK27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -14425,7 +14623,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="39" t="str">
+      <c r="E28" s="35" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -14595,7 +14793,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="40"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -14633,7 +14831,7 @@
       </c>
       <c r="O29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],O$3),"")</f>
-        <v>7</v>
+        <v>6.9736842105263159</v>
       </c>
       <c r="P29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],P$3),"")</f>
@@ -14647,7 +14845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="36"/>
+      <c r="S29" s="39"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14712,9 +14910,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK29" s="12" t="str">
+      <c r="AK29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AL29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AL$3),"")</f>
@@ -14760,7 +14958,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="37"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -14798,7 +14996,7 @@
       </c>
       <c r="O30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.3975903614457827</v>
+        <v>7.3563218390804597</v>
       </c>
       <c r="P30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14812,7 +15010,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="37"/>
+      <c r="S30" s="40"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14877,9 +15075,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK30" s="9" t="str">
+      <c r="AK30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AL30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -14925,7 +15123,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="39" t="str">
+      <c r="E31" s="35" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -15095,7 +15293,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="40"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -15133,7 +15331,7 @@
       </c>
       <c r="O32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],O$3),"")</f>
-        <v>6.916666666666667</v>
+        <v>6.9210526315789478</v>
       </c>
       <c r="P32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
@@ -15147,7 +15345,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="36"/>
+      <c r="S32" s="39"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15212,9 +15410,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK32" s="12" t="str">
+      <c r="AK32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AL$3),"")</f>
@@ -15260,7 +15458,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="41"/>
+      <c r="E33" s="37"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -15298,7 +15496,7 @@
       </c>
       <c r="O33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.072289156626506</v>
+        <v>7.068965517241379</v>
       </c>
       <c r="P33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15312,7 +15510,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="37"/>
+      <c r="S33" s="40"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15377,9 +15575,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK33" s="9" t="str">
+      <c r="AK33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -15425,7 +15623,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="39" t="str">
+      <c r="E34" s="35" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -15595,7 +15793,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="40"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -15633,7 +15831,7 @@
       </c>
       <c r="O35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],O$3),"")</f>
-        <v>7.041666666666667</v>
+        <v>7.0394736842105265</v>
       </c>
       <c r="P35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],P$3),"")</f>
@@ -15647,7 +15845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="36"/>
+      <c r="S35" s="39"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15712,9 +15910,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK35" s="12" t="str">
+      <c r="AK35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AL$3),"")</f>
@@ -15760,7 +15958,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="41"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -15798,7 +15996,7 @@
       </c>
       <c r="O36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1807228915662646</v>
+        <v>7.1724137931034484</v>
       </c>
       <c r="P36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15812,7 +16010,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="37"/>
+      <c r="S36" s="40"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15877,9 +16075,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK36" s="9" t="str">
+      <c r="AK36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -15925,7 +16123,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="39" t="str">
+      <c r="E37" s="35" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -16095,7 +16293,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="40"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -16133,7 +16331,7 @@
       </c>
       <c r="O38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],O$3),"")</f>
-        <v>6.2985074626865671</v>
+        <v>6.3285714285714283</v>
       </c>
       <c r="P38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
@@ -16147,7 +16345,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="36"/>
+      <c r="S38" s="39"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16212,9 +16410,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AJ$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="AK38" s="12" t="str">
+      <c r="AK38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AL$3),"")</f>
@@ -16260,7 +16458,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="41"/>
+      <c r="E39" s="37"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -16298,7 +16496,7 @@
       </c>
       <c r="O39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.3974358974358978</v>
+        <v>6.4197530864197532</v>
       </c>
       <c r="P39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16312,7 +16510,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="37"/>
+      <c r="S39" s="40"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16377,9 +16575,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="AK39" s="9" t="str">
+      <c r="AK39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -16425,7 +16623,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="39" t="str">
+      <c r="E40" s="35" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -16595,7 +16793,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="40"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -16633,7 +16831,7 @@
       </c>
       <c r="O41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],O$3),"")</f>
-        <v>8.4074074074074066</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="P41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
@@ -16647,7 +16845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="36"/>
+      <c r="S41" s="39"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16712,9 +16910,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AJ$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AK41" s="12" t="str">
+      <c r="AK41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AL$3),"")</f>
@@ -16760,7 +16958,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="37"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -16798,7 +16996,7 @@
       </c>
       <c r="O42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.3666666666666671</v>
+        <v>8.3015873015873023</v>
       </c>
       <c r="P42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16812,7 +17010,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="37"/>
+      <c r="S42" s="40"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16877,9 +17075,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AK42" s="9" t="str">
+      <c r="AK42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -16925,7 +17123,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="39" t="str">
+      <c r="E43" s="35" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -17095,7 +17293,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="40"/>
+      <c r="E44" s="36"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -17133,7 +17331,7 @@
       </c>
       <c r="O44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],O$3),"")</f>
-        <v>8.4259259259259256</v>
+        <v>8.3508771929824555</v>
       </c>
       <c r="P44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
@@ -17147,7 +17345,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="36"/>
+      <c r="S44" s="39"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17212,9 +17410,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK44" s="12" t="str">
+      <c r="AK44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AL$3),"")</f>
@@ -17260,7 +17458,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="37"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -17298,7 +17496,7 @@
       </c>
       <c r="O45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.4285714285714288</v>
+        <v>8.3559322033898304</v>
       </c>
       <c r="P45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -17312,7 +17510,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="37"/>
+      <c r="S45" s="40"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17377,9 +17575,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AK45" s="9" t="str">
+      <c r="AK45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -17425,7 +17623,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="39" t="str">
+      <c r="E46" s="35" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -17480,7 +17678,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="35">
+      <c r="S46" s="41">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -17595,7 +17793,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="40"/>
+      <c r="E47" s="36"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -17633,7 +17831,7 @@
       </c>
       <c r="O47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.24666666666666667</v>
+        <v>0.25028985507246376</v>
       </c>
       <c r="P47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
@@ -17647,7 +17845,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="36"/>
+      <c r="S47" s="39"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -17711,9 +17909,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="AK47" s="16" t="str">
+      <c r="AK47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.33</v>
       </c>
       <c r="AL47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AL$3)/100,"")</f>
@@ -17759,7 +17957,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="41"/>
+      <c r="E48" s="37"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -17797,7 +17995,7 @@
       </c>
       <c r="O48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28344155844155844</v>
+        <v>0.28518749999999998</v>
       </c>
       <c r="P48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -17811,7 +18009,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="37"/>
+      <c r="S48" s="40"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -17876,9 +18074,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="AK48" s="10" t="str">
+      <c r="AK48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.33</v>
       </c>
       <c r="AL48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
@@ -17924,7 +18122,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="39" t="str">
+      <c r="E49" s="35" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -17979,7 +18177,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="35">
+      <c r="S49" s="41">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -18094,7 +18292,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="40"/>
+      <c r="E50" s="36"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -18132,7 +18330,7 @@
       </c>
       <c r="O50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.1957638888888889</v>
+        <v>0.19703947368421051</v>
       </c>
       <c r="P50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
@@ -18146,7 +18344,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="36"/>
+      <c r="S50" s="39"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -18211,9 +18409,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.24249999999999999</v>
       </c>
-      <c r="AK50" s="16" t="str">
+      <c r="AK50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.22</v>
       </c>
       <c r="AL50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AL$3)/100,"")</f>
@@ -18259,7 +18457,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="41"/>
+      <c r="E51" s="37"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -18297,7 +18495,7 @@
       </c>
       <c r="O51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.20524390243902438</v>
+        <v>0.20593023255813953</v>
       </c>
       <c r="P51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18311,7 +18509,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="37"/>
+      <c r="S51" s="40"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -18376,9 +18574,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.24249999999999999</v>
       </c>
-      <c r="AK51" s="10" t="str">
+      <c r="AK51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.22</v>
       </c>
       <c r="AL51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
@@ -18424,7 +18622,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="39" t="str">
+      <c r="E52" s="35" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -18479,7 +18677,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="35">
+      <c r="S52" s="41">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -18594,7 +18792,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="40"/>
+      <c r="E53" s="36"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -18632,7 +18830,7 @@
       </c>
       <c r="O53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.76126760563380291</v>
+        <v>0.76</v>
       </c>
       <c r="P53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
@@ -18646,7 +18844,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="36"/>
+      <c r="S53" s="39"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -18711,9 +18909,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.76249999999999996</v>
       </c>
-      <c r="AK53" s="16" t="str">
+      <c r="AK53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.73750000000000004</v>
       </c>
       <c r="AL53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AL$3)/100,"")</f>
@@ -18759,7 +18957,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="41"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -18797,7 +18995,7 @@
       </c>
       <c r="O54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.72922077922077921</v>
+        <v>0.72962962962962963</v>
       </c>
       <c r="P54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18811,7 +19009,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="37"/>
+      <c r="S54" s="40"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -18876,9 +19074,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.76249999999999996</v>
       </c>
-      <c r="AK54" s="10" t="str">
+      <c r="AK54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.73750000000000004</v>
       </c>
       <c r="AL54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
@@ -18924,7 +19122,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="39" t="str">
+      <c r="E55" s="35" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -18979,7 +19177,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="35">
+      <c r="S55" s="41">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -19094,7 +19292,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="40"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -19132,7 +19330,7 @@
       </c>
       <c r="O56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28819444444444442</v>
+        <v>0.28421052631578947</v>
       </c>
       <c r="P56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
@@ -19146,7 +19344,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="36"/>
+      <c r="S56" s="39"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -19211,9 +19409,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="AK56" s="16" t="str">
+      <c r="AK56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.21249999999999999</v>
       </c>
       <c r="AL56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AL$3)/100,"")</f>
@@ -19259,7 +19457,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="41"/>
+      <c r="E57" s="37"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -19297,7 +19495,7 @@
       </c>
       <c r="O57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.27763157894736845</v>
+        <v>0.27437499999999998</v>
       </c>
       <c r="P57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -19311,7 +19509,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="37"/>
+      <c r="S57" s="40"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -19376,9 +19574,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AJ$3)/100,"")</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="AK57" s="10" t="str">
+      <c r="AK57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
-        <v/>
+        <v>0.21249999999999999</v>
       </c>
       <c r="AL57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
@@ -19424,7 +19622,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="39" t="str">
+      <c r="E58" s="35" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -19594,7 +19792,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="40"/>
+      <c r="E59" s="36"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -19632,7 +19830,7 @@
       </c>
       <c r="O59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],O$3),"")</f>
-        <v>8.3333333333333339</v>
+        <v>8.3611111111111107</v>
       </c>
       <c r="P59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
@@ -19646,7 +19844,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="36"/>
+      <c r="S59" s="39"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -19711,9 +19909,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AJ$3),"")</f>
         <v>8.3333333333333339</v>
       </c>
-      <c r="AK59" s="12" t="str">
+      <c r="AK59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AL59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AL$3),"")</f>
@@ -19759,7 +19957,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="41"/>
+      <c r="E60" s="37"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -19797,7 +19995,7 @@
       </c>
       <c r="O60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.3333333333333339</v>
+        <v>8.3611111111111107</v>
       </c>
       <c r="P60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -19811,7 +20009,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="37"/>
+      <c r="S60" s="40"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -19876,9 +20074,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AJ$3),"")</f>
         <v>8.3333333333333339</v>
       </c>
-      <c r="AK60" s="9" t="str">
+      <c r="AK60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AK$3),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AL60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AL$3),"")</f>
@@ -20000,24 +20198,24 @@
       <c r="AJ118" t="s">
         <v>516</v>
       </c>
-      <c r="AK118"/>
+      <c r="AK118" t="s">
+        <v>529</v>
+      </c>
       <c r="AL118"/>
       <c r="AM118"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -20034,16 +20232,18 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -20282,7 +20482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL176"/>
+  <dimension ref="A1:AL180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -39423,6 +39623,474 @@
         <v>2814</v>
       </c>
     </row>
+    <row r="177" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B177" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E177" t="s">
+        <v>18</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G177" s="3">
+        <v>2</v>
+      </c>
+      <c r="H177" s="3">
+        <v>7</v>
+      </c>
+      <c r="I177" s="3">
+        <v>7</v>
+      </c>
+      <c r="J177" s="3">
+        <v>7</v>
+      </c>
+      <c r="K177" s="3">
+        <v>5</v>
+      </c>
+      <c r="L177">
+        <v>38</v>
+      </c>
+      <c r="M177">
+        <v>27</v>
+      </c>
+      <c r="N177">
+        <v>62</v>
+      </c>
+      <c r="O177">
+        <v>73</v>
+      </c>
+      <c r="P177" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q177" s="3">
+        <v>7</v>
+      </c>
+      <c r="R177" s="3">
+        <v>7</v>
+      </c>
+      <c r="S177" s="3">
+        <v>7</v>
+      </c>
+      <c r="T177" s="3">
+        <v>7</v>
+      </c>
+      <c r="U177" s="3">
+        <v>7</v>
+      </c>
+      <c r="V177" t="s">
+        <v>20</v>
+      </c>
+      <c r="W177" s="3">
+        <v>7</v>
+      </c>
+      <c r="X177" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y177">
+        <v>73</v>
+      </c>
+      <c r="Z177">
+        <v>36.5</v>
+      </c>
+      <c r="AA177">
+        <v>57</v>
+      </c>
+      <c r="AB177">
+        <v>6</v>
+      </c>
+      <c r="AC177">
+        <v>28.499999999999996</v>
+      </c>
+      <c r="AD177">
+        <v>70</v>
+      </c>
+      <c r="AE177">
+        <v>4</v>
+      </c>
+      <c r="AF177">
+        <v>20</v>
+      </c>
+      <c r="AG177" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH177" s="3">
+        <v>992093</v>
+      </c>
+      <c r="AI177" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ177" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK177" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL177">
+        <v>6358</v>
+      </c>
+    </row>
+    <row r="178" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B178" t="s">
+        <v>530</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E178" t="s">
+        <v>18</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G178" s="3">
+        <v>2</v>
+      </c>
+      <c r="H178" s="3">
+        <v>7</v>
+      </c>
+      <c r="I178" s="3">
+        <v>7</v>
+      </c>
+      <c r="J178" s="3">
+        <v>7</v>
+      </c>
+      <c r="K178" s="3">
+        <v>7</v>
+      </c>
+      <c r="L178">
+        <v>18</v>
+      </c>
+      <c r="M178">
+        <v>24</v>
+      </c>
+      <c r="N178">
+        <v>82</v>
+      </c>
+      <c r="O178">
+        <v>76</v>
+      </c>
+      <c r="P178" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q178" s="3">
+        <v>7</v>
+      </c>
+      <c r="R178" s="3">
+        <v>7</v>
+      </c>
+      <c r="S178" s="3">
+        <v>7</v>
+      </c>
+      <c r="T178" s="3">
+        <v>7</v>
+      </c>
+      <c r="U178" s="3">
+        <v>7</v>
+      </c>
+      <c r="V178" t="s">
+        <v>20</v>
+      </c>
+      <c r="W178" s="3">
+        <v>7</v>
+      </c>
+      <c r="X178" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y178">
+        <v>70</v>
+      </c>
+      <c r="Z178">
+        <v>35</v>
+      </c>
+      <c r="AA178">
+        <v>38</v>
+      </c>
+      <c r="AB178">
+        <v>5</v>
+      </c>
+      <c r="AC178">
+        <v>19</v>
+      </c>
+      <c r="AD178">
+        <v>75</v>
+      </c>
+      <c r="AE178">
+        <v>5</v>
+      </c>
+      <c r="AF178">
+        <v>25</v>
+      </c>
+      <c r="AG178" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH178" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI178" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ178" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK178" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL178">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="179" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B179" t="s">
+        <v>532</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E179" t="s">
+        <v>18</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G179" s="3">
+        <v>2</v>
+      </c>
+      <c r="H179" s="3">
+        <v>7</v>
+      </c>
+      <c r="I179" s="3">
+        <v>7</v>
+      </c>
+      <c r="J179" s="3">
+        <v>7</v>
+      </c>
+      <c r="K179" s="3">
+        <v>5</v>
+      </c>
+      <c r="L179">
+        <v>28</v>
+      </c>
+      <c r="M179">
+        <v>14</v>
+      </c>
+      <c r="N179">
+        <v>72</v>
+      </c>
+      <c r="O179">
+        <v>86</v>
+      </c>
+      <c r="P179" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q179" s="3">
+        <v>7</v>
+      </c>
+      <c r="R179" s="3">
+        <v>7</v>
+      </c>
+      <c r="S179" s="3">
+        <v>7</v>
+      </c>
+      <c r="T179" s="3">
+        <v>7</v>
+      </c>
+      <c r="U179" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V179" t="s">
+        <v>169</v>
+      </c>
+      <c r="W179" s="3">
+        <v>7</v>
+      </c>
+      <c r="X179" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y179">
+        <v>55</v>
+      </c>
+      <c r="Z179">
+        <v>27.500000000000004</v>
+      </c>
+      <c r="AA179">
+        <v>44</v>
+      </c>
+      <c r="AB179">
+        <v>4</v>
+      </c>
+      <c r="AC179">
+        <v>22</v>
+      </c>
+      <c r="AD179">
+        <v>80</v>
+      </c>
+      <c r="AE179">
+        <v>5</v>
+      </c>
+      <c r="AF179">
+        <v>25</v>
+      </c>
+      <c r="AG179" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH179" s="3">
+        <v>13188</v>
+      </c>
+      <c r="AI179" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ179" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK179" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL179">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="180" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B180" t="s">
+        <v>535</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E180" t="s">
+        <v>18</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G180" s="3">
+        <v>2</v>
+      </c>
+      <c r="H180" s="3">
+        <v>7</v>
+      </c>
+      <c r="I180" s="3">
+        <v>7</v>
+      </c>
+      <c r="J180" s="3">
+        <v>7</v>
+      </c>
+      <c r="K180" s="3">
+        <v>5</v>
+      </c>
+      <c r="L180">
+        <v>18</v>
+      </c>
+      <c r="M180">
+        <v>24</v>
+      </c>
+      <c r="N180">
+        <v>82</v>
+      </c>
+      <c r="O180">
+        <v>76</v>
+      </c>
+      <c r="P180" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q180" s="3">
+        <v>7</v>
+      </c>
+      <c r="R180" s="3">
+        <v>5</v>
+      </c>
+      <c r="S180" s="3">
+        <v>7</v>
+      </c>
+      <c r="T180" s="3">
+        <v>7</v>
+      </c>
+      <c r="U180" s="3">
+        <v>7</v>
+      </c>
+      <c r="V180" t="s">
+        <v>169</v>
+      </c>
+      <c r="W180" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X180" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y180" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z180" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA180">
+        <v>37</v>
+      </c>
+      <c r="AB180">
+        <v>6</v>
+      </c>
+      <c r="AC180">
+        <v>18.5</v>
+      </c>
+      <c r="AD180">
+        <v>70</v>
+      </c>
+      <c r="AE180">
+        <v>3</v>
+      </c>
+      <c r="AF180">
+        <v>15</v>
+      </c>
+      <c r="AG180" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH180" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI180" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ180" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK180" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL180">
+        <v>4926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="21" r:id="rId3"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="548">
   <si>
     <t>ID</t>
   </si>
@@ -1697,6 +1697,39 @@
   </si>
   <si>
     <t>28/09/2026 16:36:00</t>
+  </si>
+  <si>
+    <t>6abc9cb798694d34bda8dde7</t>
+  </si>
+  <si>
+    <t>29/09/2026 22:57:58</t>
+  </si>
+  <si>
+    <t>30/09/2026 02:23:03</t>
+  </si>
+  <si>
+    <t>29/09/2026</t>
+  </si>
+  <si>
+    <t>6abc9cb798694d34bda8ddc7</t>
+  </si>
+  <si>
+    <t>29/09/2026 21:29:21</t>
+  </si>
+  <si>
+    <t>6abc9cb698694d34bda8dda3</t>
+  </si>
+  <si>
+    <t>29/09/2026 18:25:22</t>
+  </si>
+  <si>
+    <t>30/09/2026 02:23:02</t>
+  </si>
+  <si>
+    <t>6abc9cb698694d34bda8dd6d</t>
+  </si>
+  <si>
+    <t>29/09/2026 16:30:41</t>
   </si>
 </sst>
 </file>
@@ -2102,6 +2135,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2110,18 +2155,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2476,7 +2509,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46294.380655092595" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="179">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46295.431473379627" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="183">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2507,7 +2540,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="43">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="44">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2551,6 +2584,7 @@
         <s v="23/09/2026"/>
         <s v="25/09/2026"/>
         <s v="28/09/2026"/>
+        <s v="29/09/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2659,7 +2693,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="179">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="183">
   <r>
     <x v="0"/>
     <m/>
@@ -9820,12 +9854,172 @@
     <s v="assinatura"/>
     <n v="4926"/>
   </r>
+  <r>
+    <x v="8"/>
+    <s v="6abc9cb798694d34bda8dde7"/>
+    <s v="29/09/2026 22:57:58"/>
+    <s v="30/09/2026 02:23:03"/>
+    <s v="Ranieli"/>
+    <x v="43"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="21"/>
+    <n v="33"/>
+    <n v="79"/>
+    <n v="67"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="45"/>
+    <n v="22.5"/>
+    <n v="44"/>
+    <n v="8"/>
+    <n v="22"/>
+    <n v="60"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="42854"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="8964"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abc9cb798694d34bda8ddc7"/>
+    <s v="29/09/2026 21:29:21"/>
+    <s v="30/09/2026 02:23:03"/>
+    <s v="Ranieli"/>
+    <x v="43"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="70"/>
+    <n v="71"/>
+    <n v="30"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Retirou a Cartilagem,_x000a_Usou o garfo na retirada de Sassami,_x000a_Riscou o Sassami em X"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="36"/>
+    <n v="18"/>
+    <n v="49"/>
+    <n v="5"/>
+    <n v="24.5"/>
+    <n v="75"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="14121"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abc9cb698694d34bda8dda3"/>
+    <s v="29/09/2026 18:25:22"/>
+    <s v="30/09/2026 02:23:02"/>
+    <s v="Ranieli"/>
+    <x v="43"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="19"/>
+    <n v="31"/>
+    <n v="81"/>
+    <n v="69"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="56"/>
+    <n v="28.000000000000004"/>
+    <n v="45"/>
+    <n v="8"/>
+    <n v="22.5"/>
+    <n v="60"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="7"/>
+    <n v="42846"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="24877"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abc9cb698694d34bda8dd6d"/>
+    <s v="29/09/2026 16:30:41"/>
+    <s v="30/09/2026 02:23:02"/>
+    <s v="Ranieli"/>
+    <x v="43"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="5"/>
+    <n v="43"/>
+    <n v="14"/>
+    <n v="57"/>
+    <n v="86"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="44"/>
+    <n v="22"/>
+    <n v="34"/>
+    <n v="7"/>
+    <n v="17"/>
+    <n v="65"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="31477"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:AK118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="U117:AL118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="10">
@@ -9846,7 +10040,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="44">
+      <items count="45">
         <item x="26"/>
         <item x="28"/>
         <item x="27"/>
@@ -9882,6 +10076,7 @@
         <item x="23"/>
         <item x="24"/>
         <item x="42"/>
+        <item x="43"/>
         <item x="25"/>
         <item x="0"/>
         <item x="1"/>
@@ -9932,7 +10127,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="17">
+  <colItems count="18">
     <i>
       <x/>
     </i>
@@ -9983,6 +10178,9 @@
     </i>
     <i>
       <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -10067,8 +10265,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL180" totalsRowShown="0">
-  <autoFilter ref="A1:AL180"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL184" totalsRowShown="0">
+  <autoFilter ref="A1:AL184"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -10581,7 +10779,7 @@
       </c>
       <c r="AL3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>29/09/2026</v>
       </c>
       <c r="AM3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -10623,7 +10821,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="35" t="str">
+      <c r="E4" s="39" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -10793,7 +10991,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="40"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -10831,7 +11029,7 @@
       </c>
       <c r="O5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],O$3),"")</f>
-        <v>6.9589041095890414</v>
+        <v>6.9090909090909092</v>
       </c>
       <c r="P5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],P$3),"")</f>
@@ -10845,7 +11043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="39"/>
+      <c r="S5" s="36"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -10914,9 +11112,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL5" s="12" t="str">
+      <c r="AL5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AM5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AM$3),"")</f>
@@ -10958,7 +11156,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="37"/>
+      <c r="E6" s="41"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -10996,7 +11194,7 @@
       </c>
       <c r="O6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.9397590361445785</v>
+        <v>6.8965517241379306</v>
       </c>
       <c r="P6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11010,7 +11208,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="40"/>
+      <c r="S6" s="37"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11079,9 +11277,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL6" s="9" t="str">
+      <c r="AL6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AM6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -11123,7 +11321,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="35" t="str">
+      <c r="E7" s="39" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -11293,7 +11491,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="36"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -11331,7 +11529,7 @@
       </c>
       <c r="O8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],O$3),"")</f>
-        <v>7.1184210526315788</v>
+        <v>7.2625000000000002</v>
       </c>
       <c r="P8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
@@ -11345,7 +11543,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="39"/>
+      <c r="S8" s="36"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11414,9 +11612,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL8" s="12" t="str">
+      <c r="AL8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AM$3),"")</f>
@@ -11458,7 +11656,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="37"/>
+      <c r="E9" s="41"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -11496,7 +11694,7 @@
       </c>
       <c r="O9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2528735632183912</v>
+        <v>7.3736263736263732</v>
       </c>
       <c r="P9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11510,7 +11708,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="40"/>
+      <c r="S9" s="37"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11579,9 +11777,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL9" s="9" t="str">
+      <c r="AL9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -11623,7 +11821,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="35" t="str">
+      <c r="E10" s="39" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -11793,7 +11991,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="40"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -11831,7 +12029,7 @@
       </c>
       <c r="O11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],O$3),"")</f>
-        <v>6.9473684210526319</v>
+        <v>6.9249999999999998</v>
       </c>
       <c r="P11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],P$3),"")</f>
@@ -11845,7 +12043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="39"/>
+      <c r="S11" s="36"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11914,9 +12112,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL11" s="12" t="str">
+      <c r="AL11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AM11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AM$3),"")</f>
@@ -11958,7 +12156,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="37"/>
+      <c r="E12" s="41"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -11996,7 +12194,7 @@
       </c>
       <c r="O12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1264367816091951</v>
+        <v>7.0989010989010985</v>
       </c>
       <c r="P12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -12010,7 +12208,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="40"/>
+      <c r="S12" s="37"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12079,9 +12277,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL12" s="9" t="str">
+      <c r="AL12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AM12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -12123,7 +12321,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="35" t="str">
+      <c r="E13" s="39" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -12293,7 +12491,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -12331,7 +12529,7 @@
       </c>
       <c r="O14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],O$3),"")</f>
-        <v>5.3684210526315788</v>
+        <v>5.35</v>
       </c>
       <c r="P14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
@@ -12345,7 +12543,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="39"/>
+      <c r="S14" s="36"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12414,9 +12612,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AK$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="AL14" s="12" t="str">
+      <c r="AL14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AM$3),"")</f>
@@ -12458,7 +12656,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="41"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -12496,7 +12694,7 @@
       </c>
       <c r="O15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>5.5172413793103452</v>
+        <v>5.4945054945054945</v>
       </c>
       <c r="P15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -12510,7 +12708,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="40"/>
+      <c r="S15" s="37"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12579,9 +12777,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="AL15" s="9" t="str">
+      <c r="AL15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -12623,7 +12821,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="35" t="str">
+      <c r="E16" s="39" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -12678,7 +12876,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="41">
+      <c r="S16" s="35">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -12793,7 +12991,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="36"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -12831,7 +13029,7 @@
       </c>
       <c r="O17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.80776315789473685</v>
+        <v>0.80337500000000006</v>
       </c>
       <c r="P17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
@@ -12845,7 +13043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="39"/>
+      <c r="S17" s="36"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -12914,9 +13112,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AK$3)/100,"")</f>
         <v>0.745</v>
       </c>
-      <c r="AL17" s="16" t="str">
+      <c r="AL17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.72</v>
       </c>
       <c r="AM17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AM$3)/100,"")</f>
@@ -12958,7 +13156,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="37"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -12996,7 +13194,7 @@
       </c>
       <c r="O18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.80655172413793108</v>
+        <v>0.80274725274725267</v>
       </c>
       <c r="P18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -13010,7 +13208,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="40"/>
+      <c r="S18" s="37"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -13079,9 +13277,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
         <v>0.745</v>
       </c>
-      <c r="AL18" s="10" t="str">
+      <c r="AL18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.72</v>
       </c>
       <c r="AM18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
@@ -13123,7 +13321,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="35" t="str">
+      <c r="E19" s="39" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -13178,7 +13376,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="41">
+      <c r="S19" s="35">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -13293,7 +13491,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="36"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -13331,7 +13529,7 @@
       </c>
       <c r="O20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63539473684210523</v>
+        <v>0.63512500000000005</v>
       </c>
       <c r="P20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
@@ -13345,7 +13543,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="39"/>
+      <c r="S20" s="36"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13414,9 +13612,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AK$3)/100,"")</f>
         <v>0.77749999999999997</v>
       </c>
-      <c r="AL20" s="16" t="str">
+      <c r="AL20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.63</v>
       </c>
       <c r="AM20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AM$3)/100,"")</f>
@@ -13458,7 +13656,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="37"/>
+      <c r="E21" s="41"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -13496,7 +13694,7 @@
       </c>
       <c r="O21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63793103448275867</v>
+        <v>0.63758241758241763</v>
       </c>
       <c r="P21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -13510,7 +13708,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="40"/>
+      <c r="S21" s="37"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13579,9 +13777,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
         <v>0.77749999999999997</v>
       </c>
-      <c r="AL21" s="10" t="str">
+      <c r="AL21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.63</v>
       </c>
       <c r="AM21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
@@ -13623,7 +13821,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="35" t="str">
+      <c r="E22" s="39" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -13793,7 +13991,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="36"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -13831,7 +14029,7 @@
       </c>
       <c r="O23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],O$3),"")</f>
-        <v>6.7105263157894735</v>
+        <v>6.7</v>
       </c>
       <c r="P23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
@@ -13845,7 +14043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="39"/>
+      <c r="S23" s="36"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -13914,9 +14112,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL23" s="12" t="str">
+      <c r="AL23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AM23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AM$3),"")</f>
@@ -13958,7 +14156,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="37"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -13996,7 +14194,7 @@
       </c>
       <c r="O24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.7816091954022992</v>
+        <v>6.7692307692307692</v>
       </c>
       <c r="P24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14010,7 +14208,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="40"/>
+      <c r="S24" s="37"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -14079,9 +14277,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL24" s="9" t="str">
+      <c r="AL24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AM24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -14123,7 +14321,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="35" t="str">
+      <c r="E25" s="39" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -14293,7 +14491,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="36"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -14331,7 +14529,7 @@
       </c>
       <c r="O26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],O$3),"")</f>
-        <v>6.9066666666666663</v>
+        <v>6.9113924050632916</v>
       </c>
       <c r="P26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
@@ -14345,7 +14543,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="39"/>
+      <c r="S26" s="36"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14414,9 +14612,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL26" s="12" t="str">
+      <c r="AL26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AM$3),"")</f>
@@ -14458,7 +14656,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="37"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -14496,7 +14694,7 @@
       </c>
       <c r="O27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2325581395348841</v>
+        <v>7.2222222222222223</v>
       </c>
       <c r="P27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14510,7 +14708,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="40"/>
+      <c r="S27" s="37"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14579,9 +14777,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL27" s="9" t="str">
+      <c r="AL27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -14623,7 +14821,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="35" t="str">
+      <c r="E28" s="39" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -14793,7 +14991,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="36"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -14831,7 +15029,7 @@
       </c>
       <c r="O29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],O$3),"")</f>
-        <v>6.9736842105263159</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="P29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],P$3),"")</f>
@@ -14845,7 +15043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="39"/>
+      <c r="S29" s="36"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14914,9 +15112,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AK$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AL29" s="12" t="str">
+      <c r="AL29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AM$3),"")</f>
@@ -14958,7 +15156,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="37"/>
+      <c r="E30" s="41"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -14996,7 +15194,7 @@
       </c>
       <c r="O30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.3563218390804597</v>
+        <v>7.3406593406593403</v>
       </c>
       <c r="P30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15010,7 +15208,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="40"/>
+      <c r="S30" s="37"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15079,9 +15277,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AL30" s="9" t="str">
+      <c r="AL30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -15123,7 +15321,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="35" t="str">
+      <c r="E31" s="39" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -15293,7 +15491,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="36"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -15331,7 +15529,7 @@
       </c>
       <c r="O32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],O$3),"")</f>
-        <v>6.9210526315789478</v>
+        <v>6.9249999999999998</v>
       </c>
       <c r="P32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
@@ -15345,7 +15543,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="39"/>
+      <c r="S32" s="36"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15414,9 +15612,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL32" s="12" t="str">
+      <c r="AL32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AM$3),"")</f>
@@ -15458,7 +15656,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="37"/>
+      <c r="E33" s="41"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -15496,7 +15694,7 @@
       </c>
       <c r="O33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.068965517241379</v>
+        <v>7.0659340659340657</v>
       </c>
       <c r="P33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15510,7 +15708,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="40"/>
+      <c r="S33" s="37"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15579,9 +15777,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL33" s="9" t="str">
+      <c r="AL33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -15623,7 +15821,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="35" t="str">
+      <c r="E34" s="39" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -15793,7 +15991,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="36"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -15831,7 +16029,7 @@
       </c>
       <c r="O35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],O$3),"")</f>
-        <v>7.0394736842105265</v>
+        <v>7.0374999999999996</v>
       </c>
       <c r="P35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],P$3),"")</f>
@@ -15845,7 +16043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="39"/>
+      <c r="S35" s="36"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15914,9 +16112,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL35" s="12" t="str">
+      <c r="AL35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AM$3),"")</f>
@@ -15958,7 +16156,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="37"/>
+      <c r="E36" s="41"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -15996,7 +16194,7 @@
       </c>
       <c r="O36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1724137931034484</v>
+        <v>7.1648351648351651</v>
       </c>
       <c r="P36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16010,7 +16208,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="40"/>
+      <c r="S36" s="37"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16079,9 +16277,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL36" s="9" t="str">
+      <c r="AL36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -16123,7 +16321,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="35" t="str">
+      <c r="E37" s="39" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -16293,7 +16491,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="36"/>
+      <c r="E38" s="40"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -16331,7 +16529,7 @@
       </c>
       <c r="O38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],O$3),"")</f>
-        <v>6.3285714285714283</v>
+        <v>6.3378378378378377</v>
       </c>
       <c r="P38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
@@ -16345,7 +16543,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="39"/>
+      <c r="S38" s="36"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16414,9 +16612,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL38" s="12" t="str">
+      <c r="AL38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AM38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AM$3),"")</f>
@@ -16458,7 +16656,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="37"/>
+      <c r="E39" s="41"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -16496,7 +16694,7 @@
       </c>
       <c r="O39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.4197530864197532</v>
+        <v>6.4235294117647062</v>
       </c>
       <c r="P39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16510,7 +16708,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="40"/>
+      <c r="S39" s="37"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16579,9 +16777,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL39" s="9" t="str">
+      <c r="AL39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AM39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -16623,7 +16821,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="35" t="str">
+      <c r="E40" s="39" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -16793,7 +16991,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="36"/>
+      <c r="E41" s="40"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -16831,7 +17029,7 @@
       </c>
       <c r="O41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],O$3),"")</f>
-        <v>8.3333333333333339</v>
+        <v>8.3166666666666664</v>
       </c>
       <c r="P41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
@@ -16845,7 +17043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="39"/>
+      <c r="S41" s="36"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -16914,9 +17112,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL41" s="12" t="str">
+      <c r="AL41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AM41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AM$3),"")</f>
@@ -16958,7 +17156,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="37"/>
+      <c r="E42" s="41"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -16996,7 +17194,7 @@
       </c>
       <c r="O42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.3015873015873023</v>
+        <v>8.2878787878787872</v>
       </c>
       <c r="P42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -17010,7 +17208,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="40"/>
+      <c r="S42" s="37"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17079,9 +17277,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL42" s="9" t="str">
+      <c r="AL42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AM42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -17123,7 +17321,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="35" t="str">
+      <c r="E43" s="39" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -17293,7 +17491,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="36"/>
+      <c r="E44" s="40"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -17331,7 +17529,7 @@
       </c>
       <c r="O44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],O$3),"")</f>
-        <v>8.3508771929824555</v>
+        <v>8.2833333333333332</v>
       </c>
       <c r="P44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
@@ -17345,7 +17543,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="39"/>
+      <c r="S44" s="36"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17414,9 +17612,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL44" s="12" t="str">
+      <c r="AL44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AM$3),"")</f>
@@ -17458,7 +17656,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="37"/>
+      <c r="E45" s="41"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -17496,7 +17694,7 @@
       </c>
       <c r="O45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.3559322033898304</v>
+        <v>8.2903225806451619</v>
       </c>
       <c r="P45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -17510,7 +17708,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="40"/>
+      <c r="S45" s="37"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17579,9 +17777,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AL45" s="9" t="str">
+      <c r="AL45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -17623,7 +17821,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="35" t="str">
+      <c r="E46" s="39" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -17678,7 +17876,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="41">
+      <c r="S46" s="35">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -17793,7 +17991,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="36"/>
+      <c r="E47" s="40"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -17831,7 +18029,7 @@
       </c>
       <c r="O47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.25028985507246376</v>
+        <v>0.24897260273972602</v>
       </c>
       <c r="P47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
@@ -17845,7 +18043,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="39"/>
+      <c r="S47" s="36"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -17913,9 +18111,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AK$3)/100,"")</f>
         <v>0.33</v>
       </c>
-      <c r="AL47" s="16" t="str">
+      <c r="AL47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.22625000000000001</v>
       </c>
       <c r="AM47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AM$3)/100,"")</f>
@@ -17957,7 +18155,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="37"/>
+      <c r="E48" s="41"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -17995,7 +18193,7 @@
       </c>
       <c r="O48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28518749999999998</v>
+        <v>0.2823809523809524</v>
       </c>
       <c r="P48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18009,7 +18207,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="40"/>
+      <c r="S48" s="37"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -18078,9 +18276,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
         <v>0.33</v>
       </c>
-      <c r="AL48" s="10" t="str">
+      <c r="AL48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.22625000000000001</v>
       </c>
       <c r="AM48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
@@ -18122,7 +18320,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="35" t="str">
+      <c r="E49" s="39" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -18177,7 +18375,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="41">
+      <c r="S49" s="35">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -18292,7 +18490,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="36"/>
+      <c r="E50" s="40"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -18330,7 +18528,7 @@
       </c>
       <c r="O50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.19703947368421051</v>
+        <v>0.19793749999999999</v>
       </c>
       <c r="P50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
@@ -18344,7 +18542,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="39"/>
+      <c r="S50" s="36"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -18413,9 +18611,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AK$3)/100,"")</f>
         <v>0.22</v>
       </c>
-      <c r="AL50" s="16" t="str">
+      <c r="AL50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.215</v>
       </c>
       <c r="AM50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AM$3)/100,"")</f>
@@ -18457,7 +18655,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="37"/>
+      <c r="E51" s="41"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -18495,7 +18693,7 @@
       </c>
       <c r="O51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.20593023255813953</v>
+        <v>0.20633333333333334</v>
       </c>
       <c r="P51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18509,7 +18707,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="40"/>
+      <c r="S51" s="37"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -18578,9 +18776,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
         <v>0.22</v>
       </c>
-      <c r="AL51" s="10" t="str">
+      <c r="AL51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.215</v>
       </c>
       <c r="AM51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
@@ -18622,7 +18820,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="35" t="str">
+      <c r="E52" s="39" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -18677,7 +18875,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="41">
+      <c r="S52" s="35">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -18792,7 +18990,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="36"/>
+      <c r="E53" s="40"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -18830,7 +19028,7 @@
       </c>
       <c r="O53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.76</v>
+        <v>0.75443037974683547</v>
       </c>
       <c r="P53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
@@ -18844,7 +19042,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="39"/>
+      <c r="S53" s="36"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -18913,9 +19111,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AK$3)/100,"")</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="AL53" s="16" t="str">
+      <c r="AL53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="AM53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AM$3)/100,"")</f>
@@ -18957,7 +19155,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="37"/>
+      <c r="E54" s="41"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -18995,7 +19193,7 @@
       </c>
       <c r="O54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.72962962962962963</v>
+        <v>0.72588235294117653</v>
       </c>
       <c r="P54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -19009,7 +19207,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="40"/>
+      <c r="S54" s="37"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -19078,9 +19276,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="AL54" s="10" t="str">
+      <c r="AL54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="AM54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
@@ -19122,7 +19320,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="35" t="str">
+      <c r="E55" s="39" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -19177,7 +19375,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="41">
+      <c r="S55" s="35">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -19292,7 +19490,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="36"/>
+      <c r="E56" s="40"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -19330,7 +19528,7 @@
       </c>
       <c r="O56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.28421052631578947</v>
+        <v>0.27875</v>
       </c>
       <c r="P56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
@@ -19344,7 +19542,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="39"/>
+      <c r="S56" s="36"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -19413,9 +19611,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AK$3)/100,"")</f>
         <v>0.21249999999999999</v>
       </c>
-      <c r="AL56" s="16" t="str">
+      <c r="AL56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.17499999999999999</v>
       </c>
       <c r="AM56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AM$3)/100,"")</f>
@@ -19457,7 +19655,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="37"/>
+      <c r="E57" s="41"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -19495,7 +19693,7 @@
       </c>
       <c r="O57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.27437499999999998</v>
+        <v>0.26964285714285713</v>
       </c>
       <c r="P57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -19509,7 +19707,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="40"/>
+      <c r="S57" s="37"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -19578,9 +19776,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AK$3)/100,"")</f>
         <v>0.21249999999999999</v>
       </c>
-      <c r="AL57" s="10" t="str">
+      <c r="AL57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
-        <v/>
+        <v>0.17499999999999999</v>
       </c>
       <c r="AM57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
@@ -19622,7 +19820,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="35" t="str">
+      <c r="E58" s="39" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -19792,7 +19990,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="36"/>
+      <c r="E59" s="40"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -19830,7 +20028,7 @@
       </c>
       <c r="O59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],O$3),"")</f>
-        <v>8.3611111111111107</v>
+        <v>8.3026315789473681</v>
       </c>
       <c r="P59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
@@ -19844,7 +20042,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="39"/>
+      <c r="S59" s="36"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -19913,9 +20111,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AK$3),"")</f>
         <v>9</v>
       </c>
-      <c r="AL59" s="12" t="str">
+      <c r="AL59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7.25</v>
       </c>
       <c r="AM59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AM$3),"")</f>
@@ -19957,7 +20155,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="37"/>
+      <c r="E60" s="41"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -19995,7 +20193,7 @@
       </c>
       <c r="O60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.3611111111111107</v>
+        <v>8.3026315789473681</v>
       </c>
       <c r="P60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -20009,7 +20207,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="40"/>
+      <c r="S60" s="37"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -20078,9 +20276,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AK$3),"")</f>
         <v>9</v>
       </c>
-      <c r="AL60" s="9" t="str">
+      <c r="AL60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AL$3),"")</f>
-        <v/>
+        <v>7.25</v>
       </c>
       <c r="AM60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AM$3),"")</f>
@@ -20201,21 +20399,25 @@
       <c r="AK118" t="s">
         <v>529</v>
       </c>
-      <c r="AL118"/>
+      <c r="AL118" t="s">
+        <v>540</v>
+      </c>
       <c r="AM118"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -20232,18 +20434,16 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -20482,7 +20682,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL180"/>
+  <dimension ref="A1:AL184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -40091,6 +40291,474 @@
         <v>4926</v>
       </c>
     </row>
+    <row r="181" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B181" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E181" t="s">
+        <v>18</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="G181" s="3">
+        <v>2</v>
+      </c>
+      <c r="H181" s="3">
+        <v>5</v>
+      </c>
+      <c r="I181" s="3">
+        <v>10</v>
+      </c>
+      <c r="J181" s="3">
+        <v>7</v>
+      </c>
+      <c r="K181" s="3">
+        <v>5</v>
+      </c>
+      <c r="L181">
+        <v>21</v>
+      </c>
+      <c r="M181">
+        <v>33</v>
+      </c>
+      <c r="N181">
+        <v>79</v>
+      </c>
+      <c r="O181">
+        <v>67</v>
+      </c>
+      <c r="P181" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q181" s="3">
+        <v>7</v>
+      </c>
+      <c r="R181" s="3">
+        <v>7</v>
+      </c>
+      <c r="S181" s="3">
+        <v>7</v>
+      </c>
+      <c r="T181" s="3">
+        <v>7</v>
+      </c>
+      <c r="U181" s="3">
+        <v>7</v>
+      </c>
+      <c r="V181" t="s">
+        <v>169</v>
+      </c>
+      <c r="W181" s="3">
+        <v>7</v>
+      </c>
+      <c r="X181" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y181">
+        <v>45</v>
+      </c>
+      <c r="Z181">
+        <v>22.5</v>
+      </c>
+      <c r="AA181">
+        <v>44</v>
+      </c>
+      <c r="AB181">
+        <v>8</v>
+      </c>
+      <c r="AC181">
+        <v>22</v>
+      </c>
+      <c r="AD181">
+        <v>60</v>
+      </c>
+      <c r="AE181">
+        <v>4</v>
+      </c>
+      <c r="AF181">
+        <v>20</v>
+      </c>
+      <c r="AG181" s="3">
+        <v>5</v>
+      </c>
+      <c r="AH181" s="3">
+        <v>42854</v>
+      </c>
+      <c r="AI181" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ181" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK181" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL181">
+        <v>8964</v>
+      </c>
+    </row>
+    <row r="182" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B182" t="s">
+        <v>541</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E182" t="s">
+        <v>18</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="G182" s="3">
+        <v>2</v>
+      </c>
+      <c r="H182" s="3">
+        <v>5</v>
+      </c>
+      <c r="I182" s="3">
+        <v>10</v>
+      </c>
+      <c r="J182" s="3">
+        <v>7</v>
+      </c>
+      <c r="K182" s="3">
+        <v>5</v>
+      </c>
+      <c r="L182">
+        <v>29</v>
+      </c>
+      <c r="M182">
+        <v>70</v>
+      </c>
+      <c r="N182">
+        <v>71</v>
+      </c>
+      <c r="O182">
+        <v>30</v>
+      </c>
+      <c r="P182" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q182" s="3">
+        <v>7</v>
+      </c>
+      <c r="R182" s="3">
+        <v>7</v>
+      </c>
+      <c r="S182" s="3">
+        <v>7</v>
+      </c>
+      <c r="T182" s="3">
+        <v>7</v>
+      </c>
+      <c r="U182" s="3">
+        <v>5</v>
+      </c>
+      <c r="V182" t="s">
+        <v>522</v>
+      </c>
+      <c r="W182" s="3">
+        <v>7</v>
+      </c>
+      <c r="X182" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y182">
+        <v>36</v>
+      </c>
+      <c r="Z182">
+        <v>18</v>
+      </c>
+      <c r="AA182">
+        <v>49</v>
+      </c>
+      <c r="AB182">
+        <v>5</v>
+      </c>
+      <c r="AC182">
+        <v>24.5</v>
+      </c>
+      <c r="AD182">
+        <v>75</v>
+      </c>
+      <c r="AE182">
+        <v>3</v>
+      </c>
+      <c r="AF182">
+        <v>15</v>
+      </c>
+      <c r="AG182" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH182" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI182" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ182" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK182" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL182">
+        <v>14121</v>
+      </c>
+    </row>
+    <row r="183" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B183" t="s">
+        <v>543</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E183" t="s">
+        <v>18</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="G183" s="3">
+        <v>2</v>
+      </c>
+      <c r="H183" s="3">
+        <v>7</v>
+      </c>
+      <c r="I183" s="3">
+        <v>10</v>
+      </c>
+      <c r="J183" s="3">
+        <v>7</v>
+      </c>
+      <c r="K183" s="3">
+        <v>5</v>
+      </c>
+      <c r="L183">
+        <v>19</v>
+      </c>
+      <c r="M183">
+        <v>31</v>
+      </c>
+      <c r="N183">
+        <v>81</v>
+      </c>
+      <c r="O183">
+        <v>69</v>
+      </c>
+      <c r="P183" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q183" s="3">
+        <v>7</v>
+      </c>
+      <c r="R183" s="3">
+        <v>7</v>
+      </c>
+      <c r="S183" s="3">
+        <v>7</v>
+      </c>
+      <c r="T183" s="3">
+        <v>7</v>
+      </c>
+      <c r="U183" s="3">
+        <v>7</v>
+      </c>
+      <c r="V183" t="s">
+        <v>20</v>
+      </c>
+      <c r="W183" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X183" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y183">
+        <v>56</v>
+      </c>
+      <c r="Z183">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="AA183">
+        <v>45</v>
+      </c>
+      <c r="AB183">
+        <v>8</v>
+      </c>
+      <c r="AC183">
+        <v>22.5</v>
+      </c>
+      <c r="AD183">
+        <v>60</v>
+      </c>
+      <c r="AE183">
+        <v>3</v>
+      </c>
+      <c r="AF183">
+        <v>15</v>
+      </c>
+      <c r="AG183" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH183" s="3">
+        <v>42846</v>
+      </c>
+      <c r="AI183" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ183" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK183" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL183">
+        <v>24877</v>
+      </c>
+    </row>
+    <row r="184" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B184" t="s">
+        <v>546</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E184" t="s">
+        <v>18</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="G184" s="3">
+        <v>2</v>
+      </c>
+      <c r="H184" s="3">
+        <v>7</v>
+      </c>
+      <c r="I184" s="3">
+        <v>10</v>
+      </c>
+      <c r="J184" s="3">
+        <v>5</v>
+      </c>
+      <c r="K184" s="3">
+        <v>5</v>
+      </c>
+      <c r="L184">
+        <v>43</v>
+      </c>
+      <c r="M184">
+        <v>14</v>
+      </c>
+      <c r="N184">
+        <v>57</v>
+      </c>
+      <c r="O184">
+        <v>86</v>
+      </c>
+      <c r="P184" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q184" s="3">
+        <v>7</v>
+      </c>
+      <c r="R184" s="3">
+        <v>7</v>
+      </c>
+      <c r="S184" s="3">
+        <v>7</v>
+      </c>
+      <c r="T184" s="3">
+        <v>7</v>
+      </c>
+      <c r="U184" s="3">
+        <v>7</v>
+      </c>
+      <c r="V184" t="s">
+        <v>169</v>
+      </c>
+      <c r="W184" s="3">
+        <v>10</v>
+      </c>
+      <c r="X184" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y184">
+        <v>44</v>
+      </c>
+      <c r="Z184">
+        <v>22</v>
+      </c>
+      <c r="AA184">
+        <v>34</v>
+      </c>
+      <c r="AB184">
+        <v>7</v>
+      </c>
+      <c r="AC184">
+        <v>17</v>
+      </c>
+      <c r="AD184">
+        <v>65</v>
+      </c>
+      <c r="AE184">
+        <v>4</v>
+      </c>
+      <c r="AF184">
+        <v>20</v>
+      </c>
+      <c r="AG184" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH184" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI184" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ184" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK184" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL184">
+        <v>31477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="560">
   <si>
     <t>ID</t>
   </si>
@@ -1730,6 +1730,42 @@
   </si>
   <si>
     <t>29/09/2026 16:30:41</t>
+  </si>
+  <si>
+    <t>6abdeedbfa7807c931a7e3da</t>
+  </si>
+  <si>
+    <t>30/09/2026 22:49:18</t>
+  </si>
+  <si>
+    <t>01/10/2026 02:25:47</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
+  </si>
+  <si>
+    <t>6abdeedbfa7807c931a7e3b6</t>
+  </si>
+  <si>
+    <t>30/09/2026 21:38:27</t>
+  </si>
+  <si>
+    <t>6abdeedafa7807c931a7e384</t>
+  </si>
+  <si>
+    <t>30/09/2026 18:21:27</t>
+  </si>
+  <si>
+    <t>01/10/2026 02:25:46</t>
+  </si>
+  <si>
+    <t>6abdeed9fa7807c931a7e35a</t>
+  </si>
+  <si>
+    <t>30/09/2026 16:17:37</t>
+  </si>
+  <si>
+    <t>01/10/2026 02:25:45</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2171,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2144,17 +2189,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2509,7 +2545,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46295.431473379627" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="183">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46296.452924074074" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="187">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2540,7 +2576,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="44">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="45">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2585,6 +2621,7 @@
         <s v="25/09/2026"/>
         <s v="28/09/2026"/>
         <s v="29/09/2026"/>
+        <s v="30/09/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2693,7 +2730,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="183">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="187">
   <r>
     <x v="0"/>
     <m/>
@@ -10014,12 +10051,172 @@
     <s v="assinatura"/>
     <n v="31477"/>
   </r>
+  <r>
+    <x v="8"/>
+    <s v="6abdeedbfa7807c931a7e3da"/>
+    <s v="30/09/2026 22:49:18"/>
+    <s v="01/10/2026 02:25:47"/>
+    <s v="Ranieli"/>
+    <x v="44"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="38"/>
+    <n v="71"/>
+    <n v="62"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="52"/>
+    <n v="26"/>
+    <n v="57"/>
+    <n v="6"/>
+    <n v="28.499999999999996"/>
+    <n v="70"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="8910"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abdeedbfa7807c931a7e3b6"/>
+    <s v="30/09/2026 21:38:27"/>
+    <s v="01/10/2026 02:25:47"/>
+    <s v="Ranieli"/>
+    <x v="44"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="46"/>
+    <n v="75"/>
+    <n v="54"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="46"/>
+    <n v="4"/>
+    <n v="23"/>
+    <n v="80"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="10"/>
+    <n v="13188"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="13013"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abdeedafa7807c931a7e384"/>
+    <s v="30/09/2026 18:21:27"/>
+    <s v="01/10/2026 02:25:46"/>
+    <s v="Ranieli"/>
+    <x v="44"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="46"/>
+    <n v="71"/>
+    <n v="54"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="47"/>
+    <n v="23.5"/>
+    <n v="44"/>
+    <n v="5"/>
+    <n v="22"/>
+    <n v="75"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="42846"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="24684"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="6abdeed9fa7807c931a7e35a"/>
+    <s v="30/09/2026 16:17:37"/>
+    <s v="01/10/2026 02:25:45"/>
+    <s v="Ranieli"/>
+    <x v="44"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="5"/>
+    <n v="22"/>
+    <n v="53"/>
+    <n v="78"/>
+    <n v="47"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="53"/>
+    <n v="26.5"/>
+    <n v="49"/>
+    <n v="6"/>
+    <n v="24.5"/>
+    <n v="70"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="10"/>
+    <n v="995638"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="31981"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:AL118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+  <location ref="U117:AM118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="10">
@@ -10040,7 +10237,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="45">
+      <items count="46">
         <item x="26"/>
         <item x="28"/>
         <item x="27"/>
@@ -10077,6 +10274,7 @@
         <item x="24"/>
         <item x="42"/>
         <item x="43"/>
+        <item x="44"/>
         <item x="25"/>
         <item x="0"/>
         <item x="1"/>
@@ -10127,7 +10325,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="18">
+  <colItems count="19">
     <i>
       <x/>
     </i>
@@ -10181,6 +10379,9 @@
     </i>
     <i>
       <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -10265,8 +10466,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL184" totalsRowShown="0">
-  <autoFilter ref="A1:AL184"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL188" totalsRowShown="0">
+  <autoFilter ref="A1:AL188"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -10783,7 +10984,7 @@
       </c>
       <c r="AM3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>30/09/2026</v>
       </c>
       <c r="AN3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -10821,7 +11022,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="39" t="str">
+      <c r="E4" s="35" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -10991,7 +11192,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="40"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -11029,7 +11230,7 @@
       </c>
       <c r="O5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],O$3),"")</f>
-        <v>6.9090909090909092</v>
+        <v>6.9135802469135799</v>
       </c>
       <c r="P5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],P$3),"")</f>
@@ -11043,7 +11244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="36"/>
+      <c r="S5" s="39"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11116,9 +11317,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AL$3),"")</f>
         <v>6</v>
       </c>
-      <c r="AM5" s="12" t="str">
+      <c r="AM5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AN$3),"")</f>
@@ -11156,7 +11357,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="37"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -11194,7 +11395,7 @@
       </c>
       <c r="O6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.8965517241379306</v>
+        <v>6.9010989010989015</v>
       </c>
       <c r="P6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11208,7 +11409,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="37"/>
+      <c r="S6" s="40"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11281,9 +11482,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>6</v>
       </c>
-      <c r="AM6" s="9" t="str">
+      <c r="AM6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -11321,7 +11522,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="39" t="str">
+      <c r="E7" s="35" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -11491,7 +11692,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -11529,7 +11730,7 @@
       </c>
       <c r="O8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],O$3),"")</f>
-        <v>7.2625000000000002</v>
+        <v>7.2857142857142856</v>
       </c>
       <c r="P8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
@@ -11543,7 +11744,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="36"/>
+      <c r="S8" s="39"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11616,9 +11817,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AL$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AM8" s="12" t="str">
+      <c r="AM8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7.75</v>
       </c>
       <c r="AN8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AN$3),"")</f>
@@ -11656,7 +11857,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="41"/>
+      <c r="E9" s="37"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -11694,7 +11895,7 @@
       </c>
       <c r="O9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.3736263736263732</v>
+        <v>7.3894736842105262</v>
       </c>
       <c r="P9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -11708,7 +11909,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="37"/>
+      <c r="S9" s="40"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11781,9 +11982,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>10</v>
       </c>
-      <c r="AM9" s="9" t="str">
+      <c r="AM9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7.75</v>
       </c>
       <c r="AN9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -11821,7 +12022,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="39" t="str">
+      <c r="E10" s="35" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -11991,7 +12192,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="40"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -12029,7 +12230,7 @@
       </c>
       <c r="O11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],O$3),"")</f>
-        <v>6.9249999999999998</v>
+        <v>6.9047619047619051</v>
       </c>
       <c r="P11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],P$3),"")</f>
@@ -12043,7 +12244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="36"/>
+      <c r="S11" s="39"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12116,9 +12317,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AL$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AM11" s="12" t="str">
+      <c r="AM11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AN11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AN$3),"")</f>
@@ -12156,7 +12357,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="41"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -12194,7 +12395,7 @@
       </c>
       <c r="O12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0989010989010985</v>
+        <v>7.0736842105263156</v>
       </c>
       <c r="P12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -12208,7 +12409,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="37"/>
+      <c r="S12" s="40"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12281,9 +12482,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AM12" s="9" t="str">
+      <c r="AM12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AN12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -12321,7 +12522,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="39" t="str">
+      <c r="E13" s="35" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -12491,7 +12692,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="40"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -12529,7 +12730,7 @@
       </c>
       <c r="O14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],O$3),"")</f>
-        <v>5.35</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="P14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
@@ -12543,7 +12744,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="36"/>
+      <c r="S14" s="39"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12616,9 +12817,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AL$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AM14" s="12" t="str">
+      <c r="AM14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AN14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AN$3),"")</f>
@@ -12656,7 +12857,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="41"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -12694,7 +12895,7 @@
       </c>
       <c r="O15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>5.4945054945054945</v>
+        <v>5.4736842105263159</v>
       </c>
       <c r="P15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -12708,7 +12909,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="37"/>
+      <c r="S15" s="40"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -12781,9 +12982,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>5</v>
       </c>
-      <c r="AM15" s="9" t="str">
+      <c r="AM15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AN15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -12821,7 +13022,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="39" t="str">
+      <c r="E16" s="35" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -12876,7 +13077,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="41">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -12991,7 +13192,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="40"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -13029,7 +13230,7 @@
       </c>
       <c r="O17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.80337500000000006</v>
+        <v>0.80023809523809519</v>
       </c>
       <c r="P17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
@@ -13043,7 +13244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="36"/>
+      <c r="S17" s="39"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -13116,9 +13317,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AL$3)/100,"")</f>
         <v>0.72</v>
       </c>
-      <c r="AM17" s="16" t="str">
+      <c r="AM17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.73750000000000004</v>
       </c>
       <c r="AN17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AN$3)/100,"")</f>
@@ -13156,7 +13357,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="41"/>
+      <c r="E18" s="37"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -13194,7 +13395,7 @@
       </c>
       <c r="O18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.80274725274725267</v>
+        <v>0.8</v>
       </c>
       <c r="P18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -13208,7 +13409,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="37"/>
+      <c r="S18" s="40"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.78249999999999997</v>
@@ -13281,9 +13482,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
         <v>0.72</v>
       </c>
-      <c r="AM18" s="10" t="str">
+      <c r="AM18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.73750000000000004</v>
       </c>
       <c r="AN18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AN$3)/100,"")</f>
@@ -13321,7 +13522,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="39" t="str">
+      <c r="E19" s="35" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -13376,7 +13577,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="41">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -13491,7 +13692,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="40"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -13529,7 +13730,7 @@
       </c>
       <c r="O20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63512500000000005</v>
+        <v>0.63071428571428567</v>
       </c>
       <c r="P20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
@@ -13543,7 +13744,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="36"/>
+      <c r="S20" s="39"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13616,9 +13817,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AL$3)/100,"")</f>
         <v>0.63</v>
       </c>
-      <c r="AM20" s="16" t="str">
+      <c r="AM20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.54249999999999998</v>
       </c>
       <c r="AN20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AN$3)/100,"")</f>
@@ -13656,7 +13857,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="41"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -13694,7 +13895,7 @@
       </c>
       <c r="O21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.63758241758241763</v>
+        <v>0.63357894736842102</v>
       </c>
       <c r="P21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -13708,7 +13909,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="37"/>
+      <c r="S21" s="40"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.65500000000000003</v>
@@ -13781,9 +13982,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
         <v>0.63</v>
       </c>
-      <c r="AM21" s="10" t="str">
+      <c r="AM21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.54249999999999998</v>
       </c>
       <c r="AN21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AN$3)/100,"")</f>
@@ -13821,7 +14022,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="39" t="str">
+      <c r="E22" s="35" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -13991,7 +14192,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="40"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -14029,7 +14230,7 @@
       </c>
       <c r="O23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],O$3),"")</f>
-        <v>6.7</v>
+        <v>6.6428571428571432</v>
       </c>
       <c r="P23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
@@ -14043,7 +14244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="36"/>
+      <c r="S23" s="39"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -14116,9 +14317,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AL$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AM23" s="12" t="str">
+      <c r="AM23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AN23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AN$3),"")</f>
@@ -14156,7 +14357,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="41"/>
+      <c r="E24" s="37"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -14194,7 +14395,7 @@
       </c>
       <c r="O24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.7692307692307692</v>
+        <v>6.7157894736842101</v>
       </c>
       <c r="P24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14208,7 +14409,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="37"/>
+      <c r="S24" s="40"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -14281,9 +14482,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AM24" s="9" t="str">
+      <c r="AM24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="AN24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -14321,7 +14522,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="39" t="str">
+      <c r="E25" s="35" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -14491,7 +14692,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="40"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -14529,7 +14730,7 @@
       </c>
       <c r="O26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],O$3),"")</f>
-        <v>6.9113924050632916</v>
+        <v>6.9156626506024095</v>
       </c>
       <c r="P26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
@@ -14543,7 +14744,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="36"/>
+      <c r="S26" s="39"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14616,9 +14817,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM26" s="12" t="str">
+      <c r="AM26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AN$3),"")</f>
@@ -14656,7 +14857,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="41"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -14694,7 +14895,7 @@
       </c>
       <c r="O27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.2222222222222223</v>
+        <v>7.2127659574468082</v>
       </c>
       <c r="P27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -14708,7 +14909,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="37"/>
+      <c r="S27" s="40"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -14781,9 +14982,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM27" s="9" t="str">
+      <c r="AM27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -14821,7 +15022,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="39" t="str">
+      <c r="E28" s="35" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -14991,7 +15192,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="40"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -15029,7 +15230,7 @@
       </c>
       <c r="O29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],O$3),"")</f>
-        <v>6.9749999999999996</v>
+        <v>6.9761904761904763</v>
       </c>
       <c r="P29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],P$3),"")</f>
@@ -15043,7 +15244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="36"/>
+      <c r="S29" s="39"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15116,9 +15317,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM29" s="12" t="str">
+      <c r="AM29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AN$3),"")</f>
@@ -15156,7 +15357,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="37"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -15194,7 +15395,7 @@
       </c>
       <c r="O30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.3406593406593403</v>
+        <v>7.3263157894736839</v>
       </c>
       <c r="P30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15208,7 +15409,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="37"/>
+      <c r="S30" s="40"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15281,9 +15482,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM30" s="9" t="str">
+      <c r="AM30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -15321,7 +15522,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="39" t="str">
+      <c r="E31" s="35" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -15491,7 +15692,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="40"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -15529,7 +15730,7 @@
       </c>
       <c r="O32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],O$3),"")</f>
-        <v>6.9249999999999998</v>
+        <v>6.9285714285714288</v>
       </c>
       <c r="P32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
@@ -15543,7 +15744,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="36"/>
+      <c r="S32" s="39"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15616,9 +15817,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM32" s="12" t="str">
+      <c r="AM32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AN$3),"")</f>
@@ -15656,7 +15857,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="41"/>
+      <c r="E33" s="37"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -15694,7 +15895,7 @@
       </c>
       <c r="O33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.0659340659340657</v>
+        <v>7.0631578947368423</v>
       </c>
       <c r="P33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -15708,7 +15909,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="37"/>
+      <c r="S33" s="40"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -15781,9 +15982,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM33" s="9" t="str">
+      <c r="AM33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -15821,7 +16022,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="39" t="str">
+      <c r="E34" s="35" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -15991,7 +16192,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="40"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -16029,7 +16230,7 @@
       </c>
       <c r="O35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],O$3),"")</f>
-        <v>7.0374999999999996</v>
+        <v>7.0357142857142856</v>
       </c>
       <c r="P35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],P$3),"")</f>
@@ -16043,7 +16244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="36"/>
+      <c r="S35" s="39"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16116,9 +16317,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM35" s="12" t="str">
+      <c r="AM35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AN$3),"")</f>
@@ -16156,7 +16357,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="41"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -16194,7 +16395,7 @@
       </c>
       <c r="O36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>7.1648351648351651</v>
+        <v>7.1578947368421053</v>
       </c>
       <c r="P36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16208,7 +16409,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="37"/>
+      <c r="S36" s="40"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16281,9 +16482,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM36" s="9" t="str">
+      <c r="AM36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -16321,7 +16522,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="39" t="str">
+      <c r="E37" s="35" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -16491,7 +16692,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="40"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -16529,7 +16730,7 @@
       </c>
       <c r="O38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],O$3),"")</f>
-        <v>6.3378378378378377</v>
+        <v>6.3636363636363633</v>
       </c>
       <c r="P38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
@@ -16543,7 +16744,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="36"/>
+      <c r="S38" s="39"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16616,9 +16817,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AL$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AM38" s="12" t="str">
+      <c r="AM38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AN$3),"")</f>
@@ -16656,7 +16857,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="41"/>
+      <c r="E39" s="37"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -16694,7 +16895,7 @@
       </c>
       <c r="O39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>6.4235294117647062</v>
+        <v>6.4431818181818183</v>
       </c>
       <c r="P39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -16708,7 +16909,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="37"/>
+      <c r="S39" s="40"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5</v>
@@ -16781,9 +16982,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AM39" s="9" t="str">
+      <c r="AM39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -16821,7 +17022,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="39" t="str">
+      <c r="E40" s="35" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -16991,7 +17192,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="40"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -17029,7 +17230,7 @@
       </c>
       <c r="O41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],O$3),"")</f>
-        <v>8.3166666666666664</v>
+        <v>8.2539682539682548</v>
       </c>
       <c r="P41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
@@ -17043,7 +17244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="36"/>
+      <c r="S41" s="39"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17116,9 +17317,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AL$3),"")</f>
         <v>8</v>
       </c>
-      <c r="AM41" s="12" t="str">
+      <c r="AM41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AN$3),"")</f>
@@ -17156,7 +17357,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="37"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -17194,7 +17395,7 @@
       </c>
       <c r="O42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.2878787878787872</v>
+        <v>8.2318840579710137</v>
       </c>
       <c r="P42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -17208,7 +17409,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="37"/>
+      <c r="S42" s="40"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17281,9 +17482,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>8</v>
       </c>
-      <c r="AM42" s="9" t="str">
+      <c r="AM42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -17321,7 +17522,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="39" t="str">
+      <c r="E43" s="35" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -17491,7 +17692,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="40"/>
+      <c r="E44" s="36"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -17529,7 +17730,7 @@
       </c>
       <c r="O44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],O$3),"")</f>
-        <v>8.2833333333333332</v>
+        <v>8.2698412698412707</v>
       </c>
       <c r="P44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
@@ -17543,7 +17744,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="36"/>
+      <c r="S44" s="39"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17616,9 +17817,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM44" s="12" t="str">
+      <c r="AM44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AN44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AN$3),"")</f>
@@ -17656,7 +17857,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="37"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -17694,7 +17895,7 @@
       </c>
       <c r="O45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.2903225806451619</v>
+        <v>8.2769230769230777</v>
       </c>
       <c r="P45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -17708,7 +17909,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="37"/>
+      <c r="S45" s="40"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -17781,9 +17982,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AM45" s="9" t="str">
+      <c r="AM45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AN45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -17821,7 +18022,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="39" t="str">
+      <c r="E46" s="35" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -17876,7 +18077,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="35">
+      <c r="S46" s="41">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -17991,7 +18192,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="40"/>
+      <c r="E47" s="36"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -18029,7 +18230,7 @@
       </c>
       <c r="O47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.24897260273972602</v>
+        <v>0.24980519480519481</v>
       </c>
       <c r="P47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
@@ -18043,7 +18244,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="36"/>
+      <c r="S47" s="39"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -18115,9 +18316,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AL$3)/100,"")</f>
         <v>0.22625000000000001</v>
       </c>
-      <c r="AM47" s="16" t="str">
+      <c r="AM47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.26500000000000001</v>
       </c>
       <c r="AN47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AN$3)/100,"")</f>
@@ -18155,7 +18356,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="41"/>
+      <c r="E48" s="37"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -18193,7 +18394,7 @@
       </c>
       <c r="O48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.2823809523809524</v>
+        <v>0.28159090909090911</v>
       </c>
       <c r="P48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18207,7 +18408,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="37"/>
+      <c r="S48" s="40"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.21</v>
@@ -18280,9 +18481,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
         <v>0.22625000000000001</v>
       </c>
-      <c r="AM48" s="10" t="str">
+      <c r="AM48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.26500000000000001</v>
       </c>
       <c r="AN48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AN$3)/100,"")</f>
@@ -18320,7 +18521,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="39" t="str">
+      <c r="E49" s="35" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -18375,7 +18576,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="35">
+      <c r="S49" s="41">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -18490,7 +18691,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="40"/>
+      <c r="E50" s="36"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -18528,7 +18729,7 @@
       </c>
       <c r="O50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.19793749999999999</v>
+        <v>0.20017857142857143</v>
       </c>
       <c r="P50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
@@ -18542,7 +18743,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="36"/>
+      <c r="S50" s="39"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -18615,9 +18816,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AL$3)/100,"")</f>
         <v>0.215</v>
       </c>
-      <c r="AM50" s="16" t="str">
+      <c r="AM50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.245</v>
       </c>
       <c r="AN50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AN$3)/100,"")</f>
@@ -18655,7 +18856,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="41"/>
+      <c r="E51" s="37"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -18693,7 +18894,7 @@
       </c>
       <c r="O51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.20633333333333334</v>
+        <v>0.2079787234042553</v>
       </c>
       <c r="P51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -18707,7 +18908,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="37"/>
+      <c r="S51" s="40"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.20624999999999999</v>
@@ -18780,9 +18981,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
         <v>0.215</v>
       </c>
-      <c r="AM51" s="10" t="str">
+      <c r="AM51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.245</v>
       </c>
       <c r="AN51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AN$3)/100,"")</f>
@@ -18820,7 +19021,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="39" t="str">
+      <c r="E52" s="35" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -18875,7 +19076,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="35">
+      <c r="S52" s="41">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -18990,7 +19191,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="40"/>
+      <c r="E53" s="36"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -19028,7 +19229,7 @@
       </c>
       <c r="O53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.75443037974683547</v>
+        <v>0.75361445783132519</v>
       </c>
       <c r="P53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
@@ -19042,7 +19243,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="36"/>
+      <c r="S53" s="39"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -19115,9 +19316,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AL$3)/100,"")</f>
         <v>0.65</v>
       </c>
-      <c r="AM53" s="16" t="str">
+      <c r="AM53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.73750000000000004</v>
       </c>
       <c r="AN53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AN$3)/100,"")</f>
@@ -19155,7 +19356,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="41"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -19193,7 +19394,7 @@
       </c>
       <c r="O54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.72588235294117653</v>
+        <v>0.72640449438202248</v>
       </c>
       <c r="P54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -19207,7 +19408,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="37"/>
+      <c r="S54" s="40"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.76249999999999996</v>
@@ -19280,9 +19481,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
         <v>0.65</v>
       </c>
-      <c r="AM54" s="10" t="str">
+      <c r="AM54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.73750000000000004</v>
       </c>
       <c r="AN54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AN$3)/100,"")</f>
@@ -19320,7 +19521,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="39" t="str">
+      <c r="E55" s="35" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -19375,7 +19576,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="35">
+      <c r="S55" s="41">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -19490,7 +19691,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="40"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -19528,7 +19729,7 @@
       </c>
       <c r="O56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.27875</v>
+        <v>0.27380952380952378</v>
       </c>
       <c r="P56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
@@ -19542,7 +19743,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="36"/>
+      <c r="S56" s="39"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -19615,9 +19816,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AL$3)/100,"")</f>
         <v>0.17499999999999999</v>
       </c>
-      <c r="AM56" s="16" t="str">
+      <c r="AM56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.17499999999999999</v>
       </c>
       <c r="AN56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AN$3)/100,"")</f>
@@ -19655,7 +19856,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="41"/>
+      <c r="E57" s="37"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -19693,7 +19894,7 @@
       </c>
       <c r="O57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],O$3)/100,"")</f>
-        <v>0.26964285714285713</v>
+        <v>0.26534090909090913</v>
       </c>
       <c r="P57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
@@ -19707,7 +19908,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="37"/>
+      <c r="S57" s="40"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.27500000000000002</v>
@@ -19780,9 +19981,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AL$3)/100,"")</f>
         <v>0.17499999999999999</v>
       </c>
-      <c r="AM57" s="10" t="str">
+      <c r="AM57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AM$3)/100,"")</f>
-        <v/>
+        <v>0.17499999999999999</v>
       </c>
       <c r="AN57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AN$3)/100,"")</f>
@@ -19820,7 +20021,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="39" t="str">
+      <c r="E58" s="35" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -19990,7 +20191,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="40"/>
+      <c r="E59" s="36"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -20028,7 +20229,7 @@
       </c>
       <c r="O59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],O$3),"")</f>
-        <v>8.3026315789473681</v>
+        <v>8.3125</v>
       </c>
       <c r="P59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
@@ -20042,7 +20243,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="36"/>
+      <c r="S59" s="39"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -20115,9 +20316,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AL$3),"")</f>
         <v>7.25</v>
       </c>
-      <c r="AM59" s="12" t="str">
+      <c r="AM59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AN59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AN$3),"")</f>
@@ -20155,7 +20356,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="41"/>
+      <c r="E60" s="37"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -20193,7 +20394,7 @@
       </c>
       <c r="O60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],O$3),"")</f>
-        <v>8.3026315789473681</v>
+        <v>8.3125</v>
       </c>
       <c r="P60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
@@ -20207,7 +20408,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="37"/>
+      <c r="S60" s="40"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -20280,9 +20481,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AL$3),"")</f>
         <v>7.25</v>
       </c>
-      <c r="AM60" s="9" t="str">
+      <c r="AM60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AM$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AN60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AN$3),"")</f>
@@ -20402,22 +20603,22 @@
       <c r="AL118" t="s">
         <v>540</v>
       </c>
-      <c r="AM118"/>
+      <c r="AM118" t="s">
+        <v>551</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -20434,16 +20635,18 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -20682,7 +20885,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL184"/>
+  <dimension ref="A1:AL188"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -40759,6 +40962,474 @@
         <v>31477</v>
       </c>
     </row>
+    <row r="185" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B185" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E185" t="s">
+        <v>18</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="G185" s="3">
+        <v>2</v>
+      </c>
+      <c r="H185" s="3">
+        <v>7</v>
+      </c>
+      <c r="I185" s="3">
+        <v>7</v>
+      </c>
+      <c r="J185" s="3">
+        <v>7</v>
+      </c>
+      <c r="K185" s="3">
+        <v>5</v>
+      </c>
+      <c r="L185">
+        <v>29</v>
+      </c>
+      <c r="M185">
+        <v>38</v>
+      </c>
+      <c r="N185">
+        <v>71</v>
+      </c>
+      <c r="O185">
+        <v>62</v>
+      </c>
+      <c r="P185" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q185" s="3">
+        <v>7</v>
+      </c>
+      <c r="R185" s="3">
+        <v>7</v>
+      </c>
+      <c r="S185" s="3">
+        <v>7</v>
+      </c>
+      <c r="T185" s="3">
+        <v>7</v>
+      </c>
+      <c r="U185" s="3">
+        <v>7</v>
+      </c>
+      <c r="V185" t="s">
+        <v>20</v>
+      </c>
+      <c r="W185" s="3">
+        <v>7</v>
+      </c>
+      <c r="X185" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y185">
+        <v>52</v>
+      </c>
+      <c r="Z185">
+        <v>26</v>
+      </c>
+      <c r="AA185">
+        <v>57</v>
+      </c>
+      <c r="AB185">
+        <v>6</v>
+      </c>
+      <c r="AC185">
+        <v>28.499999999999996</v>
+      </c>
+      <c r="AD185">
+        <v>70</v>
+      </c>
+      <c r="AE185">
+        <v>4</v>
+      </c>
+      <c r="AF185">
+        <v>20</v>
+      </c>
+      <c r="AG185" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH185" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI185" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ185" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK185" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL185">
+        <v>8910</v>
+      </c>
+    </row>
+    <row r="186" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B186" t="s">
+        <v>552</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E186" t="s">
+        <v>18</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="G186" s="3">
+        <v>2</v>
+      </c>
+      <c r="H186" s="3">
+        <v>7</v>
+      </c>
+      <c r="I186" s="3">
+        <v>7</v>
+      </c>
+      <c r="J186" s="3">
+        <v>7</v>
+      </c>
+      <c r="K186" s="3">
+        <v>5</v>
+      </c>
+      <c r="L186">
+        <v>25</v>
+      </c>
+      <c r="M186">
+        <v>46</v>
+      </c>
+      <c r="N186">
+        <v>75</v>
+      </c>
+      <c r="O186">
+        <v>54</v>
+      </c>
+      <c r="P186" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q186" s="3">
+        <v>7</v>
+      </c>
+      <c r="R186" s="3">
+        <v>7</v>
+      </c>
+      <c r="S186" s="3">
+        <v>7</v>
+      </c>
+      <c r="T186" s="3">
+        <v>7</v>
+      </c>
+      <c r="U186" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V186" t="s">
+        <v>20</v>
+      </c>
+      <c r="W186" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X186" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y186">
+        <v>60</v>
+      </c>
+      <c r="Z186">
+        <v>30</v>
+      </c>
+      <c r="AA186">
+        <v>46</v>
+      </c>
+      <c r="AB186">
+        <v>4</v>
+      </c>
+      <c r="AC186">
+        <v>23</v>
+      </c>
+      <c r="AD186">
+        <v>80</v>
+      </c>
+      <c r="AE186">
+        <v>3</v>
+      </c>
+      <c r="AF186">
+        <v>15</v>
+      </c>
+      <c r="AG186" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH186" s="3">
+        <v>13188</v>
+      </c>
+      <c r="AI186" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ186" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK186" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL186">
+        <v>13013</v>
+      </c>
+    </row>
+    <row r="187" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B187" t="s">
+        <v>554</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E187" t="s">
+        <v>18</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="G187" s="3">
+        <v>2</v>
+      </c>
+      <c r="H187" s="3">
+        <v>7</v>
+      </c>
+      <c r="I187" s="3">
+        <v>7</v>
+      </c>
+      <c r="J187" s="3">
+        <v>7</v>
+      </c>
+      <c r="K187" s="3">
+        <v>5</v>
+      </c>
+      <c r="L187">
+        <v>29</v>
+      </c>
+      <c r="M187">
+        <v>46</v>
+      </c>
+      <c r="N187">
+        <v>71</v>
+      </c>
+      <c r="O187">
+        <v>54</v>
+      </c>
+      <c r="P187" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q187" s="3">
+        <v>7</v>
+      </c>
+      <c r="R187" s="3">
+        <v>7</v>
+      </c>
+      <c r="S187" s="3">
+        <v>7</v>
+      </c>
+      <c r="T187" s="3">
+        <v>7</v>
+      </c>
+      <c r="U187" s="3">
+        <v>7</v>
+      </c>
+      <c r="V187" t="s">
+        <v>20</v>
+      </c>
+      <c r="W187" s="3">
+        <v>7</v>
+      </c>
+      <c r="X187" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y187">
+        <v>47</v>
+      </c>
+      <c r="Z187">
+        <v>23.5</v>
+      </c>
+      <c r="AA187">
+        <v>44</v>
+      </c>
+      <c r="AB187">
+        <v>5</v>
+      </c>
+      <c r="AC187">
+        <v>22</v>
+      </c>
+      <c r="AD187">
+        <v>75</v>
+      </c>
+      <c r="AE187">
+        <v>4</v>
+      </c>
+      <c r="AF187">
+        <v>20</v>
+      </c>
+      <c r="AG187" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH187" s="3">
+        <v>42846</v>
+      </c>
+      <c r="AI187" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ187" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK187" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL187">
+        <v>24684</v>
+      </c>
+    </row>
+    <row r="188" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>SET</v>
+      </c>
+      <c r="B188" t="s">
+        <v>557</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E188" t="s">
+        <v>18</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="G188" s="3">
+        <v>2</v>
+      </c>
+      <c r="H188" s="3">
+        <v>7</v>
+      </c>
+      <c r="I188" s="3">
+        <v>10</v>
+      </c>
+      <c r="J188" s="3">
+        <v>5</v>
+      </c>
+      <c r="K188" s="3">
+        <v>5</v>
+      </c>
+      <c r="L188">
+        <v>22</v>
+      </c>
+      <c r="M188">
+        <v>53</v>
+      </c>
+      <c r="N188">
+        <v>78</v>
+      </c>
+      <c r="O188">
+        <v>47</v>
+      </c>
+      <c r="P188" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q188" s="3">
+        <v>7</v>
+      </c>
+      <c r="R188" s="3">
+        <v>7</v>
+      </c>
+      <c r="S188" s="3">
+        <v>7</v>
+      </c>
+      <c r="T188" s="3">
+        <v>7</v>
+      </c>
+      <c r="U188" s="3">
+        <v>7</v>
+      </c>
+      <c r="V188" t="s">
+        <v>20</v>
+      </c>
+      <c r="W188" s="3">
+        <v>7</v>
+      </c>
+      <c r="X188" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y188">
+        <v>53</v>
+      </c>
+      <c r="Z188">
+        <v>26.5</v>
+      </c>
+      <c r="AA188">
+        <v>49</v>
+      </c>
+      <c r="AB188">
+        <v>6</v>
+      </c>
+      <c r="AC188">
+        <v>24.5</v>
+      </c>
+      <c r="AD188">
+        <v>70</v>
+      </c>
+      <c r="AE188">
+        <v>3</v>
+      </c>
+      <c r="AF188">
+        <v>15</v>
+      </c>
+      <c r="AG188" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH188" s="3">
+        <v>995638</v>
+      </c>
+      <c r="AI188" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ188" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK188" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL188">
+        <v>31981</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="592">
   <si>
     <t>ID</t>
   </si>
@@ -1804,6 +1804,66 @@
   </si>
   <si>
     <t>01/10/2026 16:29:31</t>
+  </si>
+  <si>
+    <t>6ac486f64854db7e48d93b2c</t>
+  </si>
+  <si>
+    <t>05/10/2026 22:12:51</t>
+  </si>
+  <si>
+    <t>06/10/2026 02:28:22</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t>6ac486f54854db7e48d93b26</t>
+  </si>
+  <si>
+    <t>05/10/2026 21:29:15</t>
+  </si>
+  <si>
+    <t>06/10/2026 02:28:21</t>
+  </si>
+  <si>
+    <t>6ac486f54854db7e48d93ad0</t>
+  </si>
+  <si>
+    <t>05/10/2026 16:07:05</t>
+  </si>
+  <si>
+    <t>6ac093aadb68f2f72a0ff083</t>
+  </si>
+  <si>
+    <t>02/10/2026 22:34:52</t>
+  </si>
+  <si>
+    <t>03/10/2026 02:33:30</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>6ac093aadb68f2f72a0ff053</t>
+  </si>
+  <si>
+    <t>02/10/2026 20:46:53</t>
+  </si>
+  <si>
+    <t>6ac093a9db68f2f72a0ff047</t>
+  </si>
+  <si>
+    <t>02/10/2026 18:34:53</t>
+  </si>
+  <si>
+    <t>03/10/2026 02:33:29</t>
+  </si>
+  <si>
+    <t>6ac093a9db68f2f72a0ff01d</t>
+  </si>
+  <si>
+    <t>02/10/2026 16:21:35</t>
   </si>
 </sst>
 </file>
@@ -2209,7 +2269,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2218,17 +2287,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2583,7 +2643,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46297.442465856482" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="191">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46301.427450578703" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="198">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2615,7 +2675,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="46">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="48">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2662,6 +2722,8 @@
         <s v="29/09/2026"/>
         <s v="30/09/2026"/>
         <s v="01/10/2026"/>
+        <s v="05/10/2026"/>
+        <s v="02/10/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2770,7 +2832,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="191">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="198">
   <r>
     <x v="0"/>
     <m/>
@@ -10411,12 +10473,292 @@
     <s v="assinatura"/>
     <n v="34249"/>
   </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac486f64854db7e48d93b2c"/>
+    <s v="05/10/2026 22:12:51"/>
+    <s v="06/10/2026 02:28:22"/>
+    <s v="Ranieli"/>
+    <x v="46"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="22"/>
+    <n v="19"/>
+    <n v="78"/>
+    <n v="81"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="39"/>
+    <n v="19.5"/>
+    <n v="48"/>
+    <n v="6"/>
+    <n v="24"/>
+    <n v="70"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="7"/>
+    <n v="42641"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Selagem está conforme,_x000a_Data  de validade e produção estão de acordo,_x000a_Caixa está sem rasgos e seca"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="11403"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac486f54854db7e48d93b26"/>
+    <s v="05/10/2026 21:29:15"/>
+    <s v="06/10/2026 02:28:21"/>
+    <s v="Ranieli"/>
+    <x v="46"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="10"/>
+    <n v="17"/>
+    <n v="90"/>
+    <n v="83"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="46"/>
+    <n v="23"/>
+    <n v="39"/>
+    <n v="9"/>
+    <n v="19.5"/>
+    <n v="55"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="7"/>
+    <n v="42862"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="13958"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac486f54854db7e48d93ad0"/>
+    <s v="05/10/2026 16:07:05"/>
+    <s v="06/10/2026 02:28:21"/>
+    <s v="Ranieli"/>
+    <x v="46"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="16"/>
+    <n v="13"/>
+    <n v="84"/>
+    <n v="87"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="50"/>
+    <n v="25"/>
+    <n v="41"/>
+    <n v="6"/>
+    <n v="20.5"/>
+    <n v="70"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="33065"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac093aadb68f2f72a0ff083"/>
+    <s v="02/10/2026 22:34:52"/>
+    <s v="03/10/2026 02:33:30"/>
+    <s v="Ranieli"/>
+    <x v="47"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="22"/>
+    <n v="13"/>
+    <n v="78"/>
+    <n v="87"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="49"/>
+    <n v="24.5"/>
+    <n v="49"/>
+    <n v="6"/>
+    <n v="24.5"/>
+    <n v="70"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="992093"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="12892"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac093aadb68f2f72a0ff053"/>
+    <s v="02/10/2026 20:46:53"/>
+    <s v="03/10/2026 02:33:30"/>
+    <s v="Ranieli"/>
+    <x v="47"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="27"/>
+    <n v="10"/>
+    <n v="73"/>
+    <n v="90"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <s v=""/>
+    <n v="45"/>
+    <n v="22.5"/>
+    <n v="40"/>
+    <n v="7"/>
+    <n v="20"/>
+    <n v="65"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="7"/>
+    <n v="42838"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="19457"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac093a9db68f2f72a0ff047"/>
+    <s v="02/10/2026 18:34:53"/>
+    <s v="03/10/2026 02:33:29"/>
+    <s v="Ranieli"/>
+    <x v="47"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="19"/>
+    <n v="17"/>
+    <n v="81"/>
+    <n v="83"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="43"/>
+    <n v="21.5"/>
+    <n v="65"/>
+    <n v="7"/>
+    <n v="32.5"/>
+    <n v="65"/>
+    <n v="2"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="13188"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="2044"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac093a9db68f2f72a0ff01d"/>
+    <s v="02/10/2026 16:21:35"/>
+    <s v="03/10/2026 02:33:29"/>
+    <s v="Ranieli"/>
+    <x v="47"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="24"/>
+    <n v="14"/>
+    <n v="76"/>
+    <n v="86"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="51"/>
+    <n v="25.5"/>
+    <n v="50"/>
+    <n v="9"/>
+    <n v="25"/>
+    <n v="55"/>
+    <n v="2"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="10073"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:U118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+  <location ref="U117:W118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="11">
@@ -10438,12 +10780,14 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="47">
+      <items count="49">
         <item x="26"/>
         <item x="45"/>
         <item x="28"/>
+        <item x="47"/>
         <item x="27"/>
         <item x="14"/>
+        <item x="46"/>
         <item x="13"/>
         <item x="12"/>
         <item x="29"/>
@@ -10527,9 +10871,15 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="1">
+  <colItems count="3">
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -10615,8 +10965,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL192" totalsRowShown="0">
-  <autoFilter ref="A1:AL192"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL199" totalsRowShown="0">
+  <autoFilter ref="A1:AL199"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -11065,11 +11415,11 @@
       </c>
       <c r="V3" s="20" t="str">
         <f t="shared" ref="V3:AR3" si="0">IF(V118="","",V118)</f>
-        <v/>
+        <v>02/10/2026</v>
       </c>
       <c r="W3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>05/10/2026</v>
       </c>
       <c r="X3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -11171,7 +11521,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="39" t="str">
+      <c r="E4" s="35" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -11341,7 +11691,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="40"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -11393,18 +11743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="36"/>
+      <c r="S5" s="39"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V5" s="12" t="str">
+      <c r="V5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W5" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],X$3),"")</f>
@@ -11506,7 +11856,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="37"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -11558,18 +11908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="37"/>
+      <c r="S6" s="40"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V6" s="9" t="str">
+      <c r="V6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W6" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -11671,7 +12021,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="39" t="str">
+      <c r="E7" s="35" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -11841,7 +12191,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -11883,7 +12233,7 @@
       </c>
       <c r="P8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
-        <v>8.5</v>
+        <v>7.5454545454545459</v>
       </c>
       <c r="Q8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],Q$3),"")</f>
@@ -11893,18 +12243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="36"/>
+      <c r="S8" s="39"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="V8" s="12" t="str">
+      <c r="V8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W8" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],X$3),"")</f>
@@ -12006,7 +12356,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="41"/>
+      <c r="E9" s="37"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -12048,7 +12398,7 @@
       </c>
       <c r="P9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.5</v>
+        <v>7.5454545454545459</v>
       </c>
       <c r="Q9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -12058,18 +12408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="37"/>
+      <c r="S9" s="40"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="V9" s="9" t="str">
+      <c r="V9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W9" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -12171,7 +12521,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="39" t="str">
+      <c r="E10" s="35" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -12341,7 +12691,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="40"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -12393,18 +12743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="36"/>
+      <c r="S11" s="39"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V11" s="12" t="str">
+      <c r="V11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W11" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],X$3),"")</f>
@@ -12506,7 +12856,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="41"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -12558,18 +12908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="37"/>
+      <c r="S12" s="40"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V12" s="9" t="str">
+      <c r="V12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W12" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -12671,7 +13021,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="39" t="str">
+      <c r="E13" s="35" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -12841,7 +13191,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="40"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -12883,7 +13233,7 @@
       </c>
       <c r="P14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
-        <v>5.5</v>
+        <v>5.5454545454545459</v>
       </c>
       <c r="Q14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],Q$3),"")</f>
@@ -12893,18 +13243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="36"/>
+      <c r="S14" s="39"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="V14" s="12" t="str">
+      <c r="V14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W14" s="12" t="str">
+        <v>6</v>
+      </c>
+      <c r="W14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="X14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],X$3),"")</f>
@@ -13006,7 +13356,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="41"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -13048,7 +13398,7 @@
       </c>
       <c r="P15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>5.5</v>
+        <v>5.5454545454545459</v>
       </c>
       <c r="Q15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -13058,18 +13408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="37"/>
+      <c r="S15" s="40"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="V15" s="9" t="str">
+      <c r="V15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W15" s="9" t="str">
+        <v>6</v>
+      </c>
+      <c r="W15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="X15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -13171,7 +13521,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="39" t="str">
+      <c r="E16" s="35" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -13226,7 +13576,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="41">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -13341,7 +13691,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="40"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -13383,7 +13733,7 @@
       </c>
       <c r="P17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.8075</v>
+        <v>0.80272727272727262</v>
       </c>
       <c r="Q17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],Q$3)/100,"")</f>
@@ -13393,18 +13743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="36"/>
+      <c r="S17" s="39"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
       </c>
-      <c r="V17" s="16" t="str">
+      <c r="V17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W17" s="16" t="str">
+        <v>0.77</v>
+      </c>
+      <c r="W17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.84</v>
       </c>
       <c r="X17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],X$3)/100,"")</f>
@@ -13506,7 +13856,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="41"/>
+      <c r="E18" s="37"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -13548,7 +13898,7 @@
       </c>
       <c r="P18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.8075</v>
+        <v>0.80272727272727262</v>
       </c>
       <c r="Q18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -13558,18 +13908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="37"/>
+      <c r="S18" s="40"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
       </c>
-      <c r="V18" s="10" t="str">
+      <c r="V18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W18" s="10" t="str">
+        <v>0.77</v>
+      </c>
+      <c r="W18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.84</v>
       </c>
       <c r="X18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
@@ -13671,7 +14021,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="39" t="str">
+      <c r="E19" s="35" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -13726,7 +14076,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="41">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -13841,7 +14191,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="40"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -13883,7 +14233,7 @@
       </c>
       <c r="P20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.75249999999999995</v>
+        <v>0.8163636363636364</v>
       </c>
       <c r="Q20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],Q$3)/100,"")</f>
@@ -13893,18 +14243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="36"/>
+      <c r="S20" s="39"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
       </c>
-      <c r="V20" s="16" t="str">
+      <c r="V20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W20" s="16" t="str">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="W20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.83666666666666667</v>
       </c>
       <c r="X20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],X$3)/100,"")</f>
@@ -14006,7 +14356,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="41"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -14048,7 +14398,7 @@
       </c>
       <c r="P21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.75249999999999995</v>
+        <v>0.8163636363636364</v>
       </c>
       <c r="Q21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -14058,18 +14408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="37"/>
+      <c r="S21" s="40"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
       </c>
-      <c r="V21" s="10" t="str">
+      <c r="V21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W21" s="10" t="str">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="W21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.83666666666666667</v>
       </c>
       <c r="X21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
@@ -14171,7 +14521,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="39" t="str">
+      <c r="E22" s="35" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -14341,7 +14691,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="40"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -14383,7 +14733,7 @@
       </c>
       <c r="P23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
-        <v>6</v>
+        <v>6.0909090909090908</v>
       </c>
       <c r="Q23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],Q$3),"")</f>
@@ -14393,18 +14743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="36"/>
+      <c r="S23" s="39"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6</v>
       </c>
-      <c r="V23" s="12" t="str">
+      <c r="V23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W23" s="12" t="str">
+        <v>6</v>
+      </c>
+      <c r="W23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>6.333333333333333</v>
       </c>
       <c r="X23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],X$3),"")</f>
@@ -14506,7 +14856,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="41"/>
+      <c r="E24" s="37"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -14548,7 +14898,7 @@
       </c>
       <c r="P24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6</v>
+        <v>6.0909090909090908</v>
       </c>
       <c r="Q24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -14558,18 +14908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="37"/>
+      <c r="S24" s="40"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6</v>
       </c>
-      <c r="V24" s="9" t="str">
+      <c r="V24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W24" s="9" t="str">
+        <v>6</v>
+      </c>
+      <c r="W24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>6.333333333333333</v>
       </c>
       <c r="X24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -14671,7 +15021,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="39" t="str">
+      <c r="E25" s="35" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -14841,7 +15191,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="40"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -14883,7 +15233,7 @@
       </c>
       <c r="P26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
-        <v>7.75</v>
+        <v>7.2727272727272725</v>
       </c>
       <c r="Q26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],Q$3),"")</f>
@@ -14893,18 +15243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="36"/>
+      <c r="S26" s="39"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
       </c>
-      <c r="V26" s="12" t="str">
+      <c r="V26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W26" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],X$3),"")</f>
@@ -15006,7 +15356,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="41"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -15048,7 +15398,7 @@
       </c>
       <c r="P27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.75</v>
+        <v>7.2727272727272725</v>
       </c>
       <c r="Q27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -15058,18 +15408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="37"/>
+      <c r="S27" s="40"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
       </c>
-      <c r="V27" s="9" t="str">
+      <c r="V27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W27" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -15171,7 +15521,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="39" t="str">
+      <c r="E28" s="35" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -15341,7 +15691,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="40"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -15393,18 +15743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="36"/>
+      <c r="S29" s="39"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V29" s="12" t="str">
+      <c r="V29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W29" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],X$3),"")</f>
@@ -15506,7 +15856,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="37"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -15558,18 +15908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="37"/>
+      <c r="S30" s="40"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V30" s="9" t="str">
+      <c r="V30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W30" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -15671,7 +16021,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="39" t="str">
+      <c r="E31" s="35" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -15841,7 +16191,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="40"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -15883,7 +16233,7 @@
       </c>
       <c r="P32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
-        <v>7</v>
+        <v>6.8181818181818183</v>
       </c>
       <c r="Q32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],Q$3),"")</f>
@@ -15893,18 +16243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="36"/>
+      <c r="S32" s="39"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V32" s="12" t="str">
+      <c r="V32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W32" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>6.333333333333333</v>
       </c>
       <c r="X32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],X$3),"")</f>
@@ -16006,7 +16356,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="41"/>
+      <c r="E33" s="37"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -16048,7 +16398,7 @@
       </c>
       <c r="P33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7</v>
+        <v>6.8181818181818183</v>
       </c>
       <c r="Q33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -16058,18 +16408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="37"/>
+      <c r="S33" s="40"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V33" s="9" t="str">
+      <c r="V33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W33" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>6.333333333333333</v>
       </c>
       <c r="X33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -16171,7 +16521,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="39" t="str">
+      <c r="E34" s="35" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -16341,7 +16691,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="40"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -16393,18 +16743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="36"/>
+      <c r="S35" s="39"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V35" s="12" t="str">
+      <c r="V35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W35" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],X$3),"")</f>
@@ -16506,7 +16856,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="41"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -16558,18 +16908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="37"/>
+      <c r="S36" s="40"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V36" s="9" t="str">
+      <c r="V36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W36" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -16671,7 +17021,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="39" t="str">
+      <c r="E37" s="35" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -16841,7 +17191,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="40"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -16883,7 +17233,7 @@
       </c>
       <c r="P38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],Q$3),"")</f>
@@ -16893,18 +17243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="36"/>
+      <c r="S38" s="39"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="V38" s="12" t="str">
+      <c r="V38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W38" s="12" t="str">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="W38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>6.333333333333333</v>
       </c>
       <c r="X38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],X$3),"")</f>
@@ -17006,7 +17356,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="41"/>
+      <c r="E39" s="37"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -17048,7 +17398,7 @@
       </c>
       <c r="P39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -17058,18 +17408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="37"/>
+      <c r="S39" s="40"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="V39" s="9" t="str">
+      <c r="V39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W39" s="9" t="str">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="W39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>6.333333333333333</v>
       </c>
       <c r="X39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -17171,7 +17521,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="39" t="str">
+      <c r="E40" s="35" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -17341,7 +17691,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="40"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -17383,7 +17733,7 @@
       </c>
       <c r="P41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
-        <v>8.5</v>
+        <v>8.125</v>
       </c>
       <c r="Q41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],Q$3),"")</f>
@@ -17393,18 +17743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="36"/>
+      <c r="S41" s="39"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="V41" s="12" t="str">
+      <c r="V41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W41" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="X41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],X$3),"")</f>
@@ -17506,7 +17856,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="37"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -17548,7 +17898,7 @@
       </c>
       <c r="P42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.5</v>
+        <v>8.125</v>
       </c>
       <c r="Q42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -17558,18 +17908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="37"/>
+      <c r="S42" s="40"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="V42" s="9" t="str">
+      <c r="V42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W42" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="X42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -17671,7 +18021,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="39" t="str">
+      <c r="E43" s="35" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -17841,7 +18191,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="40"/>
+      <c r="E44" s="36"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -17883,7 +18233,7 @@
       </c>
       <c r="P44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
-        <v>7</v>
+        <v>7.4285714285714288</v>
       </c>
       <c r="Q44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],Q$3),"")</f>
@@ -17893,18 +18243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="36"/>
+      <c r="S44" s="39"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V44" s="12" t="str">
+      <c r="V44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W44" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="W44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="X44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],X$3),"")</f>
@@ -18006,7 +18356,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="37"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -18048,7 +18398,7 @@
       </c>
       <c r="P45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7</v>
+        <v>7.4285714285714288</v>
       </c>
       <c r="Q45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18058,18 +18408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="37"/>
+      <c r="S45" s="40"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
       </c>
-      <c r="V45" s="9" t="str">
+      <c r="V45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W45" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="W45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="X45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -18171,7 +18521,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="39" t="str">
+      <c r="E46" s="35" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -18226,7 +18576,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="35">
+      <c r="S46" s="41">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -18341,7 +18691,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="40"/>
+      <c r="E47" s="36"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -18383,7 +18733,7 @@
       </c>
       <c r="P47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.30166666666666669</v>
+        <v>0.252</v>
       </c>
       <c r="Q47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],Q$3)/100,"")</f>
@@ -18393,18 +18743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="36"/>
+      <c r="S47" s="39"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
       </c>
-      <c r="V47" s="16" t="str">
+      <c r="V47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W47" s="16" t="str">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="W47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="X47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],X$3)/100,"")</f>
@@ -18506,7 +18856,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="41"/>
+      <c r="E48" s="37"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -18548,7 +18898,7 @@
       </c>
       <c r="P48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.30166666666666669</v>
+        <v>0.252</v>
       </c>
       <c r="Q48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -18558,18 +18908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="37"/>
+      <c r="S48" s="40"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
       </c>
-      <c r="V48" s="10" t="str">
+      <c r="V48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W48" s="10" t="str">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="W48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="X48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
@@ -18671,7 +19021,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="39" t="str">
+      <c r="E49" s="35" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -18726,7 +19076,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="35">
+      <c r="S49" s="41">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -18841,7 +19191,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="40"/>
+      <c r="E50" s="36"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -18883,7 +19233,7 @@
       </c>
       <c r="P50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.26374999999999998</v>
+        <v>0.24681818181818183</v>
       </c>
       <c r="Q50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],Q$3)/100,"")</f>
@@ -18893,18 +19243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="36"/>
+      <c r="S50" s="39"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
       </c>
-      <c r="V50" s="16" t="str">
+      <c r="V50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W50" s="16" t="str">
+        <v>0.255</v>
+      </c>
+      <c r="W50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.21333333333333332</v>
       </c>
       <c r="X50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],X$3)/100,"")</f>
@@ -19006,7 +19356,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="41"/>
+      <c r="E51" s="37"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -19048,7 +19398,7 @@
       </c>
       <c r="P51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.26374999999999998</v>
+        <v>0.24681818181818183</v>
       </c>
       <c r="Q51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19058,18 +19408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="37"/>
+      <c r="S51" s="40"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
       </c>
-      <c r="V51" s="10" t="str">
+      <c r="V51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W51" s="10" t="str">
+        <v>0.255</v>
+      </c>
+      <c r="W51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.21333333333333332</v>
       </c>
       <c r="X51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
@@ -19171,7 +19521,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="39" t="str">
+      <c r="E52" s="35" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -19226,7 +19576,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="35">
+      <c r="S52" s="41">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -19341,7 +19691,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="40"/>
+      <c r="E53" s="36"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -19383,7 +19733,7 @@
       </c>
       <c r="P53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.67500000000000004</v>
+        <v>0.65454545454545454</v>
       </c>
       <c r="Q53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19393,18 +19743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="36"/>
+      <c r="S53" s="39"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
       </c>
-      <c r="V53" s="16" t="str">
+      <c r="V53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W53" s="16" t="str">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="W53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="X53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],X$3)/100,"")</f>
@@ -19506,7 +19856,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="41"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -19548,7 +19898,7 @@
       </c>
       <c r="P54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.67500000000000004</v>
+        <v>0.65454545454545454</v>
       </c>
       <c r="Q54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19558,18 +19908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="37"/>
+      <c r="S54" s="40"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
       </c>
-      <c r="V54" s="10" t="str">
+      <c r="V54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W54" s="10" t="str">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="W54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="X54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
@@ -19671,7 +20021,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="39" t="str">
+      <c r="E55" s="35" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -19726,7 +20076,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="35">
+      <c r="S55" s="41">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -19841,7 +20191,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="40"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -19883,7 +20233,7 @@
       </c>
       <c r="P56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.15</v>
+        <v>0.14545454545454545</v>
       </c>
       <c r="Q56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19893,18 +20243,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="36"/>
+      <c r="S56" s="39"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
       </c>
-      <c r="V56" s="16" t="str">
+      <c r="V56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W56" s="16" t="str">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="W56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="X56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],X$3)/100,"")</f>
@@ -20006,7 +20356,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="41"/>
+      <c r="E57" s="37"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -20048,7 +20398,7 @@
       </c>
       <c r="P57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.15</v>
+        <v>0.14545454545454545</v>
       </c>
       <c r="Q57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20058,18 +20408,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="37"/>
+      <c r="S57" s="40"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
       </c>
-      <c r="V57" s="10" t="str">
+      <c r="V57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],V$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="W57" s="10" t="str">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="W57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="X57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
@@ -20171,7 +20521,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="39" t="str">
+      <c r="E58" s="35" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -20341,7 +20691,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="40"/>
+      <c r="E59" s="36"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -20383,7 +20733,7 @@
       </c>
       <c r="P59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
-        <v>9</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="Q59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],Q$3),"")</f>
@@ -20393,18 +20743,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="36"/>
+      <c r="S59" s="39"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>9</v>
       </c>
-      <c r="V59" s="12" t="str">
+      <c r="V59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W59" s="12" t="str">
+        <v>9.25</v>
+      </c>
+      <c r="W59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="X59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],X$3),"")</f>
@@ -20506,7 +20856,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="41"/>
+      <c r="E60" s="37"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -20548,7 +20898,7 @@
       </c>
       <c r="P60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>9</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="Q60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -20558,18 +20908,18 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="37"/>
+      <c r="S60" s="40"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
       </c>
-      <c r="V60" s="9" t="str">
+      <c r="V60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],V$3),"")</f>
-        <v/>
-      </c>
-      <c r="W60" s="9" t="str">
+        <v>9.25</v>
+      </c>
+      <c r="W60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],W$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="X60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],X$3),"")</f>
@@ -20702,7 +21052,12 @@
       <c r="U118" t="s">
         <v>562</v>
       </c>
-      <c r="W118"/>
+      <c r="V118" t="s">
+        <v>584</v>
+      </c>
+      <c r="W118" t="s">
+        <v>575</v>
+      </c>
       <c r="X118"/>
       <c r="Y118"/>
       <c r="Z118"/>
@@ -20722,18 +21077,16 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -20750,16 +21103,18 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -20998,7 +21353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL192"/>
+  <dimension ref="A1:AL199"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -42011,6 +42366,825 @@
         <v>34249</v>
       </c>
     </row>
+    <row r="193" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B193" s="33" t="s">
+        <v>572</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G193" s="3">
+        <v>2</v>
+      </c>
+      <c r="H193" s="3">
+        <v>7</v>
+      </c>
+      <c r="I193" s="3">
+        <v>7</v>
+      </c>
+      <c r="J193" s="3">
+        <v>7</v>
+      </c>
+      <c r="K193" s="3">
+        <v>5</v>
+      </c>
+      <c r="L193">
+        <v>22</v>
+      </c>
+      <c r="M193">
+        <v>19</v>
+      </c>
+      <c r="N193">
+        <v>78</v>
+      </c>
+      <c r="O193">
+        <v>81</v>
+      </c>
+      <c r="P193" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q193" s="3">
+        <v>7</v>
+      </c>
+      <c r="R193" s="3">
+        <v>7</v>
+      </c>
+      <c r="S193" s="3">
+        <v>7</v>
+      </c>
+      <c r="T193" s="3">
+        <v>7</v>
+      </c>
+      <c r="U193" s="3">
+        <v>7</v>
+      </c>
+      <c r="V193" t="s">
+        <v>169</v>
+      </c>
+      <c r="W193" s="3">
+        <v>7</v>
+      </c>
+      <c r="X193" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y193">
+        <v>39</v>
+      </c>
+      <c r="Z193">
+        <v>19.5</v>
+      </c>
+      <c r="AA193">
+        <v>48</v>
+      </c>
+      <c r="AB193">
+        <v>6</v>
+      </c>
+      <c r="AC193">
+        <v>24</v>
+      </c>
+      <c r="AD193">
+        <v>70</v>
+      </c>
+      <c r="AE193">
+        <v>3</v>
+      </c>
+      <c r="AF193">
+        <v>15</v>
+      </c>
+      <c r="AG193" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH193" s="3">
+        <v>42641</v>
+      </c>
+      <c r="AI193" t="s">
+        <v>275</v>
+      </c>
+      <c r="AJ193" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK193" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL193">
+        <v>11403</v>
+      </c>
+    </row>
+    <row r="194" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B194" t="s">
+        <v>576</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E194" t="s">
+        <v>18</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G194" s="3">
+        <v>2</v>
+      </c>
+      <c r="H194" s="3">
+        <v>7</v>
+      </c>
+      <c r="I194" s="3">
+        <v>7</v>
+      </c>
+      <c r="J194" s="3">
+        <v>7</v>
+      </c>
+      <c r="K194" s="3">
+        <v>5</v>
+      </c>
+      <c r="L194">
+        <v>10</v>
+      </c>
+      <c r="M194">
+        <v>17</v>
+      </c>
+      <c r="N194">
+        <v>90</v>
+      </c>
+      <c r="O194">
+        <v>83</v>
+      </c>
+      <c r="P194" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q194" s="3">
+        <v>7</v>
+      </c>
+      <c r="R194" s="3">
+        <v>7</v>
+      </c>
+      <c r="S194" s="3">
+        <v>7</v>
+      </c>
+      <c r="T194" s="3">
+        <v>7</v>
+      </c>
+      <c r="U194" s="3">
+        <v>7</v>
+      </c>
+      <c r="V194" t="s">
+        <v>169</v>
+      </c>
+      <c r="W194" s="3">
+        <v>10</v>
+      </c>
+      <c r="X194" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y194">
+        <v>46</v>
+      </c>
+      <c r="Z194">
+        <v>23</v>
+      </c>
+      <c r="AA194">
+        <v>39</v>
+      </c>
+      <c r="AB194">
+        <v>9</v>
+      </c>
+      <c r="AC194">
+        <v>19.5</v>
+      </c>
+      <c r="AD194">
+        <v>55</v>
+      </c>
+      <c r="AE194">
+        <v>3</v>
+      </c>
+      <c r="AF194">
+        <v>15</v>
+      </c>
+      <c r="AG194" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH194" s="3">
+        <v>42862</v>
+      </c>
+      <c r="AI194" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ194" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK194" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL194">
+        <v>13958</v>
+      </c>
+    </row>
+    <row r="195" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B195" t="s">
+        <v>579</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E195" t="s">
+        <v>18</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G195" s="3">
+        <v>2</v>
+      </c>
+      <c r="H195" s="3">
+        <v>7</v>
+      </c>
+      <c r="I195" s="3">
+        <v>7</v>
+      </c>
+      <c r="J195" s="3">
+        <v>7</v>
+      </c>
+      <c r="K195" s="3">
+        <v>5</v>
+      </c>
+      <c r="L195">
+        <v>16</v>
+      </c>
+      <c r="M195">
+        <v>13</v>
+      </c>
+      <c r="N195">
+        <v>84</v>
+      </c>
+      <c r="O195">
+        <v>87</v>
+      </c>
+      <c r="P195" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q195" s="3">
+        <v>7</v>
+      </c>
+      <c r="R195" s="3">
+        <v>7</v>
+      </c>
+      <c r="S195" s="3">
+        <v>5</v>
+      </c>
+      <c r="T195" s="3">
+        <v>7</v>
+      </c>
+      <c r="U195" s="3">
+        <v>5</v>
+      </c>
+      <c r="V195" t="s">
+        <v>20</v>
+      </c>
+      <c r="W195" s="3">
+        <v>10</v>
+      </c>
+      <c r="X195" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y195">
+        <v>50</v>
+      </c>
+      <c r="Z195">
+        <v>25</v>
+      </c>
+      <c r="AA195">
+        <v>41</v>
+      </c>
+      <c r="AB195">
+        <v>6</v>
+      </c>
+      <c r="AC195">
+        <v>20.5</v>
+      </c>
+      <c r="AD195">
+        <v>70</v>
+      </c>
+      <c r="AE195">
+        <v>3</v>
+      </c>
+      <c r="AF195">
+        <v>15</v>
+      </c>
+      <c r="AG195" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH195" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI195" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ195" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK195" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL195">
+        <v>33065</v>
+      </c>
+    </row>
+    <row r="196" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B196" t="s">
+        <v>581</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E196" t="s">
+        <v>18</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="G196" s="3">
+        <v>2</v>
+      </c>
+      <c r="H196" s="3">
+        <v>7</v>
+      </c>
+      <c r="I196" s="3">
+        <v>7</v>
+      </c>
+      <c r="J196" s="3">
+        <v>7</v>
+      </c>
+      <c r="K196" s="3">
+        <v>5</v>
+      </c>
+      <c r="L196">
+        <v>22</v>
+      </c>
+      <c r="M196">
+        <v>13</v>
+      </c>
+      <c r="N196">
+        <v>78</v>
+      </c>
+      <c r="O196">
+        <v>87</v>
+      </c>
+      <c r="P196" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q196" s="3">
+        <v>7</v>
+      </c>
+      <c r="R196" s="3">
+        <v>7</v>
+      </c>
+      <c r="S196" s="3">
+        <v>7</v>
+      </c>
+      <c r="T196" s="3">
+        <v>7</v>
+      </c>
+      <c r="U196" s="3">
+        <v>5</v>
+      </c>
+      <c r="V196" t="s">
+        <v>20</v>
+      </c>
+      <c r="W196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X196" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y196">
+        <v>49</v>
+      </c>
+      <c r="Z196">
+        <v>24.5</v>
+      </c>
+      <c r="AA196">
+        <v>49</v>
+      </c>
+      <c r="AB196">
+        <v>6</v>
+      </c>
+      <c r="AC196">
+        <v>24.5</v>
+      </c>
+      <c r="AD196">
+        <v>70</v>
+      </c>
+      <c r="AE196">
+        <v>4</v>
+      </c>
+      <c r="AF196">
+        <v>20</v>
+      </c>
+      <c r="AG196" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH196" s="3">
+        <v>992093</v>
+      </c>
+      <c r="AI196" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ196" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK196" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL196">
+        <v>12892</v>
+      </c>
+    </row>
+    <row r="197" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B197" t="s">
+        <v>585</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E197" t="s">
+        <v>18</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="G197" s="3">
+        <v>2</v>
+      </c>
+      <c r="H197" s="3">
+        <v>7</v>
+      </c>
+      <c r="I197" s="3">
+        <v>7</v>
+      </c>
+      <c r="J197" s="3">
+        <v>7</v>
+      </c>
+      <c r="K197" s="3">
+        <v>7</v>
+      </c>
+      <c r="L197">
+        <v>27</v>
+      </c>
+      <c r="M197">
+        <v>10</v>
+      </c>
+      <c r="N197">
+        <v>73</v>
+      </c>
+      <c r="O197">
+        <v>90</v>
+      </c>
+      <c r="P197" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q197" s="3">
+        <v>7</v>
+      </c>
+      <c r="R197" s="3">
+        <v>7</v>
+      </c>
+      <c r="S197" s="3">
+        <v>7</v>
+      </c>
+      <c r="T197" s="3">
+        <v>7</v>
+      </c>
+      <c r="U197" s="3">
+        <v>7</v>
+      </c>
+      <c r="V197" t="s">
+        <v>20</v>
+      </c>
+      <c r="W197" s="3">
+        <v>7</v>
+      </c>
+      <c r="X197" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y197">
+        <v>45</v>
+      </c>
+      <c r="Z197">
+        <v>22.5</v>
+      </c>
+      <c r="AA197">
+        <v>40</v>
+      </c>
+      <c r="AB197">
+        <v>7</v>
+      </c>
+      <c r="AC197">
+        <v>20</v>
+      </c>
+      <c r="AD197">
+        <v>65</v>
+      </c>
+      <c r="AE197">
+        <v>3</v>
+      </c>
+      <c r="AF197">
+        <v>15</v>
+      </c>
+      <c r="AG197" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH197" s="3">
+        <v>42838</v>
+      </c>
+      <c r="AI197" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ197" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK197" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL197">
+        <v>19457</v>
+      </c>
+    </row>
+    <row r="198" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B198" t="s">
+        <v>587</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E198" t="s">
+        <v>18</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="G198" s="3">
+        <v>2</v>
+      </c>
+      <c r="H198" s="3">
+        <v>7</v>
+      </c>
+      <c r="I198" s="3">
+        <v>7</v>
+      </c>
+      <c r="J198" s="3">
+        <v>7</v>
+      </c>
+      <c r="K198" s="3">
+        <v>7</v>
+      </c>
+      <c r="L198">
+        <v>19</v>
+      </c>
+      <c r="M198">
+        <v>17</v>
+      </c>
+      <c r="N198">
+        <v>81</v>
+      </c>
+      <c r="O198">
+        <v>83</v>
+      </c>
+      <c r="P198" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q198" s="3">
+        <v>7</v>
+      </c>
+      <c r="R198" s="3">
+        <v>7</v>
+      </c>
+      <c r="S198" s="3">
+        <v>7</v>
+      </c>
+      <c r="T198" s="3">
+        <v>7</v>
+      </c>
+      <c r="U198" s="3">
+        <v>5</v>
+      </c>
+      <c r="V198" t="s">
+        <v>20</v>
+      </c>
+      <c r="W198" s="3">
+        <v>7</v>
+      </c>
+      <c r="X198" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y198">
+        <v>43</v>
+      </c>
+      <c r="Z198">
+        <v>21.5</v>
+      </c>
+      <c r="AA198">
+        <v>65</v>
+      </c>
+      <c r="AB198">
+        <v>7</v>
+      </c>
+      <c r="AC198">
+        <v>32.5</v>
+      </c>
+      <c r="AD198">
+        <v>65</v>
+      </c>
+      <c r="AE198">
+        <v>2</v>
+      </c>
+      <c r="AF198">
+        <v>10</v>
+      </c>
+      <c r="AG198" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH198" s="3">
+        <v>13188</v>
+      </c>
+      <c r="AI198" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ198" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK198" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL198">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="199" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B199" t="s">
+        <v>590</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E199" t="s">
+        <v>18</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="G199" s="3">
+        <v>2</v>
+      </c>
+      <c r="H199" s="3">
+        <v>7</v>
+      </c>
+      <c r="I199" s="3">
+        <v>7</v>
+      </c>
+      <c r="J199" s="3">
+        <v>7</v>
+      </c>
+      <c r="K199" s="3">
+        <v>5</v>
+      </c>
+      <c r="L199">
+        <v>24</v>
+      </c>
+      <c r="M199">
+        <v>14</v>
+      </c>
+      <c r="N199">
+        <v>76</v>
+      </c>
+      <c r="O199">
+        <v>86</v>
+      </c>
+      <c r="P199" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q199" s="3">
+        <v>7</v>
+      </c>
+      <c r="R199" s="3">
+        <v>7</v>
+      </c>
+      <c r="S199" s="3">
+        <v>7</v>
+      </c>
+      <c r="T199" s="3">
+        <v>7</v>
+      </c>
+      <c r="U199" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V199" t="s">
+        <v>20</v>
+      </c>
+      <c r="W199" s="3">
+        <v>7</v>
+      </c>
+      <c r="X199" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y199">
+        <v>51</v>
+      </c>
+      <c r="Z199">
+        <v>25.5</v>
+      </c>
+      <c r="AA199">
+        <v>50</v>
+      </c>
+      <c r="AB199">
+        <v>9</v>
+      </c>
+      <c r="AC199">
+        <v>25</v>
+      </c>
+      <c r="AD199">
+        <v>55</v>
+      </c>
+      <c r="AE199">
+        <v>2</v>
+      </c>
+      <c r="AF199">
+        <v>10</v>
+      </c>
+      <c r="AG199" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH199" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI199" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ199" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK199" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL199">
+        <v>10073</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="603">
   <si>
     <t>ID</t>
   </si>
@@ -1864,6 +1864,39 @@
   </si>
   <si>
     <t>02/10/2026 16:21:35</t>
+  </si>
+  <si>
+    <t>6ac5da49636e383ab3c2e97e</t>
+  </si>
+  <si>
+    <t>06/10/2026 22:00:17</t>
+  </si>
+  <si>
+    <t>07/10/2026 02:36:09</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>6ac5da49636e383ab3c2e978</t>
+  </si>
+  <si>
+    <t>06/10/2026 21:22:17</t>
+  </si>
+  <si>
+    <t>6ac5da48636e383ab3c2e948</t>
+  </si>
+  <si>
+    <t>06/10/2026 17:33:08</t>
+  </si>
+  <si>
+    <t>07/10/2026 02:36:08</t>
+  </si>
+  <si>
+    <t>6ac5da48636e383ab3c2e92a</t>
+  </si>
+  <si>
+    <t>06/10/2026 16:22:08</t>
   </si>
 </sst>
 </file>
@@ -2269,6 +2302,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2277,18 +2322,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2643,7 +2676,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46301.427450578703" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="198">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46302.469674305554" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="202">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2675,7 +2708,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="48">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="49">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2724,6 +2757,7 @@
         <s v="01/10/2026"/>
         <s v="05/10/2026"/>
         <s v="02/10/2026"/>
+        <s v="06/10/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2832,7 +2866,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="198">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="202">
   <r>
     <x v="0"/>
     <m/>
@@ -10753,12 +10787,172 @@
     <s v="assinatura"/>
     <n v="10073"/>
   </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac5da49636e383ab3c2e97e"/>
+    <s v="06/10/2026 22:00:17"/>
+    <s v="07/10/2026 02:36:09"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="38"/>
+    <n v="12"/>
+    <n v="62"/>
+    <n v="88"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="37"/>
+    <n v="18.5"/>
+    <n v="47"/>
+    <n v="6"/>
+    <n v="23.5"/>
+    <n v="70"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="13753"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac5da49636e383ab3c2e978"/>
+    <s v="06/10/2026 21:22:17"/>
+    <s v="07/10/2026 02:36:09"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="32"/>
+    <n v="16"/>
+    <n v="68"/>
+    <n v="84"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="48"/>
+    <n v="24"/>
+    <n v="44"/>
+    <n v="8"/>
+    <n v="22"/>
+    <n v="60"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="995638"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="15998"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac5da48636e383ab3c2e948"/>
+    <s v="06/10/2026 17:33:08"/>
+    <s v="07/10/2026 02:36:08"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="37"/>
+    <n v="24"/>
+    <n v="63"/>
+    <n v="76"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="33"/>
+    <n v="16.5"/>
+    <n v="55"/>
+    <n v="8"/>
+    <n v="27.500000000000004"/>
+    <n v="60"/>
+    <n v="7"/>
+    <n v="35"/>
+    <n v="7"/>
+    <n v="42838"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="29574"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac5da48636e383ab3c2e92a"/>
+    <s v="06/10/2026 16:22:08"/>
+    <s v="07/10/2026 02:36:08"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="22"/>
+    <n v="17"/>
+    <n v="78"/>
+    <n v="83"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="57"/>
+    <n v="28.499999999999996"/>
+    <n v="38"/>
+    <n v="7"/>
+    <n v="19"/>
+    <n v="65"/>
+    <n v="2"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="33762"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:W118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="U117:X118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="11">
@@ -10780,7 +10974,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="49">
+      <items count="50">
         <item x="26"/>
         <item x="45"/>
         <item x="28"/>
@@ -10789,6 +10983,7 @@
         <item x="14"/>
         <item x="46"/>
         <item x="13"/>
+        <item x="48"/>
         <item x="12"/>
         <item x="29"/>
         <item x="32"/>
@@ -10871,7 +11066,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="3">
+  <colItems count="4">
     <i>
       <x v="1"/>
     </i>
@@ -10880,6 +11075,9 @@
     </i>
     <i>
       <x v="6"/>
+    </i>
+    <i>
+      <x v="8"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -10965,8 +11163,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL199" totalsRowShown="0">
-  <autoFilter ref="A1:AL199"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL203" totalsRowShown="0">
+  <autoFilter ref="A1:AL203"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -11423,7 +11621,7 @@
       </c>
       <c r="X3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>06/10/2026</v>
       </c>
       <c r="Y3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -11521,7 +11719,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="35" t="str">
+      <c r="E4" s="39" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -11691,7 +11889,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="40"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -11743,7 +11941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="39"/>
+      <c r="S5" s="36"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11756,9 +11954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X5" s="12" t="str">
+      <c r="X5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],Y$3),"")</f>
@@ -11856,7 +12054,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="37"/>
+      <c r="E6" s="41"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -11908,7 +12106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="40"/>
+      <c r="S6" s="37"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -11921,9 +12119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X6" s="9" t="str">
+      <c r="X6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -12021,7 +12219,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="35" t="str">
+      <c r="E7" s="39" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -12191,7 +12389,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="36"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -12233,7 +12431,7 @@
       </c>
       <c r="P8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
-        <v>7.5454545454545459</v>
+        <v>7.4</v>
       </c>
       <c r="Q8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],Q$3),"")</f>
@@ -12243,7 +12441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="39"/>
+      <c r="S8" s="36"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -12256,9 +12454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X8" s="12" t="str">
+      <c r="X8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],Y$3),"")</f>
@@ -12356,7 +12554,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="37"/>
+      <c r="E9" s="41"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -12398,7 +12596,7 @@
       </c>
       <c r="P9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.5454545454545459</v>
+        <v>7.4</v>
       </c>
       <c r="Q9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -12408,7 +12606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="40"/>
+      <c r="S9" s="37"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -12421,9 +12619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X9" s="9" t="str">
+      <c r="X9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -12521,7 +12719,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="35" t="str">
+      <c r="E10" s="39" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -12691,7 +12889,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="40"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -12743,7 +12941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="39"/>
+      <c r="S11" s="36"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12756,9 +12954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X11" s="12" t="str">
+      <c r="X11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],Y$3),"")</f>
@@ -12856,7 +13054,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="37"/>
+      <c r="E12" s="41"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -12908,7 +13106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="40"/>
+      <c r="S12" s="37"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12921,9 +13119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X12" s="9" t="str">
+      <c r="X12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -13021,7 +13219,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="35" t="str">
+      <c r="E13" s="39" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -13191,7 +13389,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -13233,7 +13431,7 @@
       </c>
       <c r="P14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
-        <v>5.5454545454545459</v>
+        <v>5.5333333333333332</v>
       </c>
       <c r="Q14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],Q$3),"")</f>
@@ -13243,7 +13441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="39"/>
+      <c r="S14" s="36"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -13256,9 +13454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],W$3),"")</f>
         <v>5</v>
       </c>
-      <c r="X14" s="12" t="str">
+      <c r="X14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="Y14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],Y$3),"")</f>
@@ -13356,7 +13554,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="41"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -13398,7 +13596,7 @@
       </c>
       <c r="P15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>5.5454545454545459</v>
+        <v>5.5333333333333332</v>
       </c>
       <c r="Q15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -13408,7 +13606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="40"/>
+      <c r="S15" s="37"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -13421,9 +13619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>5</v>
       </c>
-      <c r="X15" s="9" t="str">
+      <c r="X15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="Y15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -13521,7 +13719,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="35" t="str">
+      <c r="E16" s="39" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -13576,7 +13774,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="41">
+      <c r="S16" s="35">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -13691,7 +13889,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="36"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -13733,7 +13931,7 @@
       </c>
       <c r="P17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.80272727272727262</v>
+        <v>0.76933333333333342</v>
       </c>
       <c r="Q17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],Q$3)/100,"")</f>
@@ -13743,7 +13941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="39"/>
+      <c r="S17" s="36"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
@@ -13756,9 +13954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],W$3)/100,"")</f>
         <v>0.84</v>
       </c>
-      <c r="X17" s="16" t="str">
+      <c r="X17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.67749999999999999</v>
       </c>
       <c r="Y17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],Y$3)/100,"")</f>
@@ -13856,7 +14054,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="37"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -13898,7 +14096,7 @@
       </c>
       <c r="P18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.80272727272727262</v>
+        <v>0.76933333333333342</v>
       </c>
       <c r="Q18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -13908,7 +14106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="40"/>
+      <c r="S18" s="37"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
@@ -13921,9 +14119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
         <v>0.84</v>
       </c>
-      <c r="X18" s="10" t="str">
+      <c r="X18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.67749999999999999</v>
       </c>
       <c r="Y18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
@@ -14021,7 +14219,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="35" t="str">
+      <c r="E19" s="39" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -14076,7 +14274,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="41">
+      <c r="S19" s="35">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -14191,7 +14389,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="36"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -14233,7 +14431,7 @@
       </c>
       <c r="P20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.8163636363636364</v>
+        <v>0.81933333333333336</v>
       </c>
       <c r="Q20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],Q$3)/100,"")</f>
@@ -14243,7 +14441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="39"/>
+      <c r="S20" s="36"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
@@ -14256,9 +14454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],W$3)/100,"")</f>
         <v>0.83666666666666667</v>
       </c>
-      <c r="X20" s="16" t="str">
+      <c r="X20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.82750000000000001</v>
       </c>
       <c r="Y20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],Y$3)/100,"")</f>
@@ -14356,7 +14554,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="37"/>
+      <c r="E21" s="41"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -14398,7 +14596,7 @@
       </c>
       <c r="P21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.8163636363636364</v>
+        <v>0.81933333333333336</v>
       </c>
       <c r="Q21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -14408,7 +14606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="40"/>
+      <c r="S21" s="37"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
@@ -14421,9 +14619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
         <v>0.83666666666666667</v>
       </c>
-      <c r="X21" s="10" t="str">
+      <c r="X21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.82750000000000001</v>
       </c>
       <c r="Y21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
@@ -14521,7 +14719,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="35" t="str">
+      <c r="E22" s="39" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -14691,7 +14889,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="36"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -14733,7 +14931,7 @@
       </c>
       <c r="P23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
-        <v>6.0909090909090908</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="Q23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],Q$3),"")</f>
@@ -14743,7 +14941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="39"/>
+      <c r="S23" s="36"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6</v>
@@ -14756,9 +14954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],W$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="X23" s="12" t="str">
+      <c r="X23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],Y$3),"")</f>
@@ -14856,7 +15054,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="37"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -14898,7 +15096,7 @@
       </c>
       <c r="P24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.0909090909090908</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="Q24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -14908,7 +15106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="40"/>
+      <c r="S24" s="37"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6</v>
@@ -14921,9 +15119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="X24" s="9" t="str">
+      <c r="X24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -15021,7 +15219,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="35" t="str">
+      <c r="E25" s="39" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -15191,7 +15389,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="36"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -15233,7 +15431,7 @@
       </c>
       <c r="P26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
-        <v>7.2727272727272725</v>
+        <v>7.2</v>
       </c>
       <c r="Q26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],Q$3),"")</f>
@@ -15243,7 +15441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="39"/>
+      <c r="S26" s="36"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -15256,9 +15454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X26" s="12" t="str">
+      <c r="X26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],Y$3),"")</f>
@@ -15356,7 +15554,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="37"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -15398,7 +15596,7 @@
       </c>
       <c r="P27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.2727272727272725</v>
+        <v>7.2</v>
       </c>
       <c r="Q27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -15408,7 +15606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="40"/>
+      <c r="S27" s="37"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -15421,9 +15619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X27" s="9" t="str">
+      <c r="X27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -15521,7 +15719,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="35" t="str">
+      <c r="E28" s="39" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -15691,7 +15889,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="36"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -15743,7 +15941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="39"/>
+      <c r="S29" s="36"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15756,9 +15954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X29" s="12" t="str">
+      <c r="X29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],Y$3),"")</f>
@@ -15856,7 +16054,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="37"/>
+      <c r="E30" s="41"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -15908,7 +16106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="40"/>
+      <c r="S30" s="37"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -15921,9 +16119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X30" s="9" t="str">
+      <c r="X30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -16021,7 +16219,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="35" t="str">
+      <c r="E31" s="39" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -16191,7 +16389,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="36"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -16233,7 +16431,7 @@
       </c>
       <c r="P32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
-        <v>6.8181818181818183</v>
+        <v>6.8666666666666663</v>
       </c>
       <c r="Q32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],Q$3),"")</f>
@@ -16243,7 +16441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="39"/>
+      <c r="S32" s="36"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16256,9 +16454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],W$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="X32" s="12" t="str">
+      <c r="X32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],Y$3),"")</f>
@@ -16356,7 +16554,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="37"/>
+      <c r="E33" s="41"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -16398,7 +16596,7 @@
       </c>
       <c r="P33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.8181818181818183</v>
+        <v>6.8666666666666663</v>
       </c>
       <c r="Q33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -16408,7 +16606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="40"/>
+      <c r="S33" s="37"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16421,9 +16619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="X33" s="9" t="str">
+      <c r="X33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -16521,7 +16719,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="35" t="str">
+      <c r="E34" s="39" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -16691,7 +16889,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="36"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -16743,7 +16941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="39"/>
+      <c r="S35" s="36"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16756,9 +16954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X35" s="12" t="str">
+      <c r="X35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],Y$3),"")</f>
@@ -16856,7 +17054,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="37"/>
+      <c r="E36" s="41"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -16908,7 +17106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="40"/>
+      <c r="S36" s="37"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16921,9 +17119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>7</v>
       </c>
-      <c r="X36" s="9" t="str">
+      <c r="X36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -17021,7 +17219,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="35" t="str">
+      <c r="E37" s="39" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -17191,7 +17389,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="36"/>
+      <c r="E38" s="40"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -17233,7 +17431,7 @@
       </c>
       <c r="P38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
-        <v>6.2</v>
+        <v>6.4285714285714288</v>
       </c>
       <c r="Q38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],Q$3),"")</f>
@@ -17243,7 +17441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="39"/>
+      <c r="S38" s="36"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -17256,9 +17454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],W$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="X38" s="12" t="str">
+      <c r="X38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],Y$3),"")</f>
@@ -17356,7 +17554,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="37"/>
+      <c r="E39" s="41"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -17398,7 +17596,7 @@
       </c>
       <c r="P39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.2</v>
+        <v>6.4285714285714288</v>
       </c>
       <c r="Q39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -17408,7 +17606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="40"/>
+      <c r="S39" s="37"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -17421,9 +17619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="X39" s="9" t="str">
+      <c r="X39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -17521,7 +17719,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="35" t="str">
+      <c r="E40" s="39" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -17691,7 +17889,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="36"/>
+      <c r="E41" s="40"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -17733,7 +17931,7 @@
       </c>
       <c r="P41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
-        <v>8.125</v>
+        <v>8.3636363636363633</v>
       </c>
       <c r="Q41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],Q$3),"")</f>
@@ -17743,7 +17941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="39"/>
+      <c r="S41" s="36"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -17756,9 +17954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],W$3),"")</f>
         <v>9</v>
       </c>
-      <c r="X41" s="12" t="str">
+      <c r="X41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="Y41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],Y$3),"")</f>
@@ -17856,7 +18054,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="37"/>
+      <c r="E42" s="41"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -17898,7 +18096,7 @@
       </c>
       <c r="P42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.125</v>
+        <v>8.3636363636363633</v>
       </c>
       <c r="Q42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -17908,7 +18106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="40"/>
+      <c r="S42" s="37"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -17921,9 +18119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>9</v>
       </c>
-      <c r="X42" s="9" t="str">
+      <c r="X42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="Y42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -18021,7 +18219,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="35" t="str">
+      <c r="E43" s="39" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -18191,7 +18389,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="36"/>
+      <c r="E44" s="40"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -18233,7 +18431,7 @@
       </c>
       <c r="P44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
-        <v>7.4285714285714288</v>
+        <v>7.3</v>
       </c>
       <c r="Q44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],Q$3),"")</f>
@@ -18243,7 +18441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="39"/>
+      <c r="S44" s="36"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -18256,9 +18454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],W$3),"")</f>
         <v>8</v>
       </c>
-      <c r="X44" s="12" t="str">
+      <c r="X44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],Y$3),"")</f>
@@ -18356,7 +18554,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="37"/>
+      <c r="E45" s="41"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -18398,7 +18596,7 @@
       </c>
       <c r="P45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.4285714285714288</v>
+        <v>7.3</v>
       </c>
       <c r="Q45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18408,7 +18606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="40"/>
+      <c r="S45" s="37"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -18421,9 +18619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>8</v>
       </c>
-      <c r="X45" s="9" t="str">
+      <c r="X45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -18521,7 +18719,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="35" t="str">
+      <c r="E46" s="39" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -18576,7 +18774,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="41">
+      <c r="S46" s="35">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -18691,7 +18889,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="36"/>
+      <c r="E47" s="40"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -18733,7 +18931,7 @@
       </c>
       <c r="P47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.252</v>
+        <v>0.24249999999999999</v>
       </c>
       <c r="Q47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],Q$3)/100,"")</f>
@@ -18743,7 +18941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="39"/>
+      <c r="S47" s="36"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
@@ -18756,9 +18954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],W$3)/100,"")</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="X47" s="16" t="str">
+      <c r="X47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.21875</v>
       </c>
       <c r="Y47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],Y$3)/100,"")</f>
@@ -18856,7 +19054,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="37"/>
+      <c r="E48" s="41"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -18898,7 +19096,7 @@
       </c>
       <c r="P48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.252</v>
+        <v>0.24249999999999999</v>
       </c>
       <c r="Q48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -18908,7 +19106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="40"/>
+      <c r="S48" s="37"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
@@ -18921,9 +19119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="X48" s="10" t="str">
+      <c r="X48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.21875</v>
       </c>
       <c r="Y48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
@@ -19021,7 +19219,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="35" t="str">
+      <c r="E49" s="39" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -19076,7 +19274,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="41">
+      <c r="S49" s="35">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -19191,7 +19389,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="36"/>
+      <c r="E50" s="40"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -19233,7 +19431,7 @@
       </c>
       <c r="P50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24681818181818183</v>
+        <v>0.24233333333333335</v>
       </c>
       <c r="Q50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19243,7 +19441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="39"/>
+      <c r="S50" s="36"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
@@ -19256,9 +19454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],W$3)/100,"")</f>
         <v>0.21333333333333332</v>
       </c>
-      <c r="X50" s="16" t="str">
+      <c r="X50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.23</v>
       </c>
       <c r="Y50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],Y$3)/100,"")</f>
@@ -19356,7 +19554,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="37"/>
+      <c r="E51" s="41"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -19398,7 +19596,7 @@
       </c>
       <c r="P51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24681818181818183</v>
+        <v>0.24233333333333335</v>
       </c>
       <c r="Q51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19408,7 +19606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="40"/>
+      <c r="S51" s="37"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
@@ -19421,9 +19619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
         <v>0.21333333333333332</v>
       </c>
-      <c r="X51" s="10" t="str">
+      <c r="X51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.23</v>
       </c>
       <c r="Y51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
@@ -19521,7 +19719,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="35" t="str">
+      <c r="E52" s="39" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -19576,7 +19774,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="41">
+      <c r="S52" s="35">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -19691,7 +19889,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="36"/>
+      <c r="E53" s="40"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -19733,7 +19931,7 @@
       </c>
       <c r="P53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.65454545454545454</v>
+        <v>0.65</v>
       </c>
       <c r="Q53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19743,7 +19941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="39"/>
+      <c r="S53" s="36"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
@@ -19756,9 +19954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],W$3)/100,"")</f>
         <v>0.65</v>
       </c>
-      <c r="X53" s="16" t="str">
+      <c r="X53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.63749999999999996</v>
       </c>
       <c r="Y53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],Y$3)/100,"")</f>
@@ -19856,7 +20054,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="37"/>
+      <c r="E54" s="41"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -19898,7 +20096,7 @@
       </c>
       <c r="P54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.65454545454545454</v>
+        <v>0.65</v>
       </c>
       <c r="Q54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19908,7 +20106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="40"/>
+      <c r="S54" s="37"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
@@ -19921,9 +20119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
         <v>0.65</v>
       </c>
-      <c r="X54" s="10" t="str">
+      <c r="X54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.63749999999999996</v>
       </c>
       <c r="Y54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
@@ -20021,7 +20219,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="35" t="str">
+      <c r="E55" s="39" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -20076,7 +20274,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="41">
+      <c r="S55" s="35">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -20191,7 +20389,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="36"/>
+      <c r="E56" s="40"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -20233,7 +20431,7 @@
       </c>
       <c r="P56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.14545454545454545</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="Q56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],Q$3)/100,"")</f>
@@ -20243,7 +20441,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="39"/>
+      <c r="S56" s="36"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
@@ -20256,9 +20454,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],W$3)/100,"")</f>
         <v>0.15</v>
       </c>
-      <c r="X56" s="16" t="str">
+      <c r="X56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="Y56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],Y$3)/100,"")</f>
@@ -20356,7 +20554,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="37"/>
+      <c r="E57" s="41"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -20398,7 +20596,7 @@
       </c>
       <c r="P57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.14545454545454545</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="Q57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20408,7 +20606,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="40"/>
+      <c r="S57" s="37"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
@@ -20421,9 +20619,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],W$3)/100,"")</f>
         <v>0.15</v>
       </c>
-      <c r="X57" s="10" t="str">
+      <c r="X57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
-        <v/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="Y57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
@@ -20521,7 +20719,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="35" t="str">
+      <c r="E58" s="39" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -20691,7 +20889,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="36"/>
+      <c r="E59" s="40"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -20733,7 +20931,7 @@
       </c>
       <c r="P59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
-        <v>8.8000000000000007</v>
+        <v>8.7142857142857135</v>
       </c>
       <c r="Q59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],Q$3),"")</f>
@@ -20743,7 +20941,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="39"/>
+      <c r="S59" s="36"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -20756,9 +20954,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],W$3),"")</f>
         <v>8</v>
       </c>
-      <c r="X59" s="12" t="str">
+      <c r="X59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="Y59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],Y$3),"")</f>
@@ -20856,7 +21054,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="37"/>
+      <c r="E60" s="41"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -20898,7 +21096,7 @@
       </c>
       <c r="P60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.8000000000000007</v>
+        <v>8.7142857142857135</v>
       </c>
       <c r="Q60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -20908,7 +21106,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="40"/>
+      <c r="S60" s="37"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -20921,9 +21119,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],W$3),"")</f>
         <v>8</v>
       </c>
-      <c r="X60" s="9" t="str">
+      <c r="X60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],X$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="Y60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],Y$3),"")</f>
@@ -21058,7 +21256,9 @@
       <c r="W118" t="s">
         <v>575</v>
       </c>
-      <c r="X118"/>
+      <c r="X118" t="s">
+        <v>595</v>
+      </c>
       <c r="Y118"/>
       <c r="Z118"/>
       <c r="AA118"/>
@@ -21077,16 +21277,18 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -21103,18 +21305,16 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -21353,7 +21553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL199"/>
+  <dimension ref="A1:AL203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -43185,6 +43385,474 @@
         <v>10073</v>
       </c>
     </row>
+    <row r="200" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B200" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E200" t="s">
+        <v>18</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="G200" s="3">
+        <v>2</v>
+      </c>
+      <c r="H200" s="3">
+        <v>7</v>
+      </c>
+      <c r="I200" s="3">
+        <v>7</v>
+      </c>
+      <c r="J200" s="3">
+        <v>7</v>
+      </c>
+      <c r="K200" s="3">
+        <v>5</v>
+      </c>
+      <c r="L200">
+        <v>38</v>
+      </c>
+      <c r="M200">
+        <v>12</v>
+      </c>
+      <c r="N200">
+        <v>62</v>
+      </c>
+      <c r="O200">
+        <v>88</v>
+      </c>
+      <c r="P200" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q200" s="3">
+        <v>7</v>
+      </c>
+      <c r="R200" s="3">
+        <v>7</v>
+      </c>
+      <c r="S200" s="3">
+        <v>7</v>
+      </c>
+      <c r="T200" s="3">
+        <v>7</v>
+      </c>
+      <c r="U200" s="3">
+        <v>7</v>
+      </c>
+      <c r="V200" t="s">
+        <v>169</v>
+      </c>
+      <c r="W200" s="3">
+        <v>10</v>
+      </c>
+      <c r="X200" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y200">
+        <v>37</v>
+      </c>
+      <c r="Z200">
+        <v>18.5</v>
+      </c>
+      <c r="AA200">
+        <v>47</v>
+      </c>
+      <c r="AB200">
+        <v>6</v>
+      </c>
+      <c r="AC200">
+        <v>23.5</v>
+      </c>
+      <c r="AD200">
+        <v>70</v>
+      </c>
+      <c r="AE200">
+        <v>4</v>
+      </c>
+      <c r="AF200">
+        <v>20</v>
+      </c>
+      <c r="AG200" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH200" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI200" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ200" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK200" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL200">
+        <v>13753</v>
+      </c>
+    </row>
+    <row r="201" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B201" t="s">
+        <v>596</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E201" t="s">
+        <v>18</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="G201" s="3">
+        <v>2</v>
+      </c>
+      <c r="H201" s="3">
+        <v>7</v>
+      </c>
+      <c r="I201" s="3">
+        <v>7</v>
+      </c>
+      <c r="J201" s="3">
+        <v>7</v>
+      </c>
+      <c r="K201" s="3">
+        <v>7</v>
+      </c>
+      <c r="L201">
+        <v>32</v>
+      </c>
+      <c r="M201">
+        <v>16</v>
+      </c>
+      <c r="N201">
+        <v>68</v>
+      </c>
+      <c r="O201">
+        <v>84</v>
+      </c>
+      <c r="P201" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q201" s="3">
+        <v>7</v>
+      </c>
+      <c r="R201" s="3">
+        <v>7</v>
+      </c>
+      <c r="S201" s="3">
+        <v>7</v>
+      </c>
+      <c r="T201" s="3">
+        <v>7</v>
+      </c>
+      <c r="U201" s="3">
+        <v>7</v>
+      </c>
+      <c r="V201" t="s">
+        <v>169</v>
+      </c>
+      <c r="W201" s="3">
+        <v>7</v>
+      </c>
+      <c r="X201" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y201">
+        <v>48</v>
+      </c>
+      <c r="Z201">
+        <v>24</v>
+      </c>
+      <c r="AA201">
+        <v>44</v>
+      </c>
+      <c r="AB201">
+        <v>8</v>
+      </c>
+      <c r="AC201">
+        <v>22</v>
+      </c>
+      <c r="AD201">
+        <v>60</v>
+      </c>
+      <c r="AE201">
+        <v>5</v>
+      </c>
+      <c r="AF201">
+        <v>25</v>
+      </c>
+      <c r="AG201" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH201" s="3">
+        <v>995638</v>
+      </c>
+      <c r="AI201" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ201" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK201" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL201">
+        <v>15998</v>
+      </c>
+    </row>
+    <row r="202" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B202" t="s">
+        <v>598</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E202" t="s">
+        <v>18</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="G202" s="3">
+        <v>2</v>
+      </c>
+      <c r="H202" s="3">
+        <v>7</v>
+      </c>
+      <c r="I202" s="3">
+        <v>7</v>
+      </c>
+      <c r="J202" s="3">
+        <v>7</v>
+      </c>
+      <c r="K202" s="3">
+        <v>5</v>
+      </c>
+      <c r="L202">
+        <v>37</v>
+      </c>
+      <c r="M202">
+        <v>24</v>
+      </c>
+      <c r="N202">
+        <v>63</v>
+      </c>
+      <c r="O202">
+        <v>76</v>
+      </c>
+      <c r="P202" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q202" s="3">
+        <v>7</v>
+      </c>
+      <c r="R202" s="3">
+        <v>7</v>
+      </c>
+      <c r="S202" s="3">
+        <v>7</v>
+      </c>
+      <c r="T202" s="3">
+        <v>7</v>
+      </c>
+      <c r="U202" s="3">
+        <v>7</v>
+      </c>
+      <c r="V202" t="s">
+        <v>169</v>
+      </c>
+      <c r="W202" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X202" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y202">
+        <v>33</v>
+      </c>
+      <c r="Z202">
+        <v>16.5</v>
+      </c>
+      <c r="AA202">
+        <v>55</v>
+      </c>
+      <c r="AB202">
+        <v>8</v>
+      </c>
+      <c r="AC202">
+        <v>27.500000000000004</v>
+      </c>
+      <c r="AD202">
+        <v>60</v>
+      </c>
+      <c r="AE202">
+        <v>7</v>
+      </c>
+      <c r="AF202">
+        <v>35</v>
+      </c>
+      <c r="AG202" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH202" s="3">
+        <v>42838</v>
+      </c>
+      <c r="AI202" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ202" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK202" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL202">
+        <v>29574</v>
+      </c>
+    </row>
+    <row r="203" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B203" t="s">
+        <v>601</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E203" t="s">
+        <v>18</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="G203" s="3">
+        <v>2</v>
+      </c>
+      <c r="H203" s="3">
+        <v>7</v>
+      </c>
+      <c r="I203" s="3">
+        <v>7</v>
+      </c>
+      <c r="J203" s="3">
+        <v>7</v>
+      </c>
+      <c r="K203" s="3">
+        <v>5</v>
+      </c>
+      <c r="L203">
+        <v>22</v>
+      </c>
+      <c r="M203">
+        <v>17</v>
+      </c>
+      <c r="N203">
+        <v>78</v>
+      </c>
+      <c r="O203">
+        <v>83</v>
+      </c>
+      <c r="P203" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q203" s="3">
+        <v>7</v>
+      </c>
+      <c r="R203" s="3">
+        <v>7</v>
+      </c>
+      <c r="S203" s="3">
+        <v>7</v>
+      </c>
+      <c r="T203" s="3">
+        <v>7</v>
+      </c>
+      <c r="U203" s="3">
+        <v>7</v>
+      </c>
+      <c r="V203" t="s">
+        <v>169</v>
+      </c>
+      <c r="W203" s="3">
+        <v>10</v>
+      </c>
+      <c r="X203" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y203">
+        <v>57</v>
+      </c>
+      <c r="Z203">
+        <v>28.499999999999996</v>
+      </c>
+      <c r="AA203">
+        <v>38</v>
+      </c>
+      <c r="AB203">
+        <v>7</v>
+      </c>
+      <c r="AC203">
+        <v>19</v>
+      </c>
+      <c r="AD203">
+        <v>65</v>
+      </c>
+      <c r="AE203">
+        <v>2</v>
+      </c>
+      <c r="AF203">
+        <v>10</v>
+      </c>
+      <c r="AG203" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH203" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI203" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ203" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK203" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL203">
+        <v>33762</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="615">
   <si>
     <t>ID</t>
   </si>
@@ -1864,6 +1864,42 @@
   </si>
   <si>
     <t>02/10/2026 16:21:35</t>
+  </si>
+  <si>
+    <t>6ac7793df6baa94e5914b017</t>
+  </si>
+  <si>
+    <t>07/10/2026 21:53:55</t>
+  </si>
+  <si>
+    <t>08/10/2026 08:06:37</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>6ac7793cf6baa94e5914b011</t>
+  </si>
+  <si>
+    <t>07/10/2026 17:30:47</t>
+  </si>
+  <si>
+    <t>08/10/2026 08:06:36</t>
+  </si>
+  <si>
+    <t>6ac77861486c261c1cacc928</t>
+  </si>
+  <si>
+    <t>07/10/2026 20:40:30</t>
+  </si>
+  <si>
+    <t>08/10/2026 08:02:57</t>
+  </si>
+  <si>
+    <t>6ac77861486c261c1cacc916</t>
+  </si>
+  <si>
+    <t>07/10/2026 16:21:03</t>
   </si>
   <si>
     <t>6ac5da49636e383ab3c2e97e</t>
@@ -2676,7 +2712,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46302.469674305554" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="202">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46303.641959259257" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="206">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2708,7 +2744,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="49">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="50">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2757,6 +2793,7 @@
         <s v="01/10/2026"/>
         <s v="05/10/2026"/>
         <s v="02/10/2026"/>
+        <s v="07/10/2026"/>
         <s v="06/10/2026"/>
       </sharedItems>
     </cacheField>
@@ -2866,7 +2903,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="202">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="206">
   <r>
     <x v="0"/>
     <m/>
@@ -10789,11 +10826,171 @@
   </r>
   <r>
     <x v="9"/>
+    <s v="6ac7793df6baa94e5914b017"/>
+    <s v="07/10/2026 21:53:55"/>
+    <s v="08/10/2026 08:06:37"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="37"/>
+    <n v="22"/>
+    <n v="63"/>
+    <n v="78"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="59"/>
+    <n v="29.5"/>
+    <n v="40"/>
+    <n v="7"/>
+    <n v="20"/>
+    <n v="65"/>
+    <n v="6"/>
+    <n v="30"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="15353"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac7793cf6baa94e5914b011"/>
+    <s v="07/10/2026 17:30:47"/>
+    <s v="08/10/2026 08:06:36"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="36"/>
+    <n v="27"/>
+    <n v="64"/>
+    <n v="73"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="51"/>
+    <n v="25.5"/>
+    <n v="37"/>
+    <n v="6"/>
+    <n v="18.5"/>
+    <n v="70"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="42862"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Selagem está conforme,_x000a_Data  de validade e produção estão de acordo"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="11342"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac77861486c261c1cacc928"/>
+    <s v="07/10/2026 20:40:30"/>
+    <s v="08/10/2026 08:02:57"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <s v=""/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="43"/>
+    <n v="25"/>
+    <n v="57"/>
+    <n v="75"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="31"/>
+    <n v="15.5"/>
+    <n v="44"/>
+    <n v="7"/>
+    <n v="22"/>
+    <n v="65"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="992039"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="4965"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac77861486c261c1cacc916"/>
+    <s v="07/10/2026 16:21:03"/>
+    <s v="08/10/2026 08:02:57"/>
+    <s v="Ranieli"/>
+    <x v="48"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="21"/>
+    <n v="71"/>
+    <n v="79"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="40"/>
+    <n v="20"/>
+    <n v="41"/>
+    <n v="6"/>
+    <n v="20.5"/>
+    <n v="70"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="35072"/>
+  </r>
+  <r>
+    <x v="9"/>
     <s v="6ac5da49636e383ab3c2e97e"/>
     <s v="06/10/2026 22:00:17"/>
     <s v="07/10/2026 02:36:09"/>
     <s v="Ranieli"/>
-    <x v="48"/>
+    <x v="49"/>
     <n v="2"/>
     <n v="7"/>
     <n v="7"/>
@@ -10833,7 +11030,7 @@
     <s v="06/10/2026 21:22:17"/>
     <s v="07/10/2026 02:36:09"/>
     <s v="Ranieli"/>
-    <x v="48"/>
+    <x v="49"/>
     <n v="2"/>
     <n v="7"/>
     <n v="7"/>
@@ -10873,7 +11070,7 @@
     <s v="06/10/2026 17:33:08"/>
     <s v="07/10/2026 02:36:08"/>
     <s v="Ranieli"/>
-    <x v="48"/>
+    <x v="49"/>
     <n v="2"/>
     <n v="7"/>
     <n v="7"/>
@@ -10913,7 +11110,7 @@
     <s v="06/10/2026 16:22:08"/>
     <s v="07/10/2026 02:36:08"/>
     <s v="Ranieli"/>
-    <x v="48"/>
+    <x v="49"/>
     <n v="2"/>
     <n v="7"/>
     <n v="7"/>
@@ -10951,8 +11148,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:X118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="U117:Y118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="11">
@@ -10974,7 +11171,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="50">
+      <items count="51">
         <item x="26"/>
         <item x="45"/>
         <item x="28"/>
@@ -10983,8 +11180,9 @@
         <item x="14"/>
         <item x="46"/>
         <item x="13"/>
+        <item x="49"/>
+        <item x="12"/>
         <item x="48"/>
-        <item x="12"/>
         <item x="29"/>
         <item x="32"/>
         <item x="11"/>
@@ -11066,7 +11264,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="5">
     <i>
       <x v="1"/>
     </i>
@@ -11078,6 +11276,9 @@
     </i>
     <i>
       <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -11163,8 +11364,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL203" totalsRowShown="0">
-  <autoFilter ref="A1:AL203"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL207" totalsRowShown="0">
+  <autoFilter ref="A1:AL207"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -11625,7 +11826,7 @@
       </c>
       <c r="Y3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>07/10/2026</v>
       </c>
       <c r="Z3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -11958,9 +12159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y5" s="12" t="str">
+      <c r="Y5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],Z$3),"")</f>
@@ -12123,9 +12324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y6" s="9" t="str">
+      <c r="Y6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -12431,7 +12632,7 @@
       </c>
       <c r="P8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
-        <v>7.4</v>
+        <v>7.3157894736842106</v>
       </c>
       <c r="Q8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],Q$3),"")</f>
@@ -12458,9 +12659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y8" s="12" t="str">
+      <c r="Y8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],Z$3),"")</f>
@@ -12596,7 +12797,7 @@
       </c>
       <c r="P9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.4</v>
+        <v>7.3157894736842106</v>
       </c>
       <c r="Q9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -12623,9 +12824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y9" s="9" t="str">
+      <c r="Y9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -12958,9 +13159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y11" s="12" t="str">
+      <c r="Y11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],Z$3),"")</f>
@@ -13123,9 +13324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y12" s="9" t="str">
+      <c r="Y12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -13431,7 +13632,7 @@
       </c>
       <c r="P14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
-        <v>5.5333333333333332</v>
+        <v>5.4210526315789478</v>
       </c>
       <c r="Q14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],Q$3),"")</f>
@@ -13458,9 +13659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],X$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="Y14" s="12" t="str">
+      <c r="Y14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Z14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],Z$3),"")</f>
@@ -13596,7 +13797,7 @@
       </c>
       <c r="P15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>5.5333333333333332</v>
+        <v>5.4210526315789478</v>
       </c>
       <c r="Q15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -13623,9 +13824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>5.5</v>
       </c>
-      <c r="Y15" s="9" t="str">
+      <c r="Y15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Z15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -13931,7 +14132,7 @@
       </c>
       <c r="P17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.76933333333333342</v>
+        <v>0.74157894736842112</v>
       </c>
       <c r="Q17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],Q$3)/100,"")</f>
@@ -13958,9 +14159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],X$3)/100,"")</f>
         <v>0.67749999999999999</v>
       </c>
-      <c r="Y17" s="16" t="str">
+      <c r="Y17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.63749999999999996</v>
       </c>
       <c r="Z17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],Z$3)/100,"")</f>
@@ -14096,7 +14297,7 @@
       </c>
       <c r="P18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.76933333333333342</v>
+        <v>0.74157894736842112</v>
       </c>
       <c r="Q18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -14123,9 +14324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
         <v>0.67749999999999999</v>
       </c>
-      <c r="Y18" s="10" t="str">
+      <c r="Y18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.63749999999999996</v>
       </c>
       <c r="Z18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
@@ -14431,7 +14632,7 @@
       </c>
       <c r="P20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.81933333333333336</v>
+        <v>0.80736842105263162</v>
       </c>
       <c r="Q20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],Q$3)/100,"")</f>
@@ -14458,9 +14659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],X$3)/100,"")</f>
         <v>0.82750000000000001</v>
       </c>
-      <c r="Y20" s="16" t="str">
+      <c r="Y20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.76249999999999996</v>
       </c>
       <c r="Z20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],Z$3)/100,"")</f>
@@ -14596,7 +14797,7 @@
       </c>
       <c r="P21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.81933333333333336</v>
+        <v>0.80736842105263162</v>
       </c>
       <c r="Q21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -14623,9 +14824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
         <v>0.82750000000000001</v>
       </c>
-      <c r="Y21" s="10" t="str">
+      <c r="Y21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.76249999999999996</v>
       </c>
       <c r="Z21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
@@ -14931,7 +15132,7 @@
       </c>
       <c r="P23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
-        <v>6.333333333333333</v>
+        <v>6.4736842105263159</v>
       </c>
       <c r="Q23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],Q$3),"")</f>
@@ -14958,9 +15159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y23" s="12" t="str">
+      <c r="Y23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],Z$3),"")</f>
@@ -15096,7 +15297,7 @@
       </c>
       <c r="P24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.333333333333333</v>
+        <v>6.4736842105263159</v>
       </c>
       <c r="Q24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -15123,9 +15324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y24" s="9" t="str">
+      <c r="Y24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -15431,7 +15632,7 @@
       </c>
       <c r="P26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
-        <v>7.2</v>
+        <v>7.1578947368421053</v>
       </c>
       <c r="Q26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],Q$3),"")</f>
@@ -15458,9 +15659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y26" s="12" t="str">
+      <c r="Y26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],Z$3),"")</f>
@@ -15596,7 +15797,7 @@
       </c>
       <c r="P27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.2</v>
+        <v>7.1578947368421053</v>
       </c>
       <c r="Q27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -15623,9 +15824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y27" s="9" t="str">
+      <c r="Y27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -15958,9 +16159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y29" s="12" t="str">
+      <c r="Y29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],Z$3),"")</f>
@@ -16123,9 +16324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y30" s="9" t="str">
+      <c r="Y30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -16431,7 +16632,7 @@
       </c>
       <c r="P32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
-        <v>6.8666666666666663</v>
+        <v>6.8947368421052628</v>
       </c>
       <c r="Q32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],Q$3),"")</f>
@@ -16458,9 +16659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y32" s="12" t="str">
+      <c r="Y32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],Z$3),"")</f>
@@ -16596,7 +16797,7 @@
       </c>
       <c r="P33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.8666666666666663</v>
+        <v>6.8947368421052628</v>
       </c>
       <c r="Q33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -16623,9 +16824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y33" s="9" t="str">
+      <c r="Y33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -16958,9 +17159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y35" s="12" t="str">
+      <c r="Y35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],Z$3),"")</f>
@@ -17123,9 +17324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y36" s="9" t="str">
+      <c r="Y36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -17431,7 +17632,7 @@
       </c>
       <c r="P38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
-        <v>6.4285714285714288</v>
+        <v>6.4444444444444446</v>
       </c>
       <c r="Q38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],Q$3),"")</f>
@@ -17458,9 +17659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y38" s="12" t="str">
+      <c r="Y38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="Z38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],Z$3),"")</f>
@@ -17596,7 +17797,7 @@
       </c>
       <c r="P39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.4285714285714288</v>
+        <v>6.4444444444444446</v>
       </c>
       <c r="Q39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -17623,9 +17824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y39" s="9" t="str">
+      <c r="Y39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="Z39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -17931,7 +18132,7 @@
       </c>
       <c r="P41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
-        <v>8.3636363636363633</v>
+        <v>8.384615384615385</v>
       </c>
       <c r="Q41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],Q$3),"")</f>
@@ -17958,9 +18159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],X$3),"")</f>
         <v>9</v>
       </c>
-      <c r="Y41" s="12" t="str">
+      <c r="Y41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="Z41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],Z$3),"")</f>
@@ -18096,7 +18297,7 @@
       </c>
       <c r="P42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.3636363636363633</v>
+        <v>8.384615384615385</v>
       </c>
       <c r="Q42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18123,9 +18324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>9</v>
       </c>
-      <c r="Y42" s="9" t="str">
+      <c r="Y42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="Z42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -18431,7 +18632,7 @@
       </c>
       <c r="P44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="Q44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],Q$3),"")</f>
@@ -18458,9 +18659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y44" s="12" t="str">
+      <c r="Y44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],Z$3),"")</f>
@@ -18596,7 +18797,7 @@
       </c>
       <c r="P45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="Q45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18623,9 +18824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Y45" s="9" t="str">
+      <c r="Y45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -18931,7 +19132,7 @@
       </c>
       <c r="P47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24249999999999999</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="Q47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],Q$3)/100,"")</f>
@@ -18958,9 +19159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],X$3)/100,"")</f>
         <v>0.21875</v>
       </c>
-      <c r="Y47" s="16" t="str">
+      <c r="Y47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.22625000000000001</v>
       </c>
       <c r="Z47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],Z$3)/100,"")</f>
@@ -19096,7 +19297,7 @@
       </c>
       <c r="P48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24249999999999999</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="Q48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19123,9 +19324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
         <v>0.21875</v>
       </c>
-      <c r="Y48" s="10" t="str">
+      <c r="Y48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.22625000000000001</v>
       </c>
       <c r="Z48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
@@ -19431,7 +19632,7 @@
       </c>
       <c r="P50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24233333333333335</v>
+        <v>0.23394736842105263</v>
       </c>
       <c r="Q50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19458,9 +19659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],X$3)/100,"")</f>
         <v>0.23</v>
       </c>
-      <c r="Y50" s="16" t="str">
+      <c r="Y50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.20250000000000001</v>
       </c>
       <c r="Z50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],Z$3)/100,"")</f>
@@ -19596,7 +19797,7 @@
       </c>
       <c r="P51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24233333333333335</v>
+        <v>0.23394736842105263</v>
       </c>
       <c r="Q51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19623,9 +19824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
         <v>0.23</v>
       </c>
-      <c r="Y51" s="10" t="str">
+      <c r="Y51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.20250000000000001</v>
       </c>
       <c r="Z51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
@@ -19931,7 +20132,7 @@
       </c>
       <c r="P53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.65</v>
+        <v>0.65526315789473688</v>
       </c>
       <c r="Q53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19958,9 +20159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],X$3)/100,"")</f>
         <v>0.63749999999999996</v>
       </c>
-      <c r="Y53" s="16" t="str">
+      <c r="Y53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="Z53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],Z$3)/100,"")</f>
@@ -20096,7 +20297,7 @@
       </c>
       <c r="P54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.65</v>
+        <v>0.65526315789473688</v>
       </c>
       <c r="Q54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20123,9 +20324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
         <v>0.63749999999999996</v>
       </c>
-      <c r="Y54" s="10" t="str">
+      <c r="Y54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="Z54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
@@ -20431,7 +20632,7 @@
       </c>
       <c r="P56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.16666666666666669</v>
+        <v>0.18421052631578949</v>
       </c>
       <c r="Q56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],Q$3)/100,"")</f>
@@ -20458,9 +20659,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],X$3)/100,"")</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="Y56" s="16" t="str">
+      <c r="Y56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.25</v>
       </c>
       <c r="Z56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],Z$3)/100,"")</f>
@@ -20596,7 +20797,7 @@
       </c>
       <c r="P57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.16666666666666669</v>
+        <v>0.18421052631578949</v>
       </c>
       <c r="Q57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20623,9 +20824,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],X$3)/100,"")</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="Y57" s="10" t="str">
+      <c r="Y57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
-        <v/>
+        <v>0.25</v>
       </c>
       <c r="Z57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
@@ -20931,7 +21132,7 @@
       </c>
       <c r="P59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
-        <v>8.7142857142857135</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="Q59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],Q$3),"")</f>
@@ -20958,9 +21159,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],X$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="Y59" s="12" t="str">
+      <c r="Y59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="Z59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],Z$3),"")</f>
@@ -21096,7 +21297,7 @@
       </c>
       <c r="P60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.7142857142857135</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="Q60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -21123,9 +21324,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],X$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="Y60" s="9" t="str">
+      <c r="Y60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],Y$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="Z60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],Z$3),"")</f>
@@ -21257,9 +21458,11 @@
         <v>575</v>
       </c>
       <c r="X118" t="s">
+        <v>607</v>
+      </c>
+      <c r="Y118" t="s">
         <v>595</v>
       </c>
-      <c r="Y118"/>
       <c r="Z118"/>
       <c r="AA118"/>
       <c r="AB118"/>
@@ -21553,7 +21756,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL203"/>
+  <dimension ref="A1:AL207"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
@@ -43421,16 +43624,16 @@
         <v>5</v>
       </c>
       <c r="L200">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M200">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="N200">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O200">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="P200" s="3">
         <v>7</v>
@@ -43453,35 +43656,35 @@
       <c r="V200" t="s">
         <v>169</v>
       </c>
-      <c r="W200" s="3">
-        <v>10</v>
-      </c>
-      <c r="X200" s="3">
-        <v>7</v>
+      <c r="W200" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X200" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="Y200">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="Z200">
-        <v>18.5</v>
+        <v>29.5</v>
       </c>
       <c r="AA200">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AB200">
+        <v>7</v>
+      </c>
+      <c r="AC200">
+        <v>20</v>
+      </c>
+      <c r="AD200">
+        <v>65</v>
+      </c>
+      <c r="AE200">
         <v>6</v>
       </c>
-      <c r="AC200">
-        <v>23.5</v>
-      </c>
-      <c r="AD200">
-        <v>70</v>
-      </c>
-      <c r="AE200">
-        <v>4</v>
-      </c>
       <c r="AF200">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AG200" s="3">
         <v>7</v>
@@ -43499,7 +43702,7 @@
         <v>22</v>
       </c>
       <c r="AL200">
-        <v>13753</v>
+        <v>15353</v>
       </c>
     </row>
     <row r="201" spans="1:38" x14ac:dyDescent="0.25">
@@ -43514,7 +43717,7 @@
         <v>597</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="E201" t="s">
         <v>18</v>
@@ -43535,19 +43738,19 @@
         <v>7</v>
       </c>
       <c r="K201" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L201">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M201">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N201">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O201">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="P201" s="3">
         <v>7</v>
@@ -43571,43 +43774,43 @@
         <v>169</v>
       </c>
       <c r="W201" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X201" s="3">
         <v>7</v>
       </c>
       <c r="Y201">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Z201">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="AA201">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AB201">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC201">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AD201">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AE201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF201">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AG201" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AH201" s="3">
-        <v>995638</v>
+        <v>42862</v>
       </c>
       <c r="AI201" t="s">
-        <v>63</v>
+        <v>323</v>
       </c>
       <c r="AJ201" t="s">
         <v>22</v>
@@ -43616,7 +43819,7 @@
         <v>22</v>
       </c>
       <c r="AL201">
-        <v>15998</v>
+        <v>11342</v>
       </c>
     </row>
     <row r="202" spans="1:38" x14ac:dyDescent="0.25">
@@ -43625,13 +43828,13 @@
         <v>OUT</v>
       </c>
       <c r="B202" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E202" t="s">
         <v>18</v>
@@ -43642,8 +43845,8 @@
       <c r="G202" s="3">
         <v>2</v>
       </c>
-      <c r="H202" s="3">
-        <v>7</v>
+      <c r="H202" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="I202" s="3">
         <v>7</v>
@@ -43655,16 +43858,16 @@
         <v>5</v>
       </c>
       <c r="L202">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M202">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N202">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="O202">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P202" s="3">
         <v>7</v>
@@ -43682,10 +43885,10 @@
         <v>7</v>
       </c>
       <c r="U202" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V202" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="W202" s="3" t="s">
         <v>28</v>
@@ -43694,37 +43897,37 @@
         <v>28</v>
       </c>
       <c r="Y202">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Z202">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA202">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB202">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC202">
-        <v>27.500000000000004</v>
+        <v>22</v>
       </c>
       <c r="AD202">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AE202">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF202">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AG202" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AH202" s="3">
-        <v>42838</v>
+        <v>992039</v>
       </c>
       <c r="AI202" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="AJ202" t="s">
         <v>22</v>
@@ -43733,7 +43936,7 @@
         <v>22</v>
       </c>
       <c r="AL202">
-        <v>29574</v>
+        <v>4965</v>
       </c>
     </row>
     <row r="203" spans="1:38" x14ac:dyDescent="0.25">
@@ -43742,13 +43945,13 @@
         <v>OUT</v>
       </c>
       <c r="B203" t="s">
+        <v>602</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="E203" t="s">
         <v>18</v>
@@ -43772,16 +43975,16 @@
         <v>5</v>
       </c>
       <c r="L203">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M203">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N203">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O203">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P203" s="3">
         <v>7</v>
@@ -43805,34 +44008,34 @@
         <v>169</v>
       </c>
       <c r="W203" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X203" s="3">
         <v>7</v>
       </c>
       <c r="Y203">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="Z203">
-        <v>28.499999999999996</v>
+        <v>20</v>
       </c>
       <c r="AA203">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AB203">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC203">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="AD203">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AE203">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF203">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AG203" s="3">
         <v>10</v>
@@ -43841,7 +44044,7 @@
         <v>15105</v>
       </c>
       <c r="AI203" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="AJ203" t="s">
         <v>22</v>
@@ -43850,6 +44053,474 @@
         <v>22</v>
       </c>
       <c r="AL203">
+        <v>35072</v>
+      </c>
+    </row>
+    <row r="204" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B204" t="s">
+        <v>604</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E204" t="s">
+        <v>18</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="G204" s="3">
+        <v>2</v>
+      </c>
+      <c r="H204" s="3">
+        <v>7</v>
+      </c>
+      <c r="I204" s="3">
+        <v>7</v>
+      </c>
+      <c r="J204" s="3">
+        <v>7</v>
+      </c>
+      <c r="K204" s="3">
+        <v>5</v>
+      </c>
+      <c r="L204">
+        <v>38</v>
+      </c>
+      <c r="M204">
+        <v>12</v>
+      </c>
+      <c r="N204">
+        <v>62</v>
+      </c>
+      <c r="O204">
+        <v>88</v>
+      </c>
+      <c r="P204" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q204" s="3">
+        <v>7</v>
+      </c>
+      <c r="R204" s="3">
+        <v>7</v>
+      </c>
+      <c r="S204" s="3">
+        <v>7</v>
+      </c>
+      <c r="T204" s="3">
+        <v>7</v>
+      </c>
+      <c r="U204" s="3">
+        <v>7</v>
+      </c>
+      <c r="V204" t="s">
+        <v>169</v>
+      </c>
+      <c r="W204" s="3">
+        <v>10</v>
+      </c>
+      <c r="X204" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y204">
+        <v>37</v>
+      </c>
+      <c r="Z204">
+        <v>18.5</v>
+      </c>
+      <c r="AA204">
+        <v>47</v>
+      </c>
+      <c r="AB204">
+        <v>6</v>
+      </c>
+      <c r="AC204">
+        <v>23.5</v>
+      </c>
+      <c r="AD204">
+        <v>70</v>
+      </c>
+      <c r="AE204">
+        <v>4</v>
+      </c>
+      <c r="AF204">
+        <v>20</v>
+      </c>
+      <c r="AG204" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH204" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI204" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ204" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK204" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL204">
+        <v>13753</v>
+      </c>
+    </row>
+    <row r="205" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B205" t="s">
+        <v>608</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E205" t="s">
+        <v>18</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="G205" s="3">
+        <v>2</v>
+      </c>
+      <c r="H205" s="3">
+        <v>7</v>
+      </c>
+      <c r="I205" s="3">
+        <v>7</v>
+      </c>
+      <c r="J205" s="3">
+        <v>7</v>
+      </c>
+      <c r="K205" s="3">
+        <v>7</v>
+      </c>
+      <c r="L205">
+        <v>32</v>
+      </c>
+      <c r="M205">
+        <v>16</v>
+      </c>
+      <c r="N205">
+        <v>68</v>
+      </c>
+      <c r="O205">
+        <v>84</v>
+      </c>
+      <c r="P205" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q205" s="3">
+        <v>7</v>
+      </c>
+      <c r="R205" s="3">
+        <v>7</v>
+      </c>
+      <c r="S205" s="3">
+        <v>7</v>
+      </c>
+      <c r="T205" s="3">
+        <v>7</v>
+      </c>
+      <c r="U205" s="3">
+        <v>7</v>
+      </c>
+      <c r="V205" t="s">
+        <v>169</v>
+      </c>
+      <c r="W205" s="3">
+        <v>7</v>
+      </c>
+      <c r="X205" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y205">
+        <v>48</v>
+      </c>
+      <c r="Z205">
+        <v>24</v>
+      </c>
+      <c r="AA205">
+        <v>44</v>
+      </c>
+      <c r="AB205">
+        <v>8</v>
+      </c>
+      <c r="AC205">
+        <v>22</v>
+      </c>
+      <c r="AD205">
+        <v>60</v>
+      </c>
+      <c r="AE205">
+        <v>5</v>
+      </c>
+      <c r="AF205">
+        <v>25</v>
+      </c>
+      <c r="AG205" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH205" s="3">
+        <v>995638</v>
+      </c>
+      <c r="AI205" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ205" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK205" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL205">
+        <v>15998</v>
+      </c>
+    </row>
+    <row r="206" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B206" t="s">
+        <v>610</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E206" t="s">
+        <v>18</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="G206" s="3">
+        <v>2</v>
+      </c>
+      <c r="H206" s="3">
+        <v>7</v>
+      </c>
+      <c r="I206" s="3">
+        <v>7</v>
+      </c>
+      <c r="J206" s="3">
+        <v>7</v>
+      </c>
+      <c r="K206" s="3">
+        <v>5</v>
+      </c>
+      <c r="L206">
+        <v>37</v>
+      </c>
+      <c r="M206">
+        <v>24</v>
+      </c>
+      <c r="N206">
+        <v>63</v>
+      </c>
+      <c r="O206">
+        <v>76</v>
+      </c>
+      <c r="P206" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q206" s="3">
+        <v>7</v>
+      </c>
+      <c r="R206" s="3">
+        <v>7</v>
+      </c>
+      <c r="S206" s="3">
+        <v>7</v>
+      </c>
+      <c r="T206" s="3">
+        <v>7</v>
+      </c>
+      <c r="U206" s="3">
+        <v>7</v>
+      </c>
+      <c r="V206" t="s">
+        <v>169</v>
+      </c>
+      <c r="W206" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X206" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y206">
+        <v>33</v>
+      </c>
+      <c r="Z206">
+        <v>16.5</v>
+      </c>
+      <c r="AA206">
+        <v>55</v>
+      </c>
+      <c r="AB206">
+        <v>8</v>
+      </c>
+      <c r="AC206">
+        <v>27.500000000000004</v>
+      </c>
+      <c r="AD206">
+        <v>60</v>
+      </c>
+      <c r="AE206">
+        <v>7</v>
+      </c>
+      <c r="AF206">
+        <v>35</v>
+      </c>
+      <c r="AG206" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH206" s="3">
+        <v>42838</v>
+      </c>
+      <c r="AI206" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ206" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK206" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL206">
+        <v>29574</v>
+      </c>
+    </row>
+    <row r="207" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B207" t="s">
+        <v>613</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E207" t="s">
+        <v>18</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="G207" s="3">
+        <v>2</v>
+      </c>
+      <c r="H207" s="3">
+        <v>7</v>
+      </c>
+      <c r="I207" s="3">
+        <v>7</v>
+      </c>
+      <c r="J207" s="3">
+        <v>7</v>
+      </c>
+      <c r="K207" s="3">
+        <v>5</v>
+      </c>
+      <c r="L207">
+        <v>22</v>
+      </c>
+      <c r="M207">
+        <v>17</v>
+      </c>
+      <c r="N207">
+        <v>78</v>
+      </c>
+      <c r="O207">
+        <v>83</v>
+      </c>
+      <c r="P207" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q207" s="3">
+        <v>7</v>
+      </c>
+      <c r="R207" s="3">
+        <v>7</v>
+      </c>
+      <c r="S207" s="3">
+        <v>7</v>
+      </c>
+      <c r="T207" s="3">
+        <v>7</v>
+      </c>
+      <c r="U207" s="3">
+        <v>7</v>
+      </c>
+      <c r="V207" t="s">
+        <v>169</v>
+      </c>
+      <c r="W207" s="3">
+        <v>10</v>
+      </c>
+      <c r="X207" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y207">
+        <v>57</v>
+      </c>
+      <c r="Z207">
+        <v>28.499999999999996</v>
+      </c>
+      <c r="AA207">
+        <v>38</v>
+      </c>
+      <c r="AB207">
+        <v>7</v>
+      </c>
+      <c r="AC207">
+        <v>19</v>
+      </c>
+      <c r="AD207">
+        <v>65</v>
+      </c>
+      <c r="AE207">
+        <v>2</v>
+      </c>
+      <c r="AF207">
+        <v>10</v>
+      </c>
+      <c r="AG207" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH207" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI207" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ207" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK207" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL207">
         <v>33762</v>
       </c>
     </row>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9195"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="IC Cortes" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="638">
   <si>
     <t>ID</t>
   </si>
@@ -1933,6 +1933,75 @@
   </si>
   <si>
     <t>06/10/2026 16:22:08</t>
+  </si>
+  <si>
+    <t>6ac9cdb20fd30db1b9055a0f</t>
+  </si>
+  <si>
+    <t>09/10/2026 21:59:05</t>
+  </si>
+  <si>
+    <t>10/10/2026 02:31:30</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>6ac9cdb10fd30db1b90559c7</t>
+  </si>
+  <si>
+    <t>09/10/2026 20:02:07</t>
+  </si>
+  <si>
+    <t>10/10/2026 02:31:29</t>
+  </si>
+  <si>
+    <t>6ac9cdb10fd30db1b90559c1</t>
+  </si>
+  <si>
+    <t>09/10/2026 17:24:19</t>
+  </si>
+  <si>
+    <t>6ac9cdb00fd30db1b90559af</t>
+  </si>
+  <si>
+    <t>09/10/2026 16:19:11</t>
+  </si>
+  <si>
+    <t>10/10/2026 02:31:28</t>
+  </si>
+  <si>
+    <t>6ac877fc898c48a2f44ba6df</t>
+  </si>
+  <si>
+    <t>08/10/2026 22:09:42</t>
+  </si>
+  <si>
+    <t>09/10/2026 02:13:32</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>6ac877fb898c48a2f44ba6d9</t>
+  </si>
+  <si>
+    <t>08/10/2026 21:24:19</t>
+  </si>
+  <si>
+    <t>09/10/2026 02:13:31</t>
+  </si>
+  <si>
+    <t>6ac877fb898c48a2f44ba6b3</t>
+  </si>
+  <si>
+    <t>08/10/2026 18:21:26</t>
+  </si>
+  <si>
+    <t>6ac877fb898c48a2f44ba695</t>
+  </si>
+  <si>
+    <t>08/10/2026 16:37:53</t>
   </si>
 </sst>
 </file>
@@ -2338,7 +2407,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2347,17 +2425,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2712,7 +2781,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46303.641959259257" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="206">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46308.563549305552" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="214">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2744,7 +2813,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="50">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="52">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2795,6 +2864,8 @@
         <s v="02/10/2026"/>
         <s v="07/10/2026"/>
         <s v="06/10/2026"/>
+        <s v="09/10/2026"/>
+        <s v="08/10/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2903,7 +2974,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="206">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="214">
   <r>
     <x v="0"/>
     <m/>
@@ -11144,12 +11215,332 @@
     <s v="assinatura"/>
     <n v="33762"/>
   </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac9cdb20fd30db1b9055a0f"/>
+    <s v="09/10/2026 21:59:05"/>
+    <s v="10/10/2026 02:31:30"/>
+    <s v="Ranieli"/>
+    <x v="50"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="22"/>
+    <n v="19"/>
+    <n v="78"/>
+    <n v="81"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <s v=""/>
+    <n v="49"/>
+    <n v="24.5"/>
+    <n v="57"/>
+    <n v="7"/>
+    <n v="28.499999999999996"/>
+    <n v="65"/>
+    <n v="6"/>
+    <n v="30"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="16087"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac9cdb10fd30db1b90559c7"/>
+    <s v="09/10/2026 20:02:07"/>
+    <s v="10/10/2026 02:31:29"/>
+    <s v="Ranieli"/>
+    <x v="50"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="22"/>
+    <n v="15"/>
+    <n v="78"/>
+    <n v="85"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="49"/>
+    <n v="24.5"/>
+    <n v="61"/>
+    <n v="7"/>
+    <n v="30.5"/>
+    <n v="65"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="995638"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="22924"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac9cdb10fd30db1b90559c1"/>
+    <s v="09/10/2026 17:24:19"/>
+    <s v="10/10/2026 02:31:29"/>
+    <s v="Ranieli"/>
+    <x v="50"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="38"/>
+    <n v="23"/>
+    <n v="62"/>
+    <n v="77"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="66"/>
+    <n v="33"/>
+    <n v="64"/>
+    <n v="5"/>
+    <n v="32"/>
+    <n v="75"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="7"/>
+    <n v="42854"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="32373"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac9cdb00fd30db1b90559af"/>
+    <s v="09/10/2026 16:19:11"/>
+    <s v="10/10/2026 02:31:28"/>
+    <s v="Ranieli"/>
+    <x v="50"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="30"/>
+    <n v="22"/>
+    <n v="70"/>
+    <n v="78"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="49"/>
+    <n v="24.5"/>
+    <n v="61"/>
+    <n v="5"/>
+    <n v="30.5"/>
+    <n v="75"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="36253"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac877fc898c48a2f44ba6df"/>
+    <s v="08/10/2026 22:09:42"/>
+    <s v="09/10/2026 02:13:32"/>
+    <s v="Ranieli"/>
+    <x v="51"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="23"/>
+    <n v="29"/>
+    <n v="77"/>
+    <n v="71"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="62"/>
+    <n v="31"/>
+    <n v="49"/>
+    <n v="5"/>
+    <n v="24.5"/>
+    <n v="75"/>
+    <n v="3"/>
+    <n v="15"/>
+    <n v="7"/>
+    <n v="40762"/>
+    <s v="Data  de validade e produção estão de acordo,_x000a_Caixa está sem rasgos e seca,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="13342"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac877fb898c48a2f44ba6d9"/>
+    <s v="08/10/2026 21:24:19"/>
+    <s v="09/10/2026 02:13:31"/>
+    <s v="Ranieli"/>
+    <x v="51"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="22"/>
+    <n v="23"/>
+    <n v="78"/>
+    <n v="77"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="42"/>
+    <n v="21"/>
+    <n v="47"/>
+    <n v="8"/>
+    <n v="23.5"/>
+    <n v="60"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="42846"/>
+    <s v="Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="16090"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac877fb898c48a2f44ba6b3"/>
+    <s v="08/10/2026 18:21:26"/>
+    <s v="09/10/2026 02:13:31"/>
+    <s v="Ranieli"/>
+    <x v="51"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="21"/>
+    <n v="25"/>
+    <n v="79"/>
+    <n v="75"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v=""/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="44"/>
+    <n v="22"/>
+    <n v="43"/>
+    <n v="5"/>
+    <n v="21.5"/>
+    <n v="75"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="995638"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme,_x000a_Caixa está sem rasgos e seca"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="27178"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6ac877fb898c48a2f44ba695"/>
+    <s v="08/10/2026 16:37:53"/>
+    <s v="09/10/2026 02:13:31"/>
+    <s v="Ranieli"/>
+    <x v="51"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="37"/>
+    <n v="23"/>
+    <n v="63"/>
+    <n v="77"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Usou o garfo na retirada de Sassami,_x000a_Retirou a Cartilagem"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="56"/>
+    <n v="28.000000000000004"/>
+    <n v="50"/>
+    <n v="4"/>
+    <n v="25"/>
+    <n v="80"/>
+    <n v="5"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Caixa está sem rasgos e seca,_x000a_Data  de validade e produção estão de acordo,_x000a_Selagem está conforme"/>
+    <s v=""/>
+    <s v=""/>
+    <n v="34480"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:Y118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+  <location ref="U117:AA118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="11">
@@ -11171,7 +11562,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="51">
+      <items count="53">
         <item x="26"/>
         <item x="45"/>
         <item x="28"/>
@@ -11184,7 +11575,9 @@
         <item x="12"/>
         <item x="48"/>
         <item x="29"/>
+        <item x="51"/>
         <item x="32"/>
+        <item x="50"/>
         <item x="11"/>
         <item x="31"/>
         <item x="10"/>
@@ -11264,7 +11657,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="5">
+  <colItems count="7">
     <i>
       <x v="1"/>
     </i>
@@ -11279,6 +11672,12 @@
     </i>
     <i>
       <x v="10"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -11364,8 +11763,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL207" totalsRowShown="0">
-  <autoFilter ref="A1:AL207"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL215" totalsRowShown="0">
+  <autoFilter ref="A1:AL215"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -11735,22 +12134,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AR118"/>
-  <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.85546875" style="25" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" style="25" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="18" width="9.140625" style="25" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
-    <col min="20" max="20" width="1.7109375" customWidth="1"/>
-    <col min="23" max="44" width="9.85546875" style="25"/>
+    <col min="1" max="2" width="9.88671875" style="25" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" style="25" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="29.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" customWidth="1"/>
+    <col min="7" max="18" width="9.109375" style="25" customWidth="1"/>
+    <col min="19" max="19" width="9.109375" customWidth="1"/>
+    <col min="20" max="20" width="1.6640625" customWidth="1"/>
+    <col min="23" max="44" width="9.88671875" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:44" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:44" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>140</v>
       </c>
@@ -11830,11 +12229,11 @@
       </c>
       <c r="Z3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>08/10/2026</v>
       </c>
       <c r="AA3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>09/10/2026</v>
       </c>
       <c r="AB3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -11905,7 +12304,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>120</v>
       </c>
@@ -11920,7 +12319,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="39" t="str">
+      <c r="E4" s="35" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -12075,7 +12474,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>120</v>
       </c>
@@ -12090,7 +12489,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="40"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -12142,7 +12541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="36"/>
+      <c r="S5" s="39"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12163,13 +12562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z5" s="12" t="str">
+      <c r="Z5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA5" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AB$3),"")</f>
@@ -12240,7 +12639,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>120</v>
       </c>
@@ -12255,7 +12654,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="37"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -12307,7 +12706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="37"/>
+      <c r="S6" s="40"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12328,13 +12727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z6" s="9" t="str">
+      <c r="Z6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA6" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -12405,7 +12804,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>120</v>
       </c>
@@ -12420,7 +12819,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="39" t="str">
+      <c r="E7" s="35" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -12575,7 +12974,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>120</v>
       </c>
@@ -12590,7 +12989,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -12632,7 +13031,7 @@
       </c>
       <c r="P8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
-        <v>7.3157894736842106</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="Q8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],Q$3),"")</f>
@@ -12642,7 +13041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="36"/>
+      <c r="S8" s="39"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -12663,13 +13062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z8" s="12" t="str">
+      <c r="Z8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA8" s="12" t="str">
+        <v>7.75</v>
+      </c>
+      <c r="AA8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AB$3),"")</f>
@@ -12740,7 +13139,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>120</v>
       </c>
@@ -12755,7 +13154,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="41"/>
+      <c r="E9" s="37"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -12797,7 +13196,7 @@
       </c>
       <c r="P9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.3157894736842106</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="Q9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -12807,7 +13206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="37"/>
+      <c r="S9" s="40"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -12828,13 +13227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z9" s="9" t="str">
+      <c r="Z9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA9" s="9" t="str">
+        <v>7.75</v>
+      </c>
+      <c r="AA9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -12905,7 +13304,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>120</v>
       </c>
@@ -12920,7 +13319,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="39" t="str">
+      <c r="E10" s="35" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -13075,7 +13474,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>120</v>
       </c>
@@ -13090,7 +13489,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="40"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -13142,7 +13541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="36"/>
+      <c r="S11" s="39"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -13163,13 +13562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z11" s="12" t="str">
+      <c r="Z11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA11" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AB$3),"")</f>
@@ -13240,7 +13639,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
         <v>120</v>
       </c>
@@ -13255,7 +13654,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="41"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -13307,7 +13706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="37"/>
+      <c r="S12" s="40"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -13328,13 +13727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z12" s="9" t="str">
+      <c r="Z12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA12" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -13405,7 +13804,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
         <v>120</v>
       </c>
@@ -13420,7 +13819,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="39" t="str">
+      <c r="E13" s="35" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -13575,7 +13974,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>120</v>
       </c>
@@ -13590,7 +13989,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="40"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -13632,7 +14031,7 @@
       </c>
       <c r="P14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
-        <v>5.4210526315789478</v>
+        <v>5.5185185185185182</v>
       </c>
       <c r="Q14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],Q$3),"")</f>
@@ -13642,7 +14041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="36"/>
+      <c r="S14" s="39"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -13663,13 +14062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],Y$3),"")</f>
         <v>5</v>
       </c>
-      <c r="Z14" s="12" t="str">
+      <c r="Z14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA14" s="12" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="AA14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AB14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AB$3),"")</f>
@@ -13740,7 +14139,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
         <v>120</v>
       </c>
@@ -13755,7 +14154,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="41"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -13797,7 +14196,7 @@
       </c>
       <c r="P15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>5.4210526315789478</v>
+        <v>5.5185185185185182</v>
       </c>
       <c r="Q15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -13807,7 +14206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="37"/>
+      <c r="S15" s="40"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -13828,13 +14227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>5</v>
       </c>
-      <c r="Z15" s="9" t="str">
+      <c r="Z15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA15" s="9" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="AA15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AB15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -13905,7 +14304,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>120</v>
       </c>
@@ -13920,7 +14319,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="39" t="str">
+      <c r="E16" s="35" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -13975,7 +14374,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="41">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -14075,7 +14474,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>120</v>
       </c>
@@ -14090,7 +14489,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="40"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -14132,7 +14531,7 @@
       </c>
       <c r="P17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.74157894736842112</v>
+        <v>0.73851851851851846</v>
       </c>
       <c r="Q17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],Q$3)/100,"")</f>
@@ -14142,7 +14541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="36"/>
+      <c r="S17" s="39"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
@@ -14163,13 +14562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],Y$3)/100,"")</f>
         <v>0.63749999999999996</v>
       </c>
-      <c r="Z17" s="16" t="str">
+      <c r="Z17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA17" s="16" t="str">
+        <v>0.74250000000000005</v>
+      </c>
+      <c r="AA17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.72</v>
       </c>
       <c r="AB17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AB$3)/100,"")</f>
@@ -14240,7 +14639,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>120</v>
       </c>
@@ -14255,7 +14654,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="41"/>
+      <c r="E18" s="37"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -14297,7 +14696,7 @@
       </c>
       <c r="P18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.74157894736842112</v>
+        <v>0.73851851851851846</v>
       </c>
       <c r="Q18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -14307,7 +14706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="37"/>
+      <c r="S18" s="40"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
@@ -14328,13 +14727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
         <v>0.63749999999999996</v>
       </c>
-      <c r="Z18" s="10" t="str">
+      <c r="Z18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA18" s="10" t="str">
+        <v>0.74250000000000005</v>
+      </c>
+      <c r="AA18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.72</v>
       </c>
       <c r="AB18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
@@ -14405,7 +14804,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>120</v>
       </c>
@@ -14420,7 +14819,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="39" t="str">
+      <c r="E19" s="35" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -14475,7 +14874,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="41">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -14575,7 +14974,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>120</v>
       </c>
@@ -14590,7 +14989,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="40"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -14632,7 +15031,7 @@
       </c>
       <c r="P20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.80736842105263162</v>
+        <v>0.79814814814814805</v>
       </c>
       <c r="Q20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],Q$3)/100,"")</f>
@@ -14642,7 +15041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="36"/>
+      <c r="S20" s="39"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
@@ -14663,13 +15062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],Y$3)/100,"")</f>
         <v>0.76249999999999996</v>
       </c>
-      <c r="Z20" s="16" t="str">
+      <c r="Z20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA20" s="16" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="AA20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.80249999999999999</v>
       </c>
       <c r="AB20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AB$3)/100,"")</f>
@@ -14740,7 +15139,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>120</v>
       </c>
@@ -14755,7 +15154,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="41"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -14797,7 +15196,7 @@
       </c>
       <c r="P21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.80736842105263162</v>
+        <v>0.79814814814814805</v>
       </c>
       <c r="Q21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -14807,7 +15206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="37"/>
+      <c r="S21" s="40"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
@@ -14828,13 +15227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
         <v>0.76249999999999996</v>
       </c>
-      <c r="Z21" s="10" t="str">
+      <c r="Z21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA21" s="10" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="AA21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.80249999999999999</v>
       </c>
       <c r="AB21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
@@ -14905,7 +15304,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>121</v>
       </c>
@@ -14920,7 +15319,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="39" t="str">
+      <c r="E22" s="35" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -15075,7 +15474,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
         <v>121</v>
       </c>
@@ -15090,7 +15489,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="40"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -15132,7 +15531,7 @@
       </c>
       <c r="P23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
-        <v>6.4736842105263159</v>
+        <v>6.5555555555555554</v>
       </c>
       <c r="Q23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],Q$3),"")</f>
@@ -15142,7 +15541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="36"/>
+      <c r="S23" s="39"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6</v>
@@ -15163,13 +15562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z23" s="12" t="str">
+      <c r="Z23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA23" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AB23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AB$3),"")</f>
@@ -15240,7 +15639,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="25" t="s">
         <v>121</v>
       </c>
@@ -15255,7 +15654,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="41"/>
+      <c r="E24" s="37"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -15297,7 +15696,7 @@
       </c>
       <c r="P24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.4736842105263159</v>
+        <v>6.5555555555555554</v>
       </c>
       <c r="Q24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -15307,7 +15706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="37"/>
+      <c r="S24" s="40"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6</v>
@@ -15328,13 +15727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z24" s="9" t="str">
+      <c r="Z24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA24" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AB24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -15405,7 +15804,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>121</v>
       </c>
@@ -15420,7 +15819,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="39" t="str">
+      <c r="E25" s="35" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -15575,7 +15974,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>121</v>
       </c>
@@ -15590,7 +15989,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="40"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -15632,7 +16031,7 @@
       </c>
       <c r="P26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
-        <v>7.1578947368421053</v>
+        <v>7.1111111111111107</v>
       </c>
       <c r="Q26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],Q$3),"")</f>
@@ -15642,7 +16041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="36"/>
+      <c r="S26" s="39"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -15663,13 +16062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z26" s="12" t="str">
+      <c r="Z26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA26" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AB$3),"")</f>
@@ -15740,7 +16139,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25" t="s">
         <v>121</v>
       </c>
@@ -15755,7 +16154,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="41"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -15797,7 +16196,7 @@
       </c>
       <c r="P27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.1578947368421053</v>
+        <v>7.1111111111111107</v>
       </c>
       <c r="Q27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -15807,7 +16206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="37"/>
+      <c r="S27" s="40"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -15828,13 +16227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z27" s="9" t="str">
+      <c r="Z27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA27" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -15905,7 +16304,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>121</v>
       </c>
@@ -15920,7 +16319,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="39" t="str">
+      <c r="E28" s="35" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -16075,7 +16474,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
         <v>121</v>
       </c>
@@ -16090,7 +16489,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="40"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -16142,7 +16541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="36"/>
+      <c r="S29" s="39"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16163,13 +16562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z29" s="12" t="str">
+      <c r="Z29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA29" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AB$3),"")</f>
@@ -16240,7 +16639,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>121</v>
       </c>
@@ -16255,7 +16654,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="37"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -16307,7 +16706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="37"/>
+      <c r="S30" s="40"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16328,13 +16727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z30" s="9" t="str">
+      <c r="Z30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA30" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -16405,7 +16804,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
         <v>121</v>
       </c>
@@ -16420,7 +16819,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="39" t="str">
+      <c r="E31" s="35" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -16575,7 +16974,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>121</v>
       </c>
@@ -16590,7 +16989,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="40"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -16632,7 +17031,7 @@
       </c>
       <c r="P32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
-        <v>6.8947368421052628</v>
+        <v>6.9259259259259256</v>
       </c>
       <c r="Q32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],Q$3),"")</f>
@@ -16642,7 +17041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="36"/>
+      <c r="S32" s="39"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16663,13 +17062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z32" s="12" t="str">
+      <c r="Z32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA32" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AB$3),"")</f>
@@ -16740,7 +17139,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="25" t="s">
         <v>121</v>
       </c>
@@ -16755,7 +17154,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="41"/>
+      <c r="E33" s="37"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -16797,7 +17196,7 @@
       </c>
       <c r="P33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.8947368421052628</v>
+        <v>6.9259259259259256</v>
       </c>
       <c r="Q33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -16807,7 +17206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="37"/>
+      <c r="S33" s="40"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16828,13 +17227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z33" s="9" t="str">
+      <c r="Z33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA33" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -16905,7 +17304,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
         <v>121</v>
       </c>
@@ -16920,7 +17319,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="39" t="str">
+      <c r="E34" s="35" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -17075,7 +17474,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" s="25" t="s">
         <v>121</v>
       </c>
@@ -17090,7 +17489,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="40"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -17142,7 +17541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="36"/>
+      <c r="S35" s="39"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -17163,13 +17562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z35" s="12" t="str">
+      <c r="Z35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA35" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AB$3),"")</f>
@@ -17240,7 +17639,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="25" t="s">
         <v>121</v>
       </c>
@@ -17255,7 +17654,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="41"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -17307,7 +17706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="37"/>
+      <c r="S36" s="40"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -17328,13 +17727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z36" s="9" t="str">
+      <c r="Z36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA36" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -17405,7 +17804,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
         <v>121</v>
       </c>
@@ -17420,7 +17819,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="39" t="str">
+      <c r="E37" s="35" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -17575,7 +17974,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
         <v>121</v>
       </c>
@@ -17590,7 +17989,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="40"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -17632,7 +18031,7 @@
       </c>
       <c r="P38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
-        <v>6.4444444444444446</v>
+        <v>6.5652173913043477</v>
       </c>
       <c r="Q38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],Q$3),"")</f>
@@ -17642,7 +18041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="36"/>
+      <c r="S38" s="39"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -17663,13 +18062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],Y$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="Z38" s="12" t="str">
+      <c r="Z38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA38" s="12" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AB$3),"")</f>
@@ -17740,7 +18139,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="25" t="s">
         <v>121</v>
       </c>
@@ -17755,7 +18154,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="41"/>
+      <c r="E39" s="37"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -17797,7 +18196,7 @@
       </c>
       <c r="P39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.4444444444444446</v>
+        <v>6.5652173913043477</v>
       </c>
       <c r="Q39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -17807,7 +18206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="37"/>
+      <c r="S39" s="40"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -17828,13 +18227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="Z39" s="9" t="str">
+      <c r="Z39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA39" s="9" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -17905,7 +18304,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>122</v>
       </c>
@@ -17920,7 +18319,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="39" t="str">
+      <c r="E40" s="35" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -18075,7 +18474,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
         <v>122</v>
       </c>
@@ -18090,7 +18489,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="40"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -18132,7 +18531,7 @@
       </c>
       <c r="P41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
-        <v>8.384615384615385</v>
+        <v>8.5789473684210531</v>
       </c>
       <c r="Q41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],Q$3),"")</f>
@@ -18142,7 +18541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="36"/>
+      <c r="S41" s="39"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -18163,13 +18562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],Y$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="Z41" s="12" t="str">
+      <c r="Z41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA41" s="12" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AB41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AB$3),"")</f>
@@ -18240,7 +18639,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="25" t="s">
         <v>122</v>
       </c>
@@ -18255,7 +18654,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="37"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -18297,7 +18696,7 @@
       </c>
       <c r="P42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.384615384615385</v>
+        <v>8.5789473684210531</v>
       </c>
       <c r="Q42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18307,7 +18706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="37"/>
+      <c r="S42" s="40"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -18328,13 +18727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="Z42" s="9" t="str">
+      <c r="Z42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA42" s="9" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AB42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -18405,7 +18804,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
         <v>122</v>
       </c>
@@ -18420,7 +18819,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="39" t="str">
+      <c r="E43" s="35" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -18575,7 +18974,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
         <v>122</v>
       </c>
@@ -18590,7 +18989,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="40"/>
+      <c r="E44" s="36"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -18632,7 +19031,7 @@
       </c>
       <c r="P44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
-        <v>7.25</v>
+        <v>7.3529411764705879</v>
       </c>
       <c r="Q44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],Q$3),"")</f>
@@ -18642,7 +19041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="36"/>
+      <c r="S44" s="39"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -18663,13 +19062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z44" s="12" t="str">
+      <c r="Z44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA44" s="12" t="str">
+        <v>8</v>
+      </c>
+      <c r="AA44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AB$3),"")</f>
@@ -18740,7 +19139,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="25" t="s">
         <v>122</v>
       </c>
@@ -18755,7 +19154,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="37"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -18797,7 +19196,7 @@
       </c>
       <c r="P45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.25</v>
+        <v>7.3529411764705879</v>
       </c>
       <c r="Q45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18807,7 +19206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="37"/>
+      <c r="S45" s="40"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -18828,13 +19227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>7</v>
       </c>
-      <c r="Z45" s="9" t="str">
+      <c r="Z45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA45" s="9" t="str">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AB45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -18905,7 +19304,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:44" s="25" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="25" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
         <v>122</v>
       </c>
@@ -18920,7 +19319,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="39" t="str">
+      <c r="E46" s="35" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -18975,7 +19374,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="35">
+      <c r="S46" s="41">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -19075,7 +19474,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
         <v>122</v>
       </c>
@@ -19090,7 +19489,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="40"/>
+      <c r="E47" s="36"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -19132,7 +19531,7 @@
       </c>
       <c r="P47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.2388888888888889</v>
+        <v>0.24557692307692305</v>
       </c>
       <c r="Q47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19142,7 +19541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="36"/>
+      <c r="S47" s="39"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
@@ -19163,13 +19562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],Y$3)/100,"")</f>
         <v>0.22625000000000001</v>
       </c>
-      <c r="Z47" s="16" t="str">
+      <c r="Z47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA47" s="16" t="str">
+        <v>0.255</v>
+      </c>
+      <c r="AA47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.26624999999999999</v>
       </c>
       <c r="AB47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AB$3)/100,"")</f>
@@ -19240,7 +19639,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="25" t="s">
         <v>122</v>
       </c>
@@ -19255,7 +19654,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="41"/>
+      <c r="E48" s="37"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -19297,7 +19696,7 @@
       </c>
       <c r="P48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.2388888888888889</v>
+        <v>0.24557692307692305</v>
       </c>
       <c r="Q48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19307,7 +19706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="37"/>
+      <c r="S48" s="40"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
@@ -19328,13 +19727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
         <v>0.22625000000000001</v>
       </c>
-      <c r="Z48" s="10" t="str">
+      <c r="Z48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA48" s="10" t="str">
+        <v>0.255</v>
+      </c>
+      <c r="AA48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.26624999999999999</v>
       </c>
       <c r="AB48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
@@ -19405,7 +19804,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A49" s="25" t="s">
         <v>123</v>
       </c>
@@ -19420,7 +19819,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="39" t="str">
+      <c r="E49" s="35" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -19475,7 +19874,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="35">
+      <c r="S49" s="41">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -19575,7 +19974,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
         <v>123</v>
       </c>
@@ -19590,7 +19989,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="40"/>
+      <c r="E50" s="36"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -19632,7 +20031,7 @@
       </c>
       <c r="P50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.23394736842105263</v>
+        <v>0.24462962962962961</v>
       </c>
       <c r="Q50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19642,7 +20041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="36"/>
+      <c r="S50" s="39"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
@@ -19663,13 +20062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],Y$3)/100,"")</f>
         <v>0.20250000000000001</v>
       </c>
-      <c r="Z50" s="16" t="str">
+      <c r="Z50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA50" s="16" t="str">
+        <v>0.23624999999999999</v>
+      </c>
+      <c r="AA50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.30375000000000002</v>
       </c>
       <c r="AB50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AB$3)/100,"")</f>
@@ -19740,7 +20139,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="25" t="s">
         <v>123</v>
       </c>
@@ -19755,7 +20154,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="41"/>
+      <c r="E51" s="37"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -19797,7 +20196,7 @@
       </c>
       <c r="P51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.23394736842105263</v>
+        <v>0.24462962962962961</v>
       </c>
       <c r="Q51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19807,7 +20206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="37"/>
+      <c r="S51" s="40"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
@@ -19828,13 +20227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
         <v>0.20250000000000001</v>
       </c>
-      <c r="Z51" s="10" t="str">
+      <c r="Z51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA51" s="10" t="str">
+        <v>0.23624999999999999</v>
+      </c>
+      <c r="AA51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.30375000000000002</v>
       </c>
       <c r="AB51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
@@ -19905,7 +20304,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
         <v>123</v>
       </c>
@@ -19920,7 +20319,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="39" t="str">
+      <c r="E52" s="35" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -19975,7 +20374,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="35">
+      <c r="S52" s="41">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -20075,7 +20474,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="25" t="s">
         <v>123</v>
       </c>
@@ -20090,7 +20489,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="40"/>
+      <c r="E53" s="36"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -20132,7 +20531,7 @@
       </c>
       <c r="P53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.65526315789473688</v>
+        <v>0.67222222222222228</v>
       </c>
       <c r="Q53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],Q$3)/100,"")</f>
@@ -20142,7 +20541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="36"/>
+      <c r="S53" s="39"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
@@ -20163,13 +20562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],Y$3)/100,"")</f>
         <v>0.67500000000000004</v>
       </c>
-      <c r="Z53" s="16" t="str">
+      <c r="Z53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA53" s="16" t="str">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="AA53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AB53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AB$3)/100,"")</f>
@@ -20240,7 +20639,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="25" t="s">
         <v>123</v>
       </c>
@@ -20255,7 +20654,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="41"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -20297,7 +20696,7 @@
       </c>
       <c r="P54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.65526315789473688</v>
+        <v>0.67222222222222228</v>
       </c>
       <c r="Q54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20307,7 +20706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="37"/>
+      <c r="S54" s="40"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
@@ -20328,13 +20727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
         <v>0.67500000000000004</v>
       </c>
-      <c r="Z54" s="10" t="str">
+      <c r="Z54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA54" s="10" t="str">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="AA54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AB54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
@@ -20405,7 +20804,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>124</v>
       </c>
@@ -20420,7 +20819,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="39" t="str">
+      <c r="E55" s="35" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -20475,7 +20874,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="35">
+      <c r="S55" s="41">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -20575,7 +20974,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>124</v>
       </c>
@@ -20590,7 +20989,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="40"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -20632,7 +21031,7 @@
       </c>
       <c r="P56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.18421052631578949</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="Q56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],Q$3)/100,"")</f>
@@ -20642,7 +21041,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="36"/>
+      <c r="S56" s="39"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
@@ -20663,13 +21062,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],Y$3)/100,"")</f>
         <v>0.25</v>
       </c>
-      <c r="Z56" s="16" t="str">
+      <c r="Z56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA56" s="16" t="str">
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="AA56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.23749999999999999</v>
       </c>
       <c r="AB56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AB$3)/100,"")</f>
@@ -20740,7 +21139,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="25" t="s">
         <v>124</v>
       </c>
@@ -20755,7 +21154,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="41"/>
+      <c r="E57" s="37"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -20797,7 +21196,7 @@
       </c>
       <c r="P57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.18421052631578949</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="Q57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20807,7 +21206,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="37"/>
+      <c r="S57" s="40"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
@@ -20828,13 +21227,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],Y$3)/100,"")</f>
         <v>0.25</v>
       </c>
-      <c r="Z57" s="10" t="str">
+      <c r="Z57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],Z$3)/100,"")</f>
-        <v/>
-      </c>
-      <c r="AA57" s="10" t="str">
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="AA57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
-        <v/>
+        <v>0.23749999999999999</v>
       </c>
       <c r="AB57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
@@ -20905,7 +21304,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>125</v>
       </c>
@@ -20920,7 +21319,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="39" t="str">
+      <c r="E58" s="35" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -21075,7 +21474,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="25" t="s">
         <v>125</v>
       </c>
@@ -21090,7 +21489,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="40"/>
+      <c r="E59" s="36"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -21132,7 +21531,7 @@
       </c>
       <c r="P59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
-        <v>8.6666666666666661</v>
+        <v>8.615384615384615</v>
       </c>
       <c r="Q59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],Q$3),"")</f>
@@ -21142,7 +21541,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="36"/>
+      <c r="S59" s="39"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -21163,13 +21562,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],Y$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="Z59" s="12" t="str">
+      <c r="Z59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA59" s="12" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="AA59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AB59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AB$3),"")</f>
@@ -21240,7 +21639,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="25" t="s">
         <v>125</v>
       </c>
@@ -21255,7 +21654,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="41"/>
+      <c r="E60" s="37"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -21297,7 +21696,7 @@
       </c>
       <c r="P60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.6666666666666661</v>
+        <v>8.615384615384615</v>
       </c>
       <c r="Q60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -21307,7 +21706,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="37"/>
+      <c r="S60" s="40"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -21328,13 +21727,13 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],Y$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="Z60" s="9" t="str">
+      <c r="Z60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],Z$3),"")</f>
-        <v/>
-      </c>
-      <c r="AA60" s="9" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="AA60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AA$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AB60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AB$3),"")</f>
@@ -21405,27 +21804,27 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L69" s="32"/>
     </row>
-    <row r="70" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L70" s="32"/>
       <c r="O70" s="32"/>
     </row>
-    <row r="71" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L71" s="32"/>
       <c r="O71" s="32"/>
     </row>
-    <row r="72" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L72" s="32"/>
       <c r="O72" s="32"/>
     </row>
-    <row r="74" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L74" s="31"/>
       <c r="O74" s="32"/>
     </row>
-    <row r="117" spans="21:39" x14ac:dyDescent="0.25">
+    <row r="117" spans="21:39" x14ac:dyDescent="0.3">
       <c r="U117" s="21" t="s">
         <v>155</v>
       </c>
@@ -21447,7 +21846,7 @@
       <c r="AL117"/>
       <c r="AM117"/>
     </row>
-    <row r="118" spans="21:39" x14ac:dyDescent="0.25">
+    <row r="118" spans="21:39" x14ac:dyDescent="0.3">
       <c r="U118" t="s">
         <v>562</v>
       </c>
@@ -21463,8 +21862,12 @@
       <c r="Y118" t="s">
         <v>595</v>
       </c>
-      <c r="Z118"/>
-      <c r="AA118"/>
+      <c r="Z118" t="s">
+        <v>630</v>
+      </c>
+      <c r="AA118" t="s">
+        <v>618</v>
+      </c>
       <c r="AB118"/>
       <c r="AC118"/>
       <c r="AD118"/>
@@ -21480,18 +21883,16 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -21508,16 +21909,18 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -21756,28 +22159,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL207"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AL215"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
     <col min="3" max="4" width="21" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="31" customWidth="1"/>
     <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="13.109375" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
     <col min="22" max="22" width="45" hidden="1" customWidth="1"/>
     <col min="23" max="24" width="19" customWidth="1"/>
@@ -21789,14 +22192,14 @@
     <col min="30" max="30" width="30" customWidth="1"/>
     <col min="31" max="31" width="19" customWidth="1"/>
     <col min="32" max="32" width="32" customWidth="1"/>
-    <col min="33" max="33" width="17.42578125" customWidth="1"/>
+    <col min="33" max="33" width="17.44140625" customWidth="1"/>
     <col min="34" max="34" width="7" customWidth="1"/>
     <col min="35" max="35" width="150" hidden="1" customWidth="1"/>
     <col min="36" max="37" width="39" hidden="1" customWidth="1"/>
     <col min="38" max="38" width="20" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -21912,7 +22315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>JAN</v>
@@ -21953,7 +22356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>JAN</v>
@@ -21994,7 +22397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>128</v>
       </c>
@@ -22034,7 +22437,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>128</v>
       </c>
@@ -22074,7 +22477,7 @@
         <v>13.57</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>129</v>
       </c>
@@ -22114,7 +22517,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>129</v>
       </c>
@@ -22154,7 +22557,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>130</v>
       </c>
@@ -22194,7 +22597,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>130</v>
       </c>
@@ -22234,7 +22637,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>131</v>
       </c>
@@ -22274,7 +22677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>131</v>
       </c>
@@ -22314,7 +22717,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>132</v>
       </c>
@@ -22354,7 +22757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>132</v>
       </c>
@@ -22394,7 +22797,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>133</v>
       </c>
@@ -22434,7 +22837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>133</v>
       </c>
@@ -22474,7 +22877,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -22591,7 +22994,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -22708,7 +23111,7 @@
         <v>4705</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -22825,7 +23228,7 @@
         <v>2933</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -22942,7 +23345,7 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23059,7 +23462,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23176,7 +23579,7 @@
         <v>7125</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23293,7 +23696,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23410,7 +23813,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23527,7 +23930,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23644,7 +24047,7 @@
         <v>4603</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23761,7 +24164,7 @@
         <v>7653</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23878,7 +24281,7 @@
         <v>4698</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23995,7 +24398,7 @@
         <v>4014</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24112,7 +24515,7 @@
         <v>5115</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24229,7 +24632,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24346,7 +24749,7 @@
         <v>4821</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24463,7 +24866,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24580,7 +24983,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24697,7 +25100,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24814,7 +25217,7 @@
         <v>4870</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24931,7 +25334,7 @@
         <v>4717</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25048,7 +25451,7 @@
         <v>3007</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25165,7 +25568,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25282,7 +25685,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25399,7 +25802,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25516,7 +25919,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25633,7 +26036,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25750,7 +26153,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25867,7 +26270,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25984,7 +26387,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26101,7 +26504,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26218,7 +26621,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26335,7 +26738,7 @@
         <v>4922</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26452,7 +26855,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26569,7 +26972,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26686,7 +27089,7 @@
         <v>5215</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26803,7 +27206,7 @@
         <v>3408</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26920,7 +27323,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27037,7 +27440,7 @@
         <v>3899</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27154,7 +27557,7 @@
         <v>3477</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27271,7 +27674,7 @@
         <v>5198</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27388,7 +27791,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27505,7 +27908,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27622,7 +28025,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27739,7 +28142,7 @@
         <v>5935</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27856,7 +28259,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27973,7 +28376,7 @@
         <v>5628</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28090,7 +28493,7 @@
         <v>5091</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28207,7 +28610,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28324,7 +28727,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28441,7 +28844,7 @@
         <v>4307</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28558,7 +28961,7 @@
         <v>5885</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28675,7 +29078,7 @@
         <v>14571</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28792,7 +29195,7 @@
         <v>3558</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28909,7 +29312,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29023,7 +29426,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29140,7 +29543,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29257,7 +29660,7 @@
         <v>9620</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29371,7 +29774,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29488,7 +29891,7 @@
         <v>3347</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29605,7 +30008,7 @@
         <v>5223</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29722,7 +30125,7 @@
         <v>3410</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29839,7 +30242,7 @@
         <v>3465</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29956,7 +30359,7 @@
         <v>4047</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30073,7 +30476,7 @@
         <v>3842</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30190,7 +30593,7 @@
         <v>7667</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30307,7 +30710,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30424,7 +30827,7 @@
         <v>4250</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30541,7 +30944,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30658,7 +31061,7 @@
         <v>3225</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30775,7 +31178,7 @@
         <v>3915</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30892,7 +31295,7 @@
         <v>4896</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31009,7 +31412,7 @@
         <v>3620</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31126,7 +31529,7 @@
         <v>3009</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31243,7 +31646,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31360,7 +31763,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31455,7 +31858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31550,7 +31953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31645,7 +32048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31737,7 +32140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31829,7 +32232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31946,7 +32349,7 @@
         <v>3620</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32063,7 +32466,7 @@
         <v>3009</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32180,7 +32583,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32297,7 +32700,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -32414,7 +32817,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32531,7 +32934,7 @@
         <v>6804</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32648,7 +33051,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32765,7 +33168,7 @@
         <v>4338</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32882,7 +33285,7 @@
         <v>3285</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32999,7 +33402,7 @@
         <v>3498</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33116,7 +33519,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33230,7 +33633,7 @@
         <v>4464</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33347,7 +33750,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33440,7 +33843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33557,7 +33960,7 @@
         <v>4823</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33674,7 +34077,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33791,7 +34194,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33908,7 +34311,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34001,7 +34404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34118,7 +34521,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34235,7 +34638,7 @@
         <v>3262</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34352,7 +34755,7 @@
         <v>3790</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34469,7 +34872,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34586,7 +34989,7 @@
         <v>5276</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34703,7 +35106,7 @@
         <v>3767</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34820,7 +35223,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34937,7 +35340,7 @@
         <v>2657</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35054,7 +35457,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35171,7 +35574,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35288,7 +35691,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="127" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35405,7 +35808,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="128" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35522,7 +35925,7 @@
         <v>3671</v>
       </c>
     </row>
-    <row r="129" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35639,7 +36042,7 @@
         <v>6007</v>
       </c>
     </row>
-    <row r="130" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35756,7 +36159,7 @@
         <v>8320</v>
       </c>
     </row>
-    <row r="131" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35873,7 +36276,7 @@
         <v>3757</v>
       </c>
     </row>
-    <row r="132" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35990,7 +36393,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="133" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36107,7 +36510,7 @@
         <v>5114</v>
       </c>
     </row>
-    <row r="134" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36224,7 +36627,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="135" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36341,7 +36744,7 @@
         <v>1141881</v>
       </c>
     </row>
-    <row r="136" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36429,7 +36832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36517,7 +36920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36605,7 +37008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36693,7 +37096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36810,7 +37213,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="141" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36927,7 +37330,7 @@
         <v>4833</v>
       </c>
     </row>
-    <row r="142" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37044,7 +37447,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="143" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37161,7 +37564,7 @@
         <v>5054</v>
       </c>
     </row>
-    <row r="144" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37278,7 +37681,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="145" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37395,7 +37798,7 @@
         <v>5114</v>
       </c>
     </row>
-    <row r="146" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37512,7 +37915,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="147" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37629,7 +38032,7 @@
         <v>1141881</v>
       </c>
     </row>
-    <row r="148" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37746,7 +38149,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="149" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37863,7 +38266,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="150" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37980,7 +38383,7 @@
         <v>3592</v>
       </c>
     </row>
-    <row r="151" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38097,7 +38500,7 @@
         <v>2783</v>
       </c>
     </row>
-    <row r="152" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38214,7 +38617,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="153" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38331,7 +38734,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="154" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38448,7 +38851,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="155" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38565,7 +38968,7 @@
         <v>3341</v>
       </c>
     </row>
-    <row r="156" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38682,7 +39085,7 @@
         <v>5707</v>
       </c>
     </row>
-    <row r="157" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38799,7 +39202,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="158" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38916,7 +39319,7 @@
         <v>4382</v>
       </c>
     </row>
-    <row r="159" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39033,7 +39436,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="160" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39150,7 +39553,7 @@
         <v>5908</v>
       </c>
     </row>
-    <row r="161" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39267,7 +39670,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="162" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39384,7 +39787,7 @@
         <v>4032</v>
       </c>
     </row>
-    <row r="163" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39501,7 +39904,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="164" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39618,7 +40021,7 @@
         <v>3844</v>
       </c>
     </row>
-    <row r="165" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39735,7 +40138,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="166" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39852,7 +40255,7 @@
         <v>4578</v>
       </c>
     </row>
-    <row r="167" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39969,7 +40372,7 @@
         <v>5257</v>
       </c>
     </row>
-    <row r="168" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40061,7 +40464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40153,7 +40556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40245,7 +40648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40337,7 +40740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40429,7 +40832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40546,7 +40949,7 @@
         <v>6547</v>
       </c>
     </row>
-    <row r="174" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40663,7 +41066,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="175" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40780,7 +41183,7 @@
         <v>5803</v>
       </c>
     </row>
-    <row r="176" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40897,7 +41300,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="177" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41014,7 +41417,7 @@
         <v>6358</v>
       </c>
     </row>
-    <row r="178" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41131,7 +41534,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="179" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41248,7 +41651,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="180" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41365,7 +41768,7 @@
         <v>4926</v>
       </c>
     </row>
-    <row r="181" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41482,7 +41885,7 @@
         <v>8964</v>
       </c>
     </row>
-    <row r="182" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41599,7 +42002,7 @@
         <v>14121</v>
       </c>
     </row>
-    <row r="183" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41716,7 +42119,7 @@
         <v>24877</v>
       </c>
     </row>
-    <row r="184" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41833,7 +42236,7 @@
         <v>31477</v>
       </c>
     </row>
-    <row r="185" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41950,7 +42353,7 @@
         <v>8910</v>
       </c>
     </row>
-    <row r="186" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42067,7 +42470,7 @@
         <v>13013</v>
       </c>
     </row>
-    <row r="187" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42184,7 +42587,7 @@
         <v>24684</v>
       </c>
     </row>
-    <row r="188" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42301,7 +42704,7 @@
         <v>31981</v>
       </c>
     </row>
-    <row r="189" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -42418,7 +42821,7 @@
         <v>27921</v>
       </c>
     </row>
-    <row r="190" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -42535,7 +42938,7 @@
         <v>11519</v>
       </c>
     </row>
-    <row r="191" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -42652,7 +43055,7 @@
         <v>4144</v>
       </c>
     </row>
-    <row r="192" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -42769,7 +43172,7 @@
         <v>34249</v>
       </c>
     </row>
-    <row r="193" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -42886,7 +43289,7 @@
         <v>11403</v>
       </c>
     </row>
-    <row r="194" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43003,7 +43406,7 @@
         <v>13958</v>
       </c>
     </row>
-    <row r="195" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43120,7 +43523,7 @@
         <v>33065</v>
       </c>
     </row>
-    <row r="196" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43237,7 +43640,7 @@
         <v>12892</v>
       </c>
     </row>
-    <row r="197" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43354,7 +43757,7 @@
         <v>19457</v>
       </c>
     </row>
-    <row r="198" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43471,7 +43874,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="199" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43588,7 +43991,7 @@
         <v>10073</v>
       </c>
     </row>
-    <row r="200" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43705,7 +44108,7 @@
         <v>15353</v>
       </c>
     </row>
-    <row r="201" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43822,7 +44225,7 @@
         <v>11342</v>
       </c>
     </row>
-    <row r="202" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43939,7 +44342,7 @@
         <v>4965</v>
       </c>
     </row>
-    <row r="203" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44056,7 +44459,7 @@
         <v>35072</v>
       </c>
     </row>
-    <row r="204" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44173,7 +44576,7 @@
         <v>13753</v>
       </c>
     </row>
-    <row r="205" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44290,7 +44693,7 @@
         <v>15998</v>
       </c>
     </row>
-    <row r="206" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44407,7 +44810,7 @@
         <v>29574</v>
       </c>
     </row>
-    <row r="207" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44522,6 +44925,942 @@
       </c>
       <c r="AL207">
         <v>33762</v>
+      </c>
+    </row>
+    <row r="208" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B208" s="33" t="s">
+        <v>615</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E208" t="s">
+        <v>18</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G208" s="3">
+        <v>2</v>
+      </c>
+      <c r="H208" s="3">
+        <v>7</v>
+      </c>
+      <c r="I208" s="3">
+        <v>7</v>
+      </c>
+      <c r="J208" s="3">
+        <v>7</v>
+      </c>
+      <c r="K208" s="3">
+        <v>7</v>
+      </c>
+      <c r="L208">
+        <v>22</v>
+      </c>
+      <c r="M208">
+        <v>19</v>
+      </c>
+      <c r="N208">
+        <v>78</v>
+      </c>
+      <c r="O208">
+        <v>81</v>
+      </c>
+      <c r="P208" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q208" s="3">
+        <v>7</v>
+      </c>
+      <c r="R208" s="3">
+        <v>7</v>
+      </c>
+      <c r="S208" s="3">
+        <v>7</v>
+      </c>
+      <c r="T208" s="3">
+        <v>7</v>
+      </c>
+      <c r="U208" s="3">
+        <v>7</v>
+      </c>
+      <c r="V208" t="s">
+        <v>169</v>
+      </c>
+      <c r="W208" s="3">
+        <v>10</v>
+      </c>
+      <c r="X208" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y208">
+        <v>49</v>
+      </c>
+      <c r="Z208">
+        <v>24.5</v>
+      </c>
+      <c r="AA208">
+        <v>57</v>
+      </c>
+      <c r="AB208">
+        <v>7</v>
+      </c>
+      <c r="AC208">
+        <v>28.499999999999996</v>
+      </c>
+      <c r="AD208">
+        <v>65</v>
+      </c>
+      <c r="AE208">
+        <v>6</v>
+      </c>
+      <c r="AF208">
+        <v>30</v>
+      </c>
+      <c r="AG208" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH208" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI208" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ208" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK208" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL208">
+        <v>16087</v>
+      </c>
+    </row>
+    <row r="209" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A209" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B209" t="s">
+        <v>619</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E209" t="s">
+        <v>18</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G209" s="3">
+        <v>2</v>
+      </c>
+      <c r="H209" s="3">
+        <v>7</v>
+      </c>
+      <c r="I209" s="3">
+        <v>7</v>
+      </c>
+      <c r="J209" s="3">
+        <v>7</v>
+      </c>
+      <c r="K209" s="3">
+        <v>5</v>
+      </c>
+      <c r="L209">
+        <v>22</v>
+      </c>
+      <c r="M209">
+        <v>15</v>
+      </c>
+      <c r="N209">
+        <v>78</v>
+      </c>
+      <c r="O209">
+        <v>85</v>
+      </c>
+      <c r="P209" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q209" s="3">
+        <v>7</v>
+      </c>
+      <c r="R209" s="3">
+        <v>7</v>
+      </c>
+      <c r="S209" s="3">
+        <v>7</v>
+      </c>
+      <c r="T209" s="3">
+        <v>7</v>
+      </c>
+      <c r="U209" s="3">
+        <v>7</v>
+      </c>
+      <c r="V209" t="s">
+        <v>169</v>
+      </c>
+      <c r="W209" s="3">
+        <v>7</v>
+      </c>
+      <c r="X209" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y209">
+        <v>49</v>
+      </c>
+      <c r="Z209">
+        <v>24.5</v>
+      </c>
+      <c r="AA209">
+        <v>61</v>
+      </c>
+      <c r="AB209">
+        <v>7</v>
+      </c>
+      <c r="AC209">
+        <v>30.5</v>
+      </c>
+      <c r="AD209">
+        <v>65</v>
+      </c>
+      <c r="AE209">
+        <v>4</v>
+      </c>
+      <c r="AF209">
+        <v>20</v>
+      </c>
+      <c r="AG209" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH209" s="3">
+        <v>995638</v>
+      </c>
+      <c r="AI209" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ209" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK209" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL209">
+        <v>22924</v>
+      </c>
+    </row>
+    <row r="210" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B210" t="s">
+        <v>622</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E210" t="s">
+        <v>18</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G210" s="3">
+        <v>2</v>
+      </c>
+      <c r="H210" s="3">
+        <v>7</v>
+      </c>
+      <c r="I210" s="3">
+        <v>7</v>
+      </c>
+      <c r="J210" s="3">
+        <v>7</v>
+      </c>
+      <c r="K210" s="3">
+        <v>5</v>
+      </c>
+      <c r="L210">
+        <v>38</v>
+      </c>
+      <c r="M210">
+        <v>23</v>
+      </c>
+      <c r="N210">
+        <v>62</v>
+      </c>
+      <c r="O210">
+        <v>77</v>
+      </c>
+      <c r="P210" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q210" s="3">
+        <v>7</v>
+      </c>
+      <c r="R210" s="3">
+        <v>7</v>
+      </c>
+      <c r="S210" s="3">
+        <v>7</v>
+      </c>
+      <c r="T210" s="3">
+        <v>7</v>
+      </c>
+      <c r="U210" s="3">
+        <v>7</v>
+      </c>
+      <c r="V210" t="s">
+        <v>169</v>
+      </c>
+      <c r="W210" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X210" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y210">
+        <v>66</v>
+      </c>
+      <c r="Z210">
+        <v>33</v>
+      </c>
+      <c r="AA210">
+        <v>64</v>
+      </c>
+      <c r="AB210">
+        <v>5</v>
+      </c>
+      <c r="AC210">
+        <v>32</v>
+      </c>
+      <c r="AD210">
+        <v>75</v>
+      </c>
+      <c r="AE210">
+        <v>5</v>
+      </c>
+      <c r="AF210">
+        <v>25</v>
+      </c>
+      <c r="AG210" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH210" s="3">
+        <v>42854</v>
+      </c>
+      <c r="AI210" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ210" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK210" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL210">
+        <v>32373</v>
+      </c>
+    </row>
+    <row r="211" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A211" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B211" t="s">
+        <v>624</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="E211" t="s">
+        <v>18</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G211" s="3">
+        <v>2</v>
+      </c>
+      <c r="H211" s="3">
+        <v>7</v>
+      </c>
+      <c r="I211" s="3">
+        <v>7</v>
+      </c>
+      <c r="J211" s="3">
+        <v>7</v>
+      </c>
+      <c r="K211" s="3">
+        <v>7</v>
+      </c>
+      <c r="L211">
+        <v>30</v>
+      </c>
+      <c r="M211">
+        <v>22</v>
+      </c>
+      <c r="N211">
+        <v>70</v>
+      </c>
+      <c r="O211">
+        <v>78</v>
+      </c>
+      <c r="P211" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q211" s="3">
+        <v>7</v>
+      </c>
+      <c r="R211" s="3">
+        <v>7</v>
+      </c>
+      <c r="S211" s="3">
+        <v>7</v>
+      </c>
+      <c r="T211" s="3">
+        <v>7</v>
+      </c>
+      <c r="U211" s="3">
+        <v>7</v>
+      </c>
+      <c r="V211" t="s">
+        <v>169</v>
+      </c>
+      <c r="W211" s="3">
+        <v>7</v>
+      </c>
+      <c r="X211" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y211">
+        <v>49</v>
+      </c>
+      <c r="Z211">
+        <v>24.5</v>
+      </c>
+      <c r="AA211">
+        <v>61</v>
+      </c>
+      <c r="AB211">
+        <v>5</v>
+      </c>
+      <c r="AC211">
+        <v>30.5</v>
+      </c>
+      <c r="AD211">
+        <v>75</v>
+      </c>
+      <c r="AE211">
+        <v>4</v>
+      </c>
+      <c r="AF211">
+        <v>20</v>
+      </c>
+      <c r="AG211" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH211" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI211" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ211" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK211" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL211">
+        <v>36253</v>
+      </c>
+    </row>
+    <row r="212" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A212" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B212" t="s">
+        <v>627</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E212" t="s">
+        <v>18</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G212" s="3">
+        <v>2</v>
+      </c>
+      <c r="H212" s="3">
+        <v>7</v>
+      </c>
+      <c r="I212" s="3">
+        <v>10</v>
+      </c>
+      <c r="J212" s="3">
+        <v>7</v>
+      </c>
+      <c r="K212" s="3">
+        <v>5</v>
+      </c>
+      <c r="L212">
+        <v>23</v>
+      </c>
+      <c r="M212">
+        <v>29</v>
+      </c>
+      <c r="N212">
+        <v>77</v>
+      </c>
+      <c r="O212">
+        <v>71</v>
+      </c>
+      <c r="P212" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q212" s="3">
+        <v>7</v>
+      </c>
+      <c r="R212" s="3">
+        <v>7</v>
+      </c>
+      <c r="S212" s="3">
+        <v>7</v>
+      </c>
+      <c r="T212" s="3">
+        <v>7</v>
+      </c>
+      <c r="U212" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V212" t="s">
+        <v>169</v>
+      </c>
+      <c r="W212" s="3">
+        <v>10</v>
+      </c>
+      <c r="X212" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y212">
+        <v>62</v>
+      </c>
+      <c r="Z212">
+        <v>31</v>
+      </c>
+      <c r="AA212">
+        <v>49</v>
+      </c>
+      <c r="AB212">
+        <v>5</v>
+      </c>
+      <c r="AC212">
+        <v>24.5</v>
+      </c>
+      <c r="AD212">
+        <v>75</v>
+      </c>
+      <c r="AE212">
+        <v>3</v>
+      </c>
+      <c r="AF212">
+        <v>15</v>
+      </c>
+      <c r="AG212" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH212" s="3">
+        <v>40762</v>
+      </c>
+      <c r="AI212" t="s">
+        <v>205</v>
+      </c>
+      <c r="AJ212" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK212" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL212">
+        <v>13342</v>
+      </c>
+    </row>
+    <row r="213" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A213" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B213" t="s">
+        <v>631</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E213" t="s">
+        <v>18</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G213" s="3">
+        <v>2</v>
+      </c>
+      <c r="H213" s="3">
+        <v>7</v>
+      </c>
+      <c r="I213" s="3">
+        <v>7</v>
+      </c>
+      <c r="J213" s="3">
+        <v>7</v>
+      </c>
+      <c r="K213" s="3">
+        <v>7</v>
+      </c>
+      <c r="L213">
+        <v>22</v>
+      </c>
+      <c r="M213">
+        <v>23</v>
+      </c>
+      <c r="N213">
+        <v>78</v>
+      </c>
+      <c r="O213">
+        <v>77</v>
+      </c>
+      <c r="P213" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q213" s="3">
+        <v>7</v>
+      </c>
+      <c r="R213" s="3">
+        <v>7</v>
+      </c>
+      <c r="S213" s="3">
+        <v>7</v>
+      </c>
+      <c r="T213" s="3">
+        <v>7</v>
+      </c>
+      <c r="U213" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V213" t="s">
+        <v>169</v>
+      </c>
+      <c r="W213" s="3">
+        <v>10</v>
+      </c>
+      <c r="X213" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y213">
+        <v>42</v>
+      </c>
+      <c r="Z213">
+        <v>21</v>
+      </c>
+      <c r="AA213">
+        <v>47</v>
+      </c>
+      <c r="AB213">
+        <v>8</v>
+      </c>
+      <c r="AC213">
+        <v>23.5</v>
+      </c>
+      <c r="AD213">
+        <v>60</v>
+      </c>
+      <c r="AE213">
+        <v>4</v>
+      </c>
+      <c r="AF213">
+        <v>20</v>
+      </c>
+      <c r="AG213" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH213" s="3">
+        <v>42846</v>
+      </c>
+      <c r="AI213" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ213" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK213" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL213">
+        <v>16090</v>
+      </c>
+    </row>
+    <row r="214" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A214" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B214" t="s">
+        <v>634</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E214" t="s">
+        <v>18</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G214" s="3">
+        <v>2</v>
+      </c>
+      <c r="H214" s="3">
+        <v>7</v>
+      </c>
+      <c r="I214" s="3">
+        <v>7</v>
+      </c>
+      <c r="J214" s="3">
+        <v>7</v>
+      </c>
+      <c r="K214" s="3">
+        <v>5</v>
+      </c>
+      <c r="L214">
+        <v>21</v>
+      </c>
+      <c r="M214">
+        <v>25</v>
+      </c>
+      <c r="N214">
+        <v>79</v>
+      </c>
+      <c r="O214">
+        <v>75</v>
+      </c>
+      <c r="P214" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q214" s="3">
+        <v>7</v>
+      </c>
+      <c r="R214" s="3">
+        <v>7</v>
+      </c>
+      <c r="S214" s="3">
+        <v>7</v>
+      </c>
+      <c r="T214" s="3">
+        <v>7</v>
+      </c>
+      <c r="U214" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V214" t="s">
+        <v>20</v>
+      </c>
+      <c r="W214" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X214" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y214">
+        <v>44</v>
+      </c>
+      <c r="Z214">
+        <v>22</v>
+      </c>
+      <c r="AA214">
+        <v>43</v>
+      </c>
+      <c r="AB214">
+        <v>5</v>
+      </c>
+      <c r="AC214">
+        <v>21.5</v>
+      </c>
+      <c r="AD214">
+        <v>75</v>
+      </c>
+      <c r="AE214">
+        <v>5</v>
+      </c>
+      <c r="AF214">
+        <v>25</v>
+      </c>
+      <c r="AG214" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH214" s="3">
+        <v>995638</v>
+      </c>
+      <c r="AI214" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ214" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK214" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL214">
+        <v>27178</v>
+      </c>
+    </row>
+    <row r="215" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B215" t="s">
+        <v>636</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E215" t="s">
+        <v>18</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G215" s="3">
+        <v>2</v>
+      </c>
+      <c r="H215" s="3">
+        <v>7</v>
+      </c>
+      <c r="I215" s="3">
+        <v>7</v>
+      </c>
+      <c r="J215" s="3">
+        <v>7</v>
+      </c>
+      <c r="K215" s="3">
+        <v>5</v>
+      </c>
+      <c r="L215">
+        <v>37</v>
+      </c>
+      <c r="M215">
+        <v>23</v>
+      </c>
+      <c r="N215">
+        <v>63</v>
+      </c>
+      <c r="O215">
+        <v>77</v>
+      </c>
+      <c r="P215" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q215" s="3">
+        <v>7</v>
+      </c>
+      <c r="R215" s="3">
+        <v>7</v>
+      </c>
+      <c r="S215" s="3">
+        <v>7</v>
+      </c>
+      <c r="T215" s="3">
+        <v>7</v>
+      </c>
+      <c r="U215" s="3">
+        <v>7</v>
+      </c>
+      <c r="V215" t="s">
+        <v>169</v>
+      </c>
+      <c r="W215" s="3">
+        <v>10</v>
+      </c>
+      <c r="X215" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y215">
+        <v>56</v>
+      </c>
+      <c r="Z215">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="AA215">
+        <v>50</v>
+      </c>
+      <c r="AB215">
+        <v>4</v>
+      </c>
+      <c r="AC215">
+        <v>25</v>
+      </c>
+      <c r="AD215">
+        <v>80</v>
+      </c>
+      <c r="AE215">
+        <v>5</v>
+      </c>
+      <c r="AF215">
+        <v>25</v>
+      </c>
+      <c r="AG215" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH215" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI215" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ215" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK215" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL215">
+        <v>34480</v>
       </c>
     </row>
   </sheetData>

--- a/IC Hashdata Sala Cortes.xlsx
+++ b/IC Hashdata Sala Cortes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9195"/>
   </bookViews>
   <sheets>
     <sheet name="IC Cortes" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="646">
   <si>
     <t>ID</t>
   </si>
@@ -2002,6 +2002,33 @@
   </si>
   <si>
     <t>08/10/2026 16:37:53</t>
+  </si>
+  <si>
+    <t>6acf1420493a357f397acf4c</t>
+  </si>
+  <si>
+    <t>13/10/2026 21:48:46</t>
+  </si>
+  <si>
+    <t>14/10/2026 02:33:20</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>6acf141f493a357f397acf34</t>
+  </si>
+  <si>
+    <t>13/10/2026 16:31:23</t>
+  </si>
+  <si>
+    <t>14/10/2026 02:33:19</t>
+  </si>
+  <si>
+    <t>Selagem está conforme,
+Data  de validade e produção estão de acordo,
+Caixa está sem rasgos e seca,
+Acomodação do produto está conforme especificação</t>
   </si>
 </sst>
 </file>
@@ -2407,6 +2434,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2415,18 +2454,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2781,7 +2808,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46308.563549305552" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="214">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Autor" refreshedDate="46309.407449305552" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="216">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1" r:id="rId2"/>
   </cacheSource>
@@ -2813,7 +2840,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Data" numFmtId="14">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="52">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-07-02T00:00:00" count="53">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-02-01T00:00:00"/>
         <d v="2026-03-01T00:00:00"/>
@@ -2866,6 +2893,7 @@
         <s v="06/10/2026"/>
         <s v="09/10/2026"/>
         <s v="08/10/2026"/>
+        <s v="13/10/2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Turno" numFmtId="0">
@@ -2974,7 +3002,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="214">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="216">
   <r>
     <x v="0"/>
     <m/>
@@ -11535,12 +11563,92 @@
     <s v=""/>
     <n v="34480"/>
   </r>
+  <r>
+    <x v="9"/>
+    <s v="6acf1420493a357f397acf4c"/>
+    <s v="13/10/2026 21:48:46"/>
+    <s v="14/10/2026 02:33:20"/>
+    <s v="Ranieli"/>
+    <x v="52"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="32"/>
+    <n v="33"/>
+    <n v="68"/>
+    <n v="67"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="5"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="48"/>
+    <n v="24"/>
+    <n v="47"/>
+    <n v="9"/>
+    <n v="23.5"/>
+    <n v="55"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="995638"/>
+    <s v="Acomodação do produto está conforme especificação,_x000a_Data  de validade e produção estão de acordo,_x000a_Caixa está sem rasgos e seca,_x000a_Selagem está conforme"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="7341"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="6acf141f493a357f397acf34"/>
+    <s v="13/10/2026 16:31:23"/>
+    <s v="14/10/2026 02:33:19"/>
+    <s v="Ranieli"/>
+    <x v="52"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="33"/>
+    <n v="39"/>
+    <n v="67"/>
+    <n v="61"/>
+    <n v="5"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="7"/>
+    <s v="Riscou o Sassami em X,_x000a_Retirou a Cartilagem"/>
+    <n v="7"/>
+    <n v="7"/>
+    <n v="66"/>
+    <n v="33"/>
+    <n v="46"/>
+    <n v="9"/>
+    <n v="23"/>
+    <n v="55"/>
+    <n v="2"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="15105"/>
+    <s v="Selagem está conforme,_x000a_Data  de validade e produção estão de acordo,_x000a_Caixa está sem rasgos e seca,_x000a_Acomodação do produto está conforme especificação"/>
+    <s v="assinatura"/>
+    <s v="assinatura"/>
+    <n v="26271"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" preserveFormatting="0" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="U117:AA118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
+  <location ref="U117:AB118" firstHeaderRow="1" firstDataRow="2" firstDataCol="0"/>
   <pivotFields count="38">
     <pivotField showAll="0">
       <items count="11">
@@ -11562,7 +11670,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="53">
+      <items count="54">
         <item x="26"/>
         <item x="45"/>
         <item x="28"/>
@@ -11584,6 +11692,7 @@
         <item x="30"/>
         <item x="9"/>
         <item x="8"/>
+        <item x="52"/>
         <item x="7"/>
         <item x="33"/>
         <item x="34"/>
@@ -11657,7 +11766,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="7">
+  <colItems count="8">
     <i>
       <x v="1"/>
     </i>
@@ -11678,6 +11787,9 @@
     </i>
     <i>
       <x v="14"/>
+    </i>
+    <i>
+      <x v="21"/>
     </i>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -11763,8 +11875,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL215" totalsRowShown="0">
-  <autoFilter ref="A1:AL215"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:AL217" totalsRowShown="0">
+  <autoFilter ref="A1:AL217"/>
   <tableColumns count="38">
     <tableColumn id="2" name="Mês" dataDxfId="16">
       <calculatedColumnFormula>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</calculatedColumnFormula>
@@ -12134,22 +12246,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AR118"/>
-  <sheetFormatPr defaultColWidth="9.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.88671875" style="25" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" style="25" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="29.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" customWidth="1"/>
-    <col min="7" max="18" width="9.109375" style="25" customWidth="1"/>
-    <col min="19" max="19" width="9.109375" customWidth="1"/>
-    <col min="20" max="20" width="1.6640625" customWidth="1"/>
-    <col min="23" max="44" width="9.88671875" style="25"/>
+    <col min="1" max="2" width="9.85546875" style="25" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="18" width="9.140625" style="25" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
+    <col min="20" max="20" width="1.7109375" customWidth="1"/>
+    <col min="23" max="44" width="9.85546875" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:44" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:44" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>140</v>
       </c>
@@ -12237,7 +12349,7 @@
       </c>
       <c r="AB3" s="20" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>13/10/2026</v>
       </c>
       <c r="AC3" s="20" t="str">
         <f t="shared" si="0"/>
@@ -12304,7 +12416,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>120</v>
       </c>
@@ -12319,7 +12431,7 @@
         <f>IF(E4=0,D3,E4)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E4" s="35" t="str">
+      <c r="E4" s="39" t="str">
         <f>Coleta!H1</f>
         <v>Carne no Back</v>
       </c>
@@ -12474,7 +12586,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>120</v>
       </c>
@@ -12489,7 +12601,7 @@
         <f>IF(E5=0,D4,E5)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="40"/>
       <c r="F5" s="23">
         <v>2</v>
       </c>
@@ -12541,7 +12653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S5" s="39"/>
+      <c r="S5" s="36"/>
       <c r="U5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12570,9 +12682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB5" s="12" t="str">
+      <c r="AB5" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC5" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D5&amp;"]"),Tabela1[Turno],$F5,Tabela1[Data],AC$3),"")</f>
@@ -12639,7 +12751,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>120</v>
       </c>
@@ -12654,7 +12766,7 @@
         <f>IF(E6=0,D5,E6)</f>
         <v>Carne no Back</v>
       </c>
-      <c r="E6" s="37"/>
+      <c r="E6" s="41"/>
       <c r="F6" s="24" t="s">
         <v>142</v>
       </c>
@@ -12706,7 +12818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S6" s="40"/>
+      <c r="S6" s="37"/>
       <c r="U6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -12735,9 +12847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB6" s="9" t="str">
+      <c r="AB6" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC6" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D6&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -12804,7 +12916,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>120</v>
       </c>
@@ -12819,7 +12931,7 @@
         <f>IF(E7=0,D6,E7)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E7" s="35" t="str">
+      <c r="E7" s="39" t="str">
         <f>Coleta!I1</f>
         <v>Peito na Asa Meyn</v>
       </c>
@@ -12974,7 +13086,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>120</v>
       </c>
@@ -12989,7 +13101,7 @@
         <f t="shared" ref="D8:D56" si="2">IF(E8=0,D7,E8)</f>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E8" s="36"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="23">
         <v>2</v>
       </c>
@@ -13031,7 +13143,7 @@
       </c>
       <c r="P8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],P$3),"")</f>
-        <v>7.333333333333333</v>
+        <v>7.5172413793103452</v>
       </c>
       <c r="Q8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],Q$3),"")</f>
@@ -13041,7 +13153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S8" s="39"/>
+      <c r="S8" s="36"/>
       <c r="U8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -13070,9 +13182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB8" s="12" t="str">
+      <c r="AB8" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC8" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D8&amp;"]"),Tabela1[Turno],$F8,Tabela1[Data],AC$3),"")</f>
@@ -13139,7 +13251,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>120</v>
       </c>
@@ -13154,7 +13266,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Meyn</v>
       </c>
-      <c r="E9" s="37"/>
+      <c r="E9" s="41"/>
       <c r="F9" s="24" t="s">
         <v>142</v>
       </c>
@@ -13196,7 +13308,7 @@
       </c>
       <c r="P9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.333333333333333</v>
+        <v>7.5172413793103452</v>
       </c>
       <c r="Q9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -13206,7 +13318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S9" s="40"/>
+      <c r="S9" s="37"/>
       <c r="U9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -13235,9 +13347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB9" s="9" t="str">
+      <c r="AB9" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC9" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D9&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -13304,7 +13416,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>120</v>
       </c>
@@ -13319,7 +13431,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E10" s="35" t="str">
+      <c r="E10" s="39" t="str">
         <f>Coleta!J1</f>
         <v>Medalhão na Asa Meyn</v>
       </c>
@@ -13474,7 +13586,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>120</v>
       </c>
@@ -13489,7 +13601,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="40"/>
       <c r="F11" s="23">
         <v>2</v>
       </c>
@@ -13531,7 +13643,7 @@
       </c>
       <c r="P11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],P$3),"")</f>
-        <v>7</v>
+        <v>7.1034482758620694</v>
       </c>
       <c r="Q11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],Q$3),"")</f>
@@ -13541,7 +13653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S11" s="39"/>
+      <c r="S11" s="36"/>
       <c r="U11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -13570,9 +13682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB11" s="12" t="str">
+      <c r="AB11" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AC11" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D11&amp;"]"),Tabela1[Turno],$F11,Tabela1[Data],AC$3),"")</f>
@@ -13639,7 +13751,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>120</v>
       </c>
@@ -13654,7 +13766,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Meyn</v>
       </c>
-      <c r="E12" s="37"/>
+      <c r="E12" s="41"/>
       <c r="F12" s="24" t="s">
         <v>142</v>
       </c>
@@ -13696,7 +13808,7 @@
       </c>
       <c r="P12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7</v>
+        <v>7.1034482758620694</v>
       </c>
       <c r="Q12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -13706,7 +13818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S12" s="40"/>
+      <c r="S12" s="37"/>
       <c r="U12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -13735,9 +13847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB12" s="9" t="str">
+      <c r="AB12" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="AC12" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D12&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -13804,7 +13916,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
         <v>120</v>
       </c>
@@ -13819,7 +13931,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E13" s="35" t="str">
+      <c r="E13" s="39" t="str">
         <f>Coleta!K1</f>
         <v>Carne no Front</v>
       </c>
@@ -13974,7 +14086,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>120</v>
       </c>
@@ -13989,7 +14101,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="23">
         <v>2</v>
       </c>
@@ -14031,7 +14143,7 @@
       </c>
       <c r="P14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],P$3),"")</f>
-        <v>5.5185185185185182</v>
+        <v>5.5517241379310347</v>
       </c>
       <c r="Q14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],Q$3),"")</f>
@@ -14041,7 +14153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S14" s="39"/>
+      <c r="S14" s="36"/>
       <c r="U14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -14070,9 +14182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AA$3),"")</f>
         <v>6</v>
       </c>
-      <c r="AB14" s="12" t="str">
+      <c r="AB14" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AC14" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D14&amp;"]"),Tabela1[Turno],$F14,Tabela1[Data],AC$3),"")</f>
@@ -14139,7 +14251,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
         <v>120</v>
       </c>
@@ -14154,7 +14266,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Front</v>
       </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="41"/>
       <c r="F15" s="24" t="s">
         <v>142</v>
       </c>
@@ -14196,7 +14308,7 @@
       </c>
       <c r="P15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>5.5185185185185182</v>
+        <v>5.5517241379310347</v>
       </c>
       <c r="Q15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -14206,7 +14318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S15" s="40"/>
+      <c r="S15" s="37"/>
       <c r="U15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>5.5</v>
@@ -14235,9 +14347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>6</v>
       </c>
-      <c r="AB15" s="9" t="str">
+      <c r="AB15" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AC15" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D15&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -14304,7 +14416,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>120</v>
       </c>
@@ -14319,7 +14431,7 @@
         <f>IF(E16=0,#REF!,E16)</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E16" s="35" t="str">
+      <c r="E16" s="39" t="str">
         <f>Coleta!N1</f>
         <v>% Eficiência da Pinçagem</v>
       </c>
@@ -14374,7 +14486,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D16&amp;"]"),Tabela1[Turno],$F16,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S16" s="41">
+      <c r="S16" s="35">
         <v>0.95</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -14474,7 +14586,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>120</v>
       </c>
@@ -14489,7 +14601,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E17" s="36"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="23">
         <v>2</v>
       </c>
@@ -14531,7 +14643,7 @@
       </c>
       <c r="P17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.73851851851851846</v>
+        <v>0.73413793103448266</v>
       </c>
       <c r="Q17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],Q$3)/100,"")</f>
@@ -14541,7 +14653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S17" s="39"/>
+      <c r="S17" s="36"/>
       <c r="U17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
@@ -14570,9 +14682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AA$3)/100,"")</f>
         <v>0.72</v>
       </c>
-      <c r="AB17" s="16" t="str">
+      <c r="AB17" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="AC17" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D17&amp;"]"),Tabela1[Turno],$F17,Tabela1[Data],AC$3)/100,"")</f>
@@ -14639,7 +14751,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>120</v>
       </c>
@@ -14654,7 +14766,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência da Pinçagem</v>
       </c>
-      <c r="E18" s="37"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="24" t="s">
         <v>142</v>
       </c>
@@ -14696,7 +14808,7 @@
       </c>
       <c r="P18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.73851851851851846</v>
+        <v>0.73413793103448266</v>
       </c>
       <c r="Q18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -14706,7 +14818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S18" s="40"/>
+      <c r="S18" s="37"/>
       <c r="U18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.8075</v>
@@ -14735,9 +14847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
         <v>0.72</v>
       </c>
-      <c r="AB18" s="10" t="str">
+      <c r="AB18" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="AC18" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D18&amp;"]"),Tabela1[Data],AC$3)/100,"")</f>
@@ -14804,7 +14916,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>120</v>
       </c>
@@ -14819,7 +14931,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E19" s="35" t="str">
+      <c r="E19" s="39" t="str">
         <f>Coleta!O1</f>
         <v>% Eficiência remoção cartilagem</v>
       </c>
@@ -14874,7 +14986,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D19&amp;"]"),Tabela1[Turno],$F19,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S19" s="41">
+      <c r="S19" s="35">
         <v>0.95</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -14974,7 +15086,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>120</v>
       </c>
@@ -14989,7 +15101,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E20" s="36"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="23">
         <v>2</v>
       </c>
@@ -15031,7 +15143,7 @@
       </c>
       <c r="P20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.79814814814814805</v>
+        <v>0.78724137931034477</v>
       </c>
       <c r="Q20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],Q$3)/100,"")</f>
@@ -15041,7 +15153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S20" s="39"/>
+      <c r="S20" s="36"/>
       <c r="U20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
@@ -15070,9 +15182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AA$3)/100,"")</f>
         <v>0.80249999999999999</v>
       </c>
-      <c r="AB20" s="16" t="str">
+      <c r="AB20" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.64</v>
       </c>
       <c r="AC20" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D20&amp;"]"),Tabela1[Turno],$F20,Tabela1[Data],AC$3)/100,"")</f>
@@ -15139,7 +15251,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>120</v>
       </c>
@@ -15154,7 +15266,7 @@
         <f t="shared" si="2"/>
         <v>% Eficiência remoção cartilagem</v>
       </c>
-      <c r="E21" s="37"/>
+      <c r="E21" s="41"/>
       <c r="F21" s="24" t="s">
         <v>142</v>
       </c>
@@ -15196,7 +15308,7 @@
       </c>
       <c r="P21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.79814814814814805</v>
+        <v>0.78724137931034477</v>
       </c>
       <c r="Q21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -15206,7 +15318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S21" s="40"/>
+      <c r="S21" s="37"/>
       <c r="U21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.75249999999999995</v>
@@ -15235,9 +15347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
         <v>0.80249999999999999</v>
       </c>
-      <c r="AB21" s="10" t="str">
+      <c r="AB21" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.64</v>
       </c>
       <c r="AC21" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D21&amp;"]"),Tabela1[Data],AC$3)/100,"")</f>
@@ -15304,7 +15416,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>121</v>
       </c>
@@ -15319,7 +15431,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E22" s="35" t="str">
+      <c r="E22" s="39" t="str">
         <f>Coleta!P1</f>
         <v>Corte Perna Cone</v>
       </c>
@@ -15474,7 +15586,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>121</v>
       </c>
@@ -15489,7 +15601,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E23" s="36"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="23">
         <v>2</v>
       </c>
@@ -15531,7 +15643,7 @@
       </c>
       <c r="P23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],P$3),"")</f>
-        <v>6.5555555555555554</v>
+        <v>6.5172413793103452</v>
       </c>
       <c r="Q23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],Q$3),"")</f>
@@ -15541,7 +15653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S23" s="39"/>
+      <c r="S23" s="36"/>
       <c r="U23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],U$3),"")</f>
         <v>6</v>
@@ -15570,9 +15682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AA$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AB23" s="12" t="str">
+      <c r="AB23" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AC23" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D23&amp;"]"),Tabela1[Turno],$F23,Tabela1[Data],AC$3),"")</f>
@@ -15639,7 +15751,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>121</v>
       </c>
@@ -15654,7 +15766,7 @@
         <f t="shared" si="2"/>
         <v>Corte Perna Cone</v>
       </c>
-      <c r="E24" s="37"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="24" t="s">
         <v>142</v>
       </c>
@@ -15696,7 +15808,7 @@
       </c>
       <c r="P24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.5555555555555554</v>
+        <v>6.5172413793103452</v>
       </c>
       <c r="Q24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -15706,7 +15818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S24" s="40"/>
+      <c r="S24" s="37"/>
       <c r="U24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6</v>
@@ -15735,9 +15847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>6.5</v>
       </c>
-      <c r="AB24" s="9" t="str">
+      <c r="AB24" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AC24" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D24&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -15804,7 +15916,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>121</v>
       </c>
@@ -15819,7 +15931,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E25" s="35" t="str">
+      <c r="E25" s="39" t="str">
         <f>Coleta!Q1</f>
         <v>Peito na Asa Cone</v>
       </c>
@@ -15974,7 +16086,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>121</v>
       </c>
@@ -15989,7 +16101,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E26" s="36"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="23">
         <v>2</v>
       </c>
@@ -16031,7 +16143,7 @@
       </c>
       <c r="P26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],P$3),"")</f>
-        <v>7.1111111111111107</v>
+        <v>7.1034482758620694</v>
       </c>
       <c r="Q26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],Q$3),"")</f>
@@ -16041,7 +16153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S26" s="39"/>
+      <c r="S26" s="36"/>
       <c r="U26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -16070,9 +16182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB26" s="12" t="str">
+      <c r="AB26" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC26" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D26&amp;"]"),Tabela1[Turno],$F26,Tabela1[Data],AC$3),"")</f>
@@ -16139,7 +16251,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
         <v>121</v>
       </c>
@@ -16154,7 +16266,7 @@
         <f t="shared" si="2"/>
         <v>Peito na Asa Cone</v>
       </c>
-      <c r="E27" s="37"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="24" t="s">
         <v>142</v>
       </c>
@@ -16196,7 +16308,7 @@
       </c>
       <c r="P27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.1111111111111107</v>
+        <v>7.1034482758620694</v>
       </c>
       <c r="Q27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -16206,7 +16318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S27" s="40"/>
+      <c r="S27" s="37"/>
       <c r="U27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7.75</v>
@@ -16235,9 +16347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB27" s="9" t="str">
+      <c r="AB27" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC27" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D27&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -16304,7 +16416,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>121</v>
       </c>
@@ -16319,7 +16431,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E28" s="35" t="str">
+      <c r="E28" s="39" t="str">
         <f>Coleta!R1</f>
         <v>Medalhão na Asa Cone</v>
       </c>
@@ -16474,7 +16586,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>121</v>
       </c>
@@ -16489,7 +16601,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E29" s="36"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="23">
         <v>2</v>
       </c>
@@ -16541,7 +16653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S29" s="39"/>
+      <c r="S29" s="36"/>
       <c r="U29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16570,9 +16682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB29" s="12" t="str">
+      <c r="AB29" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC29" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D29&amp;"]"),Tabela1[Turno],$F29,Tabela1[Data],AC$3),"")</f>
@@ -16639,7 +16751,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>121</v>
       </c>
@@ -16654,7 +16766,7 @@
         <f t="shared" si="2"/>
         <v>Medalhão na Asa Cone</v>
       </c>
-      <c r="E30" s="37"/>
+      <c r="E30" s="41"/>
       <c r="F30" s="24" t="s">
         <v>142</v>
       </c>
@@ -16706,7 +16818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S30" s="40"/>
+      <c r="S30" s="37"/>
       <c r="U30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -16735,9 +16847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB30" s="9" t="str">
+      <c r="AB30" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC30" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D30&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -16804,7 +16916,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>121</v>
       </c>
@@ -16819,7 +16931,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E31" s="35" t="str">
+      <c r="E31" s="39" t="str">
         <f>Coleta!S1</f>
         <v>Corte Peito Cone</v>
       </c>
@@ -16974,7 +17086,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>121</v>
       </c>
@@ -16989,7 +17101,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E32" s="36"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="23">
         <v>2</v>
       </c>
@@ -17031,7 +17143,7 @@
       </c>
       <c r="P32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],P$3),"")</f>
-        <v>6.9259259259259256</v>
+        <v>6.931034482758621</v>
       </c>
       <c r="Q32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],Q$3),"")</f>
@@ -17041,7 +17153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S32" s="39"/>
+      <c r="S32" s="36"/>
       <c r="U32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -17070,9 +17182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB32" s="12" t="str">
+      <c r="AB32" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC32" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D32&amp;"]"),Tabela1[Turno],$F32,Tabela1[Data],AC$3),"")</f>
@@ -17139,7 +17251,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
         <v>121</v>
       </c>
@@ -17154,7 +17266,7 @@
         <f t="shared" si="2"/>
         <v>Corte Peito Cone</v>
       </c>
-      <c r="E33" s="37"/>
+      <c r="E33" s="41"/>
       <c r="F33" s="24" t="s">
         <v>142</v>
       </c>
@@ -17196,7 +17308,7 @@
       </c>
       <c r="P33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.9259259259259256</v>
+        <v>6.931034482758621</v>
       </c>
       <c r="Q33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -17206,7 +17318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S33" s="40"/>
+      <c r="S33" s="37"/>
       <c r="U33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -17235,9 +17347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB33" s="9" t="str">
+      <c r="AB33" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC33" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D33&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -17304,7 +17416,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
         <v>121</v>
       </c>
@@ -17319,7 +17431,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E34" s="35" t="str">
+      <c r="E34" s="39" t="str">
         <f>Coleta!T1</f>
         <v>Corte Sassami Cone</v>
       </c>
@@ -17474,7 +17586,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
         <v>121</v>
       </c>
@@ -17489,7 +17601,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E35" s="36"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="23">
         <v>2</v>
       </c>
@@ -17541,7 +17653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S35" s="39"/>
+      <c r="S35" s="36"/>
       <c r="U35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -17570,9 +17682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB35" s="12" t="str">
+      <c r="AB35" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC35" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D35&amp;"]"),Tabela1[Turno],$F35,Tabela1[Data],AC$3),"")</f>
@@ -17639,7 +17751,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>121</v>
       </c>
@@ -17654,7 +17766,7 @@
         <f t="shared" si="2"/>
         <v>Corte Sassami Cone</v>
       </c>
-      <c r="E36" s="37"/>
+      <c r="E36" s="41"/>
       <c r="F36" s="24" t="s">
         <v>142</v>
       </c>
@@ -17706,7 +17818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S36" s="40"/>
+      <c r="S36" s="37"/>
       <c r="U36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -17735,9 +17847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB36" s="9" t="str">
+      <c r="AB36" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC36" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D36&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -17804,7 +17916,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
         <v>121</v>
       </c>
@@ -17819,7 +17931,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E37" s="35" t="str">
+      <c r="E37" s="39" t="str">
         <f>Coleta!U1</f>
         <v>Corte Cartilagem Cone</v>
       </c>
@@ -17974,7 +18086,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
         <v>121</v>
       </c>
@@ -17989,7 +18101,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E38" s="36"/>
+      <c r="E38" s="40"/>
       <c r="F38" s="23">
         <v>2</v>
       </c>
@@ -18031,7 +18143,7 @@
       </c>
       <c r="P38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],P$3),"")</f>
-        <v>6.5652173913043477</v>
+        <v>6.52</v>
       </c>
       <c r="Q38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],Q$3),"")</f>
@@ -18041,7 +18153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S38" s="39"/>
+      <c r="S38" s="36"/>
       <c r="U38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -18070,9 +18182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB38" s="12" t="str">
+      <c r="AB38" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AC38" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D38&amp;"]"),Tabela1[Turno],$F38,Tabela1[Data],AC$3),"")</f>
@@ -18139,7 +18251,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
         <v>121</v>
       </c>
@@ -18154,7 +18266,7 @@
         <f t="shared" si="2"/>
         <v>Corte Cartilagem Cone</v>
       </c>
-      <c r="E39" s="37"/>
+      <c r="E39" s="41"/>
       <c r="F39" s="24" t="s">
         <v>142</v>
       </c>
@@ -18196,7 +18308,7 @@
       </c>
       <c r="P39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>6.5652173913043477</v>
+        <v>6.52</v>
       </c>
       <c r="Q39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18206,7 +18318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S39" s="40"/>
+      <c r="S39" s="37"/>
       <c r="U39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>6.5</v>
@@ -18235,9 +18347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB39" s="9" t="str">
+      <c r="AB39" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AC39" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D39&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -18304,7 +18416,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>122</v>
       </c>
@@ -18319,7 +18431,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E40" s="35" t="str">
+      <c r="E40" s="39" t="str">
         <f>Coleta!W1</f>
         <v>Carne no Osso Perna Direita</v>
       </c>
@@ -18474,7 +18586,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
         <v>122</v>
       </c>
@@ -18489,7 +18601,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E41" s="36"/>
+      <c r="E41" s="40"/>
       <c r="F41" s="23">
         <v>2</v>
       </c>
@@ -18531,7 +18643,7 @@
       </c>
       <c r="P41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],P$3),"")</f>
-        <v>8.5789473684210531</v>
+        <v>8.4285714285714288</v>
       </c>
       <c r="Q41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],Q$3),"")</f>
@@ -18541,7 +18653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S41" s="39"/>
+      <c r="S41" s="36"/>
       <c r="U41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -18570,9 +18682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AA$3),"")</f>
         <v>8</v>
       </c>
-      <c r="AB41" s="12" t="str">
+      <c r="AB41" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC41" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D41&amp;"]"),Tabela1[Turno],$F41,Tabela1[Data],AC$3),"")</f>
@@ -18639,7 +18751,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>122</v>
       </c>
@@ -18654,7 +18766,7 @@
         <f t="shared" si="2"/>
         <v>Carne no Osso Perna Direita</v>
       </c>
-      <c r="E42" s="37"/>
+      <c r="E42" s="41"/>
       <c r="F42" s="24" t="s">
         <v>142</v>
       </c>
@@ -18696,7 +18808,7 @@
       </c>
       <c r="P42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.5789473684210531</v>
+        <v>8.4285714285714288</v>
       </c>
       <c r="Q42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -18706,7 +18818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S42" s="40"/>
+      <c r="S42" s="37"/>
       <c r="U42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>8.5</v>
@@ -18735,9 +18847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>8</v>
       </c>
-      <c r="AB42" s="9" t="str">
+      <c r="AB42" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC42" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D42&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -18804,7 +18916,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
         <v>122</v>
       </c>
@@ -18819,7 +18931,7 @@
         <f t="shared" ref="D43:D45" si="4">IF(E43=0,D42,E43)</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E43" s="35" t="str">
+      <c r="E43" s="39" t="str">
         <f>Coleta!X1</f>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
@@ -18974,7 +19086,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
         <v>122</v>
       </c>
@@ -18989,7 +19101,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E44" s="36"/>
+      <c r="E44" s="40"/>
       <c r="F44" s="23">
         <v>2</v>
       </c>
@@ -19031,7 +19143,7 @@
       </c>
       <c r="P44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],P$3),"")</f>
-        <v>7.3529411764705879</v>
+        <v>7.3157894736842106</v>
       </c>
       <c r="Q44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],Q$3),"")</f>
@@ -19041,7 +19153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S44" s="39"/>
+      <c r="S44" s="36"/>
       <c r="U44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -19070,9 +19182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB44" s="12" t="str">
+      <c r="AB44" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC44" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D44&amp;"]"),Tabela1[Turno],$F44,Tabela1[Data],AC$3),"")</f>
@@ -19139,7 +19251,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="25" t="s">
         <v>122</v>
       </c>
@@ -19154,7 +19266,7 @@
         <f t="shared" si="4"/>
         <v>Carne no Osso Perna Esquerda</v>
       </c>
-      <c r="E45" s="37"/>
+      <c r="E45" s="41"/>
       <c r="F45" s="24" t="s">
         <v>142</v>
       </c>
@@ -19196,7 +19308,7 @@
       </c>
       <c r="P45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>7.3529411764705879</v>
+        <v>7.3157894736842106</v>
       </c>
       <c r="Q45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -19206,7 +19318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S45" s="40"/>
+      <c r="S45" s="37"/>
       <c r="U45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>7</v>
@@ -19235,9 +19347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>7</v>
       </c>
-      <c r="AB45" s="9" t="str">
+      <c r="AB45" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC45" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D45&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -19304,7 +19416,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:44" s="25" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:44" s="25" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A46" s="25" t="s">
         <v>122</v>
       </c>
@@ -19319,7 +19431,7 @@
         <f>IF(E46=0,#REF!,E46)</f>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E46" s="35" t="str">
+      <c r="E46" s="39" t="str">
         <f>Coleta!Z1</f>
         <v>% Carne Refile Perna</v>
       </c>
@@ -19374,7 +19486,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D46&amp;"]"),Tabela1[Turno],$F46,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S46" s="41">
+      <c r="S46" s="35">
         <v>0.2</v>
       </c>
       <c r="U46" s="28" t="str">
@@ -19474,7 +19586,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A47" s="25" t="s">
         <v>122</v>
       </c>
@@ -19489,7 +19601,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E47" s="36"/>
+      <c r="E47" s="40"/>
       <c r="F47" s="23">
         <v>2</v>
       </c>
@@ -19531,7 +19643,7 @@
       </c>
       <c r="P47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24557692307692305</v>
+        <v>0.24839285714285717</v>
       </c>
       <c r="Q47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],Q$3)/100,"")</f>
@@ -19541,7 +19653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S47" s="39"/>
+      <c r="S47" s="36"/>
       <c r="U47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
@@ -19570,9 +19682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AA$3)/100,"")</f>
         <v>0.26624999999999999</v>
       </c>
-      <c r="AB47" s="16" t="str">
+      <c r="AB47" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.28499999999999998</v>
       </c>
       <c r="AC47" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D47&amp;"]"),Tabela1[Turno],$F47,Tabela1[Data],AC$3)/100,"")</f>
@@ -19639,7 +19751,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="25" t="s">
         <v>122</v>
       </c>
@@ -19654,7 +19766,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Perna</v>
       </c>
-      <c r="E48" s="37"/>
+      <c r="E48" s="41"/>
       <c r="F48" s="24" t="s">
         <v>142</v>
       </c>
@@ -19696,7 +19808,7 @@
       </c>
       <c r="P48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24557692307692305</v>
+        <v>0.24839285714285717</v>
       </c>
       <c r="Q48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -19706,7 +19818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S48" s="40"/>
+      <c r="S48" s="37"/>
       <c r="U48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.30166666666666669</v>
@@ -19735,9 +19847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
         <v>0.26624999999999999</v>
       </c>
-      <c r="AB48" s="10" t="str">
+      <c r="AB48" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.28499999999999998</v>
       </c>
       <c r="AC48" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D48&amp;"]"),Tabela1[Data],AC$3)/100,"")</f>
@@ -19804,7 +19916,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
         <v>123</v>
       </c>
@@ -19819,7 +19931,7 @@
         <f>IF(E49=0,#REF!,E49)</f>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E49" s="35" t="str">
+      <c r="E49" s="39" t="str">
         <f>Coleta!AC1</f>
         <v>% Carne Refile Peito</v>
       </c>
@@ -19874,7 +19986,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D49&amp;"]"),Tabela1[Turno],$F49,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S49" s="41">
+      <c r="S49" s="35">
         <v>0.15</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -19974,7 +20086,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A50" s="25" t="s">
         <v>123</v>
       </c>
@@ -19989,7 +20101,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E50" s="36"/>
+      <c r="E50" s="40"/>
       <c r="F50" s="23">
         <v>2</v>
       </c>
@@ -20031,7 +20143,7 @@
       </c>
       <c r="P50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24462962962962961</v>
+        <v>0.24379310344827587</v>
       </c>
       <c r="Q50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],Q$3)/100,"")</f>
@@ -20041,7 +20153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S50" s="39"/>
+      <c r="S50" s="36"/>
       <c r="U50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
@@ -20070,9 +20182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AA$3)/100,"")</f>
         <v>0.30375000000000002</v>
       </c>
-      <c r="AB50" s="16" t="str">
+      <c r="AB50" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.23250000000000001</v>
       </c>
       <c r="AC50" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D50&amp;"]"),Tabela1[Turno],$F50,Tabela1[Data],AC$3)/100,"")</f>
@@ -20139,7 +20251,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
         <v>123</v>
       </c>
@@ -20154,7 +20266,7 @@
         <f t="shared" si="2"/>
         <v>% Carne Refile Peito</v>
       </c>
-      <c r="E51" s="37"/>
+      <c r="E51" s="41"/>
       <c r="F51" s="24" t="s">
         <v>142</v>
       </c>
@@ -20196,7 +20308,7 @@
       </c>
       <c r="P51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.24462962962962961</v>
+        <v>0.24379310344827587</v>
       </c>
       <c r="Q51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20206,7 +20318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S51" s="40"/>
+      <c r="S51" s="37"/>
       <c r="U51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.26374999999999998</v>
@@ -20235,9 +20347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
         <v>0.30375000000000002</v>
       </c>
-      <c r="AB51" s="10" t="str">
+      <c r="AB51" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.23250000000000001</v>
       </c>
       <c r="AC51" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D51&amp;"]"),Tabela1[Data],AC$3)/100,"")</f>
@@ -20304,7 +20416,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A52" s="25" t="s">
         <v>123</v>
       </c>
@@ -20319,7 +20431,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E52" s="35" t="str">
+      <c r="E52" s="39" t="str">
         <f>Coleta!AD1</f>
         <v>% Peito Limpo na esteira</v>
       </c>
@@ -20374,7 +20486,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D52&amp;"]"),Tabela1[Turno],$F52,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S52" s="41">
+      <c r="S52" s="35">
         <v>0.7</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -20474,7 +20586,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A53" s="25" t="s">
         <v>123</v>
       </c>
@@ -20489,7 +20601,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E53" s="36"/>
+      <c r="E53" s="40"/>
       <c r="F53" s="23">
         <v>2</v>
       </c>
@@ -20531,7 +20643,7 @@
       </c>
       <c r="P53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.67222222222222228</v>
+        <v>0.66379310344827591</v>
       </c>
       <c r="Q53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],Q$3)/100,"")</f>
@@ -20541,7 +20653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="39"/>
+      <c r="S53" s="36"/>
       <c r="U53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
@@ -20570,9 +20682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AA$3)/100,"")</f>
         <v>0.7</v>
       </c>
-      <c r="AB53" s="16" t="str">
+      <c r="AB53" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AC53" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D53&amp;"]"),Tabela1[Turno],$F53,Tabela1[Data],AC$3)/100,"")</f>
@@ -20639,7 +20751,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
         <v>123</v>
       </c>
@@ -20654,7 +20766,7 @@
         <f t="shared" si="2"/>
         <v>% Peito Limpo na esteira</v>
       </c>
-      <c r="E54" s="37"/>
+      <c r="E54" s="41"/>
       <c r="F54" s="24" t="s">
         <v>142</v>
       </c>
@@ -20696,7 +20808,7 @@
       </c>
       <c r="P54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.67222222222222228</v>
+        <v>0.66379310344827591</v>
       </c>
       <c r="Q54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -20706,7 +20818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S54" s="40"/>
+      <c r="S54" s="37"/>
       <c r="U54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.67500000000000004</v>
@@ -20735,9 +20847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
         <v>0.7</v>
       </c>
-      <c r="AB54" s="10" t="str">
+      <c r="AB54" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AC54" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D54&amp;"]"),Tabela1[Data],AC$3)/100,"")</f>
@@ -20804,7 +20916,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A55" s="25" t="s">
         <v>124</v>
       </c>
@@ -20819,7 +20931,7 @@
         <f>IF(E55=0,#REF!,E55)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E55" s="35" t="str">
+      <c r="E55" s="39" t="str">
         <f>Coleta!AF1</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
@@ -20874,7 +20986,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D55&amp;"]"),Tabela1[Turno],$F55,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S55" s="41">
+      <c r="S55" s="35">
         <v>0.05</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -20974,7 +21086,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
         <v>124</v>
       </c>
@@ -20989,7 +21101,7 @@
         <f t="shared" si="2"/>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E56" s="36"/>
+      <c r="E56" s="40"/>
       <c r="F56" s="23">
         <v>2</v>
       </c>
@@ -21031,7 +21143,7 @@
       </c>
       <c r="P56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.1962962962962963</v>
+        <v>0.19310344827586207</v>
       </c>
       <c r="Q56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],Q$3)/100,"")</f>
@@ -21041,7 +21153,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S56" s="39"/>
+      <c r="S56" s="36"/>
       <c r="U56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
@@ -21070,9 +21182,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AA$3)/100,"")</f>
         <v>0.23749999999999999</v>
       </c>
-      <c r="AB56" s="16" t="str">
+      <c r="AB56" s="16">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="AC56" s="16" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D56&amp;"]"),Tabela1[Turno],$F56,Tabela1[Data],AC$3)/100,"")</f>
@@ -21139,7 +21251,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
         <v>124</v>
       </c>
@@ -21154,7 +21266,7 @@
         <f t="shared" ref="D57:D60" si="5">IF(E57=0,D56,E57)</f>
         <v>% Erro de Corte da Porcionadora</v>
       </c>
-      <c r="E57" s="37"/>
+      <c r="E57" s="41"/>
       <c r="F57" s="24" t="s">
         <v>142</v>
       </c>
@@ -21196,7 +21308,7 @@
       </c>
       <c r="P57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],P$3)/100,"")</f>
-        <v>0.1962962962962963</v>
+        <v>0.19310344827586207</v>
       </c>
       <c r="Q57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],Q$3)/100,"")</f>
@@ -21206,7 +21318,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Mês],R$3)/100,"")</f>
         <v/>
       </c>
-      <c r="S57" s="40"/>
+      <c r="S57" s="37"/>
       <c r="U57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],U$3)/100,"")</f>
         <v>0.15</v>
@@ -21235,9 +21347,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AA$3)/100,"")</f>
         <v>0.23749999999999999</v>
       </c>
-      <c r="AB57" s="10" t="str">
+      <c r="AB57" s="10">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AB$3)/100,"")</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="AC57" s="10" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D57&amp;"]"),Tabela1[Data],AC$3)/100,"")</f>
@@ -21304,7 +21416,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A58" s="25" t="s">
         <v>125</v>
       </c>
@@ -21319,7 +21431,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E58" s="35" t="str">
+      <c r="E58" s="39" t="str">
         <f>Coleta!AG1</f>
         <v>Qualidade Acomodação</v>
       </c>
@@ -21474,7 +21586,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A59" s="25" t="s">
         <v>125</v>
       </c>
@@ -21489,7 +21601,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E59" s="36"/>
+      <c r="E59" s="40"/>
       <c r="F59" s="23">
         <v>2</v>
       </c>
@@ -21531,7 +21643,7 @@
       </c>
       <c r="P59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],P$3),"")</f>
-        <v>8.615384615384615</v>
+        <v>8.7142857142857135</v>
       </c>
       <c r="Q59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],Q$3),"")</f>
@@ -21541,7 +21653,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S59" s="39"/>
+      <c r="S59" s="36"/>
       <c r="U59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -21570,9 +21682,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AA$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AB59" s="12" t="str">
+      <c r="AB59" s="12">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC59" s="12" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D59&amp;"]"),Tabela1[Turno],$F59,Tabela1[Data],AC$3),"")</f>
@@ -21639,7 +21751,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="25" t="s">
         <v>125</v>
       </c>
@@ -21654,7 +21766,7 @@
         <f t="shared" si="5"/>
         <v>Qualidade Acomodação</v>
       </c>
-      <c r="E60" s="37"/>
+      <c r="E60" s="41"/>
       <c r="F60" s="24" t="s">
         <v>142</v>
       </c>
@@ -21696,7 +21808,7 @@
       </c>
       <c r="P60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],P$3),"")</f>
-        <v>8.615384615384615</v>
+        <v>8.7142857142857135</v>
       </c>
       <c r="Q60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],Q$3),"")</f>
@@ -21706,7 +21818,7 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Mês],R$3),"")</f>
         <v/>
       </c>
-      <c r="S60" s="40"/>
+      <c r="S60" s="37"/>
       <c r="U60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],U$3),"")</f>
         <v>9</v>
@@ -21735,9 +21847,9 @@
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AA$3),"")</f>
         <v>8.5</v>
       </c>
-      <c r="AB60" s="9" t="str">
+      <c r="AB60" s="9">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AB$3),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC60" s="9" t="str">
         <f ca="1">IFERROR(AVERAGEIFS(INDIRECT("Tabela1["&amp;$D60&amp;"]"),Tabela1[Data],AC$3),"")</f>
@@ -21804,27 +21916,27 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="12:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:44" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L69" s="32"/>
     </row>
-    <row r="70" spans="12:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L70" s="32"/>
       <c r="O70" s="32"/>
     </row>
-    <row r="71" spans="12:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L71" s="32"/>
       <c r="O71" s="32"/>
     </row>
-    <row r="72" spans="12:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L72" s="32"/>
       <c r="O72" s="32"/>
     </row>
-    <row r="74" spans="12:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L74" s="31"/>
       <c r="O74" s="32"/>
     </row>
-    <row r="117" spans="21:39" x14ac:dyDescent="0.3">
+    <row r="117" spans="21:39" x14ac:dyDescent="0.25">
       <c r="U117" s="21" t="s">
         <v>155</v>
       </c>
@@ -21846,7 +21958,7 @@
       <c r="AL117"/>
       <c r="AM117"/>
     </row>
-    <row r="118" spans="21:39" x14ac:dyDescent="0.3">
+    <row r="118" spans="21:39" x14ac:dyDescent="0.25">
       <c r="U118" t="s">
         <v>562</v>
       </c>
@@ -21868,7 +21980,9 @@
       <c r="AA118" t="s">
         <v>618</v>
       </c>
-      <c r="AB118"/>
+      <c r="AB118" t="s">
+        <v>641</v>
+      </c>
       <c r="AC118"/>
       <c r="AD118"/>
       <c r="AE118"/>
@@ -21883,16 +21997,18 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S55:S57"/>
-    <mergeCell ref="S58:S60"/>
-    <mergeCell ref="S31:S33"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="S40:S42"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S49:S51"/>
-    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E43:E45"/>
     <mergeCell ref="E58:E60"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="S7:S9"/>
@@ -21909,18 +22025,16 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="E34:E36"/>
     <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S55:S57"/>
+    <mergeCell ref="S58:S60"/>
+    <mergeCell ref="S31:S33"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="S40:S42"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S49:S51"/>
+    <mergeCell ref="S43:S45"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:R6 G9:R9 G12:R12 G15:R15 G24:R24 G27:R27 G30:R30 G33:R33 G36:R36 G39:R39 G42:R42 G60:R60">
     <cfRule type="colorScale" priority="31">
@@ -22159,28 +22273,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL215"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AL217"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="4" width="21" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="31" customWidth="1"/>
     <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="11.33203125" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="13.109375" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
     <col min="22" max="22" width="45" hidden="1" customWidth="1"/>
     <col min="23" max="24" width="19" customWidth="1"/>
@@ -22192,14 +22306,14 @@
     <col min="30" max="30" width="30" customWidth="1"/>
     <col min="31" max="31" width="19" customWidth="1"/>
     <col min="32" max="32" width="32" customWidth="1"/>
-    <col min="33" max="33" width="17.44140625" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" customWidth="1"/>
     <col min="34" max="34" width="7" customWidth="1"/>
     <col min="35" max="35" width="150" hidden="1" customWidth="1"/>
     <col min="36" max="37" width="39" hidden="1" customWidth="1"/>
     <col min="38" max="38" width="20" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -22315,7 +22429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>JAN</v>
@@ -22356,7 +22470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>JAN</v>
@@ -22397,7 +22511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>128</v>
       </c>
@@ -22437,7 +22551,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>128</v>
       </c>
@@ -22477,7 +22591,7 @@
         <v>13.57</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>129</v>
       </c>
@@ -22517,7 +22631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>129</v>
       </c>
@@ -22557,7 +22671,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>130</v>
       </c>
@@ -22597,7 +22711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>130</v>
       </c>
@@ -22637,7 +22751,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>131</v>
       </c>
@@ -22677,7 +22791,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>131</v>
       </c>
@@ -22717,7 +22831,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>132</v>
       </c>
@@ -22757,7 +22871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>132</v>
       </c>
@@ -22797,7 +22911,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>133</v>
       </c>
@@ -22837,7 +22951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>133</v>
       </c>
@@ -22877,7 +22991,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -22994,7 +23108,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23111,7 +23225,7 @@
         <v>4705</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23228,7 +23342,7 @@
         <v>2933</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23345,7 +23459,7 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23462,7 +23576,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23579,7 +23693,7 @@
         <v>7125</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23696,7 +23810,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23813,7 +23927,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -23930,7 +24044,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24047,7 +24161,7 @@
         <v>4603</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24164,7 +24278,7 @@
         <v>7653</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24281,7 +24395,7 @@
         <v>4698</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24398,7 +24512,7 @@
         <v>4014</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24515,7 +24629,7 @@
         <v>5115</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24632,7 +24746,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24749,7 +24863,7 @@
         <v>4821</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24866,7 +24980,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -24983,7 +25097,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25100,7 +25214,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25217,7 +25331,7 @@
         <v>4870</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25334,7 +25448,7 @@
         <v>4717</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25451,7 +25565,7 @@
         <v>3007</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25568,7 +25682,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25685,7 +25799,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25802,7 +25916,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -25919,7 +26033,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26036,7 +26150,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26153,7 +26267,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26270,7 +26384,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26387,7 +26501,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26504,7 +26618,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26621,7 +26735,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26738,7 +26852,7 @@
         <v>4922</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26855,7 +26969,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -26972,7 +27086,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27089,7 +27203,7 @@
         <v>5215</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27206,7 +27320,7 @@
         <v>3408</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27323,7 +27437,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27440,7 +27554,7 @@
         <v>3899</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27557,7 +27671,7 @@
         <v>3477</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27674,7 +27788,7 @@
         <v>5198</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27791,7 +27905,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -27908,7 +28022,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28025,7 +28139,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28142,7 +28256,7 @@
         <v>5935</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28259,7 +28373,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28376,7 +28490,7 @@
         <v>5628</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28493,7 +28607,7 @@
         <v>5091</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28610,7 +28724,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28727,7 +28841,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28844,7 +28958,7 @@
         <v>4307</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -28961,7 +29075,7 @@
         <v>5885</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29078,7 +29192,7 @@
         <v>14571</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29195,7 +29309,7 @@
         <v>3558</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29312,7 +29426,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29426,7 +29540,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29543,7 +29657,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29660,7 +29774,7 @@
         <v>9620</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29774,7 +29888,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -29891,7 +30005,7 @@
         <v>3347</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30008,7 +30122,7 @@
         <v>5223</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30125,7 +30239,7 @@
         <v>3410</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30242,7 +30356,7 @@
         <v>3465</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30359,7 +30473,7 @@
         <v>4047</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30476,7 +30590,7 @@
         <v>3842</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30593,7 +30707,7 @@
         <v>7667</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30710,7 +30824,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30827,7 +30941,7 @@
         <v>4250</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -30944,7 +31058,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31061,7 +31175,7 @@
         <v>3225</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31178,7 +31292,7 @@
         <v>3915</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31295,7 +31409,7 @@
         <v>4896</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31412,7 +31526,7 @@
         <v>3620</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31529,7 +31643,7 @@
         <v>3009</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31646,7 +31760,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -31763,7 +31877,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31858,7 +31972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -31953,7 +32067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -32048,7 +32162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -32140,7 +32254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -32232,7 +32346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32349,7 +32463,7 @@
         <v>3620</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32466,7 +32580,7 @@
         <v>3009</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32583,7 +32697,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32700,7 +32814,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>AGO</v>
@@ -32817,7 +32931,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -32934,7 +33048,7 @@
         <v>6804</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33051,7 +33165,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33168,7 +33282,7 @@
         <v>4338</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33285,7 +33399,7 @@
         <v>3285</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33402,7 +33516,7 @@
         <v>3498</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33519,7 +33633,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33633,7 +33747,7 @@
         <v>4464</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33750,7 +33864,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33843,7 +33957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -33960,7 +34074,7 @@
         <v>4823</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34077,7 +34191,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34194,7 +34308,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34311,7 +34425,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34404,7 +34518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34521,7 +34635,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34638,7 +34752,7 @@
         <v>3262</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34755,7 +34869,7 @@
         <v>3790</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34872,7 +34986,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -34989,7 +35103,7 @@
         <v>5276</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35106,7 +35220,7 @@
         <v>3767</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35223,7 +35337,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35340,7 +35454,7 @@
         <v>2657</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35457,7 +35571,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35574,7 +35688,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35691,7 +35805,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="127" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35808,7 +35922,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="128" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -35925,7 +36039,7 @@
         <v>3671</v>
       </c>
     </row>
-    <row r="129" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36042,7 +36156,7 @@
         <v>6007</v>
       </c>
     </row>
-    <row r="130" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36159,7 +36273,7 @@
         <v>8320</v>
       </c>
     </row>
-    <row r="131" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36276,7 +36390,7 @@
         <v>3757</v>
       </c>
     </row>
-    <row r="132" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36393,7 +36507,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="133" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36510,7 +36624,7 @@
         <v>5114</v>
       </c>
     </row>
-    <row r="134" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36627,7 +36741,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="135" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36744,7 +36858,7 @@
         <v>1141881</v>
       </c>
     </row>
-    <row r="136" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36832,7 +36946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -36920,7 +37034,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37008,7 +37122,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37096,7 +37210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37213,7 +37327,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="141" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37330,7 +37444,7 @@
         <v>4833</v>
       </c>
     </row>
-    <row r="142" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37447,7 +37561,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="143" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37564,7 +37678,7 @@
         <v>5054</v>
       </c>
     </row>
-    <row r="144" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37681,7 +37795,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="145" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37798,7 +37912,7 @@
         <v>5114</v>
       </c>
     </row>
-    <row r="146" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -37915,7 +38029,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="147" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38032,7 +38146,7 @@
         <v>1141881</v>
       </c>
     </row>
-    <row r="148" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38149,7 +38263,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="149" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38266,7 +38380,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="150" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38383,7 +38497,7 @@
         <v>3592</v>
       </c>
     </row>
-    <row r="151" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38500,7 +38614,7 @@
         <v>2783</v>
       </c>
     </row>
-    <row r="152" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38617,7 +38731,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="153" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38734,7 +38848,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="154" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38851,7 +38965,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="155" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -38968,7 +39082,7 @@
         <v>3341</v>
       </c>
     </row>
-    <row r="156" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39085,7 +39199,7 @@
         <v>5707</v>
       </c>
     </row>
-    <row r="157" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39202,7 +39316,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="158" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39319,7 +39433,7 @@
         <v>4382</v>
       </c>
     </row>
-    <row r="159" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39436,7 +39550,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="160" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39553,7 +39667,7 @@
         <v>5908</v>
       </c>
     </row>
-    <row r="161" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39670,7 +39784,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="162" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39787,7 +39901,7 @@
         <v>4032</v>
       </c>
     </row>
-    <row r="163" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -39904,7 +40018,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="164" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40021,7 +40135,7 @@
         <v>3844</v>
       </c>
     </row>
-    <row r="165" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40138,7 +40252,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="166" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40255,7 +40369,7 @@
         <v>4578</v>
       </c>
     </row>
-    <row r="167" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40372,7 +40486,7 @@
         <v>5257</v>
       </c>
     </row>
-    <row r="168" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40464,7 +40578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40556,7 +40670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40648,7 +40762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40740,7 +40854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40832,7 +40946,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -40949,7 +41063,7 @@
         <v>6547</v>
       </c>
     </row>
-    <row r="174" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41066,7 +41180,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="175" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41183,7 +41297,7 @@
         <v>5803</v>
       </c>
     </row>
-    <row r="176" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41300,7 +41414,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="177" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41417,7 +41531,7 @@
         <v>6358</v>
       </c>
     </row>
-    <row r="178" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41534,7 +41648,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="179" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41651,7 +41765,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="180" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41768,7 +41882,7 @@
         <v>4926</v>
       </c>
     </row>
-    <row r="181" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -41885,7 +41999,7 @@
         <v>8964</v>
       </c>
     </row>
-    <row r="182" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42002,7 +42116,7 @@
         <v>14121</v>
       </c>
     </row>
-    <row r="183" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42119,7 +42233,7 @@
         <v>24877</v>
       </c>
     </row>
-    <row r="184" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42236,7 +42350,7 @@
         <v>31477</v>
       </c>
     </row>
-    <row r="185" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42353,7 +42467,7 @@
         <v>8910</v>
       </c>
     </row>
-    <row r="186" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42470,7 +42584,7 @@
         <v>13013</v>
       </c>
     </row>
-    <row r="187" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42587,7 +42701,7 @@
         <v>24684</v>
       </c>
     </row>
-    <row r="188" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>SET</v>
@@ -42704,7 +42818,7 @@
         <v>31981</v>
       </c>
     </row>
-    <row r="189" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -42821,7 +42935,7 @@
         <v>27921</v>
       </c>
     </row>
-    <row r="190" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -42938,7 +43052,7 @@
         <v>11519</v>
       </c>
     </row>
-    <row r="191" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43055,7 +43169,7 @@
         <v>4144</v>
       </c>
     </row>
-    <row r="192" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43172,7 +43286,7 @@
         <v>34249</v>
       </c>
     </row>
-    <row r="193" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43289,7 +43403,7 @@
         <v>11403</v>
       </c>
     </row>
-    <row r="194" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43406,7 +43520,7 @@
         <v>13958</v>
       </c>
     </row>
-    <row r="195" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43523,7 +43637,7 @@
         <v>33065</v>
       </c>
     </row>
-    <row r="196" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43640,7 +43754,7 @@
         <v>12892</v>
       </c>
     </row>
-    <row r="197" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43757,7 +43871,7 @@
         <v>19457</v>
       </c>
     </row>
-    <row r="198" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43874,7 +43988,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="199" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -43991,7 +44105,7 @@
         <v>10073</v>
       </c>
     </row>
-    <row r="200" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44108,7 +44222,7 @@
         <v>15353</v>
       </c>
     </row>
-    <row r="201" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44225,7 +44339,7 @@
         <v>11342</v>
       </c>
     </row>
-    <row r="202" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44342,7 +44456,7 @@
         <v>4965</v>
       </c>
     </row>
-    <row r="203" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44459,7 +44573,7 @@
         <v>35072</v>
       </c>
     </row>
-    <row r="204" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44576,7 +44690,7 @@
         <v>13753</v>
       </c>
     </row>
-    <row r="205" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44693,7 +44807,7 @@
         <v>15998</v>
       </c>
     </row>
-    <row r="206" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44810,7 +44924,7 @@
         <v>29574</v>
       </c>
     </row>
-    <row r="207" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -44927,7 +45041,7 @@
         <v>33762</v>
       </c>
     </row>
-    <row r="208" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45044,7 +45158,7 @@
         <v>16087</v>
       </c>
     </row>
-    <row r="209" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45161,7 +45275,7 @@
         <v>22924</v>
       </c>
     </row>
-    <row r="210" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45278,7 +45392,7 @@
         <v>32373</v>
       </c>
     </row>
-    <row r="211" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45395,7 +45509,7 @@
         <v>36253</v>
       </c>
     </row>
-    <row r="212" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45512,7 +45626,7 @@
         <v>13342</v>
       </c>
     </row>
-    <row r="213" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45629,7 +45743,7 @@
         <v>16090</v>
       </c>
     </row>
-    <row r="214" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45746,7 +45860,7 @@
         <v>27178</v>
       </c>
     </row>
-    <row r="215" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="str">
         <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
         <v>OUT</v>
@@ -45861,6 +45975,240 @@
       </c>
       <c r="AL215">
         <v>34480</v>
+      </c>
+    </row>
+    <row r="216" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B216" s="33" t="s">
+        <v>638</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E216" t="s">
+        <v>18</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="G216" s="3">
+        <v>2</v>
+      </c>
+      <c r="H216" s="3">
+        <v>7</v>
+      </c>
+      <c r="I216" s="3">
+        <v>10</v>
+      </c>
+      <c r="J216" s="3">
+        <v>7</v>
+      </c>
+      <c r="K216" s="3">
+        <v>5</v>
+      </c>
+      <c r="L216">
+        <v>32</v>
+      </c>
+      <c r="M216">
+        <v>33</v>
+      </c>
+      <c r="N216">
+        <v>68</v>
+      </c>
+      <c r="O216">
+        <v>67</v>
+      </c>
+      <c r="P216" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q216" s="3">
+        <v>7</v>
+      </c>
+      <c r="R216" s="3">
+        <v>7</v>
+      </c>
+      <c r="S216" s="3">
+        <v>7</v>
+      </c>
+      <c r="T216" s="3">
+        <v>7</v>
+      </c>
+      <c r="U216" s="3">
+        <v>5</v>
+      </c>
+      <c r="V216" t="s">
+        <v>20</v>
+      </c>
+      <c r="W216" s="3">
+        <v>7</v>
+      </c>
+      <c r="X216" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y216">
+        <v>48</v>
+      </c>
+      <c r="Z216">
+        <v>24</v>
+      </c>
+      <c r="AA216">
+        <v>47</v>
+      </c>
+      <c r="AB216">
+        <v>9</v>
+      </c>
+      <c r="AC216">
+        <v>23.5</v>
+      </c>
+      <c r="AD216">
+        <v>55</v>
+      </c>
+      <c r="AE216">
+        <v>4</v>
+      </c>
+      <c r="AF216">
+        <v>20</v>
+      </c>
+      <c r="AG216" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH216" s="3">
+        <v>995638</v>
+      </c>
+      <c r="AI216" t="s">
+        <v>186</v>
+      </c>
+      <c r="AJ216" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK216" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL216">
+        <v>7341</v>
+      </c>
+    </row>
+    <row r="217" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="str">
+        <f>UPPER(TEXT(Tabela1[[#This Row],[Data]],"MMM"))</f>
+        <v>OUT</v>
+      </c>
+      <c r="B217" t="s">
+        <v>642</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="E217" t="s">
+        <v>18</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="G217" s="3">
+        <v>2</v>
+      </c>
+      <c r="H217" s="3">
+        <v>7</v>
+      </c>
+      <c r="I217" s="3">
+        <v>10</v>
+      </c>
+      <c r="J217" s="3">
+        <v>10</v>
+      </c>
+      <c r="K217" s="3">
+        <v>7</v>
+      </c>
+      <c r="L217">
+        <v>33</v>
+      </c>
+      <c r="M217">
+        <v>39</v>
+      </c>
+      <c r="N217">
+        <v>67</v>
+      </c>
+      <c r="O217">
+        <v>61</v>
+      </c>
+      <c r="P217" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q217" s="3">
+        <v>7</v>
+      </c>
+      <c r="R217" s="3">
+        <v>7</v>
+      </c>
+      <c r="S217" s="3">
+        <v>7</v>
+      </c>
+      <c r="T217" s="3">
+        <v>7</v>
+      </c>
+      <c r="U217" s="3">
+        <v>7</v>
+      </c>
+      <c r="V217" t="s">
+        <v>20</v>
+      </c>
+      <c r="W217" s="3">
+        <v>7</v>
+      </c>
+      <c r="X217" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y217">
+        <v>66</v>
+      </c>
+      <c r="Z217">
+        <v>33</v>
+      </c>
+      <c r="AA217">
+        <v>46</v>
+      </c>
+      <c r="AB217">
+        <v>9</v>
+      </c>
+      <c r="AC217">
+        <v>23</v>
+      </c>
+      <c r="AD217">
+        <v>55</v>
+      </c>
+      <c r="AE217">
+        <v>2</v>
+      </c>
+      <c r="AF217">
+        <v>10</v>
+      </c>
+      <c r="AG217" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH217" s="3">
+        <v>15105</v>
+      </c>
+      <c r="AI217" t="s">
+        <v>645</v>
+      </c>
+      <c r="AJ217" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK217" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL217">
+        <v>26271</v>
       </c>
     </row>
   </sheetData>
